--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,42 +481,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t xml:space="preserve">35 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40eeH0OgCF</t>
+          <t>https://s.shopee.vn/7prMq3A5Q9</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_26688092638</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>20e232b6634d40cd43b0a947914769d6</t>
         </is>
       </c>
     </row>
@@ -528,42 +533,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
+          <t>Giấy ăn rút Topgia thùng 40 gói đa sắc cao cấp 240 tờ 4 lớp, dập vân 4D, mềm mịn, thấm hút tốt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫109.000</t>
+          <t>₫95.000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>48%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56 </t>
+          <t>3k+</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L2Z3IFnSi</t>
+          <t>https://s.shopee.vn/8fQTpa6ujS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mp0p9xne07ikdf.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_57450548196</t>
+          <t>shopee_57860887539</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>113eb535211dc5576ce1f369536e321f</t>
+          <t>f9639d41fbcd6e80bee0e8864b3f4099</t>
         </is>
       </c>
     </row>
@@ -575,42 +585,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫86.400</t>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>41%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">573 </t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VLzFbFA7l</t>
+          <t>https://s.shopee.vn/7VEWRRBM67</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_23611804472</t>
+          <t>shopee_25123423072</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
         </is>
       </c>
     </row>
@@ -622,42 +637,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫250.000</t>
+          <t>₫334.000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t>10k+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/60PiegH48g</t>
+          <t>https://s.shopee.vn/6Aj8qzGQnj</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_40176467388</t>
+          <t>shopee_24288149456</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20c8bfa466ba333c337b5df598008b75</t>
+          <t>b09e4c6f894042c3f2551d25cdee8335</t>
         </is>
       </c>
     </row>
@@ -669,47 +689,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫334.000</t>
+          <t>₫1.599.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10k+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6Aj8qzGQnj</t>
+          <t>https://s.shopee.vn/9AMkQV50iX</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_24288149456</t>
+          <t>shopee_40012750336</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>b09e4c6f894042c3f2551d25cdee8335</t>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
         </is>
       </c>
     </row>
@@ -721,37 +741,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+          <t>Sốt Chấm CayTeDai x1 CAY VỪA - Sốt Muối Chấm Lâm Vlog Cay Tê Dại x1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫85.000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70k+</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5fmsG4IKoe</t>
+          <t>https://s.shopee.vn/6pypeDDtS3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7ra0g-m9z9tckp4vtme8.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_53401541671</t>
+          <t>shopee_24389484524</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+          <t>386b9af5df5a395ff6886d6c5b9821e3</t>
         </is>
       </c>
     </row>
@@ -763,12 +793,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫172.000</t>
+          <t>₫250.000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -783,22 +813,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q6ISNHhTh</t>
+          <t>https://s.shopee.vn/60PiegH48g</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_47051514276</t>
+          <t>shopee_40176467388</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>e534da14d58fabb5a795457bc5e0648f</t>
+          <t>20c8bfa466ba333c337b5df598008b75</t>
         </is>
       </c>
     </row>
@@ -810,42 +840,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫259.424</t>
+          <t>₫172.000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5LA1rSJbUc</t>
+          <t>https://s.shopee.vn/5q6ISNHhTh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_43054873326</t>
+          <t>shopee_47051514276</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
         </is>
       </c>
     </row>
@@ -857,42 +887,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫187.000</t>
+          <t>₫86.400</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 </t>
+          <t xml:space="preserve">573 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VTS3lIy9f</t>
+          <t>https://s.shopee.vn/6VLzFbFA7l</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_55054542761</t>
+          <t>shopee_23611804472</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5f34e9db093b79d1979ce644f78054b1</t>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
         </is>
       </c>
     </row>
@@ -904,37 +934,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫90.000</t>
+          <t>₫160.000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103,5%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7fXwdkAil6</t>
+          <t>https://s.shopee.vn/7Abg2pCcm5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_40423252463</t>
+          <t>shopee_25420035796</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
         </is>
       </c>
     </row>
@@ -946,47 +981,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫189.000</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">35 </t>
+          <t xml:space="preserve">343 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7prMq3A5Q9</t>
+          <t>https://s.shopee.vn/7Kv6F8BzR4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_26688092638</t>
+          <t>shopee_25964311284</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20e232b6634d40cd43b0a947914769d6</t>
+          <t>2b2611b2a0080242b5b4208e371f4726</t>
         </is>
       </c>
     </row>
@@ -998,42 +1028,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫98.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">343 </t>
+          <t xml:space="preserve">189 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Kv6F8BzR4</t>
+          <t>https://s.shopee.vn/70IFqWDG72</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_25964311284</t>
+          <t>shopee_45358208563</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2b2611b2a0080242b5b4208e371f4726</t>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
         </is>
       </c>
     </row>
@@ -1045,47 +1075,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
+          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫159.000</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>41%</t>
+          <t>₫109.000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t xml:space="preserve">56 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7VEWRRBM67</t>
+          <t>https://s.shopee.vn/6L2Z3IFnSi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_25123423072</t>
+          <t>shopee_57450548196</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
+          <t>113eb535211dc5576ce1f369536e321f</t>
         </is>
       </c>
     </row>
@@ -1097,42 +1122,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">189 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70IFqWDG72</t>
+          <t>https://s.shopee.vn/40eeH0OgCF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_45358208563</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1144,42 +1169,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫160.000</t>
+          <t>₫187.000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">354 </t>
+          <t xml:space="preserve">14 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Abg2pCcm5</t>
+          <t>https://s.shopee.vn/5VTS3lIy9f</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_25420035796</t>
+          <t>shopee_55054542761</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
         </is>
       </c>
     </row>
@@ -1191,37 +1216,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫70.000</t>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6ffPRuEWn0</t>
+          <t>https://s.shopee.vn/903KEC5e3U</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_54407073060</t>
+          <t>shopee_51401292730</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>a99d221105436bf0694d2756ca9de059</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -1233,47 +1263,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sốt Chấm CayTeDai x1 CAY VỪA - Sốt Muối Chấm Lâm Vlog Cay Tê Dại x1</t>
+          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫85.000</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>9%</t>
+          <t>₫259.424</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70k+</t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6pypeDDtS3</t>
+          <t>https://s.shopee.vn/5LA1rSJbUc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7ra0g-m9z9tckp4vtme8.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_24389484524</t>
+          <t>shopee_43054873326</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>386b9af5df5a395ff6886d6c5b9821e3</t>
+          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
         </is>
       </c>
     </row>
@@ -1285,42 +1310,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 </t>
+          <t>₫90.000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>103,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/903KEC5e3U</t>
+          <t>https://s.shopee.vn/7fXwdkAil6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
+          <t>shopee_40423252463</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
         </is>
       </c>
     </row>
@@ -1332,47 +1352,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫1.599.000</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>4k+</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9AMkQV50iX</t>
+          <t>https://s.shopee.vn/5fmsG4IKoe</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_40012750336</t>
+          <t>shopee_53401541671</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3d93b1393727dc3578c2df28b475e423</t>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
         </is>
       </c>
     </row>
@@ -1384,47 +1394,78 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Giấy ăn rút Topgia thùng 40 gói đa sắc cao cấp 240 tờ 4 lớp, dập vân 4D, mềm mịn, thấm hút tốt</t>
+          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫95.000</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>48%</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3k+</t>
+          <t>₫70.000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8fQTpa6ujS</t>
+          <t>https://s.shopee.vn/6ffPRuEWn0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mp0p9xne07ikdf.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_57860887539</t>
+          <t>shopee_54407073060</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>f9639d41fbcd6e80bee0e8864b3f4099</t>
+          <t>a99d221105436bf0694d2756ca9de059</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>554178dfe70920170e02b7e2ce4e9285</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -788,47 +788,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
+          <t>Tên mới</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫250.000</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2k+</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>33,5%</t>
-        </is>
-      </c>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/60PiegH48g</t>
+          <t>https://</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>shopee_40176467388</t>
-        </is>
-      </c>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20c8bfa466ba333c337b5df598008b75</t>
+          <t>554178dfe70920170e02b7e2ce4e9285</t>
         </is>
       </c>
     </row>
@@ -840,12 +834,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫172.000</t>
+          <t>₫250.000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -860,22 +854,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q6ISNHhTh</t>
+          <t>https://s.shopee.vn/60PiegH48g</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_47051514276</t>
+          <t>shopee_40176467388</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>e534da14d58fabb5a795457bc5e0648f</t>
+          <t>20c8bfa466ba333c337b5df598008b75</t>
         </is>
       </c>
     </row>
@@ -887,42 +881,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫86.400</t>
+          <t>₫172.000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">573 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VLzFbFA7l</t>
+          <t>https://s.shopee.vn/5q6ISNHhTh</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_23611804472</t>
+          <t>shopee_47051514276</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
         </is>
       </c>
     </row>
@@ -934,42 +928,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫160.000</t>
+          <t>₫86.400</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">354 </t>
+          <t xml:space="preserve">573 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Abg2pCcm5</t>
+          <t>https://s.shopee.vn/6VLzFbFA7l</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_25420035796</t>
+          <t>shopee_23611804472</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
         </is>
       </c>
     </row>
@@ -981,42 +975,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
+          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫98.000</t>
+          <t>₫160.000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">343 </t>
+          <t xml:space="preserve">354 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Kv6F8BzR4</t>
+          <t>https://s.shopee.vn/7Abg2pCcm5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_25964311284</t>
+          <t>shopee_25420035796</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2b2611b2a0080242b5b4208e371f4726</t>
+          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
         </is>
       </c>
     </row>
@@ -1028,42 +1022,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">189 </t>
+          <t xml:space="preserve">343 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70IFqWDG72</t>
+          <t>https://s.shopee.vn/7Kv6F8BzR4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_45358208563</t>
+          <t>shopee_25964311284</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+          <t>2b2611b2a0080242b5b4208e371f4726</t>
         </is>
       </c>
     </row>
@@ -1075,42 +1069,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫109.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">56 </t>
+          <t xml:space="preserve">189 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L2Z3IFnSi</t>
+          <t>https://s.shopee.vn/70IFqWDG72</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_57450548196</t>
+          <t>shopee_45358208563</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>113eb535211dc5576ce1f369536e321f</t>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
         </is>
       </c>
     </row>
@@ -1122,17 +1116,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫109.000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t xml:space="preserve">56 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1142,22 +1136,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40eeH0OgCF</t>
+          <t>https://s.shopee.vn/6L2Z3IFnSi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_57450548196</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>113eb535211dc5576ce1f369536e321f</t>
         </is>
       </c>
     </row>
@@ -1169,42 +1163,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫187.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VTS3lIy9f</t>
+          <t>https://s.shopee.vn/40eeH0OgCF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_55054542761</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5f34e9db093b79d1979ce644f78054b1</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1216,42 +1210,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫187.000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 </t>
+          <t xml:space="preserve">14 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/903KEC5e3U</t>
+          <t>https://s.shopee.vn/5VTS3lIy9f</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
+          <t>shopee_55054542761</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
         </is>
       </c>
     </row>
@@ -1263,42 +1257,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫259.424</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5LA1rSJbUc</t>
+          <t>https://s.shopee.vn/903KEC5e3U</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_43054873326</t>
+          <t>shopee_51401292730</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -1310,37 +1304,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫90.000</t>
+          <t>₫259.424</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>103,5%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7fXwdkAil6</t>
+          <t>https://s.shopee.vn/5LA1rSJbUc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_40423252463</t>
+          <t>shopee_43054873326</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
         </is>
       </c>
     </row>
@@ -1352,37 +1351,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫70.000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5fmsG4IKoe</t>
+          <t>https://s.shopee.vn/6ffPRuEWn0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_53401541671</t>
+          <t>shopee_54407073060</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+          <t>e0c6a62fc61ea04e2be4b7aeac2bc373</t>
         </is>
       </c>
     </row>
@@ -1394,78 +1398,79 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫70.000</t>
+          <t>₫90.000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>103,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6ffPRuEWn0</t>
+          <t>https://s.shopee.vn/7fXwdkAil6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_54407073060</t>
+          <t>shopee_40423252463</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>a99d221105436bf0694d2756ca9de059</t>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tên mới</t>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liên hệ</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://</t>
+          <t>https://s.shopee.vn/5fmsG4IKoe</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>shopee_53401541671</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>554178dfe70920170e02b7e2ce4e9285</t>
+          <t>211a58d7bfcf3e5c73aa8e98357a53a6</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1432,48 +1432,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://s.shopee.vn/5fmsG4IKoe</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>shopee_53401541671</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>211a58d7bfcf3e5c73aa8e98357a53a6</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,41 +788,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tên mới</t>
+          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Liên hệ</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>₫250.000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://</t>
+          <t>https://s.shopee.vn/60PiegH48g</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>shopee_40176467388</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>554178dfe70920170e02b7e2ce4e9285</t>
+          <t>20c8bfa466ba333c337b5df598008b75</t>
         </is>
       </c>
     </row>
@@ -834,12 +840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫250.000</t>
+          <t>₫172.000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -854,22 +860,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/60PiegH48g</t>
+          <t>https://s.shopee.vn/5q6ISNHhTh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_40176467388</t>
+          <t>shopee_47051514276</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20c8bfa466ba333c337b5df598008b75</t>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
         </is>
       </c>
     </row>
@@ -881,42 +887,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫172.000</t>
+          <t>₫86.400</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">573 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q6ISNHhTh</t>
+          <t>https://s.shopee.vn/6VLzFbFA7l</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_47051514276</t>
+          <t>shopee_23611804472</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>e534da14d58fabb5a795457bc5e0648f</t>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
         </is>
       </c>
     </row>
@@ -928,42 +934,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫86.400</t>
+          <t>₫160.000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">573 </t>
+          <t xml:space="preserve">354 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VLzFbFA7l</t>
+          <t>https://s.shopee.vn/7Abg2pCcm5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_23611804472</t>
+          <t>shopee_25420035796</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
         </is>
       </c>
     </row>
@@ -975,42 +981,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
+          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫160.000</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">354 </t>
+          <t xml:space="preserve">343 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Abg2pCcm5</t>
+          <t>https://s.shopee.vn/7Kv6F8BzR4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_25420035796</t>
+          <t>shopee_25964311284</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
+          <t>2b2611b2a0080242b5b4208e371f4726</t>
         </is>
       </c>
     </row>
@@ -1022,42 +1028,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫98.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">343 </t>
+          <t xml:space="preserve">189 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Kv6F8BzR4</t>
+          <t>https://s.shopee.vn/70IFqWDG72</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_25964311284</t>
+          <t>shopee_45358208563</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2b2611b2a0080242b5b4208e371f4726</t>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1075,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫109.000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">189 </t>
+          <t xml:space="preserve">56 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70IFqWDG72</t>
+          <t>https://s.shopee.vn/6L2Z3IFnSi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_45358208563</t>
+          <t>shopee_57450548196</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+          <t>113eb535211dc5576ce1f369536e321f</t>
         </is>
       </c>
     </row>
@@ -1116,17 +1122,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫109.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">56 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1136,22 +1142,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L2Z3IFnSi</t>
+          <t>https://s.shopee.vn/40eeH0OgCF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_57450548196</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>113eb535211dc5576ce1f369536e321f</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1163,42 +1169,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫187.000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t xml:space="preserve">14 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40eeH0OgCF</t>
+          <t>https://s.shopee.vn/5VTS3lIy9f</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_55054542761</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
         </is>
       </c>
     </row>
@@ -1210,42 +1216,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫187.000</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 </t>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VTS3lIy9f</t>
+          <t>https://s.shopee.vn/903KEC5e3U</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_55054542761</t>
+          <t>shopee_51401292730</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5f34e9db093b79d1979ce644f78054b1</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -1257,42 +1263,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫259.424</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 </t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/903KEC5e3U</t>
+          <t>https://s.shopee.vn/5LA1rSJbUc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
+          <t>shopee_43054873326</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
         </is>
       </c>
     </row>
@@ -1304,42 +1310,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
+          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫259.424</t>
+          <t>₫70.000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5LA1rSJbUc</t>
+          <t>https://s.shopee.vn/6ffPRuEWn0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_43054873326</t>
+          <t>shopee_54407073060</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
+          <t>e0c6a62fc61ea04e2be4b7aeac2bc373</t>
         </is>
       </c>
     </row>
@@ -1351,82 +1357,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫70.000</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>₫90.000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>103,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6ffPRuEWn0</t>
+          <t>https://s.shopee.vn/7fXwdkAil6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_54407073060</t>
+          <t>shopee_40423252463</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
-        <is>
-          <t>e0c6a62fc61ea04e2be4b7aeac2bc373</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>₫90.000</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>103,5%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://s.shopee.vn/7fXwdkAil6</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>shopee_40423252463</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
         <is>
           <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
         </is>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1391,6 +1391,228 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35 </t>
+          <t>30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20e232b6634d40cd43b0a947914769d6</t>
+          <t>07e6e5ab3976d92faffeea35c0c34cf1</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,9 +1407,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1420,8 +1417,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
@@ -1444,9 +1439,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1457,8 +1449,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
@@ -1481,9 +1471,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1494,8 +1481,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
@@ -1518,9 +1503,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1531,8 +1513,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
@@ -1555,9 +1535,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1568,8 +1545,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
@@ -1592,9 +1567,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1605,9 +1577,118 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
         </is>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1599,9 +1599,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1612,8 +1609,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
@@ -1636,9 +1631,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1649,8 +1641,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
@@ -1673,9 +1663,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1686,9 +1673,44 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
         </is>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1695,9 +1695,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1708,11 +1705,50 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>554178dfe70920170e02b7e2ce4e9285</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -788,47 +788,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
+          <t>Tên mới</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫250.000</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2k+</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>33,5%</t>
-        </is>
-      </c>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/60PiegH48g</t>
+          <t>https://</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>shopee_40176467388</t>
-        </is>
-      </c>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20c8bfa466ba333c337b5df598008b75</t>
+          <t>554178dfe70920170e02b7e2ce4e9285</t>
         </is>
       </c>
     </row>
@@ -840,12 +834,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫172.000</t>
+          <t>₫250.000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -860,22 +854,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q6ISNHhTh</t>
+          <t>https://s.shopee.vn/60PiegH48g</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_47051514276</t>
+          <t>shopee_40176467388</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>e534da14d58fabb5a795457bc5e0648f</t>
+          <t>20c8bfa466ba333c337b5df598008b75</t>
         </is>
       </c>
     </row>
@@ -887,42 +881,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫86.400</t>
+          <t>₫172.000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">573 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VLzFbFA7l</t>
+          <t>https://s.shopee.vn/5q6ISNHhTh</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_23611804472</t>
+          <t>shopee_47051514276</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
         </is>
       </c>
     </row>
@@ -934,42 +928,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫160.000</t>
+          <t>₫86.400</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">354 </t>
+          <t xml:space="preserve">573 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Abg2pCcm5</t>
+          <t>https://s.shopee.vn/6VLzFbFA7l</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_25420035796</t>
+          <t>shopee_23611804472</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
         </is>
       </c>
     </row>
@@ -981,42 +975,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
+          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫98.000</t>
+          <t>₫160.000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">343 </t>
+          <t xml:space="preserve">354 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Kv6F8BzR4</t>
+          <t>https://s.shopee.vn/7Abg2pCcm5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_25964311284</t>
+          <t>shopee_25420035796</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2b2611b2a0080242b5b4208e371f4726</t>
+          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
         </is>
       </c>
     </row>
@@ -1028,42 +1022,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">189 </t>
+          <t xml:space="preserve">343 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70IFqWDG72</t>
+          <t>https://s.shopee.vn/7Kv6F8BzR4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_45358208563</t>
+          <t>shopee_25964311284</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+          <t>2b2611b2a0080242b5b4208e371f4726</t>
         </is>
       </c>
     </row>
@@ -1075,42 +1069,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫109.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">56 </t>
+          <t xml:space="preserve">189 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L2Z3IFnSi</t>
+          <t>https://s.shopee.vn/70IFqWDG72</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_57450548196</t>
+          <t>shopee_45358208563</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>113eb535211dc5576ce1f369536e321f</t>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
         </is>
       </c>
     </row>
@@ -1122,17 +1116,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫109.000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t xml:space="preserve">56 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1142,22 +1136,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40eeH0OgCF</t>
+          <t>https://s.shopee.vn/6L2Z3IFnSi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_57450548196</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>113eb535211dc5576ce1f369536e321f</t>
         </is>
       </c>
     </row>
@@ -1169,42 +1163,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫187.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VTS3lIy9f</t>
+          <t>https://s.shopee.vn/40eeH0OgCF</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_55054542761</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5f34e9db093b79d1979ce644f78054b1</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1216,42 +1210,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫187.000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 </t>
+          <t xml:space="preserve">14 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/903KEC5e3U</t>
+          <t>https://s.shopee.vn/5VTS3lIy9f</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
+          <t>shopee_55054542761</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
         </is>
       </c>
     </row>
@@ -1263,42 +1257,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫259.424</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5LA1rSJbUc</t>
+          <t>https://s.shopee.vn/903KEC5e3U</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_43054873326</t>
+          <t>shopee_51401292730</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -1310,42 +1304,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
+          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫70.000</t>
+          <t>₫259.424</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6ffPRuEWn0</t>
+          <t>https://s.shopee.vn/5LA1rSJbUc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_54407073060</t>
+          <t>shopee_43054873326</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>e0c6a62fc61ea04e2be4b7aeac2bc373</t>
+          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
         </is>
       </c>
     </row>
@@ -1357,37 +1351,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫90.000</t>
+          <t>₫70.000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>103,5%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7fXwdkAil6</t>
+          <t>https://s.shopee.vn/6ffPRuEWn0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+          <t>https://down-tx-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_40423252463</t>
+          <t>shopee_54407073060</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+          <t>e0c6a62fc61ea04e2be4b7aeac2bc373</t>
         </is>
       </c>
     </row>
@@ -1407,6 +1406,11 @@
           <t>Liên hệ</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1419,39 +1423,49 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+          <t>c1c316f99385095d7f6555355843bced</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tên mới</t>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liên hệ</t>
+          <t>₫90.000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>103,5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://</t>
+          <t>https://s.shopee.vn/7fXwdkAil6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+          <t>https://down-tx-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>shopee_40423252463</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
         </is>
       </c>
     </row>
@@ -1471,6 +1485,11 @@
           <t>Liên hệ</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1483,7 +1502,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+          <t>356f1dfb8d7ef26325d5e0e4d76809b4</t>
         </is>
       </c>
     </row>
@@ -1727,28 +1746,29 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>554178dfe70920170e02b7e2ce4e9285</t>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>₫18.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>07e6e5ab3976d92faffeea35c0c34cf1</t>
+          <t>75c7b488ba022ac3ec2bcdb8967ef630</t>
         </is>
       </c>
     </row>
@@ -806,8 +806,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>https://</t>
@@ -818,8 +816,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>554178dfe70920170e02b7e2ce4e9285</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,43 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>hash</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,37 +476,1012 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tên mới</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liên hệ</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 </t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>shopee_48200038200</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>₫86.400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">573 </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>shopee_23611804472</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>₫90.000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>103,5%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>shopee_40423252463</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bộ bút màu nước acrylic 12/24/36/48/60/80 nhanh khô, dùng cho học sinh và văn phòng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>₫43.200</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>shopee_25596612791</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>8805e1ee39897802c22d2492ddead377</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>₫119.000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>26,5%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>shopee_22243625222</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>51eb47102de9685c14261934dc30d3ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>₫334.000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19,5%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>shopee_24288149456</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>b09e4c6f894042c3f2551d25cdee8335</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>shopee_53401541671</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223 </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>shopee_40355840814</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2bd4126f7f9e643c1922d1306e949d04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₫269.000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>40k+</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>shopee_24660800592</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adc006849b07a4930b56a65d92726f32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chân Váy Lụa Dáng Đuôi Tôm – Phi Lụa Mềm Mịn, Bay Bổng, Tôn Eo Tôn Dáng, Sang Nhẹ Nhàng</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₫120.000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mf6kfi4l4potce.webp</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>shopee_29862648823</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>c398ac714ca59bd683c85ccec2b353b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189 </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>shopee_45358208563</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>₫109.000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591 </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>shopee_50254653729</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>₫172.000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>shopee_47051514276</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>₫199.000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>400k+</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>shopee_25676379719</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8797a0b343c8a948af2337da1f7954d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>shopee_51401292730</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35 </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>shopee_26688092638</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>20e232b6634d40cd43b0a947914769d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[Giá đỡ cốc USB] Vali 20 / 24 / 28 Inch Hành lý chống trầy xước Túi du lịch Vali Khóa mật khẩu Bánh xe đa năng</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>₫354.000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142 </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-m3bvt0vtvtqi50.webp</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>shopee_27520790052</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>81d5b112b09329b285dbecc5dc80b48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>₫187.000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>shopee_55054542761</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>shopee_48500941449</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>686b261362b588a5e597b2e4b9a9d984</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bình giữ nhiệt nắp vặn dung tích 1000ml, giữ nhiệt 8–12 tiếng</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>₫73.125</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-820n9-mnn1rb2kghdua0.webp</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>shopee_49459714492</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>38079881f6703b9022a2e11ecbc00500</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,44 +481,48 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫49.000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>₫109.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t xml:space="preserve">591 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_50254653729</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
         </is>
       </c>
     </row>
@@ -530,44 +534,48 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫86.400</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">573 </t>
+          <t xml:space="preserve">223 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_23611804472</t>
+          <t>shopee_40355840814</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+          <t>2bd4126f7f9e643c1922d1306e949d04</t>
         </is>
       </c>
     </row>
@@ -579,40 +587,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫90.000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35 </t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_40423252463</t>
+          <t>shopee_26688092638</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+          <t>20e232b6634d40cd43b0a947914769d6</t>
         </is>
       </c>
     </row>
@@ -624,48 +640,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bộ bút màu nước acrylic 12/24/36/48/60/80 nhanh khô, dùng cho học sinh và văn phòng</t>
+          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫43.200</t>
+          <t>₫199.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 </t>
+          <t>400k+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_25596612791</t>
+          <t>shopee_25676379719</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8805e1ee39897802c22d2492ddead377</t>
+          <t>8797a0b343c8a948af2337da1f7954d2</t>
         </is>
       </c>
     </row>
@@ -677,48 +693,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫119.000</t>
+          <t>₫334.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t>10k+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_22243625222</t>
+          <t>shopee_24288149456</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>51eb47102de9685c14261934dc30d3ce</t>
+          <t>b09e4c6f894042c3f2551d25cdee8335</t>
         </is>
       </c>
     </row>
@@ -730,12 +746,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+          <t>[Giá đỡ cốc USB] Vali 20 / 24 / 28 Inch Hành lý chống trầy xước Túi du lịch Vali Khóa mật khẩu Bánh xe đa năng</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫334.000</t>
+          <t>₫354.000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -745,33 +761,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10k+</t>
+          <t xml:space="preserve">142 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-m3bvt0vtvtqi50.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_24288149456</t>
+          <t>shopee_27520790052</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>b09e4c6f894042c3f2551d25cdee8335</t>
+          <t>81d5b112b09329b285dbecc5dc80b48e</t>
         </is>
       </c>
     </row>
@@ -783,40 +799,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+          <t>Bình giữ nhiệt nắp vặn dung tích 1000ml, giữ nhiệt 8–12 tiếng</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>₫73.125</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 </t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-820n9-mnn1rb2kghdua0.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_53401541671</t>
+          <t>shopee_49459714492</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+          <t>38079881f6703b9022a2e11ecbc00500</t>
         </is>
       </c>
     </row>
@@ -828,48 +852,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>₫269.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">223 </t>
+          <t>40k+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_40355840814</t>
+          <t>shopee_24660800592</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2bd4126f7f9e643c1922d1306e949d04</t>
+          <t>adc006849b07a4930b56a65d92726f32</t>
         </is>
       </c>
     </row>
@@ -881,48 +905,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫269.000</t>
+          <t>₫119.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40k+</t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_24660800592</t>
+          <t>shopee_22243625222</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>adc006849b07a4930b56a65d92726f32</t>
+          <t>51eb47102de9685c14261934dc30d3ce</t>
         </is>
       </c>
     </row>
@@ -934,44 +958,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chân Váy Lụa Dáng Đuôi Tôm – Phi Lụa Mềm Mịn, Bay Bổng, Tôn Eo Tôn Dáng, Sang Nhẹ Nhàng</t>
+          <t>Bộ bút màu nước acrylic 12/24/36/48/60/80 nhanh khô, dùng cho học sinh và văn phòng</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫120.000</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>₫43.200</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">4 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mf6kfi4l4potce.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_29862648823</t>
+          <t>shopee_25596612791</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>c398ac714ca59bd683c85ccec2b353b2</t>
+          <t>8805e1ee39897802c22d2492ddead377</t>
         </is>
       </c>
     </row>
@@ -983,44 +1011,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫172.000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">189 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_45358208563</t>
+          <t>shopee_47051514276</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
         </is>
       </c>
     </row>
@@ -1032,48 +1060,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
+          <t>Chân Váy Lụa Dáng Đuôi Tôm – Phi Lụa Mềm Mịn, Bay Bổng, Tôn Eo Tôn Dáng, Sang Nhẹ Nhàng</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫109.000</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
+          <t>₫120.000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">591 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mf6kfi4l4potce.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_50254653729</t>
+          <t>shopee_29862648823</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
+          <t>c398ac714ca59bd683c85ccec2b353b2</t>
         </is>
       </c>
     </row>
@@ -1085,44 +1109,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫172.000</t>
+          <t>₫86.400</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">573 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_47051514276</t>
+          <t>shopee_23611804472</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>e534da14d58fabb5a795457bc5e0648f</t>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
         </is>
       </c>
     </row>
@@ -1134,48 +1158,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫199.000</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>400k+</t>
+          <t xml:space="preserve">189 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_25676379719</t>
+          <t>shopee_45358208563</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8797a0b343c8a948af2337da1f7954d2</t>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
         </is>
       </c>
     </row>
@@ -1187,18 +1207,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1208,23 +1228,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1236,48 +1256,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫189.000</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
+          <t>₫187.000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35 </t>
+          <t xml:space="preserve">14 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_26688092638</t>
+          <t>shopee_55054542761</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20e232b6634d40cd43b0a947914769d6</t>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
         </is>
       </c>
     </row>
@@ -1289,48 +1305,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Giá đỡ cốc USB] Vali 20 / 24 / 28 Inch Hành lý chống trầy xước Túi du lịch Vali Khóa mật khẩu Bánh xe đa năng</t>
+          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫354.000</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">142 </t>
+          <t xml:space="preserve">12 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-m3bvt0vtvtqi50.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_27520790052</t>
+          <t>shopee_48500941449</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>81d5b112b09329b285dbecc5dc80b48e</t>
+          <t>686b261362b588a5e597b2e4b9a9d984</t>
         </is>
       </c>
     </row>
@@ -1342,44 +1354,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫187.000</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 </t>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_55054542761</t>
+          <t>shopee_51401292730</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5f34e9db093b79d1979ce644f78054b1</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -1391,44 +1403,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫90.000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 </t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>103,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_48500941449</t>
+          <t>shopee_40423252463</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>686b261362b588a5e597b2e4b9a9d984</t>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
         </is>
       </c>
     </row>
@@ -1440,48 +1448,1052 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bình giữ nhiệt nắp vặn dung tích 1000ml, giữ nhiệt 8–12 tiếng</t>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫73.125</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 </t>
-        </is>
-      </c>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-820n9-mnn1rb2kghdua0.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_49459714492</t>
+          <t>shopee_53401541671</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>38079881f6703b9022a2e11ecbc00500</t>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>₫160.000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354 </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>58,5%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25420035796?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>shopee_25420035796</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>₫98.000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">343 </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25964311284?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>shopee_25964311284</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2b2611b2a0080242b5b4208e371f4726</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Quạt điện cầm tay ngoài trời mới, gió mát mạnh, loại đeo cổ, có thể sạc lại</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>₫656.153</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42602218674?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ravd-ma8jgmmdacn983.webp</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>shopee_42602218674</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>b390ca409ecd3388bd2d3f84964ca9f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25123423072?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>shopee_25123423072</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>₫70.000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>27,5%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54407073060?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>shopee_54407073060</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>a99d221105436bf0694d2756ca9de059</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth Mini Không Dây Thiết Kế Nhỏ Gọn Sang Trọng Nghe Nhạc Hay Có Móc Treo Giá Rẻ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>₫199.000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>300k+</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28708632089?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkuq1bj48zyc61.webp</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>shopee_28708632089</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>16606867986f8d3cb5faba17c90f053d</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>₫295.000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>shopee_25241658670</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0711dda9bc0242bae934dfe448902fd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sốt Chấm CayTeDai x1 CAY VỪA - Sốt Muối Chấm Lâm Vlog Cay Tê Dại x1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>₫85.000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>700k+</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24389484524?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9z9tckp4vtme8.webp</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>shopee_24389484524</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>01c5cdb269ac93e19d8001ac9eb26a1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Can Nước Xả Vải Comfort Professional Cho Da Nhạy Cảm Dịu Nhẹ 5l</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>₫190.228</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/46754637218?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn29sxx6qpz57a.webp</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>shopee_46754637218</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>67ae5735d2918e7800bfe810edf04702</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>₫250.000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40176467388?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>shopee_40176467388</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>20c8bfa466ba333c337b5df598008b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>(Tặng Remote) Gậy chụp ảnh Selfie 4 chân A14 1M8 điều khiển từ xa có phân loại đèn trợ sáng Tripod chụp ảnh cầm nhỏ gọn.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>₫216.000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>30k+</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47806465186?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmo1fxngu39hc3.webp</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>shopee_47806465186</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>cd04e1e720636148adbed3325a40a7cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>₫1.599.000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>shopee_40012750336</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4 Can [ 20.000ml ] Nước Xả Vải Hương Comfor Thơm Ngát , Mềm Mại</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>₫255.000</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92 </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50108806335?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn1b48wvhlvpb9.webp</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>shopee_50108806335</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>9b546b316e54cc270d012c1348b96bfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[MUA 1 TẶNG 1] Tẩy Tế Bào Chết Cho Da Mặt Cocoon Cà Phê Đắk Lắk 150ml</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>₫182.000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55253482757?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjh9jsou7fgn45.webp</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>shopee_55253482757</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>7da862655be8b51909d2e099063e66de</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pin dự phòng 20000mAh, sạc nhanh, cáp 3 trong 1, dung lượng lớn, thiết yếu cho du lịch và chơi game.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>₫70.000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50101468541?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgne2h0vw83u8b.webp</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>shopee_50101468541</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>dbd9cd1b5ca9df96f73cbfb352cf0591</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Giày Asics Nam Nữ, Giày Sneaker Đen Xám Full Box Bill</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>₫399.000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>8k+</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26158119242?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mixb657woow08a.webp</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>shopee_26158119242</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>7c2f684fb48f5eebeadf50d3754e7ccd</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>(Có Sẵn) Máy làm đá mini công suất lớn hoàntoàn tự động 15kg đá Tạo Đá Siêu Tốc Trong 6 - 8 Phút</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>₫1.880.000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>24,5%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26961948374?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq4mosqy1p8g6e.webp</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>shopee_26961948374</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>23db99dbec2d3279aa37bb7d76450094</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Máy Khoan | Máy Khoan Điện BOSH | Bộ Vali Đủ Đồ Nghề Chuyên Dùng Cam Kết Motor Đồng | Có chức năng búa khoan tường</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>₫470.000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43502085828?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-ma65e9eebhdka9.webp</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>shopee_43502085828</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>94518cb23cd29e6434116e922258c3e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quạt Mini Cầm Tay HandyFan – Quạt Du Lịch Tích Điện Để Bàn, Quạt Sự Kiện Làm Mát Di gĐộn</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>₫38.260</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42069955748?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meton2o35fcwc5.webp</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>shopee_42069955748</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5ec5473040f6ddd57f28f6a440a54001</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Trà Đen Kinh Bắc Bịch 500gr - 250gr (Đậm Đà Vị Trà - Trà Sữa Thơm Béo)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>₫95.000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24388293580?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mojva4wkwlcb70.webp</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>shopee_24388293580</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>d51301fcf971b263ee723a76fbd1ced9</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -481,22 +481,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
+          <t>Quạt Mini Cầm Tay HandyFan – Quạt Du Lịch Tích Điện Để Bàn, Quạt Sự Kiện Làm Mát Di gĐộn</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫109.000</t>
+          <t>₫38.260</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">591 </t>
+          <t>10k+</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -506,23 +506,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42069955748?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meton2o35fcwc5.webp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>shopee_50254653729</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>shopee_42069955748</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>giam 50% nhnh</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
+          <t>5ec5473040f6ddd57f28f6a440a54001</t>
         </is>
       </c>
     </row>
@@ -534,12 +538,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>₫109.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,33 +553,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223 </t>
+          <t xml:space="preserve">591 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_40355840814</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>shopee_50254653729</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2bd4126f7f9e643c1922d1306e949d04</t>
+          <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
         </is>
       </c>
     </row>
@@ -587,7 +595,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -602,33 +610,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">35 </t>
+          <t xml:space="preserve">223 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_26688092638</t>
+          <t>shopee_40355840814</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20e232b6634d40cd43b0a947914769d6</t>
+          <t>2bd4126f7f9e643c1922d1306e949d04</t>
         </is>
       </c>
     </row>
@@ -640,48 +648,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫199.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>400k+</t>
+          <t xml:space="preserve">35 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_25676379719</t>
+          <t>shopee_26688092638</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8797a0b343c8a948af2337da1f7954d2</t>
+          <t>20e232b6634d40cd43b0a947914769d6</t>
         </is>
       </c>
     </row>
@@ -693,48 +701,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫334.000</t>
+          <t>₫199.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10k+</t>
+          <t>400k+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_24288149456</t>
+          <t>shopee_25676379719</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>b09e4c6f894042c3f2551d25cdee8335</t>
+          <t>8797a0b343c8a948af2337da1f7954d2</t>
         </is>
       </c>
     </row>
@@ -746,48 +754,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Giá đỡ cốc USB] Vali 20 / 24 / 28 Inch Hành lý chống trầy xước Túi du lịch Vali Khóa mật khẩu Bánh xe đa năng</t>
+          <t>Loa Bluetooth Mini Không Dây Thiết Kế Nhỏ Gọn Sang Trọng Nghe Nhạc Hay Có Móc Treo Giá Rẻ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫354.000</t>
+          <t>₫199.000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">142 </t>
+          <t>300k+</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28708632089?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-m3bvt0vtvtqi50.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkuq1bj48zyc61.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_27520790052</t>
+          <t>shopee_28708632089</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>81d5b112b09329b285dbecc5dc80b48e</t>
+          <t>16606867986f8d3cb5faba17c90f053d</t>
         </is>
       </c>
     </row>
@@ -799,48 +807,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bình giữ nhiệt nắp vặn dung tích 1000ml, giữ nhiệt 8–12 tiếng</t>
+          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫73.125</t>
+          <t>₫159.000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 </t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25123423072?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-820n9-mnn1rb2kghdua0.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_49459714492</t>
+          <t>shopee_25123423072</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>38079881f6703b9022a2e11ecbc00500</t>
+          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
         </is>
       </c>
     </row>
@@ -852,48 +860,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫269.000</t>
+          <t>₫334.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40k+</t>
+          <t>10k+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_24660800592</t>
+          <t>shopee_24288149456</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>adc006849b07a4930b56a65d92726f32</t>
+          <t>b09e4c6f894042c3f2551d25cdee8335</t>
         </is>
       </c>
     </row>
@@ -905,48 +913,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+          <t>[Giá đỡ cốc USB] Vali 20 / 24 / 28 Inch Hành lý chống trầy xước Túi du lịch Vali Khóa mật khẩu Bánh xe đa năng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫119.000</t>
+          <t>₫354.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">142 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-m3bvt0vtvtqi50.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_22243625222</t>
+          <t>shopee_27520790052</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>51eb47102de9685c14261934dc30d3ce</t>
+          <t>81d5b112b09329b285dbecc5dc80b48e</t>
         </is>
       </c>
     </row>
@@ -958,48 +966,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bộ bút màu nước acrylic 12/24/36/48/60/80 nhanh khô, dùng cho học sinh và văn phòng</t>
+          <t>(Tặng Remote) Gậy chụp ảnh Selfie 4 chân A14 1M8 điều khiển từ xa có phân loại đèn trợ sáng Tripod chụp ảnh cầm nhỏ gọn.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫43.200</t>
+          <t>₫216.000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 </t>
+          <t>30k+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47806465186?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmo1fxngu39hc3.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_25596612791</t>
+          <t>shopee_47806465186</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8805e1ee39897802c22d2492ddead377</t>
+          <t>cd04e1e720636148adbed3325a40a7cf</t>
         </is>
       </c>
     </row>
@@ -1011,44 +1019,48 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫172.000</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>₫295.000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_47051514276</t>
+          <t>shopee_25241658670</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>e534da14d58fabb5a795457bc5e0648f</t>
+          <t>0711dda9bc0242bae934dfe448902fd0</t>
         </is>
       </c>
     </row>
@@ -1060,44 +1072,48 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chân Váy Lụa Dáng Đuôi Tôm – Phi Lụa Mềm Mịn, Bay Bổng, Tôn Eo Tôn Dáng, Sang Nhẹ Nhàng</t>
+          <t>Bình giữ nhiệt nắp vặn dung tích 1000ml, giữ nhiệt 8–12 tiếng</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫120.000</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>₫73.125</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">4 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mf6kfi4l4potce.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-820n9-mnn1rb2kghdua0.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_29862648823</t>
+          <t>shopee_49459714492</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>c398ac714ca59bd683c85ccec2b353b2</t>
+          <t>38079881f6703b9022a2e11ecbc00500</t>
         </is>
       </c>
     </row>
@@ -1109,44 +1125,48 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+          <t>Giày Asics Nam Nữ, Giày Sneaker Đen Xám Full Box Bill</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫86.400</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>₫399.000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">573 </t>
+          <t>8k+</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26158119242?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mixb657woow08a.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_23611804472</t>
+          <t>shopee_26158119242</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+          <t>7c2f684fb48f5eebeadf50d3754e7ccd</t>
         </is>
       </c>
     </row>
@@ -1158,44 +1178,48 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+          <t>Can Nước Xả Vải Comfort Professional Cho Da Nhạy Cảm Dịu Nhẹ 5l</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫149.000</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>₫190.228</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">189 </t>
+          <t>5k+</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/46754637218?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn29sxx6qpz57a.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_45358208563</t>
+          <t>shopee_46754637218</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+          <t>67ae5735d2918e7800bfe810edf04702</t>
         </is>
       </c>
     </row>
@@ -1207,44 +1231,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫49.000</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>₫269.000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t>40k+</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_24660800592</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>adc006849b07a4930b56a65d92726f32</t>
         </is>
       </c>
     </row>
@@ -1256,44 +1284,48 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫187.000</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>₫1.599.000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 </t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_55054542761</t>
+          <t>shopee_40012750336</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5f34e9db093b79d1979ce644f78054b1</t>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
         </is>
       </c>
     </row>
@@ -1305,44 +1337,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>₫119.000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_48500941449</t>
+          <t>shopee_22243625222</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>686b261362b588a5e597b2e4b9a9d984</t>
+          <t>51eb47102de9685c14261934dc30d3ce</t>
         </is>
       </c>
     </row>
@@ -1354,44 +1390,48 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>Bộ bút màu nước acrylic 12/24/36/48/60/80 nhanh khô, dùng cho học sinh và văn phòng</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>₫43.200</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 </t>
+          <t xml:space="preserve">4 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
+          <t>shopee_25596612791</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>8805e1ee39897802c22d2492ddead377</t>
         </is>
       </c>
     </row>
@@ -1403,40 +1443,48 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+          <t>(Có Sẵn) Máy làm đá mini công suất lớn hoàntoàn tự động 15kg đá Tạo Đá Siêu Tốc Trong 6 - 8 Phút</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫90.000</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>₫1.880.000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>103,5%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26961948374?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq4mosqy1p8g6e.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_40423252463</t>
+          <t>shopee_26961948374</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+          <t>23db99dbec2d3279aa37bb7d76450094</t>
         </is>
       </c>
     </row>
@@ -1448,40 +1496,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+          <t>Sốt Chấm CayTeDai x1 CAY VỪA - Sốt Muối Chấm Lâm Vlog Cay Tê Dại x1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>₫85.000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>700k+</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24389484524?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9z9tckp4vtme8.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_53401541671</t>
+          <t>shopee_24389484524</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+          <t>01c5cdb269ac93e19d8001ac9eb26a1b</t>
         </is>
       </c>
     </row>
@@ -1493,44 +1549,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
+          <t>Máy Khoan | Máy Khoan Điện BOSH | Bộ Vali Đủ Đồ Nghề Chuyên Dùng Cam Kết Motor Đồng | Có chức năng búa khoan tường</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>₫160.000</t>
+          <t>₫470.000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">354 </t>
+          <t>7k+</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25420035796?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43502085828?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-ma65e9eebhdka9.webp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>shopee_25420035796</t>
+          <t>shopee_43502085828</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
+          <t>94518cb23cd29e6434116e922258c3e7</t>
         </is>
       </c>
     </row>
@@ -1542,44 +1598,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
+          <t>Trà Đen Kinh Bắc Bịch 500gr - 250gr (Đậm Đà Vị Trà - Trà Sữa Thơm Béo)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>₫98.000</t>
+          <t>₫95.000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">343 </t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25964311284?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24388293580?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mojva4wkwlcb70.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>shopee_25964311284</t>
+          <t>shopee_24388293580</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2b2611b2a0080242b5b4208e371f4726</t>
+          <t>d51301fcf971b263ee723a76fbd1ced9</t>
         </is>
       </c>
     </row>
@@ -1591,44 +1647,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quạt điện cầm tay ngoài trời mới, gió mát mạnh, loại đeo cổ, có thể sạc lại</t>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>₫656.153</t>
+          <t>₫172.000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42602218674?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ravd-ma8jgmmdacn983.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>shopee_42602218674</t>
+          <t>shopee_47051514276</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>b390ca409ecd3388bd2d3f84964ca9f7</t>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
         </is>
       </c>
     </row>
@@ -1640,48 +1696,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
+          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>₫159.000</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
+          <t>₫250.000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25123423072?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40176467388?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>shopee_25123423072</t>
+          <t>shopee_40176467388</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
+          <t>20c8bfa466ba333c337b5df598008b75</t>
         </is>
       </c>
     </row>
@@ -1693,40 +1745,44 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
+          <t>[MUA 1 TẶNG 1] Tẩy Tế Bào Chết Cho Da Mặt Cocoon Cà Phê Đắk Lắk 150ml</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>₫70.000</t>
+          <t>₫182.000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54407073060?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55253482757?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjh9jsou7fgn45.webp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>shopee_54407073060</t>
+          <t>shopee_55253482757</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>a99d221105436bf0694d2756ca9de059</t>
+          <t>7da862655be8b51909d2e099063e66de</t>
         </is>
       </c>
     </row>
@@ -1738,48 +1794,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Loa Bluetooth Mini Không Dây Thiết Kế Nhỏ Gọn Sang Trọng Nghe Nhạc Hay Có Móc Treo Giá Rẻ</t>
+          <t>Chân Váy Lụa Dáng Đuôi Tôm – Phi Lụa Mềm Mịn, Bay Bổng, Tôn Eo Tôn Dáng, Sang Nhẹ Nhàng</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>₫199.000</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
+          <t>₫120.000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>300k+</t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28708632089?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkuq1bj48zyc61.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mf6kfi4l4potce.webp</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>shopee_28708632089</t>
+          <t>shopee_29862648823</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>16606867986f8d3cb5faba17c90f053d</t>
+          <t>c398ac714ca59bd683c85ccec2b353b2</t>
         </is>
       </c>
     </row>
@@ -1791,48 +1843,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>₫295.000</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
+          <t>₫86.400</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t xml:space="preserve">573 </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>shopee_25241658670</t>
+          <t>shopee_23611804472</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0711dda9bc0242bae934dfe448902fd0</t>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
         </is>
       </c>
     </row>
@@ -1844,48 +1892,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sốt Chấm CayTeDai x1 CAY VỪA - Sốt Muối Chấm Lâm Vlog Cay Tê Dại x1</t>
+          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>₫85.000</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
+          <t>₫160.000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>700k+</t>
+          <t xml:space="preserve">354 </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24389484524?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25420035796?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9z9tckp4vtme8.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>shopee_24389484524</t>
+          <t>shopee_25420035796</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>01c5cdb269ac93e19d8001ac9eb26a1b</t>
+          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
         </is>
       </c>
     </row>
@@ -1897,48 +1941,44 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Can Nước Xả Vải Comfort Professional Cho Da Nhạy Cảm Dịu Nhẹ 5l</t>
+          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>₫190.228</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
+          <t>₫98.000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5k+</t>
+          <t xml:space="preserve">343 </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/46754637218?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25964311284?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn29sxx6qpz57a.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>shopee_46754637218</t>
+          <t>shopee_25964311284</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>67ae5735d2918e7800bfe810edf04702</t>
+          <t>2b2611b2a0080242b5b4208e371f4726</t>
         </is>
       </c>
     </row>
@@ -1950,44 +1990,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>₫250.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">189 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40176467388?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>shopee_40176467388</t>
+          <t>shopee_45358208563</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>20c8bfa466ba333c337b5df598008b75</t>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
         </is>
       </c>
     </row>
@@ -1999,48 +2039,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>(Tặng Remote) Gậy chụp ảnh Selfie 4 chân A14 1M8 điều khiển từ xa có phân loại đèn trợ sáng Tripod chụp ảnh cầm nhỏ gọn.</t>
+          <t>4 Can [ 20.000ml ] Nước Xả Vải Hương Comfor Thơm Ngát , Mềm Mại</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>₫216.000</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
+          <t>₫255.000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30k+</t>
+          <t xml:space="preserve">92 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/47806465186?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50108806335?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmo1fxngu39hc3.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn1b48wvhlvpb9.webp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>shopee_47806465186</t>
+          <t>shopee_50108806335</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>cd04e1e720636148adbed3325a40a7cf</t>
+          <t>9b546b316e54cc270d012c1348b96bfd</t>
         </is>
       </c>
     </row>
@@ -2052,48 +2088,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>₫1.599.000</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
+          <t>₫49.000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>shopee_40012750336</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3d93b1393727dc3578c2df28b475e423</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -2105,44 +2137,44 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4 Can [ 20.000ml ] Nước Xả Vải Hương Comfor Thơm Ngát , Mềm Mại</t>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>₫255.000</t>
+          <t>₫187.000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">92 </t>
+          <t xml:space="preserve">14 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50108806335?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn1b48wvhlvpb9.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>shopee_50108806335</t>
+          <t>shopee_55054542761</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>9b546b316e54cc270d012c1348b96bfd</t>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
         </is>
       </c>
     </row>
@@ -2154,44 +2186,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Tẩy Tế Bào Chết Cho Da Mặt Cocoon Cà Phê Đắk Lắk 150ml</t>
+          <t>Quạt điện cầm tay ngoài trời mới, gió mát mạnh, loại đeo cổ, có thể sạc lại</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>₫182.000</t>
+          <t>₫656.153</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">13 </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55253482757?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42602218674?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjh9jsou7fgn45.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ravd-ma8jgmmdacn983.webp</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>shopee_55253482757</t>
+          <t>shopee_42602218674</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>7da862655be8b51909d2e099063e66de</t>
+          <t>b390ca409ecd3388bd2d3f84964ca9f7</t>
         </is>
       </c>
     </row>
@@ -2203,16 +2235,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pin dự phòng 20000mAh, sạc nhanh, cáp 3 trong 1, dung lượng lớn, thiết yếu cho du lịch và chơi game.</t>
+          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>₫70.000</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 </t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -2220,23 +2256,23 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50101468541?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgne2h0vw83u8b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>shopee_50101468541</t>
+          <t>shopee_48500941449</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>dbd9cd1b5ca9df96f73cbfb352cf0591</t>
+          <t>686b261362b588a5e597b2e4b9a9d984</t>
         </is>
       </c>
     </row>
@@ -2248,48 +2284,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Giày Asics Nam Nữ, Giày Sneaker Đen Xám Full Box Bill</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>₫399.000</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>23%</t>
-        </is>
-      </c>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8k+</t>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26158119242?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mixb657woow08a.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>shopee_26158119242</t>
+          <t>shopee_51401292730</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7c2f684fb48f5eebeadf50d3754e7ccd</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -2301,48 +2333,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(Có Sẵn) Máy làm đá mini công suất lớn hoàntoàn tự động 15kg đá Tạo Đá Siêu Tốc Trong 6 - 8 Phút</t>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>₫1.880.000</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>14%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1k+</t>
-        </is>
-      </c>
+          <t>₫90.000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>103,5%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26961948374?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq4mosqy1p8g6e.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>shopee_26961948374</t>
+          <t>shopee_40423252463</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>23db99dbec2d3279aa37bb7d76450094</t>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
         </is>
       </c>
     </row>
@@ -2354,44 +2378,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Máy Khoan | Máy Khoan Điện BOSH | Bộ Vali Đủ Đồ Nghề Chuyên Dùng Cam Kết Motor Đồng | Có chức năng búa khoan tường</t>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>₫470.000</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>7k+</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/43502085828?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.VAstLUP8tz.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-ma65e9eebhdka9.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>shopee_43502085828</t>
+          <t>shopee_53401541671</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>94518cb23cd29e6434116e922258c3e7</t>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
         </is>
       </c>
     </row>
@@ -2403,48 +2423,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quạt Mini Cầm Tay HandyFan – Quạt Du Lịch Tích Điện Để Bàn, Quạt Sự Kiện Làm Mát Di gĐộn</t>
+          <t>Pin dự phòng 20000mAh, sạc nhanh, cáp 3 trong 1, dung lượng lớn, thiết yếu cho du lịch và chơi game.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>₫38.260</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>10k+</t>
-        </is>
-      </c>
+          <t>₫70.000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42069955748?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50101468541?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meton2o35fcwc5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgne2h0vw83u8b.webp</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>shopee_42069955748</t>
+          <t>shopee_50101468541</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>5ec5473040f6ddd57f28f6a440a54001</t>
+          <t>dbd9cd1b5ca9df96f73cbfb352cf0591</t>
         </is>
       </c>
     </row>
@@ -2456,44 +2468,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Trà Đen Kinh Bắc Bịch 500gr - 250gr (Đậm Đà Vị Trà - Trà Sữa Thơm Béo)</t>
+          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>₫95.000</t>
+          <t>₫70.000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>4k+</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24388293580?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54407073060?trace=%7B%22trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.z9um4nFaUR.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mojva4wkwlcb70.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>shopee_24388293580</t>
+          <t>shopee_54407073060</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>d51301fcf971b263ee723a76fbd1ced9</t>
+          <t>a99d221105436bf0694d2756ca9de059</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>giam 50% nhnh</t>
+          <t>giam 50% nhanh tauy nao</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -576,11 +576,7 @@
           <t>shopee_50254653729</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,1018 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>₫49.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 </t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>shopee_48200038200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>₫86.400</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">573 </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>shopee_23611804472</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>₫90.000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>103,5%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>shopee_40423252463</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bộ bút màu nước acrylic 12/24/36/48/60/80 nhanh khô, dùng cho học sinh và văn phòng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>₫43.200</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>shopee_25596612791</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>8805e1ee39897802c22d2492ddead377</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>₫119.000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>26,5%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>shopee_22243625222</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>51eb47102de9685c14261934dc30d3ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>₫334.000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19,5%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>shopee_24288149456</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>b09e4c6f894042c3f2551d25cdee8335</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>shopee_53401541671</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223 </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>shopee_40355840814</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2bd4126f7f9e643c1922d1306e949d04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₫269.000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>40k+</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>shopee_24660800592</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adc006849b07a4930b56a65d92726f32</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chân Váy Lụa Dáng Đuôi Tôm – Phi Lụa Mềm Mịn, Bay Bổng, Tôn Eo Tôn Dáng, Sang Nhẹ Nhàng</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₫120.000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mf6kfi4l4potce.webp</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>shopee_29862648823</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>c398ac714ca59bd683c85ccec2b353b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189 </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>shopee_45358208563</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>₫109.000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591 </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>shopee_50254653729</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>₫172.000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>shopee_47051514276</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>₫199.000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>400k+</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>shopee_25676379719</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8797a0b343c8a948af2337da1f7954d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>shopee_51401292730</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35 </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>shopee_26688092638</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>20e232b6634d40cd43b0a947914769d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[Giá đỡ cốc USB] Vali 20 / 24 / 28 Inch Hành lý chống trầy xước Túi du lịch Vali Khóa mật khẩu Bánh xe đa năng</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>₫354.000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142 </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/cn-11134207-7ras8-m3bvt0vtvtqi50.webp</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>shopee_27520790052</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>81d5b112b09329b285dbecc5dc80b48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>₫187.000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>shopee_55054542761</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>shopee_48500941449</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>686b261362b588a5e597b2e4b9a9d984</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bình giữ nhiệt nắp vặn dung tích 1000ml, giữ nhiệt 8–12 tiếng</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>₫73.125</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-820n9-mnn1rb2kghdua0.webp</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>shopee_49459714492</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>38079881f6703b9022a2e11ecbc00500</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1485,6 +1485,43 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,44 +481,48 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫49.000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>₫109.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t xml:space="preserve">591 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_50254653729</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
         </is>
       </c>
     </row>
@@ -530,44 +534,48 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫86.400</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">573 </t>
+          <t xml:space="preserve">223 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_23611804472</t>
+          <t>shopee_40355840814</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+          <t>2bd4126f7f9e643c1922d1306e949d04</t>
         </is>
       </c>
     </row>
@@ -579,40 +587,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫90.000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35 </t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_40423252463</t>
+          <t>shopee_26688092638</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+          <t>20e232b6634d40cd43b0a947914769d6</t>
         </is>
       </c>
     </row>
@@ -624,48 +640,48 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bộ bút màu nước acrylic 12/24/36/48/60/80 nhanh khô, dùng cho học sinh và văn phòng</t>
+          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫43.200</t>
+          <t>₫199.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 </t>
+          <t>400k+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_25596612791</t>
+          <t>shopee_25676379719</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8805e1ee39897802c22d2492ddead377</t>
+          <t>8797a0b343c8a948af2337da1f7954d2</t>
         </is>
       </c>
     </row>
@@ -677,48 +693,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫119.000</t>
+          <t>₫334.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t>10k+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_22243625222</t>
+          <t>shopee_24288149456</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>51eb47102de9685c14261934dc30d3ce</t>
+          <t>b09e4c6f894042c3f2551d25cdee8335</t>
         </is>
       </c>
     </row>
@@ -730,12 +746,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+          <t>[Giá đỡ cốc USB] Vali 20 / 24 / 28 Inch Hành lý chống trầy xước Túi du lịch Vali Khóa mật khẩu Bánh xe đa năng</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫334.000</t>
+          <t>₫354.000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -745,33 +761,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10k+</t>
+          <t xml:space="preserve">142 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/cn-11134207-7ras8-m3bvt0vtvtqi50.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_24288149456</t>
+          <t>shopee_27520790052</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>b09e4c6f894042c3f2551d25cdee8335</t>
+          <t>81d5b112b09329b285dbecc5dc80b48e</t>
         </is>
       </c>
     </row>
@@ -783,40 +799,48 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+          <t>Bình giữ nhiệt nắp vặn dung tích 1000ml, giữ nhiệt 8–12 tiếng</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>₫73.125</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 </t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-820n9-mnn1rb2kghdua0.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_53401541671</t>
+          <t>shopee_49459714492</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+          <t>38079881f6703b9022a2e11ecbc00500</t>
         </is>
       </c>
     </row>
@@ -828,48 +852,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>₫269.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">223 </t>
+          <t>40k+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_40355840814</t>
+          <t>shopee_24660800592</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2bd4126f7f9e643c1922d1306e949d04</t>
+          <t>adc006849b07a4930b56a65d92726f32</t>
         </is>
       </c>
     </row>
@@ -881,48 +905,48 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫269.000</t>
+          <t>₫119.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40k+</t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_24660800592</t>
+          <t>shopee_22243625222</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>adc006849b07a4930b56a65d92726f32</t>
+          <t>51eb47102de9685c14261934dc30d3ce</t>
         </is>
       </c>
     </row>
@@ -934,44 +958,48 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chân Váy Lụa Dáng Đuôi Tôm – Phi Lụa Mềm Mịn, Bay Bổng, Tôn Eo Tôn Dáng, Sang Nhẹ Nhàng</t>
+          <t>Bộ bút màu nước acrylic 12/24/36/48/60/80 nhanh khô, dùng cho học sinh và văn phòng</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫120.000</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>₫43.200</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">4 </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mf6kfi4l4potce.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_29862648823</t>
+          <t>shopee_25596612791</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>c398ac714ca59bd683c85ccec2b353b2</t>
+          <t>8805e1ee39897802c22d2492ddead377</t>
         </is>
       </c>
     </row>
@@ -983,44 +1011,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫172.000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">189 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_45358208563</t>
+          <t>shopee_47051514276</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
         </is>
       </c>
     </row>
@@ -1032,48 +1060,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
+          <t>Chân Váy Lụa Dáng Đuôi Tôm – Phi Lụa Mềm Mịn, Bay Bổng, Tôn Eo Tôn Dáng, Sang Nhẹ Nhàng</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫109.000</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
+          <t>₫120.000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">591 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mf6kfi4l4potce.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_50254653729</t>
+          <t>shopee_29862648823</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
+          <t>c398ac714ca59bd683c85ccec2b353b2</t>
         </is>
       </c>
     </row>
@@ -1085,44 +1109,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫172.000</t>
+          <t>₫86.400</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">573 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_47051514276</t>
+          <t>shopee_23611804472</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>e534da14d58fabb5a795457bc5e0648f</t>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
         </is>
       </c>
     </row>
@@ -1134,48 +1158,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫199.000</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>400k+</t>
+          <t xml:space="preserve">189 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_25676379719</t>
+          <t>shopee_45358208563</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8797a0b343c8a948af2337da1f7954d2</t>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
         </is>
       </c>
     </row>
@@ -1187,18 +1207,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1208,23 +1228,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1236,48 +1256,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫189.000</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
+          <t>₫187.000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">35 </t>
+          <t xml:space="preserve">14 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_26688092638</t>
+          <t>shopee_55054542761</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20e232b6634d40cd43b0a947914769d6</t>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
         </is>
       </c>
     </row>
@@ -1289,48 +1305,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Giá đỡ cốc USB] Vali 20 / 24 / 28 Inch Hành lý chống trầy xước Túi du lịch Vali Khóa mật khẩu Bánh xe đa năng</t>
+          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫354.000</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">142 </t>
+          <t xml:space="preserve">12 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/cn-11134207-7ras8-m3bvt0vtvtqi50.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_27520790052</t>
+          <t>shopee_48500941449</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>81d5b112b09329b285dbecc5dc80b48e</t>
+          <t>686b261362b588a5e597b2e4b9a9d984</t>
         </is>
       </c>
     </row>
@@ -1342,44 +1354,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫187.000</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 </t>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_55054542761</t>
+          <t>shopee_51401292730</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5f34e9db093b79d1979ce644f78054b1</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -1391,44 +1403,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫90.000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 </t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>103,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_48500941449</t>
+          <t>shopee_40423252463</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>686b261362b588a5e597b2e4b9a9d984</t>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
         </is>
       </c>
     </row>
@@ -1440,85 +1448,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bình giữ nhiệt nắp vặn dung tích 1000ml, giữ nhiệt 8–12 tiếng</t>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫73.125</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 </t>
-        </is>
-      </c>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-820n9-mnn1rb2kghdua0.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_49459714492</t>
+          <t>shopee_53401541671</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>38079881f6703b9022a2e11ecbc00500</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Tên mới</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Liên hệ</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/50XCGtug5U</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -519,7 +519,6 @@
           <t>shopee_50254653729</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>724ccb10ab6e50dc8ee18d62e4d7d9a5</t>
@@ -559,7 +558,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4LHVTfxDRI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -572,7 +571,6 @@
           <t>shopee_40355840814</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>2bd4126f7f9e643c1922d1306e949d04</t>
@@ -612,7 +610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/LlMiKCRYe</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -625,7 +623,6 @@
           <t>shopee_26688092638</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>20e232b6634d40cd43b0a947914769d6</t>
@@ -665,7 +662,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4fuLsHvwlS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -678,7 +675,6 @@
           <t>shopee_25676379719</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>8797a0b343c8a948af2337da1f7954d2</t>
@@ -718,7 +714,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3LOyHq11T4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -731,7 +727,6 @@
           <t>shopee_24288149456</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>b09e4c6f894042c3f2551d25cdee8335</t>
@@ -771,7 +766,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27520790052?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/W4mudBoDh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -784,7 +779,6 @@
           <t>shopee_27520790052</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>81d5b112b09329b285dbecc5dc80b48e</t>
@@ -824,7 +818,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49459714492?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1113VY9uCq</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -837,7 +831,6 @@
           <t>shopee_49459714492</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>38079881f6703b9022a2e11ecbc00500</t>
@@ -877,7 +870,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4Vavfywa6L</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -890,7 +883,6 @@
           <t>shopee_24660800592</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>adc006849b07a4930b56a65d92726f32</t>
@@ -930,7 +922,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3qLEskz7S9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -943,7 +935,6 @@
           <t>shopee_22243625222</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>51eb47102de9685c14261934dc30d3ce</t>
@@ -983,7 +974,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3g1ogRzkn6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -996,7 +987,6 @@
           <t>shopee_25596612791</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>8805e1ee39897802c22d2492ddead377</t>
@@ -1019,7 +1009,6 @@
           <t>₫172.000</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>2k+</t>
@@ -1032,7 +1021,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5AqcTCu2kX</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1045,7 +1034,6 @@
           <t>shopee_47051514276</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>e534da14d58fabb5a795457bc5e0648f</t>
@@ -1068,7 +1056,6 @@
           <t>₫120.000</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>2k+</t>
@@ -1081,7 +1068,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29862648823?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/40ef53yU7G</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1094,7 +1081,6 @@
           <t>shopee_29862648823</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>c398ac714ca59bd683c85ccec2b353b2</t>
@@ -1117,7 +1103,6 @@
           <t>₫86.400</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">573 </t>
@@ -1130,7 +1115,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2g9HUc3Yos</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1143,7 +1128,6 @@
           <t>shopee_23611804472</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
@@ -1166,7 +1150,6 @@
           <t>₫149.000</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">189 </t>
@@ -1179,7 +1162,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4Ay5HMxqmJ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1192,7 +1175,6 @@
           <t>shopee_45358208563</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
@@ -1215,7 +1197,6 @@
           <t>₫49.000</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">24 </t>
@@ -1228,7 +1209,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3B5Y5X1enx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1241,7 +1222,6 @@
           <t>shopee_48200038200</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>db2b85f0d5e40a41400e4929b228f7ff</t>
@@ -1264,7 +1244,6 @@
           <t>₫187.000</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">14 </t>
@@ -1277,7 +1256,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/18WJiDiEc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1290,7 +1269,6 @@
           <t>shopee_55054542761</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>5f34e9db093b79d1979ce644f78054b1</t>
@@ -1313,7 +1291,6 @@
           <t>₫356.000</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve">12 </t>
@@ -1326,7 +1303,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/BRwW1D4tf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1339,7 +1316,6 @@
           <t>shopee_48500941449</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>686b261362b588a5e597b2e4b9a9d984</t>
@@ -1362,7 +1338,6 @@
           <t>₫356.000</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t xml:space="preserve">6 </t>
@@ -1375,7 +1350,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4qDm4avJQV</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1388,7 +1363,6 @@
           <t>shopee_51401292730</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
@@ -1411,8 +1385,6 @@
           <t>₫90.000</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>103,5%</t>
@@ -1420,7 +1392,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2qShgv2vTv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1433,7 +1405,6 @@
           <t>shopee_40423252463</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
@@ -1456,8 +1427,6 @@
           <t>₫356.000</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -1465,7 +1434,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.a2YzDSQoHX.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3ViOU90O87</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1478,7 +1447,6 @@
           <t>shopee_53401541671</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>aef6c3542d96a164f2f808809d3f5b09</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,12 +850,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫269.000</t>
+          <t>₫289.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4Vavfywa6L</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>adc006849b07a4930b56a65d92726f32</t>
+          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
         </is>
       </c>
     </row>
@@ -917,17 +917,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLEskz7S9</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>51eb47102de9685c14261934dc30d3ce</t>
+          <t>06b67e3715cbcf93cd06e235b20e67a3</t>
         </is>
       </c>
     </row>
@@ -1450,6 +1450,793 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>aef6c3542d96a164f2f808809d3f5b09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>₫198.000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>300k+</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26858030583?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>shopee_26858030583</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0a64138bac7926d086d7164638e7ac2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>₫168.000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>50k+</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24450360446?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>shopee_24450360446</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>₫288.000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>600k+</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24034739910?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>shopee_24034739910</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>₫209.000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/13724863422?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>shopee_13724863422</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5b19f9c4bae575f6667040d2b121506e</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61 </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53557782402?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>shopee_53557782402</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7e7089f2ec53f1c298a3e90f64318125</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>₫599.000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27176838116?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>shopee_27176838116</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>₫266.000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42357015741?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>shopee_42357015741</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>9f60e820ba2ef23d798f65a0378e9b54</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>₫826.000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1tr+</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26464017128?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>shopee_26464017128</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0063c3803f4f95d096d307a3278cb4bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>₫215.000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>200k+</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28126833083?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>shopee_28126833083</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>a5781b11dd1125ec606b7cba8deda0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>₫1.599.000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>shopee_40012750336</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>₫229.000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28200539872?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>shopee_28200539872</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>4be218b81a6be9c55c23210e5f4e379b</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kệ đặt chậu hoa, chậu cây cảnh 6 tầng, chậu hoa cây cảnh khung sắt chắc chắn, kệ decor có bánh xe</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>₫265.000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928 </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26319252965?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>shopee_26319252965</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>e8c259bd483858e228b0c2099ebeb852</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>₫225.000</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>shopee_25241658670</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>4e3452edfd64b6b785d3f600faf050e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>₫98.000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>800k+</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29807844451?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>shopee_29807844451</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>36268a94496dd6a3162249faf14ee638</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>₫450.000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48107000510?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>shopee_48107000510</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LHVTfxDRI</t>
+          <t>https://s.shopee.vn/80Ay8hESxH</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/AKYsuz5aDd</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9fJC7l87ZR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9HUc3Yos</t>
+          <t>https://s.shopee.vn/6ffaYFJXf9</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B5Y5X1enx</t>
+          <t>https://s.shopee.vn/AAFSig6DYc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26858030583?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9pccK47UES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1499,7 +1499,6 @@
           <t>shopee_26858030583</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>0a64138bac7926d086d7164638e7ac2b</t>
@@ -1539,7 +1538,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24450360446?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9UzlvS8kuQ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1552,7 +1551,6 @@
           <t>shopee_24450360446</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
@@ -1592,7 +1590,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24034739910?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9KgLj99OFP</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1605,7 +1603,6 @@
           <t>shopee_24034739910</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
@@ -1645,7 +1642,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/13724863422?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/AUsJ7I4wse</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1658,7 +1655,6 @@
           <t>shopee_13724863422</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>5b19f9c4bae575f6667040d2b121506e</t>
@@ -1681,7 +1677,6 @@
           <t>₫149.000</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">61 </t>
@@ -1694,7 +1689,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53557782402?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9zw2WN6qtb</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1707,7 +1702,6 @@
           <t>shopee_53557782402</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>7e7089f2ec53f1c298a3e90f64318125</t>
@@ -1747,7 +1741,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27176838116?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8V7EjcCYwK</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1760,7 +1754,6 @@
           <t>shopee_27176838116</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
@@ -1800,7 +1793,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42357015741?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8KnoXJDCHJ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1813,7 +1806,6 @@
           <t>shopee_42357015741</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>9f60e820ba2ef23d798f65a0378e9b54</t>
@@ -1853,7 +1845,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26464017128?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8AUOL0DpcI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1866,7 +1858,6 @@
           <t>shopee_26464017128</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>0063c3803f4f95d096d307a3278cb4bd</t>
@@ -1906,7 +1897,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28126833083?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9AMvWqA1aW</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1919,7 +1910,6 @@
           <t>shopee_28126833083</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>a5781b11dd1125ec606b7cba8deda0d2</t>
@@ -1959,7 +1949,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/903VKXAevV</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1972,7 +1962,6 @@
           <t>shopee_40012750336</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>3d93b1393727dc3578c2df28b475e423</t>
@@ -2012,7 +2001,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28200539872?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8pk58EBIGU</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2025,7 +2014,6 @@
           <t>shopee_28200539872</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>4be218b81a6be9c55c23210e5f4e379b</t>
@@ -2065,7 +2053,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26319252965?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8fQevvBvbT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2078,7 +2066,6 @@
           <t>shopee_26319252965</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>e8c259bd483858e228b0c2099ebeb852</t>
@@ -2118,7 +2105,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7Abr9AHdeC</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2131,7 +2118,6 @@
           <t>shopee_25241658670</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>4e3452edfd64b6b785d3f600faf050e4</t>
@@ -2171,7 +2157,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29807844451?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/70IQwrIGzB</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2184,7 +2170,6 @@
           <t>shopee_29807844451</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>36268a94496dd6a3162249faf14ee638</t>
@@ -2207,7 +2192,6 @@
           <t>₫450.000</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t xml:space="preserve">2 </t>
@@ -2220,7 +2204,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48107000510?trace=%7B%22trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.pAyF0sxf2N.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6pz0kYIuKA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2233,7 +2217,6 @@
           <t>shopee_48107000510</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>e8a4d05f34cae74562b2fa16a54ff6af</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,1026 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>₫198.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>300k+</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4AyGUyq8ud</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>shopee_26858030583</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0a64138bac7926d086d7164638e7ac2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>₫119.000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24,5%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3g1zu3s2vY</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>shopee_22243625222</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>06b67e3715cbcf93cd06e235b20e67a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>₫168.000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50k+</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3qLQ6MrPab</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>shopee_24450360446</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>₫288.000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>600k+</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3LP9VRtJbW</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>shopee_24034739910</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>₫209.000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3ViZhksgGZ</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>shopee_13724863422</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5b19f9c4bae575f6667040d2b121506e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>₫289.000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>40k+</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/30mJ6puaHU</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>shopee_24660800592</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62 </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3B5jJ8twwX</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>shopee_53557782402</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>be4aca7de97245e2c4faa260b67482fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>₫49.000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2g9SiDvqxS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>shopee_48200038200</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₫599.000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2qSsuWvDcV</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>shopee_27176838116</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₫826.000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1tr+</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7prYricBTU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>shopee_26464017128</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0063c3803f4f95d096d307a3278cb4bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>₫268.000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7fY8fPcooT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>shopee_42357015741</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223 </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7VEiT6dS9S</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>shopee_40355840814</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2bd4126f7f9e643c1922d1306e949d04</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>₫295.000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>200k+</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7KvIGne5UR</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>shopee_28126833083</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>768e867948552026756bd7e356cfca04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>₫1.599.000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7Abs4UeipQ</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>shopee_40012750336</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>₫229.000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/70IRsBfMAP</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>shopee_28200539872</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>4be218b81a6be9c55c23210e5f4e379b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kệ đặt chậu hoa, chậu cây cảnh 6 tầng, chậu hoa cây cảnh khung sắt chắc chắn, kệ decor có bánh xe</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>₫265.000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928 </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6pz1fsfzVO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>shopee_26319252965</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>e8c259bd483858e228b0c2099ebeb852</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>₫225.000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6ffbTZgcqN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>shopee_25241658670</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>4e3452edfd64b6b785d3f600faf050e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>₫98.000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>800k+</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6VMBHGhGBM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>shopee_29807844451</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>36268a94496dd6a3162249faf14ee638</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>₫450.000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6L2l4xhtWL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>shopee_48107000510</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>₫140.000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621 </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6AjKseiWrK</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>shopee_28657885709</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4AyGUyq8ud</t>
+          <t>https://s.shopee.vn/W4y8KFcm6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3g1zu3s2vY</t>
+          <t>https://s.shopee.vn/LlXw1GG75</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLQ6MrPab</t>
+          <t>https://s.shopee.vn/2BDC7O9HOS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LP9VRtJbW</t>
+          <t>https://s.shopee.vn/20tlv59ujR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3ViZhksgGZ</t>
+          <t>https://s.shopee.vn/2Vq2W080iY</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/30mJ6puaHU</t>
+          <t>https://s.shopee.vn/2LWcJh8e3X</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B5jJ8twwX</t>
+          <t>https://s.shopee.vn/1VxVKABokO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9SiDvqxS</t>
+          <t>https://s.shopee.vn/1Le57rCS5N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2qSsuWvDcV</t>
+          <t>https://s.shopee.vn/1qaLimAY4U</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7prYricBTU</t>
+          <t>https://s.shopee.vn/1gGvWTBBPT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7fY8fPcooT</t>
+          <t>https://s.shopee.vn/3ViZhq4Cgq</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7VEiT6dS9S</t>
+          <t>https://s.shopee.vn/3LP9VX4q1p</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7KvIGne5UR</t>
+          <t>https://s.shopee.vn/3qLQ6S2w0w</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Abs4UeipQ</t>
+          <t>https://s.shopee.vn/3g1zu93ZLv</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70IRsBfMAP</t>
+          <t>https://s.shopee.vn/2qSsuc6k2m</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6pz1fsfzVO</t>
+          <t>https://s.shopee.vn/2g9SiJ7NNl</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6ffbTZgcqN</t>
+          <t>https://s.shopee.vn/3B5jJE5TMs</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VMBHGhGBM</t>
+          <t>https://s.shopee.vn/30mJ6v66hr</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L2l4xhtWL</t>
+          <t>https://s.shopee.vn/4qDxIHz7zE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6AjKseiWrK</t>
+          <t>https://s.shopee.vn/4fuX5yzlKD</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/products.xlsx
+++ b/products.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W4y8KFcm6</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26858030583?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -519,6 +519,7 @@
           <t>shopee_26858030583</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>0a64138bac7926d086d7164638e7ac2b</t>
@@ -558,12 +559,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/LlXw1GG75</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -571,6 +572,7 @@
           <t>shopee_22243625222</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>06b67e3715cbcf93cd06e235b20e67a3</t>
@@ -610,12 +612,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDC7O9HOS</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24450360446?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -623,6 +625,7 @@
           <t>shopee_24450360446</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
@@ -662,12 +665,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20tlv59ujR</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24034739910?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -675,6 +678,7 @@
           <t>shopee_24034739910</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
@@ -714,12 +718,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2Vq2W080iY</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/13724863422?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -727,6 +731,7 @@
           <t>shopee_13724863422</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>5b19f9c4bae575f6667040d2b121506e</t>
@@ -766,12 +771,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LWcJh8e3X</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -779,6 +784,7 @@
           <t>shopee_24660800592</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
@@ -801,6 +807,7 @@
           <t>₫149.000</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">62 </t>
@@ -813,12 +820,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1VxVKABokO</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53557782402?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -826,6 +833,7 @@
           <t>shopee_53557782402</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>be4aca7de97245e2c4faa260b67482fb</t>
@@ -848,6 +856,7 @@
           <t>₫49.000</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">24 </t>
@@ -860,12 +869,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Le57rCS5N</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -873,6 +882,7 @@
           <t>shopee_48200038200</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>db2b85f0d5e40a41400e4929b228f7ff</t>
@@ -912,12 +922,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qaLimAY4U</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27176838116?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -925,6 +935,7 @@
           <t>shopee_27176838116</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
@@ -964,12 +975,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gGvWTBBPT</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26464017128?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -977,6 +988,7 @@
           <t>shopee_26464017128</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>0063c3803f4f95d096d307a3278cb4bd</t>
@@ -1016,12 +1028,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3ViZhq4Cgq</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42357015741?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1029,6 +1041,7 @@
           <t>shopee_42357015741</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
@@ -1068,12 +1081,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LP9VX4q1p</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1081,6 +1094,7 @@
           <t>shopee_40355840814</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>2bd4126f7f9e643c1922d1306e949d04</t>
@@ -1120,12 +1134,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLQ6S2w0w</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28126833083?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1133,6 +1147,7 @@
           <t>shopee_28126833083</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>768e867948552026756bd7e356cfca04</t>
@@ -1172,12 +1187,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3g1zu93ZLv</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1185,6 +1200,7 @@
           <t>shopee_40012750336</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>3d93b1393727dc3578c2df28b475e423</t>
@@ -1224,12 +1240,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2qSsuc6k2m</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28200539872?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1237,6 +1253,7 @@
           <t>shopee_28200539872</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>4be218b81a6be9c55c23210e5f4e379b</t>
@@ -1276,12 +1293,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9SiJ7NNl</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26319252965?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1289,6 +1306,7 @@
           <t>shopee_26319252965</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>e8c259bd483858e228b0c2099ebeb852</t>
@@ -1328,12 +1346,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B5jJE5TMs</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1341,6 +1359,7 @@
           <t>shopee_25241658670</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>4e3452edfd64b6b785d3f600faf050e4</t>
@@ -1380,12 +1399,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/30mJ6v66hr</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29807844451?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1393,6 +1412,7 @@
           <t>shopee_29807844451</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>36268a94496dd6a3162249faf14ee638</t>
@@ -1415,6 +1435,7 @@
           <t>₫450.000</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">2 </t>
@@ -1427,12 +1448,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4qDxIHz7zE</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48107000510?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1440,6 +1461,7 @@
           <t>shopee_48107000510</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
@@ -1462,6 +1484,7 @@
           <t>₫140.000</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">621 </t>
@@ -1474,12 +1497,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4fuX5yzlKD</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28657885709?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1487,6 +1510,7 @@
           <t>shopee_28657885709</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>de6906faf8cfe3f1157d9c7636c6eb90</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26858030583?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/W4y9dO9UD</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -519,7 +519,6 @@
           <t>shopee_26858030583</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>0a64138bac7926d086d7164638e7ac2b</t>
@@ -559,7 +558,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/18hYiQ3V8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -572,7 +571,6 @@
           <t>shopee_22243625222</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>06b67e3715cbcf93cd06e235b20e67a3</t>
@@ -612,7 +610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24450360446?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/BS7l1PQAB</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -625,7 +623,6 @@
           <t>shopee_24450360446</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
@@ -665,7 +662,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24034739910?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2LWcL0HAlc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -678,7 +675,6 @@
           <t>shopee_24034739910</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
@@ -718,7 +714,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/13724863422?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -731,7 +727,6 @@
           <t>shopee_13724863422</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>5b19f9c4bae575f6667040d2b121506e</t>
@@ -771,7 +766,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/20tlwOIRRa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -784,7 +779,6 @@
           <t>shopee_24660800592</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
@@ -807,7 +801,6 @@
           <t>₫149.000</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">62 </t>
@@ -820,7 +813,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53557782402?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2BDC8hHo6d</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -833,7 +826,6 @@
           <t>shopee_53557782402</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>be4aca7de97245e2c4faa260b67482fb</t>
@@ -856,7 +848,6 @@
           <t>₫49.000</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">24 </t>
@@ -869,7 +860,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -882,7 +873,6 @@
           <t>shopee_48200038200</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>db2b85f0d5e40a41400e4929b228f7ff</t>
@@ -922,7 +912,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27176838116?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1qaLk5J4mb</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -935,7 +925,6 @@
           <t>shopee_27176838116</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
@@ -975,7 +964,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26464017128?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1Le59AKynW</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -988,7 +977,6 @@
           <t>shopee_26464017128</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>0063c3803f4f95d096d307a3278cb4bd</t>
@@ -1028,7 +1016,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42357015741?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1041,7 +1029,6 @@
           <t>shopee_42357015741</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
@@ -1081,7 +1068,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3g1zvSC640</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1094,7 +1081,6 @@
           <t>shopee_40355840814</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>2bd4126f7f9e643c1922d1306e949d04</t>
@@ -1134,7 +1120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28126833083?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1147,7 +1133,6 @@
           <t>shopee_28126833083</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>768e867948552026756bd7e356cfca04</t>
@@ -1187,7 +1172,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3LP9WqDMjy</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1200,7 +1185,6 @@
           <t>shopee_40012750336</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>3d93b1393727dc3578c2df28b475e423</t>
@@ -1240,7 +1224,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28200539872?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3ViZj9CjP1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1253,7 +1237,6 @@
           <t>shopee_28200539872</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>4be218b81a6be9c55c23210e5f4e379b</t>
@@ -1293,7 +1276,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26319252965?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/30mJ8EEdPw</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1306,7 +1289,6 @@
           <t>shopee_26319252965</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>e8c259bd483858e228b0c2099ebeb852</t>
@@ -1346,7 +1328,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3B5jKXE04z</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1359,7 +1341,6 @@
           <t>shopee_25241658670</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>4e3452edfd64b6b785d3f600faf050e4</t>
@@ -1399,7 +1380,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29807844451?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2g9SjcFu5u</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1412,7 +1393,6 @@
           <t>shopee_29807844451</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>36268a94496dd6a3162249faf14ee638</t>
@@ -1435,7 +1415,6 @@
           <t>₫450.000</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">2 </t>
@@ -1448,7 +1427,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48107000510?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2qSsvvFGkx</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1461,7 +1440,6 @@
           <t>shopee_48107000510</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
@@ -1484,7 +1462,6 @@
           <t>₫140.000</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">621 </t>
@@ -1497,7 +1474,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28657885709?trace=%7B%22trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.yo9aCDYGyt.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/50XNVu71MO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1510,7 +1487,6 @@
           <t>shopee_28657885709</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>de6906faf8cfe3f1157d9c7636c6eb90</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,47 +481,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫198.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>300k+</t>
+          <t xml:space="preserve">223 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W4y9dO9UD</t>
+          <t>https://s.shopee.vn/3g1zvSC640</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>shopee_26858030583</t>
+          <t>shopee_40355840814</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0a64138bac7926d086d7164638e7ac2b</t>
+          <t>2bd4126f7f9e643c1922d1306e949d04</t>
         </is>
       </c>
     </row>
@@ -533,47 +533,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫119.000</t>
+          <t>₫268.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t>7k+</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/18hYiQ3V8</t>
+          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_22243625222</t>
+          <t>shopee_42357015741</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>06b67e3715cbcf93cd06e235b20e67a3</t>
+          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
         </is>
       </c>
     </row>
@@ -585,22 +585,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
+          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫168.000</t>
+          <t>₫229.000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50k+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BS7l1PQAB</t>
+          <t>https://s.shopee.vn/3ViZj9CjP1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_24450360446</t>
+          <t>shopee_28200539872</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
+          <t>4be218b81a6be9c55c23210e5f4e379b</t>
         </is>
       </c>
     </row>
@@ -637,22 +637,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
+          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫288.000</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>600k+</t>
+          <t>800k+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -662,22 +662,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LWcL0HAlc</t>
+          <t>https://s.shopee.vn/2g9SjcFu5u</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_24034739910</t>
+          <t>shopee_29807844451</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
+          <t>36268a94496dd6a3162249faf14ee638</t>
         </is>
       </c>
     </row>
@@ -689,17 +689,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
+          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫209.000</t>
+          <t>₫225.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -709,27 +709,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
+          <t>https://s.shopee.vn/3B5jKXE04z</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_13724863422</t>
+          <t>shopee_25241658670</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>5b19f9c4bae575f6667040d2b121506e</t>
+          <t>4e3452edfd64b6b785d3f600faf050e4</t>
         </is>
       </c>
     </row>
@@ -741,47 +741,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫289.000</t>
+          <t>₫826.000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>40k+</t>
+          <t>1tr+</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20tlwOIRRa</t>
+          <t>https://s.shopee.vn/1Le59AKynW</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_24660800592</t>
+          <t>shopee_26464017128</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
+          <t>0063c3803f4f95d096d307a3278cb4bd</t>
         </is>
       </c>
     </row>
@@ -793,42 +793,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
+          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫209.000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>30%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">62 </t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDC8hHo6d</t>
+          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_53557782402</t>
+          <t>shopee_13724863422</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>be4aca7de97245e2c4faa260b67482fb</t>
+          <t>5b19f9c4bae575f6667040d2b121506e</t>
         </is>
       </c>
     </row>
@@ -840,42 +845,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫198.000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>24%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t>300k+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
+          <t>https://s.shopee.vn/W4y9dO9UD</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_26858030583</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>0a64138bac7926d086d7164638e7ac2b</t>
         </is>
       </c>
     </row>
@@ -887,47 +897,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
+          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫599.000</t>
+          <t>₫168.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t>50k+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qaLk5J4mb</t>
+          <t>https://s.shopee.vn/BS7l1PQAB</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_27176838116</t>
+          <t>shopee_24450360446</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
+          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
         </is>
       </c>
     </row>
@@ -939,47 +949,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫826.000</t>
+          <t>₫1.599.000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1tr+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Le59AKynW</t>
+          <t>https://s.shopee.vn/3LP9WqDMjy</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_26464017128</t>
+          <t>shopee_40012750336</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0063c3803f4f95d096d307a3278cb4bd</t>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
         </is>
       </c>
     </row>
@@ -991,47 +1001,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫268.000</t>
+          <t>₫119.000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7k+</t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
+          <t>https://s.shopee.vn/18hYiQ3V8</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_42357015741</t>
+          <t>shopee_22243625222</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
+          <t>06b67e3715cbcf93cd06e235b20e67a3</t>
         </is>
       </c>
     </row>
@@ -1043,47 +1053,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>₫295.000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">223 </t>
+          <t>200k+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3g1zvSC640</t>
+          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_40355840814</t>
+          <t>shopee_28126833083</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2bd4126f7f9e643c1922d1306e949d04</t>
+          <t>768e867948552026756bd7e356cfca04</t>
         </is>
       </c>
     </row>
@@ -1095,47 +1105,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫295.000</t>
+          <t>₫289.000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>200k+</t>
+          <t>40k+</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
+          <t>https://s.shopee.vn/20tlwOIRRa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_28126833083</t>
+          <t>shopee_24660800592</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>768e867948552026756bd7e356cfca04</t>
+          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
         </is>
       </c>
     </row>
@@ -1147,47 +1157,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫1.599.000</t>
+          <t>₫288.000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t>600k+</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LP9WqDMjy</t>
+          <t>https://s.shopee.vn/2LWcL0HAlc</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_40012750336</t>
+          <t>shopee_24034739910</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3d93b1393727dc3578c2df28b475e423</t>
+          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
         </is>
       </c>
     </row>
@@ -1199,47 +1209,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
+          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫229.000</t>
+          <t>₫599.000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3ViZj9CjP1</t>
+          <t>https://s.shopee.vn/1qaLk5J4mb</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_28200539872</t>
+          <t>shopee_27176838116</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4be218b81a6be9c55c23210e5f4e379b</t>
+          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
         </is>
       </c>
     </row>
@@ -1303,47 +1313,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
+          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫225.000</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>₫140.000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t xml:space="preserve">621 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B5jKXE04z</t>
+          <t>https://s.shopee.vn/50XNVu71MO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_25241658670</t>
+          <t>shopee_28657885709</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4e3452edfd64b6b785d3f600faf050e4</t>
+          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
         </is>
       </c>
     </row>
@@ -1355,47 +1360,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
+          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫98.000</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>800k+</t>
+          <t xml:space="preserve">62 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9SjcFu5u</t>
+          <t>https://s.shopee.vn/2BDC8hHo6d</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_29807844451</t>
+          <t>shopee_53557782402</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>36268a94496dd6a3162249faf14ee638</t>
+          <t>be4aca7de97245e2c4faa260b67482fb</t>
         </is>
       </c>
     </row>
@@ -1407,42 +1407,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫450.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2qSsvvFGkx</t>
+          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_48107000510</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1454,42 +1454,83 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
+          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫140.000</t>
+          <t>₫450.000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">621 </t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/50XNVu71MO</t>
+          <t>https://s.shopee.vn/2qSsvvFGkx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_28657885709</t>
+          <t>shopee_48107000510</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
+          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>b1a466d2102f73101b9a158f8177c46c</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -1514,8 +1514,6 @@
           <t>55</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>https://</t>
@@ -1526,8 +1524,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>b1a466d2102f73101b9a158f8177c46c</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,52 +476,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+          <t>Tên mới</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>Liên hệ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223 </t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>25,5%</t>
+          <t>55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3g1zvSC640</t>
+          <t>https://</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>shopee_40355840814</t>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2bd4126f7f9e643c1922d1306e949d04</t>
+          <t>b1a466d2102f73101b9a158f8177c46c</t>
         </is>
       </c>
     </row>
@@ -533,47 +518,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫268.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7k+</t>
+          <t xml:space="preserve">224 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_42357015741</t>
+          <t>shopee_40355840814</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
+          <t>4d0361ea42311469477d46b6238caac3</t>
         </is>
       </c>
     </row>
@@ -585,47 +570,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
+          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫229.000</t>
+          <t>₫268.000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t>7k+</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3ViZj9CjP1</t>
+          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_28200539872</t>
+          <t>shopee_42357015741</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4be218b81a6be9c55c23210e5f4e379b</t>
+          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
         </is>
       </c>
     </row>
@@ -637,47 +622,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
+          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫98.000</t>
+          <t>₫229.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>800k+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9SjcFu5u</t>
+          <t>https://s.shopee.vn/3ViZj9CjP1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_29807844451</t>
+          <t>shopee_28200539872</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>36268a94496dd6a3162249faf14ee638</t>
+          <t>4be218b81a6be9c55c23210e5f4e379b</t>
         </is>
       </c>
     </row>
@@ -689,12 +674,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
+          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫225.000</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -704,32 +689,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t>800k+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B5jKXE04z</t>
+          <t>https://s.shopee.vn/2g9SjcFu5u</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_25241658670</t>
+          <t>shopee_29807844451</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4e3452edfd64b6b785d3f600faf050e4</t>
+          <t>36268a94496dd6a3162249faf14ee638</t>
         </is>
       </c>
     </row>
@@ -741,47 +726,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
+          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫826.000</t>
+          <t>₫225.000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1tr+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Le59AKynW</t>
+          <t>https://s.shopee.vn/3B5jKXE04z</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_26464017128</t>
+          <t>shopee_25241658670</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0063c3803f4f95d096d307a3278cb4bd</t>
+          <t>4e3452edfd64b6b785d3f600faf050e4</t>
         </is>
       </c>
     </row>
@@ -793,47 +778,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
+          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫209.000</t>
+          <t>₫826.000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t>1tr+</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
+          <t>https://s.shopee.vn/1Le59AKynW</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_13724863422</t>
+          <t>shopee_26464017128</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5b19f9c4bae575f6667040d2b121506e</t>
+          <t>0063c3803f4f95d096d307a3278cb4bd</t>
         </is>
       </c>
     </row>
@@ -845,47 +830,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
+          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫198.000</t>
+          <t>₫209.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>300k+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W4y9dO9UD</t>
+          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_26858030583</t>
+          <t>shopee_13724863422</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0a64138bac7926d086d7164638e7ac2b</t>
+          <t>5b19f9c4bae575f6667040d2b121506e</t>
         </is>
       </c>
     </row>
@@ -897,12 +882,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
+          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫168.000</t>
+          <t>₫198.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -912,32 +897,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50k+</t>
+          <t>300k+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BS7l1PQAB</t>
+          <t>https://s.shopee.vn/W4y9dO9UD</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_24450360446</t>
+          <t>shopee_26858030583</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
+          <t>0a64138bac7926d086d7164638e7ac2b</t>
         </is>
       </c>
     </row>
@@ -949,22 +934,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫1.599.000</t>
+          <t>₫168.000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t>50k+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -974,22 +959,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LP9WqDMjy</t>
+          <t>https://s.shopee.vn/BS7l1PQAB</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_40012750336</t>
+          <t>shopee_24450360446</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3d93b1393727dc3578c2df28b475e423</t>
+          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
         </is>
       </c>
     </row>
@@ -1001,12 +986,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫119.000</t>
+          <t>₫1.599.000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1016,32 +1001,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/18hYiQ3V8</t>
+          <t>https://s.shopee.vn/3LP9WqDMjy</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_22243625222</t>
+          <t>shopee_40012750336</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>06b67e3715cbcf93cd06e235b20e67a3</t>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
         </is>
       </c>
     </row>
@@ -1053,47 +1038,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫295.000</t>
+          <t>₫119.000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>200k+</t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
+          <t>https://s.shopee.vn/18hYiQ3V8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_28126833083</t>
+          <t>shopee_22243625222</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>768e867948552026756bd7e356cfca04</t>
+          <t>06b67e3715cbcf93cd06e235b20e67a3</t>
         </is>
       </c>
     </row>
@@ -1105,47 +1090,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫289.000</t>
+          <t>₫295.000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>40k+</t>
+          <t>200k+</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20tlwOIRRa</t>
+          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_24660800592</t>
+          <t>shopee_28126833083</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
+          <t>768e867948552026756bd7e356cfca04</t>
         </is>
       </c>
     </row>
@@ -1157,47 +1142,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫288.000</t>
+          <t>₫289.000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>600k+</t>
+          <t>40k+</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LWcL0HAlc</t>
+          <t>https://s.shopee.vn/20tlwOIRRa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_24034739910</t>
+          <t>shopee_24660800592</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
+          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
         </is>
       </c>
     </row>
@@ -1209,47 +1194,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
+          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫599.000</t>
+          <t>₫288.000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t>600k+</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qaLk5J4mb</t>
+          <t>https://s.shopee.vn/2LWcL0HAlc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_27176838116</t>
+          <t>shopee_24034739910</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
+          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
         </is>
       </c>
     </row>
@@ -1261,47 +1246,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kệ đặt chậu hoa, chậu cây cảnh 6 tầng, chậu hoa cây cảnh khung sắt chắc chắn, kệ decor có bánh xe</t>
+          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫265.000</t>
+          <t>₫599.000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">928 </t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/30mJ8EEdPw</t>
+          <t>https://s.shopee.vn/1qaLk5J4mb</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_26319252965</t>
+          <t>shopee_27176838116</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>e8c259bd483858e228b0c2099ebeb852</t>
+          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
         </is>
       </c>
     </row>
@@ -1313,42 +1298,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
+          <t>Kệ đặt chậu hoa, chậu cây cảnh 6 tầng, chậu hoa cây cảnh khung sắt chắc chắn, kệ decor có bánh xe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫140.000</t>
+          <t>₫265.000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">621 </t>
+          <t xml:space="preserve">928 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/50XNVu71MO</t>
+          <t>https://s.shopee.vn/30mJ8EEdPw</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_28657885709</t>
+          <t>shopee_26319252965</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
+          <t>e8c259bd483858e228b0c2099ebeb852</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1350,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
+          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫140.000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">62 </t>
+          <t xml:space="preserve">621 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDC8hHo6d</t>
+          <t>https://s.shopee.vn/50XNVu71MO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_53557782402</t>
+          <t>shopee_28657885709</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>be4aca7de97245e2c4faa260b67482fb</t>
+          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
         </is>
       </c>
     </row>
@@ -1407,42 +1397,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t xml:space="preserve">62 </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
+          <t>https://s.shopee.vn/2BDC8hHo6d</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_53557782402</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>be4aca7de97245e2c4faa260b67482fb</t>
         </is>
       </c>
     </row>
@@ -1454,79 +1444,934 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫450.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2qSsvvFGkx</t>
+          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_48107000510</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tên mới</t>
+          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liên hệ</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>55</t>
+          <t>₫450.000</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://</t>
+          <t>https://s.shopee.vn/2qSsvvFGkx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>shopee_48107000510</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>b1a466d2102f73101b9a158f8177c46c</t>
+          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quà tặng LOGO Kho báu sạc xuyên biên giới tùy chỉnh có cáp có thể tháo rời 2000mAh Mini Power Bank</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>₫272.130</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/52612730419?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824h9-mpumuqfytdl835.webp</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>shopee_52612730419</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>067055d9440e75ddba8282da81c3481f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tai nghe không dây Tai nghe Bluetooth Không rò rỉ Trò chơi Máy tính di động Mô hình riêng Tai nghe khử tiếng ồn</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>₫437.974</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21 </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40332039212?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824gm-mpx2g6f5b218a4.webp</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>shopee_40332039212</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>c5caa4d1917f9bdc176b0b7b95dd10a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Điều Hòa Mini Hơi Nước Siêu Mát - Quạt Điều Hòa Mini Để Bàn Nhỏ Gọn</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>₫196.000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90 </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41756393542?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwv5cxzv1wea.webp</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>shopee_41756393542</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>805a83d7c2dca12627628dabf0d639fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thích hợp cho Apple Sạc dự phòng không dây từ tính Thích hợp cho Sạc dự phòng không dây magsafe 5.000mAh</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>₫297.323</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23 </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54661835387?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-823o9-mp7jhyybqmma7a.webp</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>shopee_54661835387</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>44e8b25475ffc538983334a291905a4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tai nghe Bluetooth chuyên nghiệp Q71 | Chống mồ hôi, chống trượt và thời lượng pin cực dài Âm nhạc thể thao</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>₫120.000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45750965028?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqeynei83yk52.webp</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>shopee_45750965028</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>d0300a481504fb63329e2ff3f7c18a38</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth Siêu Trầm 360 Độ Âm Thanh Vòm Bass Mạnh Có Đèn Nhiều Màu âm thanh cực đã</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42424643784?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mf0ylbkygo3sa7.webp</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>shopee_42424643784</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>9c8523cf0dd0260781157b10a01f0169</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>shopee_53401541671</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tai nghe Bluetooth không dây Pro6 Mini: Sang trọng, Chống ồn, Tương thích với mọi điện thoại</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>₫50.000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57301683598?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mghz6alwbp59a7.webp</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>shopee_57301683598</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>d065e379133010f610a0f3d34b2f8746</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Quạt điều hòa phun sương quạt không cánh, Quạt hơi nước 6 cấp độ tính năng hẹn giờ Với Mosquito Repellent tấm</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42257303883?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbrwti98f7n6a1.webp</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>shopee_42257303883</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0c7431e5f758f272df0d6d7e46cbc6b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gối tựa ô tô công thái học cao cấp, Cao su non Memory Foam mềm mại êm ái - The ComfyPrime LIFXY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>₫650.000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812 </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54355250128?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mqklsavlob9d7b.webp</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>shopee_54355250128</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>08789068712f22c0e7b5e6d13e093d55</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20000mah đa chức năng xách tay sạc kho báu｜Công suất lớn với 4 cáp sạc nhanh</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>₫198.000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/44850786084?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mggnqwp1w5cd18.webp</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>shopee_44850786084</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>e8d80b1947cd4ab9d432090972bba88c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tai Nghe Bluetooth PRO4 Không Dây TWS Cảm Ứng Chạm Khử Tiếng Ồn Dùng Chơi Game, Nghe Nhạc - PR04 HOT HOT HOT</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>₫209.000</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>50k+</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29029784452?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134201-7ra0g-m7ekmpklql8c5d.webp</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>shopee_29029784452</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>d4767bb5964aa1e6262f71f624f391a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>shopee_26688092638</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>f49544faffe4bbd3aeb4b1edcabefc44</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth Pro 10 Thiết Kế Đẹp, Âm Thanh Sống Động, Công Suất 30W Thiết Kế Hợp Để Mang Đi Du Lịch</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>₫499.000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>400k+</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26257417460?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mfy6u2kcmhvw32.webp</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>shopee_26257417460</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>4eb9d419184c6176d84cfc5d91ff9e0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[Quà tặng nhỏ gọn trong lòng bàn tay] Pin dự phòng mini 5000mAh sạc nhanh hai đầu Quà tặng thời trang, tiện dụng cho b</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>₫198.000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49550938313?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqbea9w00spfa.webp</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>shopee_49550938313</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>e669e6968c37d2f2b554b3441960d4ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>kéo cắt cây cảnh Nhật SK5,kéo cắt cành trên cao,cành cây khô thép Cắt sắc nét,Tay cầm Thoải mái Bọt biển</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>₫81.000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368 </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51908128978?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mm8szj3qkrut23.webp</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>shopee_51908128978</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0594349909ea04dba9251177b0c930d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Balo thời trang cặp sách học sinh phong cách Hàn Quốc chất liệu vải polieter chống thấm nước có ngăn đựng laptop G 877</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>₫129.000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/12705585947?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7qukw-lj6fqhb01yj0a7.webp</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>shopee_12705585947</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>b6744dec37d28210cf2ae0f6c46eec6e</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5fnAdtqGf1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W4y9dO9UD</t>
+          <t>https://s.shopee.vn/7fYF1ZiebD</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2qSsvvFGkx</t>
+          <t>https://s.shopee.vn/7VEopGjHw8</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1546,7 +1546,6 @@
           <t>₫272.130</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">8 </t>
@@ -1559,7 +1558,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/52612730419?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/80B5QBhNvB</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1572,7 +1571,6 @@
           <t>shopee_52612730419</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>067055d9440e75ddba8282da81c3481f</t>
@@ -1595,7 +1593,6 @@
           <t>₫437.974</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">21 </t>
@@ -1608,7 +1605,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40332039212?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8V7M16fTuI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1621,7 +1618,6 @@
           <t>shopee_40332039212</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>c5caa4d1917f9bdc176b0b7b95dd10a6</t>
@@ -1661,7 +1657,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41756393542?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8Knvong7FH</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1674,7 +1670,6 @@
           <t>shopee_41756393542</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>805a83d7c2dca12627628dabf0d639fa</t>
@@ -1697,7 +1692,6 @@
           <t>₫297.323</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">23 </t>
@@ -1710,7 +1704,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54661835387?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7KvOcxjvH7</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1723,7 +1717,6 @@
           <t>shopee_54661835387</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>44e8b25475ffc538983334a291905a4a</t>
@@ -1746,7 +1739,6 @@
           <t>₫120.000</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">2 </t>
@@ -1759,7 +1751,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45750965028?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7prfDsi1GE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1772,7 +1764,6 @@
           <t>shopee_45750965028</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>d0300a481504fb63329e2ff3f7c18a38</t>
@@ -1812,7 +1803,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42424643784?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6pz822lpI4</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1825,7 +1816,6 @@
           <t>shopee_42424643784</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>9c8523cf0dd0260781157b10a01f0169</t>
@@ -1848,8 +1838,6 @@
           <t>₫356.000</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -1857,7 +1845,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6ffhpjmSd3</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1870,7 +1858,6 @@
           <t>shopee_53401541671</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>aef6c3542d96a164f2f808809d3f5b09</t>
@@ -1893,8 +1880,6 @@
           <t>₫50.000</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -1902,7 +1887,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/57301683598?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7AbyQekYcA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1915,7 +1900,6 @@
           <t>shopee_57301683598</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>d065e379133010f610a0f3d34b2f8746</t>
@@ -1955,7 +1939,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42257303883?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/70IYELlBx9</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1968,7 +1952,6 @@
           <t>shopee_42257303883</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>0c7431e5f758f272df0d6d7e46cbc6b5</t>
@@ -1991,7 +1974,6 @@
           <t>₫650.000</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">812 </t>
@@ -2004,7 +1986,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54355250128?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6AjREooMe0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2017,7 +1999,6 @@
           <t>shopee_54355250128</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>08789068712f22c0e7b5e6d13e093d55</t>
@@ -2040,8 +2021,6 @@
           <t>₫198.000</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -2049,7 +2028,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44850786084?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/60Q12Vozyz</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2062,7 +2041,6 @@
           <t>shopee_44850786084</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>e8d80b1947cd4ab9d432090972bba88c</t>
@@ -2102,7 +2080,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29029784452?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6VMHdQn5y6</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2115,7 +2093,6 @@
           <t>shopee_29029784452</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>d4767bb5964aa1e6262f71f624f391a9</t>
@@ -2155,7 +2132,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6L2rR7njJ5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2168,7 +2145,6 @@
           <t>shopee_26688092638</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>f49544faffe4bbd3aeb4b1edcabefc44</t>
@@ -2191,7 +2167,6 @@
           <t>₫499.000</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>400k+</t>
@@ -2204,7 +2179,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26257417460?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5VTkRaqtzw</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2217,7 +2192,6 @@
           <t>shopee_26257417460</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>4eb9d419184c6176d84cfc5d91ff9e0d</t>
@@ -2240,7 +2214,6 @@
           <t>₫198.000</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">6 </t>
@@ -2253,7 +2226,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49550938313?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5LAKFHrXKv</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2266,7 +2239,6 @@
           <t>shopee_49550938313</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>e669e6968c37d2f2b554b3441960d4ec</t>
@@ -2306,7 +2278,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51908128978?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5q6aqCpdK2</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2319,7 +2291,6 @@
           <t>shopee_51908128978</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>0594349909ea04dba9251177b0c930d6</t>
@@ -2342,7 +2313,6 @@
           <t>₫129.000</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>1k+</t>
@@ -2355,7 +2325,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/12705585947?trace=%7B%22trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.knQ2ogFBmZ.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4qE3eMtRLs</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2368,7 +2338,6 @@
           <t>shopee_12705585947</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>b6744dec37d28210cf2ae0f6c46eec6e</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,12 +518,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+          <t>Loa Bluetooth Siêu Trầm 360 Độ Âm Thanh Vòm Bass Mạnh Có Đèn Nhiều Màu âm thanh cực đã</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>₫159.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -533,32 +533,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5fnAdtqGf1</t>
+          <t>https://s.shopee.vn/6pz822lpI4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mf0ylbkygo3sa7.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_40355840814</t>
+          <t>shopee_42424643784</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4d0361ea42311469477d46b6238caac3</t>
+          <t>9c8523cf0dd0260781157b10a01f0169</t>
         </is>
       </c>
     </row>
@@ -570,47 +570,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
+          <t>kéo cắt cây cảnh Nhật SK5,kéo cắt cành trên cao,cành cây khô thép Cắt sắc nét,Tay cầm Thoải mái Bọt biển</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫268.000</t>
+          <t>₫81.000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7k+</t>
+          <t xml:space="preserve">368 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
+          <t>https://s.shopee.vn/5q6aqCpdK2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mm8szj3qkrut23.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_42357015741</t>
+          <t>shopee_51908128978</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
+          <t>0594349909ea04dba9251177b0c930d6</t>
         </is>
       </c>
     </row>
@@ -622,47 +622,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫229.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t xml:space="preserve">224 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3ViZj9CjP1</t>
+          <t>https://s.shopee.vn/5fnAdtqGf1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_28200539872</t>
+          <t>shopee_40355840814</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4be218b81a6be9c55c23210e5f4e379b</t>
+          <t>4d0361ea42311469477d46b6238caac3</t>
         </is>
       </c>
     </row>
@@ -674,47 +674,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
+          <t>Điều Hòa Mini Hơi Nước Siêu Mát - Quạt Điều Hòa Mini Để Bàn Nhỏ Gọn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫98.000</t>
+          <t>₫196.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>800k+</t>
+          <t xml:space="preserve">90 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9SjcFu5u</t>
+          <t>https://s.shopee.vn/8Knvong7FH</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwv5cxzv1wea.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_29807844451</t>
+          <t>shopee_41756393542</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>36268a94496dd6a3162249faf14ee638</t>
+          <t>805a83d7c2dca12627628dabf0d639fa</t>
         </is>
       </c>
     </row>
@@ -726,47 +726,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫225.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t xml:space="preserve">36 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B5jKXE04z</t>
+          <t>https://s.shopee.vn/6L2rR7njJ5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_25241658670</t>
+          <t>shopee_26688092638</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4e3452edfd64b6b785d3f600faf050e4</t>
+          <t>f49544faffe4bbd3aeb4b1edcabefc44</t>
         </is>
       </c>
     </row>
@@ -778,47 +778,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
+          <t>Quạt điều hòa phun sương quạt không cánh, Quạt hơi nước 6 cấp độ tính năng hẹn giờ Với Mosquito Repellent tấm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫826.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1tr+</t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Le59AKynW</t>
+          <t>https://s.shopee.vn/70IYELlBx9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbrwti98f7n6a1.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_26464017128</t>
+          <t>shopee_42257303883</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0063c3803f4f95d096d307a3278cb4bd</t>
+          <t>0c7431e5f758f272df0d6d7e46cbc6b5</t>
         </is>
       </c>
     </row>
@@ -830,47 +830,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
+          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫209.000</t>
+          <t>₫268.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t>7k+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
+          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_13724863422</t>
+          <t>shopee_42357015741</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5b19f9c4bae575f6667040d2b121506e</t>
+          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
         </is>
       </c>
     </row>
@@ -882,47 +882,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
+          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫198.000</t>
+          <t>₫229.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>300k+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7fYF1ZiebD</t>
+          <t>https://s.shopee.vn/3ViZj9CjP1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_26858030583</t>
+          <t>shopee_28200539872</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0a64138bac7926d086d7164638e7ac2b</t>
+          <t>4be218b81a6be9c55c23210e5f4e379b</t>
         </is>
       </c>
     </row>
@@ -934,47 +934,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
+          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫168.000</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>50k+</t>
+          <t>800k+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BS7l1PQAB</t>
+          <t>https://s.shopee.vn/2g9SjcFu5u</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_24450360446</t>
+          <t>shopee_29807844451</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
+          <t>36268a94496dd6a3162249faf14ee638</t>
         </is>
       </c>
     </row>
@@ -986,47 +986,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫1.599.000</t>
+          <t>₫225.000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LP9WqDMjy</t>
+          <t>https://s.shopee.vn/3B5jKXE04z</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_40012750336</t>
+          <t>shopee_25241658670</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3d93b1393727dc3578c2df28b475e423</t>
+          <t>4e3452edfd64b6b785d3f600faf050e4</t>
         </is>
       </c>
     </row>
@@ -1038,47 +1038,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+          <t>Tai Nghe Bluetooth PRO4 Không Dây TWS Cảm Ứng Chạm Khử Tiếng Ồn Dùng Chơi Game, Nghe Nhạc - PR04 HOT HOT HOT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫119.000</t>
+          <t>₫209.000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t>50k+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/18hYiQ3V8</t>
+          <t>https://s.shopee.vn/6VMHdQn5y6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134201-7ra0g-m7ekmpklql8c5d.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_22243625222</t>
+          <t>shopee_29029784452</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>06b67e3715cbcf93cd06e235b20e67a3</t>
+          <t>d4767bb5964aa1e6262f71f624f391a9</t>
         </is>
       </c>
     </row>
@@ -1090,47 +1090,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
+          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫295.000</t>
+          <t>₫826.000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>200k+</t>
+          <t>1tr+</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
+          <t>https://s.shopee.vn/1Le59AKynW</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_28126833083</t>
+          <t>shopee_26464017128</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>768e867948552026756bd7e356cfca04</t>
+          <t>0063c3803f4f95d096d307a3278cb4bd</t>
         </is>
       </c>
     </row>
@@ -1142,47 +1142,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫289.000</t>
+          <t>₫209.000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>40k+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20tlwOIRRa</t>
+          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_24660800592</t>
+          <t>shopee_13724863422</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
+          <t>5b19f9c4bae575f6667040d2b121506e</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
+          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫288.000</t>
+          <t>₫198.000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>600k+</t>
+          <t>300k+</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1219,22 +1219,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LWcL0HAlc</t>
+          <t>https://s.shopee.vn/7fYF1ZiebD</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_24034739910</t>
+          <t>shopee_26858030583</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
+          <t>0a64138bac7926d086d7164638e7ac2b</t>
         </is>
       </c>
     </row>
@@ -1246,47 +1246,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
+          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫599.000</t>
+          <t>₫168.000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t>50k+</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qaLk5J4mb</t>
+          <t>https://s.shopee.vn/BS7l1PQAB</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_27176838116</t>
+          <t>shopee_24450360446</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
+          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
         </is>
       </c>
     </row>
@@ -1298,47 +1298,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kệ đặt chậu hoa, chậu cây cảnh 6 tầng, chậu hoa cây cảnh khung sắt chắc chắn, kệ decor có bánh xe</t>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫265.000</t>
+          <t>₫1.599.000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">928 </t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/30mJ8EEdPw</t>
+          <t>https://s.shopee.vn/3LP9WqDMjy</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_26319252965</t>
+          <t>shopee_40012750336</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>e8c259bd483858e228b0c2099ebeb852</t>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
         </is>
       </c>
     </row>
@@ -1350,42 +1350,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫140.000</t>
+          <t>₫119.000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">621 </t>
+          <t xml:space="preserve">772 </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/50XNVu71MO</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_28657885709</t>
+          <t>shopee_22243625222</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
+          <t>399716bb972df0ab32724f6fefb65c81</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1402,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
+          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫295.000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>19%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">62 </t>
+          <t>200k+</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1417,22 +1427,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDC8hHo6d</t>
+          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_53557782402</t>
+          <t>shopee_28126833083</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>be4aca7de97245e2c4faa260b67482fb</t>
+          <t>768e867948552026756bd7e356cfca04</t>
         </is>
       </c>
     </row>
@@ -1444,42 +1454,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫289.000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>15%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t>40k+</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
+          <t>https://s.shopee.vn/20tlwOIRRa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_24660800592</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
         </is>
       </c>
     </row>
@@ -1491,42 +1506,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
+          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>₫450.000</t>
+          <t>₫288.000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>12%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t>600k+</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7VEopGjHw8</t>
+          <t>https://s.shopee.vn/2LWcL0HAlc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>shopee_48107000510</t>
+          <t>shopee_24034739910</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
+          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
         </is>
       </c>
     </row>
@@ -1538,42 +1558,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quà tặng LOGO Kho báu sạc xuyên biên giới tùy chỉnh có cáp có thể tháo rời 2000mAh Mini Power Bank</t>
+          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>₫272.130</t>
+          <t>₫599.000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 </t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/80B5QBhNvB</t>
+          <t>https://s.shopee.vn/1qaLk5J4mb</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824h9-mpumuqfytdl835.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>shopee_52612730419</t>
+          <t>shopee_27176838116</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>067055d9440e75ddba8282da81c3481f</t>
+          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
         </is>
       </c>
     </row>
@@ -1585,42 +1610,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tai nghe không dây Tai nghe Bluetooth Không rò rỉ Trò chơi Máy tính di động Mô hình riêng Tai nghe khử tiếng ồn</t>
+          <t>Kệ đặt chậu hoa, chậu cây cảnh 6 tầng, chậu hoa cây cảnh khung sắt chắc chắn, kệ decor có bánh xe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>₫437.974</t>
+          <t>₫265.000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 </t>
+          <t xml:space="preserve">928 </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8V7M16fTuI</t>
+          <t>https://s.shopee.vn/30mJ8EEdPw</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824gm-mpx2g6f5b218a4.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>shopee_40332039212</t>
+          <t>shopee_26319252965</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>c5caa4d1917f9bdc176b0b7b95dd10a6</t>
+          <t>e8c259bd483858e228b0c2099ebeb852</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1662,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Điều Hòa Mini Hơi Nước Siêu Mát - Quạt Điều Hòa Mini Để Bàn Nhỏ Gọn</t>
+          <t>Loa Bluetooth Pro 10 Thiết Kế Đẹp, Âm Thanh Sống Động, Công Suất 30W Thiết Kế Hợp Để Mang Đi Du Lịch</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>₫196.000</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>₫499.000</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">90 </t>
+          <t>400k+</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8Knvong7FH</t>
+          <t>https://s.shopee.vn/5VTkRaqtzw</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwv5cxzv1wea.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mfy6u2kcmhvw32.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>shopee_41756393542</t>
+          <t>shopee_26257417460</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>805a83d7c2dca12627628dabf0d639fa</t>
+          <t>4eb9d419184c6176d84cfc5d91ff9e0d</t>
         </is>
       </c>
     </row>
@@ -1684,42 +1709,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thích hợp cho Apple Sạc dự phòng không dây từ tính Thích hợp cho Sạc dự phòng không dây magsafe 5.000mAh</t>
+          <t>Balo thời trang cặp sách học sinh phong cách Hàn Quốc chất liệu vải polieter chống thấm nước có ngăn đựng laptop G 877</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>₫297.323</t>
+          <t>₫129.000</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7KvOcxjvH7</t>
+          <t>https://s.shopee.vn/4qE3eMtRLs</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-823o9-mp7jhyybqmma7a.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7qukw-lj6fqhb01yj0a7.webp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>shopee_54661835387</t>
+          <t>shopee_12705585947</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>44e8b25475ffc538983334a291905a4a</t>
+          <t>b6744dec37d28210cf2ae0f6c46eec6e</t>
         </is>
       </c>
     </row>
@@ -1731,42 +1756,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tai nghe Bluetooth chuyên nghiệp Q71 | Chống mồ hôi, chống trượt và thời lượng pin cực dài Âm nhạc thể thao</t>
+          <t>Gối tựa ô tô công thái học cao cấp, Cao su non Memory Foam mềm mại êm ái - The ComfyPrime LIFXY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>₫120.000</t>
+          <t>₫650.000</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">812 </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7prfDsi1GE</t>
+          <t>https://s.shopee.vn/6AjREooMe0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqeynei83yk52.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mqklsavlob9d7b.webp</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>shopee_45750965028</t>
+          <t>shopee_54355250128</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>d0300a481504fb63329e2ff3f7c18a38</t>
+          <t>08789068712f22c0e7b5e6d13e093d55</t>
         </is>
       </c>
     </row>
@@ -1778,47 +1803,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Loa Bluetooth Siêu Trầm 360 Độ Âm Thanh Vòm Bass Mạnh Có Đèn Nhiều Màu âm thanh cực đã</t>
+          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>₫159.000</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>₫140.000</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">621 </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6pz822lpI4</t>
+          <t>https://s.shopee.vn/50XNVu71MO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mf0ylbkygo3sa7.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>shopee_42424643784</t>
+          <t>shopee_28657885709</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>9c8523cf0dd0260781157b10a01f0169</t>
+          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
         </is>
       </c>
     </row>
@@ -1830,37 +1850,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62 </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6ffhpjmSd3</t>
+          <t>https://s.shopee.vn/2BDC8hHo6d</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>shopee_53401541671</t>
+          <t>shopee_53557782402</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+          <t>be4aca7de97245e2c4faa260b67482fb</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1897,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tai nghe Bluetooth không dây Pro6 Mini: Sang trọng, Chống ồn, Tương thích với mọi điện thoại</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>₫50.000</t>
+          <t>₫49.000</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1887,22 +1917,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7AbyQekYcA</t>
+          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mghz6alwbp59a7.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>shopee_57301683598</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>d065e379133010f610a0f3d34b2f8746</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1914,47 +1944,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quạt điều hòa phun sương quạt không cánh, Quạt hơi nước 6 cấp độ tính năng hẹn giờ Với Mosquito Repellent tấm</t>
+          <t>Thích hợp cho Apple Sạc dự phòng không dây từ tính Thích hợp cho Sạc dự phòng không dây magsafe 5.000mAh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>₫149.000</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>₫297.323</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">23 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70IYELlBx9</t>
+          <t>https://s.shopee.vn/7KvOcxjvH7</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbrwti98f7n6a1.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-823o9-mp7jhyybqmma7a.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>shopee_42257303883</t>
+          <t>shopee_54661835387</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0c7431e5f758f272df0d6d7e46cbc6b5</t>
+          <t>44e8b25475ffc538983334a291905a4a</t>
         </is>
       </c>
     </row>
@@ -1966,42 +1991,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gối tựa ô tô công thái học cao cấp, Cao su non Memory Foam mềm mại êm ái - The ComfyPrime LIFXY</t>
+          <t>Tai nghe không dây Tai nghe Bluetooth Không rò rỉ Trò chơi Máy tính di động Mô hình riêng Tai nghe khử tiếng ồn</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>₫650.000</t>
+          <t>₫437.974</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">812 </t>
+          <t xml:space="preserve">21 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6AjREooMe0</t>
+          <t>https://s.shopee.vn/8V7M16fTuI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mqklsavlob9d7b.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824gm-mpx2g6f5b218a4.webp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>shopee_54355250128</t>
+          <t>shopee_40332039212</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>08789068712f22c0e7b5e6d13e093d55</t>
+          <t>c5caa4d1917f9bdc176b0b7b95dd10a6</t>
         </is>
       </c>
     </row>
@@ -2013,37 +2038,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20000mah đa chức năng xách tay sạc kho báu｜Công suất lớn với 4 cáp sạc nhanh</t>
+          <t>Quà tặng LOGO Kho báu sạc xuyên biên giới tùy chỉnh có cáp có thể tháo rời 2000mAh Mini Power Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>₫198.000</t>
+          <t>₫272.130</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/60Q12Vozyz</t>
+          <t>https://s.shopee.vn/80B5QBhNvB</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mggnqwp1w5cd18.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824h9-mpumuqfytdl835.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>shopee_44850786084</t>
+          <t>shopee_52612730419</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>e8d80b1947cd4ab9d432090972bba88c</t>
+          <t>067055d9440e75ddba8282da81c3481f</t>
         </is>
       </c>
     </row>
@@ -2055,47 +2085,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tai Nghe Bluetooth PRO4 Không Dây TWS Cảm Ứng Chạm Khử Tiếng Ồn Dùng Chơi Game, Nghe Nhạc - PR04 HOT HOT HOT</t>
+          <t>[Quà tặng nhỏ gọn trong lòng bàn tay] Pin dự phòng mini 5000mAh sạc nhanh hai đầu Quà tặng thời trang, tiện dụng cho b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>₫209.000</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>₫198.000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>50k+</t>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VMHdQn5y6</t>
+          <t>https://s.shopee.vn/5LAKFHrXKv</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134201-7ra0g-m7ekmpklql8c5d.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqbea9w00spfa.webp</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>shopee_29029784452</t>
+          <t>shopee_49550938313</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>d4767bb5964aa1e6262f71f624f391a9</t>
+          <t>e669e6968c37d2f2b554b3441960d4ec</t>
         </is>
       </c>
     </row>
@@ -2107,47 +2132,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+          <t>Tai nghe Bluetooth chuyên nghiệp Q71 | Chống mồ hôi, chống trượt và thời lượng pin cực dài Âm nhạc thể thao</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>₫189.000</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>₫120.000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 </t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L2rR7njJ5</t>
+          <t>https://s.shopee.vn/7prfDsi1GE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqeynei83yk52.webp</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>shopee_26688092638</t>
+          <t>shopee_45750965028</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>f49544faffe4bbd3aeb4b1edcabefc44</t>
+          <t>d0300a481504fb63329e2ff3f7c18a38</t>
         </is>
       </c>
     </row>
@@ -2159,42 +2179,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Loa Bluetooth Pro 10 Thiết Kế Đẹp, Âm Thanh Sống Động, Công Suất 30W Thiết Kế Hợp Để Mang Đi Du Lịch</t>
+          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>₫499.000</t>
+          <t>₫450.000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>400k+</t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VTkRaqtzw</t>
+          <t>https://s.shopee.vn/7VEopGjHw8</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mfy6u2kcmhvw32.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>shopee_26257417460</t>
+          <t>shopee_48107000510</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4eb9d419184c6176d84cfc5d91ff9e0d</t>
+          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
         </is>
       </c>
     </row>
@@ -2206,17 +2226,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[Quà tặng nhỏ gọn trong lòng bàn tay] Pin dự phòng mini 5000mAh sạc nhanh hai đầu Quà tặng thời trang, tiện dụng cho b</t>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>₫198.000</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 </t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2226,22 +2241,22 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5LAKFHrXKv</t>
+          <t>https://s.shopee.vn/6ffhpjmSd3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqbea9w00spfa.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>shopee_49550938313</t>
+          <t>shopee_53401541671</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>e669e6968c37d2f2b554b3441960d4ec</t>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
         </is>
       </c>
     </row>
@@ -2253,47 +2268,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>kéo cắt cây cảnh Nhật SK5,kéo cắt cành trên cao,cành cây khô thép Cắt sắc nét,Tay cầm Thoải mái Bọt biển</t>
+          <t>Tai nghe Bluetooth không dây Pro6 Mini: Sang trọng, Chống ồn, Tương thích với mọi điện thoại</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>₫81.000</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">368 </t>
+          <t>₫50.000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q6aqCpdK2</t>
+          <t>https://s.shopee.vn/7AbyQekYcA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mm8szj3qkrut23.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mghz6alwbp59a7.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>shopee_51908128978</t>
+          <t>shopee_57301683598</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0594349909ea04dba9251177b0c930d6</t>
+          <t>d065e379133010f610a0f3d34b2f8746</t>
         </is>
       </c>
     </row>
@@ -2305,42 +2310,678 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Balo thời trang cặp sách học sinh phong cách Hàn Quốc chất liệu vải polieter chống thấm nước có ngăn đựng laptop G 877</t>
+          <t>20000mah đa chức năng xách tay sạc kho báu｜Công suất lớn với 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>₫129.000</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1k+</t>
+          <t>₫198.000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4qE3eMtRLs</t>
+          <t>https://s.shopee.vn/60Q12Vozyz</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7qukw-lj6fqhb01yj0a7.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mggnqwp1w5cd18.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>shopee_12705585947</t>
+          <t>shopee_44850786084</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>b6744dec37d28210cf2ae0f6c46eec6e</t>
+          <t>e8d80b1947cd4ab9d432090972bba88c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bàn phím ba chế độ Bluetooth không dây Wolf Tu L98 RGB Laptop Trò chơi văn phòng Phim có dây Bàn phím im lặng</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>₫527.716</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41432192875?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-82596-mq528nmp9ipsc8.webp</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>shopee_41432192875</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>616e5acadf9695fdb46b8859a9f975bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Giày JD1 low các phối màu, giày JD1 cổ thấp full bill box</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>₫990.000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29850280626?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mfhyusf8mmmi94.webp</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>shopee_29850280626</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fda90cc2b042321567ef3ba1767002d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>X87 Tai nghe Bluetooth Music HiFi Stereo Thể thao Chống nước Chống ồn Tương thích với mọi nền tảng Phát trực tiếp Cuộc</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>₫184.800</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48000121383?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg7n5txlx4wab0.webp</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>shopee_48000121383</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>e22500ec34950bead88934adbf090931</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>₫109.000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56 </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57450548196?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>shopee_57450548196</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>113eb535211dc5576ce1f369536e321f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>895B Tai nghe không dây Bluetooth Tai nghe chơi game chất lượng âm thanh HiFi, thời lượng pin dài</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>₫180.000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43725797287?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg7vtlkzdi4r7f.webp</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>shopee_43725797287</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5051cd8699875c55748b7d6a35aaf524</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>‌Quạt Điều Hòa Mini Để Bàn - Làm Mát Phun Sương Đa Năng Sạc USB - Dùng Cho Gia đình/Văn Phòng - Hàng Chính Hãng Siêu êm</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/44056006107?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbeznrglphhzba.webp</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>shopee_44056006107</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>d6ac7b3cd6ddaf2e4b418c3e3219fbc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pin dự phòng 20000mAh, sạc nhanh, cáp 3 trong 1, dung lượng lớn, thiết yếu cho du lịch và chơi game.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>₫70.000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50101468541?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgne2h0vw83u8b.webp</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>shopee_50101468541</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>dbd9cd1b5ca9df96f73cbfb352cf0591</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Máy hút bụi cầm tay mini cao cấp R6053 - Hút cực mạnh - Công Suất 120W - Dùng Hút Cả Nhà Và Xe - HB6,Dùng liên tục 5 giờ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>₫360.000</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25868513907?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ra0g-m87jow0yorjic9.webp</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>shopee_25868513907</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>d4f85350ef2340d1c9195e696dd97afa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Q86 Vintage máy ảnh mới trong tai phong cách thoải mái đôi tai HD màn hình chạy thể thao tai nghe bluetooth JF</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>₫218.000</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50450668064?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgjnstldc0svde.webp</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>shopee_50450668064</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>71c309837e3f3d718f0f15a81924aa5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth Mini Không Dây Thiết Kế Nhỏ Gọn Sang Trọng Nghe Nhạc Hay Có Móc Treo Giá Rẻ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>₫199.000</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>300k+</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28708632089?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mkuq1bj48zyc61.webp</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>shopee_28708632089</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>16606867986f8d3cb5faba17c90f053d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>shopee_51401292730</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Gối Tựa Đầu Ô tô Trẻ Em Cao Su Non Memory Foam Êm Ái, Công Thái Học Chuẩn Y Khoa | KidRest</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>₫680.000</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134 </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50555002230?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mnjl1q1xys5i38.webp</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>shopee_50555002230</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>410196c9b773b4858fc695fdecf9f711</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cốc ép trái cây cầm tay nhỏ gọn, hoàn toàn tự động, đa chức năng, lý tưởng cho học sinh, dễ sử dụng</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>₫179.000</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64 </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25895712227?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbf2ofv4dnn83d.webp</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>shopee_25895712227</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>7b260132ce735087b2f95677d3f537c0</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5fnAdtqGf1</t>
+          <t>https://s.shopee.vn/40eyrauSBO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7fYF1ZiebD</t>
+          <t>https://s.shopee.vn/2BDKgE1Qtr</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1Vxdt03yFf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7KvOcxjvH7</t>
+          <t>https://s.shopee.vn/1gH45J3Kue</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7prfDsi1GE</t>
+          <t>https://s.shopee.vn/1LeDgh4bac</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7VEopGjHw8</t>
+          <t>https://s.shopee.vn/W56hA7mHZ</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/60Q12Vozyz</t>
+          <t>https://s.shopee.vn/2LWksX0nYq</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2360,7 +2360,6 @@
           <t>₫527.716</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">7 </t>
@@ -2373,7 +2372,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41432192875?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1qaUHc2hZh</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2386,7 +2385,6 @@
           <t>shopee_41432192875</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>616e5acadf9695fdb46b8859a9f975bf</t>
@@ -2426,7 +2424,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29850280626?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2VqB4q0ADt</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2439,7 +2437,6 @@
           <t>shopee_29850280626</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>fda90cc2b042321567ef3ba1767002d7</t>
@@ -2462,8 +2459,6 @@
           <t>₫184.800</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -2471,7 +2466,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48000121383?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/20tuTv24Eo</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2484,7 +2479,6 @@
           <t>shopee_48000121383</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>e22500ec34950bead88934adbf090931</t>
@@ -2507,7 +2501,6 @@
           <t>₫109.000</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t xml:space="preserve">56 </t>
@@ -2520,7 +2513,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/57450548196?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/LlgUr8PcW</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2533,7 +2526,6 @@
           <t>shopee_57450548196</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>113eb535211dc5576ce1f369536e321f</t>
@@ -2556,8 +2548,6 @@
           <t>₫180.000</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -2565,7 +2555,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/43725797287?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/18q6F9gIU</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2578,7 +2568,6 @@
           <t>shopee_43725797287</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>5051cd8699875c55748b7d6a35aaf524</t>
@@ -2618,7 +2607,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44056006107?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/BSGIY92xX</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2631,7 +2620,6 @@
           <t>shopee_44056006107</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>d6ac7b3cd6ddaf2e4b418c3e3219fbc1</t>
@@ -2654,8 +2642,6 @@
           <t>₫70.000</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -2663,7 +2649,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50101468541?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/111NI55sGi</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2676,7 +2662,6 @@
           <t>shopee_50101468541</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>dbd9cd1b5ca9df96f73cbfb352cf0591</t>
@@ -2716,7 +2701,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25868513907?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1BKnUO5Evl</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2729,7 +2714,6 @@
           <t>shopee_25868513907</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>d4f85350ef2340d1c9195e696dd97afa</t>
@@ -2752,8 +2736,6 @@
           <t>₫218.000</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -2761,7 +2743,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50450668064?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/gOWtT78wg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2774,7 +2756,6 @@
           <t>shopee_50450668064</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>71c309837e3f3d718f0f15a81924aa5b</t>
@@ -2814,7 +2795,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28708632089?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/qhx5m6Vbj</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2827,7 +2808,6 @@
           <t>shopee_28708632089</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>16606867986f8d3cb5faba17c90f053d</t>
@@ -2850,7 +2830,6 @@
           <t>₫356.000</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t xml:space="preserve">6 </t>
@@ -2863,7 +2842,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4LHpGCtBVQ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2876,7 +2855,6 @@
           <t>shopee_51401292730</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
@@ -2899,7 +2877,6 @@
           <t>₫680.000</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t xml:space="preserve">134 </t>
@@ -2912,7 +2889,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50555002230?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4VbFSVsYAT</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2925,7 +2902,6 @@
           <t>shopee_50555002230</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>410196c9b773b4858fc695fdecf9f711</t>
@@ -2965,7 +2941,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25895712227?trace=%7B%22trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.ZzlFd54BfL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4AyP3ttoqR</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2978,7 +2954,6 @@
           <t>shopee_25895712227</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>7b260132ce735087b2f95677d3f537c0</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,37 +476,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tên mới</t>
+          <t>Loa Bluetooth Siêu Trầm 360 Độ Âm Thanh Vòm Bass Mạnh Có Đèn Nhiều Màu âm thanh cực đã</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liên hệ</t>
+          <t>₫159.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://</t>
+          <t>https://s.shopee.vn/6pz822lpI4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mf0ylbkygo3sa7.webp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>shopee_42424643784</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>b1a466d2102f73101b9a158f8177c46c</t>
+          <t>9c8523cf0dd0260781157b10a01f0169</t>
         </is>
       </c>
     </row>
@@ -518,12 +533,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Loa Bluetooth Siêu Trầm 360 Độ Âm Thanh Vòm Bass Mạnh Có Đèn Nhiều Màu âm thanh cực đã</t>
+          <t>kéo cắt cây cảnh Nhật SK5,kéo cắt cành trên cao,cành cây khô thép Cắt sắc nét,Tay cầm Thoải mái Bọt biển</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫159.000</t>
+          <t>₫81.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -533,32 +548,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">368 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6pz822lpI4</t>
+          <t>https://s.shopee.vn/5q6aqCpdK2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mf0ylbkygo3sa7.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mm8szj3qkrut23.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_42424643784</t>
+          <t>shopee_51908128978</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>9c8523cf0dd0260781157b10a01f0169</t>
+          <t>0594349909ea04dba9251177b0c930d6</t>
         </is>
       </c>
     </row>
@@ -570,12 +585,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kéo cắt cây cảnh Nhật SK5,kéo cắt cành trên cao,cành cây khô thép Cắt sắc nét,Tay cầm Thoải mái Bọt biển</t>
+          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫81.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -585,32 +600,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">368 </t>
+          <t xml:space="preserve">224 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q6aqCpdK2</t>
+          <t>https://s.shopee.vn/40eyrauSBO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mm8szj3qkrut23.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_51908128978</t>
+          <t>shopee_40355840814</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0594349909ea04dba9251177b0c930d6</t>
+          <t>4d0361ea42311469477d46b6238caac3</t>
         </is>
       </c>
     </row>
@@ -622,12 +637,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quạt điều hòa hơi nước mini để bàn - phun sương có 6 cấp độ gió</t>
+          <t>Điều Hòa Mini Hơi Nước Siêu Mát - Quạt Điều Hòa Mini Để Bàn Nhỏ Gọn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>₫196.000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -637,32 +652,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">224 </t>
+          <t xml:space="preserve">90 </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40eyrauSBO</t>
+          <t>https://s.shopee.vn/8Knvong7FH</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwv5cxzv1wea.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_40355840814</t>
+          <t>shopee_41756393542</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4d0361ea42311469477d46b6238caac3</t>
+          <t>805a83d7c2dca12627628dabf0d639fa</t>
         </is>
       </c>
     </row>
@@ -674,12 +689,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Điều Hòa Mini Hơi Nước Siêu Mát - Quạt Điều Hòa Mini Để Bàn Nhỏ Gọn</t>
+          <t>Cốc ép trái cây cầm tay nhỏ gọn, hoàn toàn tự động, đa chức năng, lý tưởng cho học sinh, dễ sử dụng</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫196.000</t>
+          <t>₫179.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -689,32 +704,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">90 </t>
+          <t xml:space="preserve">64 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8Knvong7FH</t>
+          <t>https://s.shopee.vn/4AyP3ttoqR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwv5cxzv1wea.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbf2ofv4dnn83d.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_41756393542</t>
+          <t>shopee_25895712227</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>805a83d7c2dca12627628dabf0d639fa</t>
+          <t>7b260132ce735087b2f95677d3f537c0</t>
         </is>
       </c>
     </row>
@@ -778,12 +793,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quạt điều hòa phun sương quạt không cánh, Quạt hơi nước 6 cấp độ tính năng hẹn giờ Với Mosquito Repellent tấm</t>
+          <t>‌Quạt Điều Hòa Mini Để Bàn - Làm Mát Phun Sương Đa Năng Sạc USB - Dùng Cho Gia đình/Văn Phòng - Hàng Chính Hãng Siêu êm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -793,32 +808,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">7 </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70IYELlBx9</t>
+          <t>https://s.shopee.vn/BSGIY92xX</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbrwti98f7n6a1.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbeznrglphhzba.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_42257303883</t>
+          <t>shopee_44056006107</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0c7431e5f758f272df0d6d7e46cbc6b5</t>
+          <t>d6ac7b3cd6ddaf2e4b418c3e3219fbc1</t>
         </is>
       </c>
     </row>
@@ -830,47 +845,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
+          <t>Quạt điều hòa phun sương quạt không cánh, Quạt hơi nước 6 cấp độ tính năng hẹn giờ Với Mosquito Repellent tấm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫268.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7k+</t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
+          <t>https://s.shopee.vn/70IYELlBx9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbrwti98f7n6a1.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_42357015741</t>
+          <t>shopee_42257303883</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
+          <t>0c7431e5f758f272df0d6d7e46cbc6b5</t>
         </is>
       </c>
     </row>
@@ -882,47 +897,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
+          <t>Máy hút bụi cầm tay mini cao cấp R6053 - Hút cực mạnh - Công Suất 120W - Dùng Hút Cả Nhà Và Xe - HB6,Dùng liên tục 5 giờ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫229.000</t>
+          <t>₫360.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3ViZj9CjP1</t>
+          <t>https://s.shopee.vn/1BKnUO5Evl</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ra0g-m87jow0yorjic9.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_28200539872</t>
+          <t>shopee_25868513907</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4be218b81a6be9c55c23210e5f4e379b</t>
+          <t>d4f85350ef2340d1c9195e696dd97afa</t>
         </is>
       </c>
     </row>
@@ -934,47 +949,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
+          <t>Loa Bluetooth Mini Không Dây Thiết Kế Nhỏ Gọn Sang Trọng Nghe Nhạc Hay Có Móc Treo Giá Rẻ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫98.000</t>
+          <t>₫199.000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>800k+</t>
+          <t>300k+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9SjcFu5u</t>
+          <t>https://s.shopee.vn/qhx5m6Vbj</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mkuq1bj48zyc61.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_29807844451</t>
+          <t>shopee_28708632089</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>36268a94496dd6a3162249faf14ee638</t>
+          <t>16606867986f8d3cb5faba17c90f053d</t>
         </is>
       </c>
     </row>
@@ -986,47 +1001,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
+          <t>TNW W16/W17 Micro Cài Áo Không Dây 2 trong 1 Mic Thu Âm Không Dây Micro Lavalier không dây cho ip&amp;android</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫225.000</t>
+          <t>₫268.000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t>7k+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B5jKXE04z</t>
+          <t>https://s.shopee.vn/1VxVLTKLSZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-meh0b10xhibr74.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_25241658670</t>
+          <t>shopee_42357015741</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4e3452edfd64b6b785d3f600faf050e4</t>
+          <t>fa02ea15e7c6cfdad69662416d63d1cf</t>
         </is>
       </c>
     </row>
@@ -1038,47 +1053,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tai Nghe Bluetooth PRO4 Không Dây TWS Cảm Ứng Chạm Khử Tiếng Ồn Dùng Chơi Game, Nghe Nhạc - PR04 HOT HOT HOT</t>
+          <t>Nhiệt Kế Hồng Ngoại Đo Nhiệt Độ Trán Sinocare AET-R1D1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫209.000</t>
+          <t>₫229.000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>50k+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VMHdQn5y6</t>
+          <t>https://s.shopee.vn/3ViZj9CjP1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134201-7ra0g-m7ekmpklql8c5d.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_29029784452</t>
+          <t>shopee_28200539872</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>d4767bb5964aa1e6262f71f624f391a9</t>
+          <t>4be218b81a6be9c55c23210e5f4e379b</t>
         </is>
       </c>
     </row>
@@ -1090,47 +1105,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
+          <t>Máy rửa xe cầm tay cao áp chạy bằng pin sạc, súng rửa xe dùng cho gia đình có chế độ phun xương tạo bọt cao cấp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫826.000</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1tr+</t>
+          <t>800k+</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Le59AKynW</t>
+          <t>https://s.shopee.vn/2g9SjcFu5u</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhiwjn84bnpb7.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_26464017128</t>
+          <t>shopee_29807844451</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0063c3803f4f95d096d307a3278cb4bd</t>
+          <t>36268a94496dd6a3162249faf14ee638</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1157,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
+          <t>Sạc dự phòng 30000mah 50000mah sạc nhanh pin dung lượng lớn tích hợp dây sạc cho điện thoại SP1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫209.000</t>
+          <t>₫225.000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1162,27 +1177,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
+          <t>https://s.shopee.vn/3B5jKXE04z</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_13724863422</t>
+          <t>shopee_25241658670</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5b19f9c4bae575f6667040d2b121506e</t>
+          <t>4e3452edfd64b6b785d3f600faf050e4</t>
         </is>
       </c>
     </row>
@@ -1194,47 +1209,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
+          <t>Tai Nghe Bluetooth PRO4 Không Dây TWS Cảm Ứng Chạm Khử Tiếng Ồn Dùng Chơi Game, Nghe Nhạc - PR04 HOT HOT HOT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫198.000</t>
+          <t>₫209.000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>300k+</t>
+          <t>50k+</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDKgE1Qtr</t>
+          <t>https://s.shopee.vn/6VMHdQn5y6</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134201-7ra0g-m7ekmpklql8c5d.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_26858030583</t>
+          <t>shopee_29029784452</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0a64138bac7926d086d7164638e7ac2b</t>
+          <t>d4767bb5964aa1e6262f71f624f391a9</t>
         </is>
       </c>
     </row>
@@ -1246,47 +1261,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
+          <t>Loa Bluetooth M72 Pro Có Sẵn 2 Micro Không Dây Hát Karaoke Nghe Nhạc Bass Cực Đỉnh Đời Mới 2025 DC55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫168.000</t>
+          <t>₫826.000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>50k+</t>
+          <t>1tr+</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BS7l1PQAB</t>
+          <t>https://s.shopee.vn/1Le59AKynW</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgesj4j0qhoq82.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_24450360446</t>
+          <t>shopee_26464017128</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
+          <t>0063c3803f4f95d096d307a3278cb4bd</t>
         </is>
       </c>
     </row>
@@ -1298,47 +1313,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+          <t>Sữa tắm gội nam giới hương nước hoa Gentleman 3 in 1 Nerman 350ml</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫1.599.000</t>
+          <t>₫209.000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LP9WqDMjy</t>
+          <t>https://s.shopee.vn/2Vq2XJGXQf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-mc7bpvfaqmdx00.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_40012750336</t>
+          <t>shopee_13724863422</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3d93b1393727dc3578c2df28b475e423</t>
+          <t>5b19f9c4bae575f6667040d2b121506e</t>
         </is>
       </c>
     </row>
@@ -1350,47 +1365,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
+          <t>Quạt Cầm Tay Sò Lạnh K801, Màn Hình Kỹ Thuật Số Lạnh Sâu Nhanh, Pin 4000mAh,Đèn LED, Sạc Type-C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫119.000</t>
+          <t>₫198.000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">772 </t>
+          <t>300k+</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Vxdt03yFf</t>
+          <t>https://s.shopee.vn/2BDKgE1Qtr</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-momp4yxx1dkw29.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_22243625222</t>
+          <t>shopee_26858030583</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>399716bb972df0ab32724f6fefb65c81</t>
+          <t>0a64138bac7926d086d7164638e7ac2b</t>
         </is>
       </c>
     </row>
@@ -1402,47 +1417,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
+          <t>Giày JD1 low các phối màu, giày JD1 cổ thấp full bill box</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫295.000</t>
+          <t>₫990.000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>200k+</t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
+          <t>https://s.shopee.vn/2VqB4q0ADt</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mfhyusf8mmmi94.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_28126833083</t>
+          <t>shopee_29850280626</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>768e867948552026756bd7e356cfca04</t>
+          <t>fda90cc2b042321567ef3ba1767002d7</t>
         </is>
       </c>
     </row>
@@ -1454,22 +1469,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
+          <t>(Tặng 6 thạch healthy) COMBO TỨ ĐẠI ĐÙI GÀ - ĂN CÙNG BÀ TUYẾT M67</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫289.000</t>
+          <t>₫168.000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40k+</t>
+          <t>50k+</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1479,22 +1494,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20tlwOIRRa</t>
+          <t>https://s.shopee.vn/BS7l1PQAB</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mo98kbbi9ssk5b.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_24660800592</t>
+          <t>shopee_24450360446</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
+          <t>046cfe0ffef71ccb2a0ea8b40b8cf3ea</t>
         </is>
       </c>
     </row>
@@ -1506,47 +1521,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>₫288.000</t>
+          <t>₫1.599.000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>600k+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LWcL0HAlc</t>
+          <t>https://s.shopee.vn/3LP9WqDMjy</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>shopee_24034739910</t>
+          <t>shopee_40012750336</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1573,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
+          <t>Combo Micro K9 và mũ lọc gió, giúp lọc ồn, thu xa, kết nối điện thoại quay video, livetream</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>₫599.000</t>
+          <t>₫119.000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t xml:space="preserve">772 </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qaLk5J4mb</t>
+          <t>https://s.shopee.vn/1Vxdt03yFf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>shopee_27176838116</t>
+          <t>shopee_22243625222</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
+          <t>399716bb972df0ab32724f6fefb65c81</t>
         </is>
       </c>
     </row>
@@ -1610,47 +1625,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kệ đặt chậu hoa, chậu cây cảnh 6 tầng, chậu hoa cây cảnh khung sắt chắc chắn, kệ decor có bánh xe</t>
+          <t>Sạc dự phòng 20000 30000MAH sạc nhanh PD120W/20W trong suốt tích hợp 4 dây sạc tích hợp đèn led SP1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>₫265.000</t>
+          <t>₫295.000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">928 </t>
+          <t>200k+</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/30mJ8EEdPw</t>
+          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>shopee_26319252965</t>
+          <t>shopee_28126833083</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>e8c259bd483858e228b0c2099ebeb852</t>
+          <t>768e867948552026756bd7e356cfca04</t>
         </is>
       </c>
     </row>
@@ -1662,17 +1677,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Loa Bluetooth Pro 10 Thiết Kế Đẹp, Âm Thanh Sống Động, Công Suất 30W Thiết Kế Hợp Để Mang Đi Du Lịch</t>
+          <t>Loa Bluetooth FLIP 6 Mới nhất âm thanh cực đỉnh có bass Bluetooth 5.1 NEW HOT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>₫499.000</t>
+          <t>₫289.000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>15%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>400k+</t>
+          <t>40k+</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1682,22 +1702,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VTkRaqtzw</t>
+          <t>https://s.shopee.vn/20tlwOIRRa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mfy6u2kcmhvw32.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>shopee_26257417460</t>
+          <t>shopee_24660800592</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4eb9d419184c6176d84cfc5d91ff9e0d</t>
+          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
         </is>
       </c>
     </row>
@@ -1709,42 +1729,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Balo thời trang cặp sách học sinh phong cách Hàn Quốc chất liệu vải polieter chống thấm nước có ngăn đựng laptop G 877</t>
+          <t>Máy Hút Bụi Cầm Tay Không Dây 5IN1, Lực Hút 18000PA Siêu Khỏe Công Suất 120W, Hút bụi cầm tay không dây khoẻ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>₫129.000</t>
+          <t>₫288.000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>12%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t>600k+</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4qE3eMtRLs</t>
+          <t>https://s.shopee.vn/2LWcL0HAlc</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7qukw-lj6fqhb01yj0a7.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmhivmvz72mc9c.webp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>shopee_12705585947</t>
+          <t>shopee_24034739910</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>b6744dec37d28210cf2ae0f6c46eec6e</t>
+          <t>40c75c69a5db9fe8970b91ecb056a0c9</t>
         </is>
       </c>
     </row>
@@ -1756,42 +1781,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gối tựa ô tô công thái học cao cấp, Cao su non Memory Foam mềm mại êm ái - The ComfyPrime LIFXY</t>
+          <t>Sạc Dự Phòng Không Dây, Pin Dự Phòng Kiêm Củ Sạc Công Suất 22,5W 20000mAh, Sạc Cho Táo Và Android</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>₫650.000</t>
+          <t>₫599.000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">812 </t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6AjREooMe0</t>
+          <t>https://s.shopee.vn/1qaLk5J4mb</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mqklsavlob9d7b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe249ssw5jh23.webp</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>shopee_54355250128</t>
+          <t>shopee_27176838116</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>08789068712f22c0e7b5e6d13e093d55</t>
+          <t>8e36ced28f54484fc17b0083f6dcd3a6</t>
         </is>
       </c>
     </row>
@@ -1803,42 +1833,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
+          <t>Kệ đặt chậu hoa, chậu cây cảnh 6 tầng, chậu hoa cây cảnh khung sắt chắc chắn, kệ decor có bánh xe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>₫140.000</t>
+          <t>₫265.000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>7%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">621 </t>
+          <t xml:space="preserve">928 </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/50XNVu71MO</t>
+          <t>https://s.shopee.vn/30mJ8EEdPw</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>shopee_28657885709</t>
+          <t>shopee_26319252965</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
+          <t>e8c259bd483858e228b0c2099ebeb852</t>
         </is>
       </c>
     </row>
@@ -1850,42 +1885,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
+          <t>Loa Bluetooth Pro 10 Thiết Kế Đẹp, Âm Thanh Sống Động, Công Suất 30W Thiết Kế Hợp Để Mang Đi Du Lịch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫499.000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">62 </t>
+          <t>400k+</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDC8hHo6d</t>
+          <t>https://s.shopee.vn/5VTkRaqtzw</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mfy6u2kcmhvw32.webp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>shopee_53557782402</t>
+          <t>shopee_26257417460</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>be4aca7de97245e2c4faa260b67482fb</t>
+          <t>4eb9d419184c6176d84cfc5d91ff9e0d</t>
         </is>
       </c>
     </row>
@@ -1897,42 +1932,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>Balo thời trang cặp sách học sinh phong cách Hàn Quốc chất liệu vải polieter chống thấm nước có ngăn đựng laptop G 877</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫129.000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
+          <t>https://s.shopee.vn/4qE3eMtRLs</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7qukw-lj6fqhb01yj0a7.webp</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
+          <t>shopee_12705585947</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>b6744dec37d28210cf2ae0f6c46eec6e</t>
         </is>
       </c>
     </row>
@@ -1944,42 +1979,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Thích hợp cho Apple Sạc dự phòng không dây từ tính Thích hợp cho Sạc dự phòng không dây magsafe 5.000mAh</t>
+          <t>Gối tựa ô tô công thái học cao cấp, Cao su non Memory Foam mềm mại êm ái - The ComfyPrime LIFXY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>₫297.323</t>
+          <t>₫650.000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 </t>
+          <t xml:space="preserve">812 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gH45J3Kue</t>
+          <t>https://s.shopee.vn/6AjREooMe0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-823o9-mp7jhyybqmma7a.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mqklsavlob9d7b.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>shopee_54661835387</t>
+          <t>shopee_54355250128</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>44e8b25475ffc538983334a291905a4a</t>
+          <t>08789068712f22c0e7b5e6d13e093d55</t>
         </is>
       </c>
     </row>
@@ -1991,42 +2026,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tai nghe không dây Tai nghe Bluetooth Không rò rỉ Trò chơi Máy tính di động Mô hình riêng Tai nghe khử tiếng ồn</t>
+          <t>Đèn năng lượng mặt trời công suất 1200w Chống Nước IP68 An toàn Tự động bật tắt Bảo hành 10 năm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>₫437.974</t>
+          <t>₫140.000</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 </t>
+          <t xml:space="preserve">621 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8V7M16fTuI</t>
+          <t>https://s.shopee.vn/50XNVu71MO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824gm-mpx2g6f5b218a4.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-lyxig39igh8t4b.webp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>shopee_40332039212</t>
+          <t>shopee_28657885709</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>c5caa4d1917f9bdc176b0b7b95dd10a6</t>
+          <t>de6906faf8cfe3f1157d9c7636c6eb90</t>
         </is>
       </c>
     </row>
@@ -2038,42 +2073,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Quà tặng LOGO Kho báu sạc xuyên biên giới tùy chỉnh có cáp có thể tháo rời 2000mAh Mini Power Bank</t>
+          <t>Gối Tựa Đầu Ô tô Trẻ Em Cao Su Non Memory Foam Êm Ái, Công Thái Học Chuẩn Y Khoa | KidRest</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>₫272.130</t>
+          <t>₫680.000</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 </t>
+          <t xml:space="preserve">134 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/80B5QBhNvB</t>
+          <t>https://s.shopee.vn/4VbFSVsYAT</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824h9-mpumuqfytdl835.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mnjl1q1xys5i38.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>shopee_52612730419</t>
+          <t>shopee_50555002230</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>067055d9440e75ddba8282da81c3481f</t>
+          <t>410196c9b773b4858fc695fdecf9f711</t>
         </is>
       </c>
     </row>
@@ -2085,42 +2120,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[Quà tặng nhỏ gọn trong lòng bàn tay] Pin dự phòng mini 5000mAh sạc nhanh hai đầu Quà tặng thời trang, tiện dụng cho b</t>
+          <t>HÀNG CÓ SẴN. Bơm lốp mini di động dùng pin sạc cao cấp dùng cho Ô tô, Xe đạp, Xe máy, Xe điện, Bóng đá.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>₫198.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 </t>
+          <t xml:space="preserve">62 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5LAKFHrXKv</t>
+          <t>https://s.shopee.vn/2BDC8hHo6d</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqbea9w00spfa.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mmb951m944cgd5.webp</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>shopee_49550938313</t>
+          <t>shopee_53557782402</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>e669e6968c37d2f2b554b3441960d4ec</t>
+          <t>be4aca7de97245e2c4faa260b67482fb</t>
         </is>
       </c>
     </row>
@@ -2132,17 +2167,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tai nghe Bluetooth chuyên nghiệp Q71 | Chống mồ hôi, chống trượt và thời lượng pin cực dài Âm nhạc thể thao</t>
+          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>₫120.000</t>
+          <t>₫109.000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">56 </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2152,22 +2187,22 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1LeDgh4bac</t>
+          <t>https://s.shopee.vn/LlgUr8PcW</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqeynei83yk52.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>shopee_45750965028</t>
+          <t>shopee_57450548196</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>d0300a481504fb63329e2ff3f7c18a38</t>
+          <t>113eb535211dc5576ce1f369536e321f</t>
         </is>
       </c>
     </row>
@@ -2179,42 +2214,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>₫450.000</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W56hA7mHZ</t>
+          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>shopee_48107000510</t>
+          <t>shopee_48200038200</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -2226,37 +2261,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+          <t>Thích hợp cho Apple Sạc dự phòng không dây từ tính Thích hợp cho Sạc dự phòng không dây magsafe 5.000mAh</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>₫356.000</t>
+          <t>₫297.323</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6ffhpjmSd3</t>
+          <t>https://s.shopee.vn/1gH45J3Kue</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-823o9-mp7jhyybqmma7a.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>shopee_53401541671</t>
+          <t>shopee_54661835387</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+          <t>44e8b25475ffc538983334a291905a4a</t>
         </is>
       </c>
     </row>
@@ -2268,37 +2308,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tai nghe Bluetooth không dây Pro6 Mini: Sang trọng, Chống ồn, Tương thích với mọi điện thoại</t>
+          <t>Tai nghe không dây Tai nghe Bluetooth Không rò rỉ Trò chơi Máy tính di động Mô hình riêng Tai nghe khử tiếng ồn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>₫50.000</t>
+          <t>₫437.974</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21 </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7AbyQekYcA</t>
+          <t>https://s.shopee.vn/8V7M16fTuI</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mghz6alwbp59a7.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824gm-mpx2g6f5b218a4.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>shopee_57301683598</t>
+          <t>shopee_40332039212</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>d065e379133010f610a0f3d34b2f8746</t>
+          <t>c5caa4d1917f9bdc176b0b7b95dd10a6</t>
         </is>
       </c>
     </row>
@@ -2310,37 +2355,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20000mah đa chức năng xách tay sạc kho báu｜Công suất lớn với 4 cáp sạc nhanh</t>
+          <t>Quà tặng LOGO Kho báu sạc xuyên biên giới tùy chỉnh có cáp có thể tháo rời 2000mAh Mini Power Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>₫198.000</t>
+          <t>₫272.130</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LWksX0nYq</t>
+          <t>https://s.shopee.vn/80B5QBhNvB</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mggnqwp1w5cd18.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824h9-mpumuqfytdl835.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>shopee_44850786084</t>
+          <t>shopee_52612730419</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>e8d80b1947cd4ab9d432090972bba88c</t>
+          <t>067055d9440e75ddba8282da81c3481f</t>
         </is>
       </c>
     </row>
@@ -2399,47 +2449,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Giày JD1 low các phối màu, giày JD1 cổ thấp full bill box</t>
+          <t>[Quà tặng nhỏ gọn trong lòng bàn tay] Pin dự phòng mini 5000mAh sạc nhanh hai đầu Quà tặng thời trang, tiện dụng cho b</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>₫990.000</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>24%</t>
+          <t>₫198.000</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2VqB4q0ADt</t>
+          <t>https://s.shopee.vn/5LAKFHrXKv</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mfhyusf8mmmi94.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqbea9w00spfa.webp</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>shopee_29850280626</t>
+          <t>shopee_49550938313</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fda90cc2b042321567ef3ba1767002d7</t>
+          <t>e669e6968c37d2f2b554b3441960d4ec</t>
         </is>
       </c>
     </row>
@@ -2451,12 +2496,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>X87 Tai nghe Bluetooth Music HiFi Stereo Thể thao Chống nước Chống ồn Tương thích với mọi nền tảng Phát trực tiếp Cuộc</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>₫184.800</t>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2466,22 +2516,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20tuTv24Eo</t>
+          <t>https://s.shopee.vn/4LHpGCtBVQ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg7n5txlx4wab0.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>shopee_48000121383</t>
+          <t>shopee_51401292730</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>e22500ec34950bead88934adbf090931</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -2493,17 +2543,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
+          <t>Tai nghe Bluetooth chuyên nghiệp Q71 | Chống mồ hôi, chống trượt và thời lượng pin cực dài Âm nhạc thể thao</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>₫109.000</t>
+          <t>₫120.000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">56 </t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2513,22 +2563,22 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/LlgUr8PcW</t>
+          <t>https://s.shopee.vn/1LeDgh4bac</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgqeynei83yk52.webp</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>shopee_57450548196</t>
+          <t>shopee_45750965028</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>113eb535211dc5576ce1f369536e321f</t>
+          <t>d0300a481504fb63329e2ff3f7c18a38</t>
         </is>
       </c>
     </row>
@@ -2540,37 +2590,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>895B Tai nghe không dây Bluetooth Tai nghe chơi game chất lượng âm thanh HiFi, thời lượng pin dài</t>
+          <t>Camera imou thông minh trong nhà IMOU IPC-A32EP (Ranger 2, 3MP)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>₫180.000</t>
+          <t>₫450.000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/18q6F9gIU</t>
+          <t>https://s.shopee.vn/W56hA7mHZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg7vtlkzdi4r7f.webp</t>
+          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mljb2qd8vmkl19.webp</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>shopee_43725797287</t>
+          <t>shopee_48107000510</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>5051cd8699875c55748b7d6a35aaf524</t>
+          <t>e8a4d05f34cae74562b2fa16a54ff6af</t>
         </is>
       </c>
     </row>
@@ -2582,47 +2637,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>‌Quạt Điều Hòa Mini Để Bàn - Làm Mát Phun Sương Đa Năng Sạc USB - Dùng Cho Gia đình/Văn Phòng - Hàng Chính Hãng Siêu êm</t>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>₫189.000</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 </t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BSGIY92xX</t>
+          <t>https://s.shopee.vn/6ffhpjmSd3</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbeznrglphhzba.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>shopee_44056006107</t>
+          <t>shopee_53401541671</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>d6ac7b3cd6ddaf2e4b418c3e3219fbc1</t>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2679,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pin dự phòng 20000mAh, sạc nhanh, cáp 3 trong 1, dung lượng lớn, thiết yếu cho du lịch và chơi game.</t>
+          <t>Tai nghe Bluetooth không dây Pro6 Mini: Sang trọng, Chống ồn, Tương thích với mọi điện thoại</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>₫70.000</t>
+          <t>₫50.000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2649,22 +2694,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/111NI55sGi</t>
+          <t>https://s.shopee.vn/7AbyQekYcA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgne2h0vw83u8b.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mghz6alwbp59a7.webp</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>shopee_50101468541</t>
+          <t>shopee_57301683598</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>dbd9cd1b5ca9df96f73cbfb352cf0591</t>
+          <t>d065e379133010f610a0f3d34b2f8746</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2721,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Máy hút bụi cầm tay mini cao cấp R6053 - Hút cực mạnh - Công Suất 120W - Dùng Hút Cả Nhà Và Xe - HB6,Dùng liên tục 5 giờ</t>
+          <t>20000mah đa chức năng xách tay sạc kho báu｜Công suất lớn với 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>₫360.000</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>100k+</t>
+          <t>₫198.000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1BKnUO5Evl</t>
+          <t>https://s.shopee.vn/2LWksX0nYq</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ra0g-m87jow0yorjic9.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mggnqwp1w5cd18.webp</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>shopee_25868513907</t>
+          <t>shopee_44850786084</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>d4f85350ef2340d1c9195e696dd97afa</t>
+          <t>e8d80b1947cd4ab9d432090972bba88c</t>
         </is>
       </c>
     </row>
@@ -2728,12 +2763,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Q86 Vintage máy ảnh mới trong tai phong cách thoải mái đôi tai HD màn hình chạy thể thao tai nghe bluetooth JF</t>
+          <t>X87 Tai nghe Bluetooth Music HiFi Stereo Thể thao Chống nước Chống ồn Tương thích với mọi nền tảng Phát trực tiếp Cuộc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>₫218.000</t>
+          <t>₫184.800</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2743,22 +2778,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/gOWtT78wg</t>
+          <t>https://s.shopee.vn/20tuTv24Eo</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgjnstldc0svde.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg7n5txlx4wab0.webp</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>shopee_50450668064</t>
+          <t>shopee_48000121383</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>71c309837e3f3d718f0f15a81924aa5b</t>
+          <t>e22500ec34950bead88934adbf090931</t>
         </is>
       </c>
     </row>
@@ -2770,47 +2805,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Loa Bluetooth Mini Không Dây Thiết Kế Nhỏ Gọn Sang Trọng Nghe Nhạc Hay Có Móc Treo Giá Rẻ</t>
+          <t>895B Tai nghe không dây Bluetooth Tai nghe chơi game chất lượng âm thanh HiFi, thời lượng pin dài</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>₫199.000</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>300k+</t>
+          <t>₫180.000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/qhx5m6Vbj</t>
+          <t>https://s.shopee.vn/18q6F9gIU</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mkuq1bj48zyc61.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mg7vtlkzdi4r7f.webp</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>shopee_28708632089</t>
+          <t>shopee_43725797287</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>16606867986f8d3cb5faba17c90f053d</t>
+          <t>5051cd8699875c55748b7d6a35aaf524</t>
         </is>
       </c>
     </row>
@@ -2822,17 +2847,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>Pin dự phòng 20000mAh, sạc nhanh, cáp 3 trong 1, dung lượng lớn, thiết yếu cho du lịch và chơi game.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 </t>
+          <t>₫70.000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2842,22 +2862,22 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LHpGCtBVQ</t>
+          <t>https://s.shopee.vn/111NI55sGi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgne2h0vw83u8b.webp</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
+          <t>shopee_50101468541</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>dbd9cd1b5ca9df96f73cbfb352cf0591</t>
         </is>
       </c>
     </row>
@@ -2869,94 +2889,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gối Tựa Đầu Ô tô Trẻ Em Cao Su Non Memory Foam Êm Ái, Công Thái Học Chuẩn Y Khoa | KidRest</t>
+          <t>Q86 Vintage máy ảnh mới trong tai phong cách thoải mái đôi tai HD màn hình chạy thể thao tai nghe bluetooth JF</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>₫680.000</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134 </t>
+          <t>₫218.000</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4VbFSVsYAT</t>
+          <t>https://s.shopee.vn/gOWtT78wg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mnjl1q1xys5i38.webp</t>
+          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-820l4-mgjnstldc0svde.webp</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>shopee_50555002230</t>
+          <t>shopee_50450668064</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>410196c9b773b4858fc695fdecf9f711</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Cốc ép trái cây cầm tay nhỏ gọn, hoàn toàn tự động, đa chức năng, lý tưởng cho học sinh, dễ sử dụng</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>₫179.000</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64 </t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>30,5%</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://s.shopee.vn/4AyP3ttoqR</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbf2ofv4dnn83d.webp</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>shopee_25895712227</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>7b260132ce735087b2f95677d3f537c0</t>
+          <t>71c309837e3f3d718f0f15a81924aa5b</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">368 </t>
+          <t xml:space="preserve">375 </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -558,12 +558,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q6aqCpdK2</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51908128978?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mm8szj3qkrut23.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mm8szj3qkrut23.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0594349909ea04dba9251177b0c930d6</t>
+          <t>8659c12911db4509edcd9eea805e8e61</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫209.000</t>
+          <t>₫138.000</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VMHdQn5y6</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29029784452?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134201-7ra0g-m7ekmpklql8c5d.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134201-7ra0g-m7ekmpklql8c5d.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>d4767bb5964aa1e6262f71f624f391a9</t>
+          <t>77a25e2c1903f25c6446f41166a33516</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>₫295.000</t>
+          <t>₫225.000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLQ7lBSj3</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28126833083?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-moslwhqqrzsw8b.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>768e867948552026756bd7e356cfca04</t>
+          <t>cc971ef6911267b80e734ba817d2de13</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>₫289.000</t>
+          <t>₫288.000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20tlwOIRRa</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-ltyoc9n0dmvl60.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>bbfd1bb09e4b635b7624807c5ea5ac6e</t>
+          <t>4df64ee316c94e2bbf1966c683e1992a</t>
         </is>
       </c>
     </row>
@@ -1984,27 +1984,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>₫650.000</t>
+          <t>₫552.500</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>17%</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">812 </t>
+          <t xml:space="preserve">855 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6AjREooMe0</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54355250128?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mqklsavlob9d7b.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mqklsavlob9d7b.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2014,7 +2019,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>08789068712f22c0e7b5e6d13e093d55</t>
+          <t>570dee9883866d5eb112097d78872194</t>
         </is>
       </c>
     </row>
@@ -2078,27 +2083,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>₫680.000</t>
+          <t>₫578.000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>15%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">134 </t>
+          <t xml:space="preserve">137 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4VbFSVsYAT</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50555002230?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-81ztc-mnjl1q1xys5i38.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mnjl1q1xys5i38.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2108,7 +2118,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>410196c9b773b4858fc695fdecf9f711</t>
+          <t>9a3402ddf56a7207ff7e51948c23508b</t>
         </is>
       </c>
     </row>
@@ -2269,9 +2279,10 @@
           <t>₫297.323</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 </t>
+          <t xml:space="preserve">28 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2281,12 +2292,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gH45J3Kue</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54661835387?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-823o9-mp7jhyybqmma7a.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-823o9-mp7jhyybqmma7a.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2296,7 +2307,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>44e8b25475ffc538983334a291905a4a</t>
+          <t>f3f5f0966fb36f71a414e97297232ace</t>
         </is>
       </c>
     </row>
@@ -2316,9 +2327,10 @@
           <t>₫437.974</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">21 </t>
+          <t xml:space="preserve">27 </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2328,12 +2340,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8V7M16fTuI</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40332039212?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824gm-mpx2g6f5b218a4.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-824gm-mpx2g6f5b218a4.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2343,7 +2355,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>c5caa4d1917f9bdc176b0b7b95dd10a6</t>
+          <t>1663fe3121c7d7648ffdde5c19d5ffd5</t>
         </is>
       </c>
     </row>
@@ -2363,9 +2375,10 @@
           <t>₫272.130</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 </t>
+          <t xml:space="preserve">12 </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2375,12 +2388,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/80B5QBhNvB</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/52612730419?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/sg-11134201-824h9-mpumuqfytdl835.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-824h9-mpumuqfytdl835.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2390,7 +2403,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>067055d9440e75ddba8282da81c3481f</t>
+          <t>17bbb45eb78b47d7c34695bbf38c85c4</t>
         </is>
       </c>
     </row>
@@ -2920,6 +2933,2050 @@
       <c r="K51" t="inlineStr">
         <is>
           <t>71c309837e3f3d718f0f15a81924aa5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ốp điện thoại từ tính Matte Gạc cao cấp Thích hợp cho iPhone17 Pro Max Apple 16Pro MAX</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>₫111.002</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54113369613?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-825bd-mq8wn4liimfg0f.webp</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>shopee_54113369613</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>03d510a21d58edf3d77e58473c22f575</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chuột không dây Bluetooth W &amp; P Di động ba chế độ im lặng Thích hợp cho máy tính xách tay Apple Macbook</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>₫855.146</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53263324968?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-8259b-mq7mvw0f400e11.webp</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>shopee_53263324968</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4504250be76f3ea71ec7faa0e50ce355</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Đèn LED Để Bàn Đa Năng, Đèn Học Để Bàn Chống Cận Cao Cấp Với 3 Màu Sáng Và Đồng Hồ LCD Sắc Nét HOT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>400k+</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/18591723306?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134201-7qukw-lk9c5erawpzw9e.webp</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>shopee_18591723306</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0f053f3f609ead54c09c487185bf21e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Tai nghe Bluetooth không dây Không mở trong tai Thoải mái khi mặc</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>₫384.545</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/46213516840?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-825af-mqbynsvp9pu750.webp</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>shopee_46213516840</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>acf1e56507bb75bacc07a49cf4610f45</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Quạt Cổ Treo Không Lá Lười Di Động 100 Tốc Độ Cao Cổ Treo Quạt Nhỏ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>₫263.351</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56513668531?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-825as-mqfxvdh0g9ho92.webp</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>shopee_56513668531</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>6472dfcb91ee3f10c54a61c9396ce262</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chuột không dây LEOBOG GM2 Trò chơi chơi chơi Game văn phòng Bluetooth có dây ba chế độ FPS Ngói lol Chuyên dụng pro</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>₫439.817</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51013200090?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/cn-11134207-820l4-mq51upskvjeo2d.webp</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>shopee_51013200090</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>8009cf052b2b98242dfb7fbdb473ebd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Màn hình kỹ thuật số USB 100 tốc độ Gấp tốc độ cao Pháo không khí nhỏ Turbo Bán chạy Quạt cầm tay Mini cầm tay hàng loạt</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>₫129.914</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54513171684?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/cn-11134207-820l4-mq4n99ekt1cc87.webp</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>shopee_54513171684</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>3534084a052e79832c099582f83873c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>(Wholesale) X55, tai nghe ngủ, không thấm nước, giảm tiếng ồn, chất lượng âm thanh HIFI, tai nghe</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>₫56.000</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40525647070?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mg60z1mc50y213.webp</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>shopee_40525647070</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>857229f41048f1f496374267914d9108</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Thích Hợp Cho Apple 15promax Phim Cường Lực 16 Full Màn Hình 14plus Phim Riêng Tư 13 Chống Ánh Sáng Xanh 12 Phim Điện Thoại Di Động 11XR</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>₫63.775</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45 </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49511823677?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-823od-mp6ozylf7eh88e.webp</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>shopee_49511823677</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2b2af17cf98fe9f6d989b1cbef5abc3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Áo Điều Hòa Nhật Bản SWI/KAW Pin 10-15H Quạt Mát Không Chổi Than, Chống Nắng Nóng, Bảo Hành 12 Tháng</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>₫342.000</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27484697336?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-ma7ugakscmnc4e.webp</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>shopee_27484697336</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>8773f7b4732ba967021b5c2ba6e80b86</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25123423072?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>shopee_25123423072</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ngoài Trời Có Thể Gập Lại Ghế Di Động Nhẹ Mặt Trăng Ghế Ba Tốc Độ Có Thể Điều Chỉnh Tựa Lưng Cao Ghế Câu Cá Cắm Trại Bàn Ghế Nghỉ Trưa Recliner</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>₫642.923</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25748311349?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-8259l-mq8xypu4ts7i82.webp</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>shopee_25748311349</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>240caeb9da1473c32237c7f2e3f4dc0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>(Siêu phẩm mới) DJI Osmo Pocket 4P Camera Vlog 4K | CMOS 1-inch (DJI OP 4P)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>₫11.500.000</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56213044633?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mqotnltafle7f0.webp</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>shopee_56213044633</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>11b1abcb04f8572d3ebce06ca94fb5b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Toàn năng 4 dây sạc nhanh｜Pin dự phòng 20000mAh dung lượng lớn Đèn LED báo phần trăm Thiết yếu cho chơi game và du lịch</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgq7f3r8av4d0e.webp</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>shopee_48500941449</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>686b261362b588a5e597b2e4b9a9d984</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ĐÈN NĂNG LƯỢNG MẶT TRỜI MAX TECH 80W - 180W - 200W - 300W - 400W SOLAR LIGHT - PIN SẠC TRỌN DỜI - D1060</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>₫200.000</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/4537242491?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lm6x0l2cp3of46.webp</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>shopee_4537242491</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>beea6c89d2940e4426862501b5557fa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Máy bơm lốp ô tô , Máy bơm lốp Mini có độ chính xác cao Bơm bơm hơi điện tử bơm hơi nhanh cho xe máy, xe đạp, ô tô</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>₫188.000</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/44606828138?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmvu03n37aiuee.webp</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>shopee_44606828138</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>96776330d0d92e7ee493b039c5e0c375</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>(CÂN CHÍNH XÁC 100% - CHỌN MÀU) CÂN SỨC KHỎE ĐIỆN TỬ ISCALE SE MAX 180KG CAO CẤP - CÂN ĐIỆN TỬ CAO CẤP - CÂN SỨC KHỎE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>₫169.000</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809 </t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mjgu0jf0h535f4.webp</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>shopee_50254653729</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>44b0d17153a4822354959c61794c8ef1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth BoomBox phiên bản mới đèn led cùng âm thanh bass căng công suất 20w pin trâu REMI OFFICIAL</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>₫199.000</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>400k+</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mkpnpvtgsdmpdf.webp</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>shopee_25676379719</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>8797a0b343c8a948af2337da1f7954d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pin dự phòng 20000mAh, dung lượng cao, sạc nhanh, tương thích với mọi điện thoại di động và máy tính bảng.</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48201510573?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mh0bxbbc23v185.webp</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>shopee_48201510573</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>9a6f048436bdf3b3ac3abc642b1fc308</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Đai ngồi ô tô cho bé CECILA đai bảo vệ an toàn trên xe ô tô cho bé 1-9 tuổi dễ dàng sử dụng</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>₫235.000</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48403837828?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mir267jw6ozq25.webp</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>shopee_48403837828</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>6c003b1d65980a5b0704f653a4ef8a10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ĐÈN NĂNG LƯỢNG MẶT TRỜI MAX TECH 400W - 80W - 200W - 300W - 180W SOLAR LIGHT - ĐIỀU KHIỂN TỪ XA - D1145</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>₫200.000</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">716 </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/5864774152?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lm6x0l2crwtb95.webp</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>shopee_5864774152</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>4a09897ee7d33b260ec67ea1e8079951</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Máy xay tỏi và tiêu cầm tay điện mini - Máy xay tỏi và tiêu tiện lợi, Máy xay nhà bếp</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>₫165.690</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">551 </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51300953146?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgrkmgobo64v0c.webp</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>shopee_51300953146</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>6c5d0a6c01f151e144292c300ef9d90b</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Quạt Tích Điện Pin 10 Cell Dùng Liên Tục 8-10H, Quạt Makita Để Bàn 2 Cấp Độ Gió Siêu Mát.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>₫185.000</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27137628373?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mb2iowohfd1db1.webp</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>shopee_27137628373</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>d7c9b876d8664c2df389ab44f5363639</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pin dự phòng Mega-Power 30000mAh | Sạc nhanh 22.5W, Cáp đôi cho Du lịch Sinh ra cho những chuyến đi dài,</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>₫278.000</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 </t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48900836040?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgnvlko07763bf.webp</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>shopee_48900836040</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>d8cea489e529d5706472e802e82cbdc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>₫334.000</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>shopee_24288149456</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>3ab082fd60013c76170b7ba6b1a8fe5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Quạt Tích Điện Pin 10 Cell Dùng Liên Tục 8H, Quạt Để Bàn 2 Cấp Độ Gió Siêu Mát</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>₫335.000</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26985013216?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-m91d1et6lton51.webp</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>shopee_26985013216</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>df43a8b645001a422be65d0f50d79dd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tai Nghe A12 Ultimate, Full viền màn hình 1.65 inch, Có loa hộp sạc,Chuông báo thức, Kết Nối App, Phù Hợp Mọi Máy</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>₫269.900</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28106687731?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mr1i20d6zocn33.webp</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>shopee_28106687731</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>4e0e93abedf8ba580ea21161bb95bf62</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Máy Cạo Râu Mini 2 Lưỡi Cạo Nổi Máy Cạo Râu Đa Năng Đầu Cạo Chống Nước Đèn Rọi Ray ASAKI - R2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>₫153.000</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>600k+</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29201881549?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134201-7r98o-lw6lpzhyr3kh0c.webp</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>shopee_29201881549</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>95a060a6a1a9f056fe980aff47e9c28c</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Máy Đo Nồng Độ Cồn C07, Máy Thổi Nồng Độ Cồn Cao Cấp Đo Bằng Cách Thổi Vào Thiết Bị Chính Xác Sau 3S An Toàn Khi Lái Xe</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>₫219.000</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25368635737?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lst8geoarc90e6.webp</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>shopee_25368635737</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>bce7fb76652260ec5cdc8a69a5a6c491</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kawaii Hộp Đựng Bút Chì Túi Lật Hộp Đơn Giản Trở Lại Trường Học Cho Studnets Đồ Dùng Văn Phòng Phẩm</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>₫36.720</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33 </t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42460450626?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-7rblz-m5fl5s22zthz9b.webp</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>shopee_42460450626</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>25270d5911f56764353e305246df88b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Gối Tựa Đầu &amp; Tựa Lưng Ô Tô HELLO LEIBOO Công Thái Học Tai Thỏ Memory Foam Mềm Mại - ComfyRab</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>₫331.500</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">836 </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27793764192?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mqkm75nskjk0c8.webp</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>shopee_27793764192</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1e6196fc5d982bdc12707ef79d61e261</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Mạ vàng cá ba chiều Thích hợp cho vỏ điện thoại iPhone17 16promax Apple 16 Flash Summer 17pro Fresh Case</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>₫222.359</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50111808512?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-823qo-mp6nyj9u0ydd07.webp</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>shopee_50111808512</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>f4729f65318b01de1dfd6f34e400d5aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Giày Thể Thao Chạy Bộ Nam Nữ GOYA STRIDES 3 Năm 2026 4 - Siêu Êm, Thoáng Khí, Thời Trang</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>₫859.000</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24303430608?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-ml1io2b8jf9d6c.webp</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>shopee_24303430608</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>a11de9775195b2b1ee15378bcb608329</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Quạt Cây Đứng Gropa Chính Hãng Điều Khiển Từ Xa, 7 Cánh Siêu Mát, Công Suất 40W, Tiết Kiệm Điện</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>₫468.000</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45659444466?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-moh1c2p1sgln67.webp</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>shopee_45659444466</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>b84153b6e5b832107178073806b75509</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>₫86.400</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579 </t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>shopee_23611804472</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>78d8105a297b5f0084b34b0f11d6c98e</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Tai nghe bluetooth A10 chip 5.4 bản mới nhất 2025,tai nghe không dây pin trâu cảm ứng nhạy cùng đèn led và âm thanh đình</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>9k+</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25723427507?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-m8nhkiwn8d4y9e.webp</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>shopee_25723427507</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>428ae3af83236b364b462afd36c73004</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Gối kê chân hỗ trợ điều trị suy giãn tĩnh mạch chân- Chính hãng Yorokobi</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>₫726.000</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/14762823526?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7qukw-lj3y46878l3m6e.webp</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>shopee_14762823526</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>ea2afbd5b2208d17df1b5d2f5cd79166</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Đèn năng lượng mặt trời mới năm 2026 có 120 viên LED lớn chống nước dùng ngoài trời và gia đình đèn vườn siêu sáng</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>₫466.980</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/44502217924?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mhjx4vgutgqu8c.webp</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>shopee_44502217924</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>e0c84f5f63f223fbd44508fe88b6bae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GOOJODOQ J201 IPX5 chống nước, giảm tiếng ồn, tai nghe không dây,tai nghe Bluetooth 5.3 tích hợp micro, âm thanh tốt.</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>₫166.420</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25605030831?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/cn-11134207-7r98o-lqn2kjmpl2k536.webp</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>shopee_25605030831</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>6a574bb5b5476c542fb5c59e92ea2344</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Máy Bơm Lốp Ô Tô, Xe Máy Cầm Tay Không Dây Thông Minh Bơm Nhanh, Dùng Đa Năng Cho Mọi Loại Xe, Tích Hợp Sạc Nhanh</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>6k+</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57002768810?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mi09wrlgruo1e8.webp</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>shopee_57002768810</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>e35c11bd089c63b3d034ddc80d5b0ddb</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,17 +605,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40eyrauSBO</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mbdmzx0xspfl87.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4d0361ea42311469477d46b6238caac3</t>
+          <t>abc8afac3d495901ce41349afcd81c38</t>
         </is>
       </c>
     </row>
@@ -704,22 +704,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">64 </t>
+          <t xml:space="preserve">65 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4AyP3ttoqR</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25895712227?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbf2ofv4dnn83d.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mbf2ofv4dnn83d.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7b260132ce735087b2f95677d3f537c0</t>
+          <t>7d9461aee3ca87fa0df8cf09df1591af</t>
         </is>
       </c>
     </row>
@@ -756,22 +756,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">36 </t>
+          <t xml:space="preserve">37 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L2rR7njJ5</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>f49544faffe4bbd3aeb4b1edcabefc44</t>
+          <t>e3516fdd0d8662ed7d391bdc1860f204</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4k+</t>
+          <t>5k+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3ViZj9CjP1</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28200539872?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgruskfrfocoe3.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4be218b81a6be9c55c23210e5f4e379b</t>
+          <t>f88d4f92a3e0d3ee20654e706807ba08</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">772 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Vxdt03yFf</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-bs-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mbiya3vjzvg4df.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>399716bb972df0ab32724f6fefb65c81</t>
+          <t>06b67e3715cbcf93cd06e235b20e67a3</t>
         </is>
       </c>
     </row>
@@ -4977,6 +4977,3693 @@
       <c r="K91" t="inlineStr">
         <is>
           <t>e35c11bd089c63b3d034ddc80d5b0ddb</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Chấm Bi Trái Cây Xanh Thích Hợp Cho Apple 17 Ốp Lưng Điện Thoại iPhone16PROMAX Niche 14 Hai Lớp 13 Ốp Lưng Cứng 12</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>₫74.966</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 </t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/52311852241?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-823r4-mp6qdel419ttb3.webp</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>shopee_52311852241</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>dc62b67d379a16cffadaa0ac02c97dac</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ERAZER XT66PRO Tai nghe Bluetooth 5.4 không dây, màn hình LED, 13 giờ, ASMR, AI Translator, APP, DIY</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>₫190.000</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24189047033?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-7rfi4-m3xdi44xdyua59.webp</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>shopee_24189047033</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fc0d79956e1eb0d81e0013bcd21625eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Kem Chống Nắng d'Al.ba Waterfull TONE UP PINK Correcting Sun Cream SPF50+ PA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>₫125.000</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40861459503?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-md0433ql7cjjce.webp</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>shopee_40861459503</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>3ec0def6b7060b0dadb29000c86a6bfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Sạc Dự Phòng 30000mAh 2 Output USB 2 Input Micro Type-C - Hỗ Trợ Sạc Nhanh</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>₫225.000</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>500k+</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27668212483?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mq3nxbhkhou863.webp</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>shopee_27668212483</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>bb99a0e50c77384b3611c3af010d5030</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>(Hàng Việt Nam Chất Lượng Cao) Quạt Tích Điện Mini Để Bàn Điện Cơ 89 Làm Mát Cực Nhanh, Sử Dụng Liên Tục Nhiều Giờ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>₫240.000</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42669048844?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-meuchzj3re9z6d.webp</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>shopee_42669048844</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>bcadc773f14eb10fd16720bd493171a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Combo 5 Túi Nước Xả Vải Hygiene Thái Lan – Lưu Hương Lâu, Mềm Mịn Quần Áo</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>₫119.000</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108 </t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50408976150?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mn510u9b20w19d.webp</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>shopee_50408976150</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>843fe12cbb5abaedb335c91811c1b145</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Đai ngồi ô tô cho bé CECILA Gối Nệm Y Tế, đai an toàn giữ cố định, gọn nhẹ,phù hợp mọi loại ghế</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>₫235.000</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51103772945?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mipktap22n7odd.webp</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>shopee_51103772945</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>5bdfc7f72d70cbd9fab5bd6afe03d4d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Thùng 10 gói khăn ướt 100 tờ Gumi không cồn,không parabens cao cấp dành cho bé</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227 </t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/44471928567?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-824ga-mpwxyu7xwumk84.webp</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>shopee_44471928567</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>e3cb35ca2680fbcf0f2520e9cbcec93e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>12 / 24 / 36 / 48 / 60 / 80 Acrylic Bút Đánh Dấu Bộ Bút Màu Nước Nhanh Khô Bút Đánh Dấu Đánh Dấu Cho Học Sinh Văn Phòng Phẩm Đồ Dùng Học Tập &amp; Văn Phòng</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>₫43.200</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 </t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-824iw-mdwpohbfbvnl03.webp</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>shopee_25596612791</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>8dc264fc633bc905e082b2489f0c02b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Đèn Pha Năng Lượng Mặt Trời TP SOLAR Công Suất 200W, 300W, 600W Chiếu Sáng 100-300m2, Vỏ Hợp Kim Nhôm, Sáng Xuyên Đêm</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>₫890.000</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23036581925?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mq46ci8qsni856.webp</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>shopee_23036581925</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2c4a0b8a884266a40c60bfc539e80ad5</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Quạt mini cầm tay 4000 mAh di động có thể sạc gió mạnh 199 tốc độ turbo phản lực</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>₫43.900</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622 </t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/44752890776?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mi2qa1wemnsxe9.webp</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>shopee_44752890776</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>9dacabc66036d8b166c7966b3ba15ba3</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Máy đo huyết áp Sinocare BA801 Chính Hãng</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>₫369.000</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>30k+</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/8300505418?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgrurhiamznva1.webp</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>shopee_8300505418</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>cdb3c601dc0868e36251dfd62b903624</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Giày thể thao chạy bộ nam nữ Goya Plus năm 2026 02T, siêu nhẹ, siêu êm nẩy vượt trội</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>₫599.000</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/21034391764?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mqzy4jh44ttx02.webp</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>shopee_21034391764</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>495c3576b40570d840f0e4d072c72d26</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>[MUA 1 TẶNG 1] Nước Giặt Dnee Chính Hãng Dung Tích Can 3000ml - Nước Giặt Thái Thơm Dịu An Toàn (Chuẩn Thái)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>₫100.000</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/52152057334?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134201-820l4-mi03mnakjthefe.webp</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>shopee_52152057334</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>951f1b565f395b5976e55d6ec6b07e39</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Sạc Dự Phòng 30000mah Sạc Nhanh Màn Hình Led, Tích Hợp 2 Đầu Sạc Tiện Dụng, Sạc Cho Iphone Và Android</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>₫237.500</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>400k+</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27706747428?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-me9vzu1kmozk27.webp</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>shopee_27706747428</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>1e95315b276ce63ffe9086121fe04fa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Áo điều hòa Nhật Bản AKITA, pin 74000Mah làm mát liên tục từ 12-14h bảo hành 12 tháng lỗi 1 đổi 1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>₫728.000</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23551902288?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mjza0u4b54ap5c.webp</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>shopee_23551902288</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>f5d8a9c8ad728ccf5535598d557aef72</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>(TRỢ GIÁ) Nước giặt Dnee 3000ml-Nước Giặt Xả Cho Bé an toàn (Chính hãng) -Thơm Dịu An Toàn Cho Làn Da Bé</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>₫200.000</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42977051612?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-misxkf2976yvab.webp</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>shopee_42977051612</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>dbd9a9ba2e5f094ef6c519dfa9eb3af2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Quạt cầm tay mini làm mát bằng bán dẫn, có chức năng chườm lạnh, sạc USB tiện lợi Quạt mini sò lạnh turbo quạt</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>₫37.760</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26337641149?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mb29hbiy09nc57.webp</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>shopee_26337641149</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>27e5ae00af0c1c8df0e0e6b150d4dc56</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Áo chống nắng nam chất Thun lạnh cao cấp ,có che trán,vành mũ rộng chống nắng UPF 50+</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>₫129.000</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/18144006340?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mo8dtzg7kxz6c3.webp</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>shopee_18144006340</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>6eda20a4e830e6a8732947aefd89e735</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cân sức khỏe điện tử chính hãng iScale SE 180kg màn hình LCD rõ nét kính cường lực cao cấp thiết kế gọn nhẹ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>₫104.000</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>600k+</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27907844567?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmhm4l34fsw255.webp</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>shopee_27907844567</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>7efa08cae8d3e7e707880fa076dd8ae9</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Túi Đựng Bút Hình Bánh Mì Nướng Hoạt Hình Dễ Thương Sức Chứa Lớn</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>₫66.959</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">737 </t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22732163462?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-23030-ytbqp6vieoov12.webp</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>shopee_22732163462</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>f19cf2e5742a72ae3cc5fce04ae20e62</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sạc Dựng Phòng Trong Suốt 30000mAh Với 2 Cổng Sạc Nhanh 22.5w và PD 20W Kèm 4 Đầu Sạc Màn Hình LED</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>₫225.000</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>600k+</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28818204493?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mosltly0nea598.webp</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>shopee_28818204493</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>adf291487dc2a895e78c827d58e8477e</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Camera imou AI thông minh trong nhà IPC-A32EP Ranger 2 3MP Báo động đàm thoại 2 chiều</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>₫429.000</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 </t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48206924962?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134211-81ztc-mmdhowv666fj26.webp</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>shopee_48206924962</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>f63ba553945656ebea53614801e64c5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Tripod điện thoại chân máy ảnh máy quay phim Weifeng WT 3520 hàng chính hãng tặng kèm kẹp điện thoại</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>₫279.000</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>30k+</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28670254239?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mpiuqggy88pb8e.webp</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>shopee_28670254239</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>c0641d91a45dab55a0c42e201a104b39</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>COMBO 3 Chai -VỊ MUỐI CHẤM ĐẶC SẢN 3 MIỀN | Chấm hải sản,thịt nướng,chấm lẩu,gà ủ muối</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29550030387?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-m6aov84x7p2web.webp</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>shopee_29550030387</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>30211b6208265d501ea299aba75d10e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Trắng 20000 mAh Điện thoại di động Công suất lớn Sạc nhanh 4 dây trong 1 cho tất cả các thiết bị</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50501303597?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgqah90t1dl8cb.webp</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>shopee_50501303597</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>24ed9af980ec0f9808c91423629177a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>[New 2026] Quạt Tích Điện Lồng Sắt không xoay Pin phổ thông, Đế Pin 21V- 2 Mức Gió, Sử Dụng 4-8 -12 Tiếng Hot Nhất 2026.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>₫275.000</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>400k+</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29405257458?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mp3d7fdhfv2mda.webp</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>shopee_29405257458</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2e2f2342bb2a3d14d15830159a5ca43d</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Chân Quay Máy Ảnh Điện Thoại Tripod 360 1m4 &amp; 1m7 HULAKO Gập Gọn 55cm Tripod Quay Vlog Chụp Ảnh, Quay Video Đa Thiết Bị</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>₫249.000</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29905169981?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mcprrbgkm3sd5e.webp</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>shopee_29905169981</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>943ad0064124e8383189c47d9438b71e</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ghế bập bênh thư giãn giả mây khung thép sử dụng ngoài trời ban công sân vườn bảo hành 36 tháng/Relax Haven HCM</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>₫350.000</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24476449221?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lui366jemp0l71.webp</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>shopee_24476449221</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>ee85c046c2aac41ce5d5736af9031876</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>sạc dự phòng mini 5000mah Mang theo bên mình ,cáp sạc nhanh</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>₫50.000</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56801324918?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mh0mbnood6316f.webp</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>shopee_56801324918</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>5eb25e05ead35952a364b97c71270744</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Áo Điều Hòa YAMA JAPAN 18V Áo Bảo Hộ Gắn Quạt Trang Phục Lao Động Làm Mát Cơ Thể Pin 50000mAH</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>₫615.200</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24942159580?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mnhngfnzwr2a89.webp</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>shopee_24942159580</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>f542618bbc84e3e7e16e7b1bedade92e</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Áo chống nắng 2 lớp UPF 50+ chống tia UV nam nữ khoá kéo cổ cao M08 Rico</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>₫175.000</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/21089968899?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mo20pzyy3ev93d.webp</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>shopee_21089968899</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>d1b11e1fbfc7a9fc5e82568b594016e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Giày Thể Thao Chạy Bộ Nam Nữ GOYA STRIDES 3 Năm 2026 1 - Siêu Êm, Thoáng Khí,Thời Trang</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>₫859.000</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/20186938284?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mq91iy6hdtkx92.webp</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>shopee_20186938284</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>501f5df183f0fbf762d9e977e7c711b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Dây Sạc Nhanh 3 Đầu Sạc Được Mọi Dòng Máy 120W 3in1 Silicon Dài 2M TypeC</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>₫30.000</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196 </t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27639086679?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mckid5pcgql838.webp</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>shopee_27639086679</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>32f43d2e32e7029e46af981930318f7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Camera YooSee Ngoài Trời 2 Mắt Xem 2 Góc Cùng Lúc 15.0Mpx, Góc Rộng Nét - BẢO HÀNH 1 NĂM</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>₫549.000</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22870283058?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7qukw-lhqgiry6impx77.webp</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>shopee_22870283058</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2065d9e1b9375f18deb271ca68ab52a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>🔥🔥Quạt Tích Điện Pin 10-15 Cell Dùng Liên Tục 4-8H, Quạt Makita Để Bàn 2 Cấp Độ Gió Siêu Mát</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>₫151.580</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26671193851?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-7rfgf-m3zuap1sauuaa9.webp</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>shopee_26671193851</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>476a780bcb6b273a2e15410bb5c59779</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Quạt cầm tay công suất lớn, pin dung lượng lớn có thể sạc lại - Dùng cho cắm trại, ngoài trời và trên ô tô</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>₫369.599</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49761263683?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/cn-11134207-820l4-moqx3na6vsi75b.webp</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>shopee_49761263683</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>ef47c0a0091be28cbd87707790f38cab</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Áo chống nắng Nam Nữ 2 lớp đủ màu, áo khoác chống nắng ngăn tia UV thông hơi thoáng khí thời trang</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>8k+</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22466400575?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-m90k8ueknb0n38.webp</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>shopee_22466400575</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>95ee8c3b64815f32a2aef4d98cfad3b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Mic Thu Âm Không Dây Cho Điện Thoại M31, Bật Tắt Lọc Ồn - Micro Ghi Âm Cài Áo, Quay Video, Làm Vlog ,Livestream</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>₫419.000</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22876955030?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-m1qkg32xm667b6.webp</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>shopee_22876955030</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>561913646136774b13556bcda9b7e9aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Sạc nhanh SHIRA 20000 mAh, tích hợp 4 cổng sạc, màn hình LED, PD 22.5W, tiện lợi, BH 12 tháng</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>₫409.000</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>30k+</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28031106552?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mhhnknprsw0037.webp</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>shopee_28031106552</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>8ae9d98ee56a5902e44cd1d00e7ec5f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Quạt Tích Điện 8inch Chất Liệu Full Thép Không Rỉ Dùng Pin Phổ Thông M21 Quạt Sạc Pin Tích Điện Với 2 Mức Độ Gió Siêu Êm</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>₫399.000</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>6k+</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24482376499?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mm8gojf1swed01.webp</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>shopee_24482376499</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>c7dbec252ef50f4f6b2ca7b2b9975276</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Áo điều hòa Nhật Bản kèm pin Japan 98000mAh – Quạt 9 cánh không chổi than, làm mát nhanh, bảo hành 12 tháng</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>₫200.000</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>90k+</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27908058153?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-m9r3kz7qmi6ad9.webp</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>shopee_27908058153</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>e3a4450cf32030352794d32594b08e8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Robot Smart Gadgets quét nhà hút bụi lau nhà thông minh, Máy Hút Bụi robot mini đa chức năng giá rẻ HOT</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>₫177.000</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>600k+</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29951889800?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134201-7r98o-lw6n7g963ttnde.webp</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>shopee_29951889800</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>57ea15dc74d1cec0632fa010c225190b</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>(Tặng Remote) Gậy chụp ảnh Selfie 4 chân A14 1M8 điều khiển từ xa có phân loại đèn trợ sáng Tripod chụp ảnh SPO1</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>₫210.000</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>30k+</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53304499944?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mkfnm6ypzzlu48.webp</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>shopee_53304499944</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>88bda96e14cc1ddd260b7e2d1ec63619</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ghế học sinh chống gù cho các bé, Đệm Cao Su Siêu Êm, tăng giảm chiều cao theo độ tuổi</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>₫508.000</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57161457910?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mps1c9kliuj209.webp</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>shopee_57161457910</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>aecd3e3b92a69cce9a08c4ee44a7872e</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Camera IP Wifi Trong Nhà IMOU Ranger 2 I A32EP 3MP I A52P 5mp Xoay 360 Độ, Đàm Thoại Hai Chiều - TRANGIATELECOM</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>₫690.000</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">796 </t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22247566032?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mjfzvurvc1z7bc.webp</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>shopee_22247566032</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>10d1999cb5d2ee63aa1fd48a774c4517</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>[belif Official] Mặt nạ ngủ dưỡng ẩm và phục hồi da chuyên sâu belif Multi Vitamin Mask 75ml</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>₫370.000</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/21316981412?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mqzneigo1hqf27.webp</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>shopee_21316981412</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>9da2b21d568c951fc13ec59640c28ab5</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Quạt Tích Điện Tự Động Xoay, Quạt Kẹp Xe Đẩy, Quạt Để Bàn Góc Xoay 160°, Không Gây Tiếng Ồn NKC20</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>₫382.000</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>30k+</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/21587529485?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-moq98bblmlmp54.webp</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>shopee_21587529485</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>35e49e91d61b5dcb9065d51dbb0758a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Máy rửa xe Cầm Tay 2 Pin 10 Cell 199V - Máy xịt rửa sân vườn xịt rửa cao áp có tạo bọt tuyết.</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>₫399.000</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>200k+</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23048465072?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7qukw-ljiwu7jbp98id7.webp</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>shopee_23048465072</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>09e054aff7542e67d8007297b0f23d4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Đèn ngủ hình vịt ngọt ngào ngủ bằng silicon mềm có sạc USB Tắc Trẻ Em Kid Trang Trí Phòng Ngủ Quà Tặng Sinh Nhật</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>₫205.615</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41812351373?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mh7df34704y758.webp</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>shopee_41812351373</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>510afd16b80a5c9043692b780fec30b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Vỏ trong suốt, pin dự phòng 20000mAh, sạc siêu nhanh 20W, có thể sạc cùng lúc 4 thiết bị.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>₫338.000</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55001547088?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgne1cu9zbwt96.webp</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>shopee_55001547088</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>03eadf27c544b2e022f7da9d3bbabaea</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Kem chống nắng dAlba Waterfull Tone-Up Sun Cream SPF50 50ml</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>₫899.000</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">383 </t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25873580719?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-luzvsg0ikmc258.webp</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>shopee_25873580719</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>3b6947ec4126f6eff02d2c94ca395f8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Loa Bluetooth karaoke Output 100W Bass mạnh treble rời âm thanh đỉnh cao bảo hành chính hãng</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>₫820.000</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24626378450?trace=%7B%22trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.A5Cb7JvWdXl.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmuqna8phzphfb.webp</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>shopee_24626378450</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>d39b4c67291ab3c999a7c1120e92d2ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>[PIN 60000mAp Bản Mới Nhất M] Quạt cầm tay tích điện dung lượng pin khủng, màn hình LED thông minh</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>₫69.000</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">620 </t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53262036720?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mpbwyn8plde7ef.webp</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>shopee_53262036720</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>16c6f74141f16a55f4991df348d414db</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Mic Thu Âm Không Dây Cài Áo Cho Điện Thoại M31 - Bản 2 Mic, Bật/Tắt Lọc Ồn Dùng Cho Quay Video</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>₫489.000</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26368401110?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-m2w8wzjylfyeed.webp</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>shopee_26368401110</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>649869c9ee98e8a4f35d1a1879ec344d</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Đệm Ô Tô Ghế Sau Gấp Gọn Bằng Da Cao Cấp, Nệm Xe Hơi Bằng Da Gấp Gon Thông Minh BenStore 12</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>₫498.000</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24715006419?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lz01tj0tk4v528.webp</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>shopee_24715006419</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>53e8e24b1e2b2566e39d316df2e53f24</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>[MUA 10 TẶNG 10] Khăn giấy rút treo tường Sương Mai TopGia 10bịch 10000 tờ 4 lớp tặng bộ chăm sóc cá nhân</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>₫106.000</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>8k+</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29330908242?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mo4zddzsjkshf0.webp</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>shopee_29330908242</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>7b5f2982b4b82daac0d6a0d7b3e125ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Gậy chụp ảnh 4 chân Tripod điện thoại livestream, quay phim, chụp ảnh kéo dài 180cm, có remote</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>₫240.000</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26609161628?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-m6jmn3jlt1yw70.webp</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>shopee_26609161628</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>7d9743e5e1856ab0d185694bb884a3b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Micro Puluz không dây điện thoại cài áo khử nhiễu chống ồn nhỏ gọn ghi âm livestream trợ giảng quay phim - Chính hãng</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>₫358.000</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/44361887230?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-7rdvk-md4ptww3vfb457.webp</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>shopee_44361887230</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>59a4a273ac03deef5dcf4a911ab9ddf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Balo nam nữ đi học đi làm BAMA Border Backpack cặp chống nước nhiều ngăn đựng laptop 13 14 15.6 inch</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>₫607.200</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>40k+</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/17478287414?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mq3mlzhu9k3k0c.webp</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>shopee_17478287414</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>16d521c128e88b52999382482b222dae</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Sạc Dự Phòng 50.000mAh, Công suất cực đại 120W, Thiết kế 4 dây sạc sẵn, Màn hình LED thông minh %Pin</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>₫619.286</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>30k+</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25025939212?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mq5r7sy71w5q1d.webp</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>shopee_25025939212</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>e18de07c7209bfa843deec2cb7b5fef4</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Sáp Thơm Cô Đặc Dành Cho Xe Hơi - THALO Hương Liệu Thiên Nhiên (Đại Dương/Trà Ô Long/Hoa Hồng)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>₫169.000</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>6k+</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28283275690?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mpryg01ci1hoa7.webp</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>shopee_28283275690</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>b41323cb245f82f8a2f8537da1a7ebcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Combo Hai Túi Nước Xả Vải Hygiene Expert Care Hương Hoa Hồng 2200ml</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>₫77.199</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26380471027?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-m7n1nmp0uptf67.webp</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>shopee_26380471027</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>7c295922148bdf86654db80928b26351</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Giày thể thao chạy bộ nam nữ Goya Plus năm 2026 siêu nhẹ, siêu êm, chống trơn trượt, siêu thoáng khí</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>₫629.000</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>80k+</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22712863299?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mqzy1c7q1ogce0.webp</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>shopee_22712863299</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>9107e27b0192c1f62f3946118bbaf39a</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Bướm ba chiều dập nổi Thích hợp cho Apple 16promax Trong suốt iPhone17 Spring 17pro Vỏ điện thoại hoa</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>₫9.053</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43931508312?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-823qp-mp6faoxvsnbi51.webp</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>shopee_43931508312</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>b31e4715bafc1d1b5083b295bdcf22e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Bơm Lốp Kích Bình ắc Quy Ô Tô 4 Trong 1 Wisezen Có Thể Dùng Làm Pin Sạc Dự Phòng Tích Hợp đèn LED Dễ Thao Tác</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>₫879.000</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28189555996?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmrd6bimu4g508.webp</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>shopee_28189555996</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>73d048b0854caa7a91453bbd412a6387</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Áo polo nam MÃ ĐÁO THÀNH CÔNG [Tặng hộp gói quà] Vải FeelMax Phom chuẩn, Sang trọng - SIXMEN</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>₫357.999</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>50k+</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22467549746?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mhn7fjqkf7k18a.webp</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>shopee_22467549746</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>072f3de904828851673bcf7c418facd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>​​Máy Ép Tách Bã Gia Đình - Ép Trái Cây Rau Củ, Làm Sữa Đậu &amp; Đồ Ăn Dặm, Miệng Rộng Không Cần Cắt, Lọc Tự Động​​</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>₫188.000</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 </t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29141056268?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-824jg-me6ri40e7ncx0e.webp</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>shopee_29141056268</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>8edbc229f616139128ceedea60244c9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Đen 20000 mAh điện thoại di động công suất lớn 4 dây trong 1 hỗ trợ Tất cả điện thoại và máy tính bảng</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>₫74.000</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55601293829?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mh0d5s70ak2072.webp</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>shopee_55601293829</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>aca9223f612b9ad64b14ec2a8aa285af</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Loa bluetooth Heavy Bass 16 không dây công suất lớn, âm thanh hay, led nháy theo nhạc</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>₫1.109.000</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25476379844?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mmuq2jwjdurs3b.webp</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>shopee_25476379844</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>bdb82a8de1c2434f6dd8e3f1f958dd13</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Máy Thổi Bụi Cầm Tay 1050W 28000rpm Dùng Pin 10/15/20 Cell, Thổi Lá Sân Vườn, Bảo Hành 1 Năm</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>₫219.000</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29478583279?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgzztrbtgl570d.webp</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>shopee_29478583279</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>21ea839067b4ba0fa3b97364e5d426f9</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K162"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B5jKXE04z</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mpe2jjd3b2fifb.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4e3452edfd64b6b785d3f600faf050e4</t>
+          <t>13179ebb6a344232219ab4e9a5f511d5</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">928 </t>
+          <t xml:space="preserve">929 </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/30mJ8EEdPw</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26319252965?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-aka-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-m37a3n329d6452.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>e8c259bd483858e228b0c2099ebeb852</t>
+          <t>9be2ff1341154d061edea9bd47d4b9b7</t>
         </is>
       </c>
     </row>
@@ -8664,6 +8664,948 @@
       <c r="K162" t="inlineStr">
         <is>
           <t>21ea839067b4ba0fa3b97364e5d426f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Bộ Bàn Trang Điểm Tặng Ghế M02, Thiết Kế Thông Minh, Phong Cách Tinh Tế - Nội Thất UKZ Việt Nam</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>₫1.950.000</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320 </t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28219551159?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ras8-mcoxhnnvqv1818.webp</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>shopee_28219551159</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>17ce2bb24934bd26fd2ba2c36f4e650b</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Pin dự phòng 20000mAh, sạc nhanh 22,5W, tích hợp 3 cáp sạc nhanh</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>₫70.000</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40326452239?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mgne1rcrsow93e.webp</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>shopee_40326452239</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>71266b29f97fec9170f44031095cef83</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Xe đạp điện trợ lực gấp, dễ dàng để vào cốp xe ô tô, động cơ 400W, pin Lithium, bảo hành 18 tháng, xe thay thế</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>₫5.208.600</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173 </t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27723604940?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-7ra1w-m51nwlsidayo00.webp</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>shopee_27723604940</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>d6db447ac80166fb5d0961c4e2c9d273</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Áo điều hòa KAW cao cấp, Dung lượng pin 50000mAh, 35000mAh siêu khủng 16 - 20 tiếng, Hàng chính hãng</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>₫777.100</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24881878780?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mqbep0mlzqwy74.webp</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>shopee_24881878780</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>48ff58e514bdb34e2a41c60a8e792f8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Đêm Dài Gợi Cảm Gợi Cảm Đam Mê Phù Hợp Với Trong Suốt Cám Dỗ Gợi Cảm Vớ Một Mảnh Lưới Quần Áo Đồng Phục 5311</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>₫45.145</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26 </t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50609103568?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-81zua-mn8h3tqpl5hh91.webp</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>shopee_50609103568</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>7324de2bad783a97ea0a646574095856</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Combo Sữa tắm gội nam 3in1 350ml &amp; Sữa rửa mặt 100ml &amp; Dung dịch vệ sinh 120ml &amp; Nước hoa 10ml Rhys Man - Combo Nam Tính</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>₫399.000</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>200k+</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/16177289192?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mq38so18gnpoa8.webp</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>shopee_16177289192</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>eae232afd049c80a2af240c5c3dd2bd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Bơm lốp ô tô Bơm lốp xe hơi điện tử tự ngắt Bomlopoto bomlopxehoi</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>₫379.000</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">974 </t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28204986393?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lxjlw67n7zdn87.webp</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>shopee_28204986393</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>bd20df9adc0703b78a1c975ce4cdeee8</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Ghế mây thư giãn bập bênh ngoài trời kèm nệm - Sản phẩm chuẩn kích thước dành cho người lớn đọc sách từ HOME MÂY</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>₫1.827.000</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110 </t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/12713806757?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-23010-q3gtbtn6wxlv22.webp</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>shopee_12713806757</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>f12ebbeda1c1644d96b8391cb1e3bdba</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Bộ Củ Cáp Sạc Nhanh PD20W Hoco C76 Plus 3A Kèm Cáp Type-C To I.P 1M Tương Thích IP 6/7/8/X/11/12/13/14/Pro/Max</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>₫160.900</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>21,5%</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27355490606?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mq37nyscc4xs56.webp</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>shopee_27355490606</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>daf5f7f832e8f00563c4d964a7d4900b</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Áo điều hòa Nhật Bản, quạt áo điều hòa công suất 25V, hoạt động liên tục 12-14h mát cực nhanh</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>₫659.000</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24541157970?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-moaufjwlaby9f7.webp</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>shopee_24541157970</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>abc90d899bbec885e09125c44f741ac2</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Giày thể thao đa năng nam nữ GOYA DAILY năm 2026 - Đế RB chống trơn trượt, hạn chế mài mòn</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>₫499.000</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266 </t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29735213712?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-820l4-mk0hnda0xr7s86.webp</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>shopee_29735213712</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>61ac1c1d7e39b9eacf82290b7b470571</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Loa bluetooth Charge 3 mini nghe nhạc âm thanh bass đỉnh,loa không dây giá rẻ nhỏ gọn có chỗ cắm thẻ nhớ tiện lợi có BH</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>₫218.000</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>400k+</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25953042905?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7r98o-lz1rkf5jus7hf3.webp</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>shopee_25953042905</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>5e04773ba0117227bc8a1d7ba15f42e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sạc dự phòng 20000mah có tích hợp 4 cáp sạc nhanh màn hình led hiện thị dung lượng sạc được cho nhiều thiết bị r08</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>₫279.000</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27967005864?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/sg-11134201-8259w-mqojnax62g3n29.webp</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>shopee_27967005864</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>27b9991b9b2186b758a765ce318f78cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Máy Bơm Lốp Xe Ô Tô Điện Tử TOYOTA Thông Minh Tự Ngắt XeAuto Cao Cấp màn LCD - Lỗi 1 đổi 1 - Bảo Hành 14 Tháng Đổi Mới</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>₫475.000</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>90k+</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24084775706?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134201-7r98o-lyxr033uqqhtcf.webp</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>shopee_24084775706</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>6b9897edc010e2ac69c7176cd054dee4</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>(Tặng 1 gói sốt) COMBO 15 CHÂN GÀ BÀ TUYẾT MIX - ĂN CÙNG BÀ TUYẾT M119</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>₫157.500</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>6k+</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57304427402?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mo67pbfgogzq2b.webp</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>shopee_57304427402</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>d9c2a8b793544c048bf01c2e3aa0e293</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Quạt cầm tay N68 100 cấp độ gió, Quạt tích điện mini pin cao 5 000 mah hiển thị led, tuabin gió mạnh, dùng lâu</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>₫43.900</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49611674735?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mp21w1dn30gde6.webp</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>shopee_49611674735</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>e39f48ef9f7296426b8e8f888947027c</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>[SIZE TO BẢN CAO CẤP] Khăn giấy rút TOPGIA dạng bịch treo tường tiện lợi siêu dai mềm mịn</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>₫135.000</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28944864596?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-81ztc-mp0p82nq2igw9e.webp</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>shopee_28944864596</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>5ae8f6c88fbc3b0a1e3223a69bb0ed67</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Kính râm thời trang V5 dành cho nam, gọng vuông mắt kính kiểu mới - Chống UV400 đi ngày và đêm Titan</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>₫168.000</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29657463965?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://down-ws-vn.img.susercontent.com/vn-11134207-7ra0g-m8h4anlalje666.webp</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>shopee_29657463965</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>882090caa8be3142d51cbb067685900a</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51908128978?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8KoEvr9Dm0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40355840814?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9V0CK3WzUT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1BKnUO5Evl</t>
+          <t>https://s.shopee.vn/2VqRz8VQbw</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/qhx5m6Vbj</t>
+          <t>https://s.shopee.vn/7AcHXiDf9Q</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28200539872?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3LPYyfSFwW</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25241658670?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5fnTl0laH8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29029784452?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/W5NbSd2fk</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDKgE1Qtr</t>
+          <t>https://s.shopee.vn/1LeUazZrzo</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2VqB4q0ADt</t>
+          <t>https://s.shopee.vn/9fJcWJ495B</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22243625222?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/AKZJJX1bjF</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28126833083?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5VU3YeK0XG</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24660800592?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2g9sBRUnHT</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LWcL0HAlc</t>
+          <t>https://s.shopee.vn/1qalBuXxxs</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26319252965?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4VbWMrq1e3</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VTkRaqtzw</t>
+          <t>https://s.shopee.vn/8AUojbc4CL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4qE3eMtRLs</t>
+          <t>https://s.shopee.vn/4LI6AVORtd</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54355250128?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1970Xewgh</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/50XNVu71MO</t>
+          <t>https://s.shopee.vn/8AUojY9r71</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50555002230?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3g2PNHQzFZ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/LlgUr8PcW</t>
+          <t>https://s.shopee.vn/2qTINkU9wU</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gGvXmJi7Y</t>
+          <t>https://s.shopee.vn/8V7f8A8aR3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2279,7 +2279,6 @@
           <t>₫297.323</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">28 </t>
@@ -2292,7 +2291,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54661835387?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1VxunIZEdq</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2327,7 +2326,6 @@
           <t>₫437.974</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">27 </t>
@@ -2340,7 +2338,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40332039212?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9pd2ic3VjB</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2375,7 +2373,6 @@
           <t>₫272.130</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t xml:space="preserve">12 </t>
@@ -2388,7 +2385,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/52612730419?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/BSXCqeJLi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2529,7 +2526,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LHpGCtBVQ</t>
+          <t>https://s.shopee.vn/8pkVWm7Jm6</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2623,7 +2620,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W56hA7mHZ</t>
+          <t>https://s.shopee.vn/1BL4OgaVJo</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2665,7 +2662,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6ffhpjmSd3</t>
+          <t>https://s.shopee.vn/6AjkLsHTBK</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2749,7 +2746,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LWksX0nYq</t>
+          <t>https://s.shopee.vn/7VF7wKCOTS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2875,7 +2872,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/111NI55sGi</t>
+          <t>https://s.shopee.vn/4AyfyCP5Ec</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2952,8 +2949,6 @@
           <t>₫111.002</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>83,5%</t>
@@ -2961,7 +2956,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54113369613?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9Kgm7h5Pk6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2974,7 +2969,6 @@
           <t>shopee_54113369613</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>03d510a21d58edf3d77e58473c22f575</t>
@@ -2997,7 +2991,6 @@
           <t>₫855.146</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t xml:space="preserve">9 </t>
@@ -3010,7 +3003,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53263324968?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9V0CK04mP9</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3023,7 +3016,6 @@
           <t>shopee_53263324968</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>4504250be76f3ea71ec7faa0e50ce355</t>
@@ -3063,7 +3055,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/18591723306?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/903vj56gQ4</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3076,7 +3068,6 @@
           <t>shopee_18591723306</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>0f053f3f609ead54c09c487185bf21e4</t>
@@ -3099,7 +3090,6 @@
           <t>₫384.545</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">3 </t>
@@ -3112,7 +3102,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/46213516840?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9ANLvO6357</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3125,7 +3115,6 @@
           <t>shopee_46213516840</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>acf1e56507bb75bacc07a49cf4610f45</t>
@@ -3148,7 +3137,6 @@
           <t>₫263.351</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t xml:space="preserve">1 </t>
@@ -3161,7 +3149,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56513668531?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8fR5KT7x62</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3174,7 +3162,6 @@
           <t>shopee_56513668531</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>6472dfcb91ee3f10c54a61c9396ce262</t>
@@ -3197,7 +3184,6 @@
           <t>₫439.817</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t xml:space="preserve">2 </t>
@@ -3210,7 +3196,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51013200090?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8pkVWm7Jl5</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3223,7 +3209,6 @@
           <t>shopee_51013200090</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>8009cf052b2b98242dfb7fbdb473ebd7</t>
@@ -3246,7 +3231,6 @@
           <t>₫129.914</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t xml:space="preserve">8 </t>
@@ -3259,7 +3243,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54513171684?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/80BOXFAURy</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3272,7 +3256,6 @@
           <t>shopee_54513171684</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>3534084a052e79832c099582f83873c2</t>
@@ -3295,7 +3278,6 @@
           <t>₫56.000</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t xml:space="preserve">6 </t>
@@ -3308,7 +3290,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40525647070?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2LX1mpW3wv</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3321,7 +3303,6 @@
           <t>shopee_40525647070</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>857229f41048f1f496374267914d9108</t>
@@ -3344,7 +3325,6 @@
           <t>₫63.775</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t xml:space="preserve">45 </t>
@@ -3357,7 +3337,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49511823677?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2BDbaWWhHu</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3370,7 +3350,6 @@
           <t>shopee_49511823677</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>2b2af17cf98fe9f6d989b1cbef5abc3f</t>
@@ -3410,7 +3389,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27484697336?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/20uBODXKct</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3423,7 +3402,6 @@
           <t>shopee_27484697336</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>8773f7b4732ba967021b5c2ba6e80b86</t>
@@ -3463,7 +3441,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25123423072?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1gHKzbYbIr</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3476,7 +3454,6 @@
           <t>shopee_25123423072</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>b3069fd70bc4376a9e159dbdae54e01f</t>
@@ -3499,8 +3476,6 @@
           <t>₫642.923</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>83,5%</t>
@@ -3508,7 +3483,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25748311349?trace=%7B%22trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.3H7YB2PbL45.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1LeUazZryp</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3521,7 +3496,6 @@
           <t>shopee_25748311349</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>240caeb9da1473c32237c7f2e3f4dc0d</t>
@@ -3544,7 +3518,6 @@
           <t>₫11.500.000</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t xml:space="preserve">5 </t>
@@ -3557,7 +3530,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56213044633?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/111eCNb8en</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3570,7 +3543,6 @@
           <t>shopee_56213044633</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>11b1abcb04f8572d3ebce06ca94fb5b5</t>
@@ -3593,7 +3565,6 @@
           <t>₫356.000</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t xml:space="preserve">12 </t>
@@ -3606,7 +3577,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48500941449?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/qiE04blzm</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3619,7 +3590,6 @@
           <t>shopee_48500941449</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>686b261362b588a5e597b2e4b9a9d984</t>
@@ -3659,7 +3629,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/4537242491?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/gOnnlcPKl</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3672,7 +3642,6 @@
           <t>shopee_4537242491</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>beea6c89d2940e4426862501b5557fa7</t>
@@ -3712,7 +3681,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44606828138?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/LlxP9dg0j</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3725,7 +3694,6 @@
           <t>shopee_44606828138</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>96776330d0d92e7ee493b039c5e0c375</t>
@@ -3765,7 +3733,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50254653729?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5ArDA2LHCi</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3778,7 +3746,6 @@
           <t>shopee_50254653729</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>44b0d17153a4822354959c61794c8ef1</t>
@@ -3818,7 +3785,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25676379719?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/50XmxjLuXh</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3831,7 +3798,6 @@
           <t>shopee_25676379719</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>8797a0b343c8a948af2337da1f7954d2</t>
@@ -3854,8 +3820,6 @@
           <t>₫356.000</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -3863,7 +3827,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48201510573?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4qEMlQMXsg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3876,7 +3840,6 @@
           <t>shopee_48201510573</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>9a6f048436bdf3b3ac3abc642b1fc308</t>
@@ -3916,7 +3879,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48403837828?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4fuwZ7NBDf</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3929,7 +3892,6 @@
           <t>shopee_48403837828</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>6c003b1d65980a5b0704f653a4ef8a10</t>
@@ -3969,7 +3931,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/5864774152?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4VbWMoNoYe</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3982,7 +3944,6 @@
           <t>shopee_5864774152</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>4a09897ee7d33b260ec67ea1e8079951</t>
@@ -4022,7 +3983,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51300953146?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/40fFltPiZb</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4035,7 +3996,6 @@
           <t>shopee_51300953146</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>6c5d0a6c01f151e144292c300ef9d90b</t>
@@ -4075,7 +4035,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27137628373?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3qLpZaQLua</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4088,7 +4048,6 @@
           <t>shopee_27137628373</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>d7c9b876d8664c2df389ab44f5363639</t>
@@ -4111,7 +4070,6 @@
           <t>₫278.000</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t xml:space="preserve">3 </t>
@@ -4124,7 +4082,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48900836040?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3VizAyRcaY</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4137,7 +4095,6 @@
           <t>shopee_48900836040</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>d8cea489e529d5706472e802e82cbdc7</t>
@@ -4177,7 +4134,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3LPYyfSFvX</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4190,7 +4147,6 @@
           <t>shopee_24288149456</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>3ab082fd60013c76170b7ba6b1a8fe5e</t>
@@ -4230,7 +4186,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26985013216?trace=%7B%22trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.4plfRoTziH3.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3B68mMStGW</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4243,7 +4199,6 @@
           <t>shopee_26985013216</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>df43a8b645001a422be65d0f50d79dd4</t>
@@ -4283,7 +4238,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28106687731?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/30mia3TWbV</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4296,7 +4251,6 @@
           <t>shopee_28106687731</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>4e0e93abedf8ba580ea21161bb95bf62</t>
@@ -4336,7 +4290,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29201881549?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7pryKwB7nU</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4349,7 +4303,6 @@
           <t>shopee_29201881549</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>95a060a6a1a9f056fe980aff47e9c28c</t>
@@ -4389,7 +4342,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25368635737?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7fYY8dBl8T</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4402,7 +4355,6 @@
           <t>shopee_25368635737</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>bce7fb76652260ec5cdc8a69a5a6c491</t>
@@ -4442,7 +4394,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42460450626?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7Kvhk1D1oR</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4455,7 +4407,6 @@
           <t>shopee_42460450626</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>25270d5911f56764353e305246df88b1</t>
@@ -4495,7 +4446,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27793764192?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/70IrLPEIUP</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4508,7 +4459,6 @@
           <t>shopee_27793764192</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>1e6196fc5d982bdc12707ef79d61e261</t>
@@ -4531,8 +4481,6 @@
           <t>₫222.359</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>83,5%</t>
@@ -4540,7 +4488,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50111808512?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6pzR96EvpO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4553,7 +4501,6 @@
           <t>shopee_50111808512</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>f4729f65318b01de1dfd6f34e400d5aa</t>
@@ -4593,7 +4540,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24303430608?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6fg0wnFZAN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4606,7 +4553,6 @@
           <t>shopee_24303430608</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>a11de9775195b2b1ee15378bcb608329</t>
@@ -4646,7 +4592,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45659444466?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6VMakUGCVM</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4659,7 +4605,6 @@
           <t>shopee_45659444466</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>b84153b6e5b832107178073806b75509</t>
@@ -4682,7 +4627,6 @@
           <t>₫86.400</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t xml:space="preserve">579 </t>
@@ -4695,7 +4639,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6L3AYBGpqL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4708,7 +4652,6 @@
           <t>shopee_23611804472</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>78d8105a297b5f0084b34b0f11d6c98e</t>
@@ -4748,7 +4691,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25723427507?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/60QK9ZI6WJ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4761,7 +4704,6 @@
           <t>shopee_25723427507</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>428ae3af83236b364b462afd36c73004</t>
@@ -4801,7 +4743,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/14762823526?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5q6txGIjrI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4814,7 +4756,6 @@
           <t>shopee_14762823526</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>ea2afbd5b2208d17df1b5d2f5cd79166</t>
@@ -4854,7 +4795,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44502217924?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5fnTkxJNCH</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4867,7 +4808,6 @@
           <t>shopee_44502217924</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>e0c84f5f63f223fbd44508fe88b6bae3</t>
@@ -4907,7 +4847,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25605030831?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5LAdMLKdsF</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4920,7 +4860,6 @@
           <t>shopee_25605030831</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>6a574bb5b5476c542fb5c59e92ea2344</t>
@@ -4960,7 +4899,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/57002768810?trace=%7B%22trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.5Tq57wcznCL.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/AUsjVq0yOG</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4973,7 +4912,6 @@
           <t>shopee_57002768810</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>e35c11bd089c63b3d034ddc80d5b0ddb</t>
@@ -4996,7 +4934,6 @@
           <t>₫74.966</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t xml:space="preserve">4 </t>
@@ -5009,7 +4946,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/52311852241?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/AAFt7E2F4E</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5022,7 +4959,6 @@
           <t>shopee_52311852241</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>dc62b67d379a16cffadaa0ac02c97dac</t>
@@ -5062,7 +4998,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24189047033?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9zwSuv2sPD</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5075,7 +5011,6 @@
           <t>shopee_24189047033</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>fc0d79956e1eb0d81e0013bcd21625eb</t>
@@ -5115,7 +5050,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40861459503?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9pd2ic3VkC</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5128,7 +5063,6 @@
           <t>shopee_40861459503</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>3ec0def6b7060b0dadb29000c86a6bfd</t>
@@ -5168,7 +5102,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27668212483?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9V0CK04mQA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5181,7 +5115,6 @@
           <t>shopee_27668212483</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>bb99a0e50c77384b3611c3af010d5030</t>
@@ -5204,7 +5137,6 @@
           <t>₫240.000</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t xml:space="preserve">1 </t>
@@ -5217,7 +5149,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42669048844?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9Kgm7h5Pl9</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5230,7 +5162,6 @@
           <t>shopee_42669048844</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>bcadc773f14eb10fd16720bd493171a0</t>
@@ -5270,7 +5201,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50408976150?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9ANLvO6368</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5283,7 +5214,6 @@
           <t>shopee_50408976150</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>843fe12cbb5abaedb335c91811c1b145</t>
@@ -5323,7 +5253,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51103772945?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/903vj56gR7</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5336,7 +5266,6 @@
           <t>shopee_51103772945</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>5bdfc7f72d70cbd9fab5bd6afe03d4d9</t>
@@ -5376,7 +5305,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44471928567?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8fR5KT7x75</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5389,7 +5318,6 @@
           <t>shopee_44471928567</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>e3cb35ca2680fbcf0f2520e9cbcec93e</t>
@@ -5429,7 +5357,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25596612791?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8V7f8A8aS4</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5442,7 +5370,6 @@
           <t>shopee_25596612791</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>8dc264fc633bc905e082b2489f0c02b3</t>
@@ -5482,7 +5409,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/23036581925?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8KoEvr9Dn3</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5495,7 +5422,6 @@
           <t>shopee_23036581925</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>2c4a0b8a884266a40c60bfc539e80ad5</t>
@@ -5535,7 +5461,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44752890776?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8AUojY9r82</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5548,7 +5474,6 @@
           <t>shopee_44752890776</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>9dacabc66036d8b166c7966b3ba15ba3</t>
@@ -5588,7 +5513,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/8300505418?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/80BOXFAUT1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5601,7 +5526,6 @@
           <t>shopee_8300505418</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>cdb3c601dc0868e36251dfd62b903624</t>
@@ -5641,7 +5565,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/21034391764?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/20uBODXKds</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5654,7 +5578,6 @@
           <t>shopee_21034391764</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>495c3576b40570d840f0e4d072c72d26</t>
@@ -5694,7 +5617,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/52152057334?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2BDbaWWhIv</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5707,7 +5630,6 @@
           <t>shopee_52152057334</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>951f1b565f395b5976e55d6ec6b07e39</t>
@@ -5747,7 +5669,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27706747428?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2LX1mpW3xy</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5760,7 +5682,6 @@
           <t>shopee_27706747428</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>1e95315b276ce63ffe9086121fe04fa9</t>
@@ -5800,7 +5721,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/23551902288?trace=%7B%22trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.8IZdau0GFKb.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2VqRz8VQd1</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5813,7 +5734,6 @@
           <t>shopee_23551902288</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>f5d8a9c8ad728ccf5535598d557aef72</t>
@@ -5836,7 +5756,6 @@
           <t>₫200.000</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>3k+</t>
@@ -5849,7 +5768,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42977051612?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1VxunIZEer</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5862,7 +5781,6 @@
           <t>shopee_42977051612</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>dbd9a9ba2e5f094ef6c519dfa9eb3af2</t>
@@ -5902,7 +5820,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26337641149?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1gHKzbYbJu</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5915,7 +5833,6 @@
           <t>shopee_26337641149</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>27e5ae00af0c1c8df0e0e6b150d4dc56</t>
@@ -5955,7 +5872,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/18144006340?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1qalBuXxyx</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5968,7 +5885,6 @@
           <t>shopee_18144006340</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>6eda20a4e830e6a8732947aefd89e735</t>
@@ -6008,7 +5924,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27907844567?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/gOnnlcPLk</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6021,7 +5937,6 @@
           <t>shopee_27907844567</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>7efa08cae8d3e7e707880fa076dd8ae9</t>
@@ -6061,7 +5976,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22732163462?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/qiE04bm0n</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6074,7 +5989,6 @@
           <t>shopee_22732163462</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>f19cf2e5742a72ae3cc5fce04ae20e62</t>
@@ -6114,7 +6028,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28818204493?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/111eCNb8fq</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6127,7 +6041,6 @@
           <t>shopee_28818204493</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>adf291487dc2a895e78c827d58e8477e</t>
@@ -6150,7 +6063,6 @@
           <t>₫429.000</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t xml:space="preserve">11 </t>
@@ -6163,7 +6075,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48206924962?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1BL4OgaVKt</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6176,7 +6088,6 @@
           <t>shopee_48206924962</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>f63ba553945656ebea53614801e64c5d</t>
@@ -6216,7 +6127,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28670254239?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/1970Xewhg</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6229,7 +6140,6 @@
           <t>shopee_28670254239</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>c0641d91a45dab55a0c42e201a104b39</t>
@@ -6269,7 +6179,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29550030387?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/BSXCqeJMj</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6282,7 +6192,6 @@
           <t>shopee_29550030387</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>30211b6208265d501ea299aba75d10e9</t>
@@ -6305,8 +6214,6 @@
           <t>₫356.000</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -6314,7 +6221,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50501303597?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/LlxP9dg1m</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6327,7 +6234,6 @@
           <t>shopee_50501303597</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>24ed9af980ec0f9808c91423629177a1</t>
@@ -6367,7 +6273,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29405257458?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/W5NbSd2gp</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6380,7 +6286,6 @@
           <t>shopee_29405257458</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>2e2f2342bb2a3d14d15830159a5ca43d</t>
@@ -6420,7 +6325,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29905169981?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4fuwZ7NBEe</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6433,7 +6338,6 @@
           <t>shopee_29905169981</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>943ad0064124e8383189c47d9438b71e</t>
@@ -6461,7 +6365,6 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>43,5%</t>
@@ -6469,7 +6372,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24476449221?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4qEMlQMXth</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6482,7 +6385,6 @@
           <t>shopee_24476449221</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>ee85c046c2aac41ce5d5736af9031876</t>
@@ -6505,8 +6407,6 @@
           <t>₫50.000</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -6514,7 +6414,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56801324918?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/50XmxjLuYk</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6527,7 +6427,6 @@
           <t>shopee_56801324918</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>5eb25e05ead35952a364b97c71270744</t>
@@ -6567,7 +6466,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24942159580?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5ArDA2LHDn</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6580,7 +6479,6 @@
           <t>shopee_24942159580</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>f542618bbc84e3e7e16e7b1bedade92e</t>
@@ -6620,7 +6518,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/21089968899?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/40fFltPiaa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6633,7 +6531,6 @@
           <t>shopee_21089968899</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>d1b11e1fbfc7a9fc5e82568b594016e1</t>
@@ -6673,7 +6570,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/20186938284?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4AyfyCP5Fd</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6686,7 +6583,6 @@
           <t>shopee_20186938284</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>501f5df183f0fbf762d9e977e7c711b9</t>
@@ -6709,7 +6605,6 @@
           <t>₫30.000</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t xml:space="preserve">196 </t>
@@ -6722,7 +6617,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27639086679?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4LI6AVORug</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6735,7 +6630,6 @@
           <t>shopee_27639086679</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>32f43d2e32e7029e46af981930318f7e</t>
@@ -6775,7 +6669,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22870283058?trace=%7B%22trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50fiCSY0JJp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4VbWMoNoZj</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6788,7 +6682,6 @@
           <t>shopee_22870283058</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>2065d9e1b9375f18deb271ca68ab52a6</t>
@@ -6841,7 +6734,6 @@
           <t>shopee_26671193851</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>476a780bcb6b273a2e15410bb5c59779</t>
@@ -6869,7 +6761,6 @@
           <t>20%</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -6890,7 +6781,6 @@
           <t>shopee_49761263683</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>ef47c0a0091be28cbd87707790f38cab</t>
@@ -6943,7 +6833,6 @@
           <t>shopee_22466400575</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>95ee8c3b64815f32a2aef4d98cfad3b7</t>
@@ -6996,7 +6885,6 @@
           <t>shopee_22876955030</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>561913646136774b13556bcda9b7e9aa</t>
@@ -7049,7 +6937,6 @@
           <t>shopee_28031106552</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>8ae9d98ee56a5902e44cd1d00e7ec5f8</t>
@@ -7072,7 +6959,6 @@
           <t>₫399.000</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>6k+</t>
@@ -7098,7 +6984,6 @@
           <t>shopee_24482376499</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>c7dbec252ef50f4f6b2ca7b2b9975276</t>
@@ -7151,7 +7036,6 @@
           <t>shopee_27908058153</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>e3a4450cf32030352794d32594b08e8b</t>
@@ -7204,7 +7088,6 @@
           <t>shopee_29951889800</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>57ea15dc74d1cec0632fa010c225190b</t>
@@ -7257,7 +7140,6 @@
           <t>shopee_53304499944</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>88bda96e14cc1ddd260b7e2d1ec63619</t>
@@ -7310,7 +7192,6 @@
           <t>shopee_57161457910</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>aecd3e3b92a69cce9a08c4ee44a7872e</t>
@@ -7363,7 +7244,6 @@
           <t>shopee_22247566032</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>10d1999cb5d2ee63aa1fd48a774c4517</t>
@@ -7416,7 +7296,6 @@
           <t>shopee_21316981412</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>9da2b21d568c951fc13ec59640c28ab5</t>
@@ -7469,7 +7348,6 @@
           <t>shopee_21587529485</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>35e49e91d61b5dcb9065d51dbb0758a2</t>
@@ -7492,7 +7370,6 @@
           <t>₫399.000</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>200k+</t>
@@ -7518,7 +7395,6 @@
           <t>shopee_23048465072</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>09e054aff7542e67d8007297b0f23d4b</t>
@@ -7541,7 +7417,6 @@
           <t>₫205.615</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>1k+</t>
@@ -7567,7 +7442,6 @@
           <t>shopee_41812351373</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>510afd16b80a5c9043692b780fec30b2</t>
@@ -7590,8 +7464,6 @@
           <t>₫338.000</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -7612,7 +7484,6 @@
           <t>shopee_55001547088</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>03eadf27c544b2e022f7da9d3bbabaea</t>
@@ -7665,7 +7536,6 @@
           <t>shopee_25873580719</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>3b6947ec4126f6eff02d2c94ca395f8d</t>
@@ -7718,7 +7588,6 @@
           <t>shopee_24626378450</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>d39b4c67291ab3c999a7c1120e92d2ec</t>
@@ -7758,7 +7627,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53262036720?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9fJcWMWM9W</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7771,7 +7640,6 @@
           <t>shopee_53262036720</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>16c6f74141f16a55f4991df348d414db</t>
@@ -7811,7 +7679,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26368401110?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9pd2ifVioZ</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7824,7 +7692,6 @@
           <t>shopee_26368401110</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>649869c9ee98e8a4f35d1a1879ec344d</t>
@@ -7864,7 +7731,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24715006419?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8fR5KWaABM</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7877,7 +7744,6 @@
           <t>shopee_24715006419</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>53e8e24b1e2b2566e39d316df2e53f24</t>
@@ -7917,7 +7783,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29330908242?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8pkVWpZWqP</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7930,7 +7796,6 @@
           <t>shopee_29330908242</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>7b5f2982b4b82daac0d6a0d7b3e125ab</t>
@@ -7970,7 +7835,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26609161628?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/903vj8YtVS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7983,7 +7848,6 @@
           <t>shopee_26609161628</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>7d9743e5e1856ab0d185694bb884a3b3</t>
@@ -8023,7 +7887,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44361887230?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/9ANLvRYGAV</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8036,7 +7900,6 @@
           <t>shopee_44361887230</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>59a4a273ac03deef5dcf4a911ab9ddf2</t>
@@ -8076,7 +7939,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/17478287414?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/80BOXIchXI</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8089,7 +7952,6 @@
           <t>shopee_17478287414</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>16d521c128e88b52999382482b222dae</t>
@@ -8129,7 +7991,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25025939212?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8KoEvubQrO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -8142,7 +8004,6 @@
           <t>shopee_25025939212</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>e18de07c7209bfa843deec2cb7b5fef4</t>
@@ -8182,7 +8043,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28283275690?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/8V7f8DanWR</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8195,7 +8056,6 @@
           <t>shopee_28283275690</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>b41323cb245f82f8a2f8537da1a7ebcd</t>
@@ -8235,7 +8095,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26380471027?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7Kvhk4fEtE</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -8248,7 +8108,6 @@
           <t>shopee_26380471027</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>7c295922148bdf86654db80928b26351</t>
@@ -8288,7 +8147,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22712863299?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7VF7wNebYH</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8301,7 +8160,6 @@
           <t>shopee_22712863299</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>9107e27b0192c1f62f3946118bbaf39a</t>
@@ -8341,7 +8199,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/43931508312?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7fYY8gdyDK</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8354,7 +8212,6 @@
           <t>shopee_43931508312</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>b31e4715bafc1d1b5083b295bdcf22e8</t>
@@ -8394,7 +8251,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28189555996?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7pryKzdKsN</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8407,7 +8264,6 @@
           <t>shopee_28189555996</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>73d048b0854caa7a91453bbd412a6387</t>
@@ -8447,7 +8303,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22467549746?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6fg0wqhmFA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8460,7 +8316,6 @@
           <t>shopee_22467549746</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>072f3de904828851673bcf7c418facd0</t>
@@ -8483,7 +8338,6 @@
           <t>₫188.000</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
           <t xml:space="preserve">1 </t>
@@ -8496,7 +8350,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29141056268?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6pzR99h8uD</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -8509,7 +8363,6 @@
           <t>shopee_29141056268</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>8edbc229f616139128ceedea60244c9d</t>
@@ -8532,8 +8385,6 @@
           <t>₫74.000</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -8541,7 +8392,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55601293829?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/70IrLSgVZG</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8554,7 +8405,6 @@
           <t>shopee_55601293829</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>aca9223f612b9ad64b14ec2a8aa285af</t>
@@ -8594,7 +8444,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25476379844?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/7AcHXlfsEJ</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8607,7 +8457,6 @@
           <t>shopee_25476379844</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>bdb82a8de1c2434f6dd8e3f1f958dd13</t>
@@ -8647,7 +8496,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29478583279?trace=%7B%22trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.50z9dVI5Gfp.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/60QK9ckJb6</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8660,7 +8509,6 @@
           <t>shopee_29478583279</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>21ea839067b4ba0fa3b97364e5d426f9</t>
@@ -8700,7 +8548,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28219551159?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6AjkLvjgG9</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8713,7 +8561,6 @@
           <t>shopee_28219551159</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>17ce2bb24934bd26fd2ba2c36f4e650b</t>
@@ -8736,8 +8583,6 @@
           <t>₫70.000</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>53,5%</t>
@@ -8745,7 +8590,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40326452239?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6L3AYEj2vC</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8758,7 +8603,6 @@
           <t>shopee_40326452239</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>71266b29f97fec9170f44031095cef83</t>
@@ -8798,7 +8642,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27723604940?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/6VMakXiPaF</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8811,7 +8655,6 @@
           <t>shopee_27723604940</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>d6db447ac80166fb5d0961c4e2c9d273</t>
@@ -8851,7 +8694,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24881878780?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5LAdMOmqx2</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8864,7 +8707,6 @@
           <t>shopee_24881878780</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>48ff58e514bdb34e2a41c60a8e792f8b</t>
@@ -8904,7 +8746,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50609103568?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5VU3YhmDc5</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8917,7 +8759,6 @@
           <t>shopee_50609103568</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>7324de2bad783a97ea0a646574095856</t>
@@ -8957,7 +8798,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/16177289192?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5q6txJkwwB</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8970,7 +8811,6 @@
           <t>shopee_16177289192</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>eae232afd049c80a2af240c5c3dd2bd3</t>
@@ -9010,7 +8850,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28204986393?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4fuwZApOIy</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9023,7 +8863,6 @@
           <t>shopee_28204986393</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>bd20df9adc0703b78a1c975ce4cdeee8</t>
@@ -9046,7 +8885,6 @@
           <t>₫1.827.000</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t xml:space="preserve">110 </t>
@@ -9059,7 +8897,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/12713806757?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4qEMlToky1</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9072,7 +8910,6 @@
           <t>shopee_12713806757</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>f12ebbeda1c1644d96b8391cb1e3bdba</t>
@@ -9112,7 +8949,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27355490606?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/50Xmxmo7d4</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9125,7 +8962,6 @@
           <t>shopee_27355490606</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>daf5f7f832e8f00563c4d964a7d4900b</t>
@@ -9165,7 +9001,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24541157970?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/5ArDA5nUI7</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9178,7 +9014,6 @@
           <t>shopee_24541157970</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>abc90d899bbec885e09125c44f741ac2</t>
@@ -9218,7 +9053,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29735213712?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/40fFlwrveu</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9231,7 +9066,6 @@
           <t>shopee_29735213712</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>61ac1c1d7e39b9eacf82290b7b470571</t>
@@ -9271,7 +9105,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25953042905?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4AyfyFrIJx</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9284,7 +9118,6 @@
           <t>shopee_25953042905</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>5e04773ba0117227bc8a1d7ba15f42e8</t>
@@ -9324,7 +9157,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27967005864?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/4LI6AYqez0</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -9337,7 +9170,6 @@
           <t>shopee_27967005864</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>27b9991b9b2186b758a765ce318f78cd</t>
@@ -9377,7 +9209,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24084775706?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3LPYyiuT0q</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -9390,7 +9222,6 @@
           <t>shopee_24084775706</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>6b9897edc010e2ac69c7176cd054dee4</t>
@@ -9430,7 +9261,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/57304427402?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3VizB1tpft</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -9443,7 +9274,6 @@
           <t>shopee_57304427402</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>d9c2a8b793544c048bf01c2e3aa0e293</t>
@@ -9483,7 +9313,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49611674735?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3g2PNKtCKw</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -9496,7 +9326,6 @@
           <t>shopee_49611674735</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
           <t>e39f48ef9f7296426b8e8f888947027c</t>
@@ -9536,7 +9365,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28944864596?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/3qLpZdsYzz</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9549,7 +9378,6 @@
           <t>shopee_28944864596</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>5ae8f6c88fbc3b0a1e3223a69bb0ed67</t>
@@ -9589,7 +9417,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29657463965?trace=%7B%22trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B473578%2C447104%2C568974%2C646439%2C712496%2C447311%2C516441%5D%2C%22root_trace_id%22%3A%220.1g9bBAauDwv.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://s.shopee.vn/2g9sBUx0Mm</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9602,7 +9430,6 @@
           <t>shopee_29657463965</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>882090caa8be3142d51cbb067685900a</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,946 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ba lô balo nữ Balo hai dây nam sức chứa lớn, balo công sở du lịch, balo đựng máy tính, balo leo núi, cặp sách cho học sinh cấp hai, cấp ba và sinh viên mới</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>₫406.080</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1Vy0J4aovB</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824he-mphj3jd8ghe795.webp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>shopee_43581717685</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>a19c668113d92115e35797b4a5937e66</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>balo nhỏ balo cho bé gái Cặp sách túi đi học nữ sinh đại học ba lô chống nước học sinh cấp 2 ba lô ba lô du lịch leo núi màu trơn phong cách Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>₫486.000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1gHQVNaBaE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gr-mpg9mvm0ssn63b.webp</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>shopee_55562188110</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>34435c447873629ead327f2be54813b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>balo đi học balo hello kitty Ba lô nhỏ đầy màu sắc dành cho Xiaomi, ba lô thể thao du lịch thường ngày nam nữ 20 lít, ba lô cặp sách chống nước</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>₫441.720</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1qaqhgZYFH</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gs-mpgiy09gklxq09.webp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>shopee_57112205850</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>54d878c6c65625fc02a00b34e30d3c12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>balo nữ hàn quốc balo đi học Cặp sách ba lô nữ sinh học sinh tiểu học ba lô dung tích lớn phong cách học đường giá trị cao ba lô dễ phối dễ thương cho bé gái</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>₫231.120</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/20uGtzYuuK</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8259j-mqbo8qvobtvy12.webp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>shopee_46513834378</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6dccc799e89677a3b8a91dc9dcb585c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>balo da nữ balo học sinh cấp 2 Balo sọc xanh sữa bạc hà ba lô búp bê táo sang trọng trái tim thiếu nữ đáng yêu ba lô quà tặng cặp sách học sinh</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>₫319.680</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2BDh6IYHZN</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gv-mpgcomu01z4b60.webp</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>shopee_29495051765</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>f3a841a3c0957cd70fa49d3ccef86a06</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>balo nữ cặp sách nữ Cặp sách trong suốt mẫu mới 2023 ba lô thoáng khí học sinh trung học nữ ba lô nam trung học màu hồng xanh lá cây ba lô du lịch</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>₫449.280</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2LX7IbXeEQ</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i8-mphi79coqk245c.webp</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>shopee_46162260924</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6a56f947a0131e736ae385e94fd682de</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cặp sách cho bé lớp 1 ba lô Balo nữ phong cách sóng chấm bi ba lô nữ nhỏ ba lô du lịch học sinh đáng yêu mẫu mới mùa xuân 2026 cặp sách nhỏ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>₫439.560</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2VqXUuX0tT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j1-mpgg0qfn8um9bc.webp</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>shopee_42181702947</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3e694351ee8088216a2e44475e09884f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>balo nữ hàn quốc balo đi học Ba lô nữ có giá trị cao cho học sinh trung học cơ sở mẫu mới ba lô thường ngày thời trang học sinh trung học ba lô túi máy tính cặp sách nam</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>₫461.160</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/19CWJgWy0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ah-mqj2yz9kxo1t5a.webp</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>shopee_57213814691</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>12ce00c571c0b8c4cb1f0a3e9e7504ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>balo học sinh cấp 2 balo đi học Cặp sách có thể giấu đồ, ba lô nữ phong cách Mori, ba lô dung tích lớn dành cho học sinh trung học cơ sở và trung học phổ thông phiên bản Hàn Quốc, ba lô màu tương phản</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₫552.960</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/BScicftd3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8258t-mqj3s80qcw7g6d.webp</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>shopee_43132502044</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>86734ce868b965f11b930b3e43b25e2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>balo cho bé gái balo học sinh cấp 2 Túi du lịch cặp sách học sinh dung tích lớn ba lô trường tiểu học ba lô trường trung học ba lô nam nữ đơn giản túi máy tính kinh doanh</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₫406.080</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/Lm2uvfGI6</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824if-mpghprn6rgu97e.webp</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>shopee_45512220556</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>068ebd4b7dcd40c730b6824c1a132f90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ba lô balo da nữ Trẻ em ngày trẻ em bút chì mới cặp sách kt mèo ba lô ba lô trẻ em mẫu giáo bé gái ba lô dây rút túi đau</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>₫264.600</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/W5T7Eecx9</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j7-mpgmu3ixwe0w27.webp</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>shopee_53612210400</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6f38ca329b74eaeae813ba5b09e934fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>balo cho bé trai balo da Ba lô hai vai ba lô du lịch thời trang instagram có thể cầm tay đơn giản sức chứa lớn mẫu mới cho nữ ba lô gọn nhẹ cặp sách</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>₫246.240</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/gOtJXdzcC</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824il-mpgf6xsmf0um55.webp</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>shopee_45712209882</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>26bed99f3e2953b9b4655506074f1437</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>balo học sinh cấp 2 balo đi học Cặp sách học sinh ba lô cá tính thời trang phong cách Hàn Quốc cho nữ học sinh trung học ba lô đi học dễ phối đồ học sinh tiểu học ba lô du lịch dung tích lớn túi ni lông trường học ngoại khóa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>₫459.000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/qiJVqdMHF</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ad-mqj4bslj1l3fff.webp</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>shopee_44963847577</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>69fbfad24c101b9fb1a3655e594eaf2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>cặp sách cho bé lớp 1 cặp sách nữ Ba lô mini ba lô táo đỏ đáng yêu nữ ba lô hoạt hình Nhật Bản túi vải nhỏ kiểu tây ba lô học sinh</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>₫375.840</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/111ji9ciwI</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gl-mpgc6zz301sbc8.webp</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>shopee_42581705612</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5794aafc81d054d2152cc6f6f3588399</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>balo hello kitty balo học sinh Ba lô học sinh đại học dung tích lớn thoải mái Hàn Quốc ba lô học sinh trung học nữ ba lô cặp sách hình vịt hoạt hình dễ thương dễ thương</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>₫403.920</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1BL9uSc5bL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgf8d61jb4b2d.webp</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>shopee_47862218379</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fa30ebfee016a53d0f28e79b7fbd8919</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sẵn💝Balo đi học nữ, cặp sách nữ basic, balo laptop 14inch, balo chống thấm, cặp đi học hàn quốc, balo thời trang SIÊU RẺ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>₫240.000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/40fLHfRIqu</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mi4533uwkpvrf3.webp</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>shopee_27562400542</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5f9c2c15a47c3763a333e24aac9f5902</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>balo nhỏ balo hello kitty Ba lô đơn giản, túi khiêu vũ, ba lô hai dây, thiết kế bắt mắt, nhẹ gọn phù hợp học đường, cặp sách cho học sinh cấp hai và cấp ba, dễ phối đồ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>₫402.840</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4AylTyQfVx</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i3-mphm3qwfng1u11.webp</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>shopee_47862271030</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>bebd98cd961d7c5870d10a4d6ced6e5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>balo balo nữ hàn quốc Ba lô đeo hai vai cho nam, túi du lịch công sở sức chứa lớn, ba lô đựng máy tính thời trang sành điệu, cặp sách học sinh cấp hai, cấp ba và sinh viên</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>₫338.040</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4LIBgHQ2B0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gb-mpgmfmcey8zkd4.webp</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>shopee_45262235420</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>caf40f77cf658483280c372f312e3d1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>balo nữ balo da Balo nhỏ dễ thương phong cách ins kiểu Nhật dành cho nữ; cặp sách học sinh cấp hai; balo du lịch đeo hai dây nhẹ nhàng cho học sinh cấp ba</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>₫384.480</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4VbbsaPOq3</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgkad9m04cifb.webp</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>shopee_44081706775</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>d9923c72e24f554ec9f07147ab2d3589</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>balo cho bé trai balo Cặp sách màu trơn dung tích lớn phong cách Hàn Quốc tối giản, balo hai dây nam nữ học sinh cấp hai – cấp ba kiểu dáng bắt mắt, balo thường ngày</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>₫502.200</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4fv24tOlV6</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824h4-mphnn9kn0mbl92.webp</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>shopee_49562263043</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>45b2ea36dd9337286eb82a8a84eca91c</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,17 +622,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>balo nữ hàn quốc balo đi học Cặp sách ba lô nữ sinh học sinh tiểu học ba lô dung tích lớn phong cách học đường giá trị cao ba lô dễ phối dễ thương cho bé gái</t>
+          <t>balo da nữ balo học sinh cấp 2 Balo sọc xanh sữa bạc hà ba lô búp bê táo sang trọng trái tim thiếu nữ đáng yêu ba lô quà tặng cặp sách học sinh</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫231.120</t>
+          <t>₫319.680</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -642,22 +642,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20uGtzYuuK</t>
+          <t>https://s.shopee.vn/2BDh6IYHZN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8259j-mqbo8qvobtvy12.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gv-mpgcomu01z4b60.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_46513834378</t>
+          <t>shopee_29495051765</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6dccc799e89677a3b8a91dc9dcb585c2</t>
+          <t>f3a841a3c0957cd70fa49d3ccef86a06</t>
         </is>
       </c>
     </row>
@@ -669,12 +669,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>balo da nữ balo học sinh cấp 2 Balo sọc xanh sữa bạc hà ba lô búp bê táo sang trọng trái tim thiếu nữ đáng yêu ba lô quà tặng cặp sách học sinh</t>
+          <t>balo nữ cặp sách nữ Cặp sách trong suốt mẫu mới 2023 ba lô thoáng khí học sinh trung học nữ ba lô nam trung học màu hồng xanh lá cây ba lô du lịch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫319.680</t>
+          <t>₫449.280</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -689,22 +689,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDh6IYHZN</t>
+          <t>https://s.shopee.vn/2LX7IbXeEQ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gv-mpgcomu01z4b60.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i8-mphi79coqk245c.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_29495051765</t>
+          <t>shopee_46162260924</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>f3a841a3c0957cd70fa49d3ccef86a06</t>
+          <t>6a56f947a0131e736ae385e94fd682de</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>balo nữ cặp sách nữ Cặp sách trong suốt mẫu mới 2023 ba lô thoáng khí học sinh trung học nữ ba lô nam trung học màu hồng xanh lá cây ba lô du lịch</t>
+          <t>cặp sách cho bé lớp 1 ba lô Balo nữ phong cách sóng chấm bi ba lô nữ nhỏ ba lô du lịch học sinh đáng yêu mẫu mới mùa xuân 2026 cặp sách nhỏ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫449.280</t>
+          <t>₫439.560</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -736,22 +736,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LX7IbXeEQ</t>
+          <t>https://s.shopee.vn/2VqXUuX0tT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i8-mphi79coqk245c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j1-mpgg0qfn8um9bc.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_46162260924</t>
+          <t>shopee_42181702947</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6a56f947a0131e736ae385e94fd682de</t>
+          <t>3e694351ee8088216a2e44475e09884f</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cặp sách cho bé lớp 1 ba lô Balo nữ phong cách sóng chấm bi ba lô nữ nhỏ ba lô du lịch học sinh đáng yêu mẫu mới mùa xuân 2026 cặp sách nhỏ</t>
+          <t>balo cho bé gái balo học sinh cấp 2 Túi du lịch cặp sách học sinh dung tích lớn ba lô trường tiểu học ba lô trường trung học ba lô nam nữ đơn giản túi máy tính kinh doanh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫439.560</t>
+          <t>₫406.080</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -783,22 +783,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2VqXUuX0tT</t>
+          <t>https://s.shopee.vn/Lm2uvfGI6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j1-mpgg0qfn8um9bc.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824if-mpghprn6rgu97e.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_42181702947</t>
+          <t>shopee_45512220556</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3e694351ee8088216a2e44475e09884f</t>
+          <t>068ebd4b7dcd40c730b6824c1a132f90</t>
         </is>
       </c>
     </row>
@@ -810,17 +810,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>balo nữ hàn quốc balo đi học Ba lô nữ có giá trị cao cho học sinh trung học cơ sở mẫu mới ba lô thường ngày thời trang học sinh trung học ba lô túi máy tính cặp sách nam</t>
+          <t>ba lô balo da nữ Trẻ em ngày trẻ em bút chì mới cặp sách kt mèo ba lô ba lô trẻ em mẫu giáo bé gái ba lô dây rút túi đau</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫461.160</t>
+          <t>₫264.600</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -830,22 +830,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/19CWJgWy0</t>
+          <t>https://s.shopee.vn/W5T7Eecx9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ah-mqj2yz9kxo1t5a.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j7-mpgmu3ixwe0w27.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_57213814691</t>
+          <t>shopee_53612210400</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12ce00c571c0b8c4cb1f0a3e9e7504ca</t>
+          <t>6f38ca329b74eaeae813ba5b09e934fc</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>balo học sinh cấp 2 balo đi học Cặp sách có thể giấu đồ, ba lô nữ phong cách Mori, ba lô dung tích lớn dành cho học sinh trung học cơ sở và trung học phổ thông phiên bản Hàn Quốc, ba lô màu tương phản</t>
+          <t>balo cho bé trai balo da Ba lô hai vai ba lô du lịch thời trang instagram có thể cầm tay đơn giản sức chứa lớn mẫu mới cho nữ ba lô gọn nhẹ cặp sách</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫552.960</t>
+          <t>₫246.240</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -877,22 +877,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BScicftd3</t>
+          <t>https://s.shopee.vn/gOtJXdzcC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8258t-mqj3s80qcw7g6d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824il-mpgf6xsmf0um55.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_43132502044</t>
+          <t>shopee_45712209882</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>86734ce868b965f11b930b3e43b25e2c</t>
+          <t>26bed99f3e2953b9b4655506074f1437</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>balo cho bé gái balo học sinh cấp 2 Túi du lịch cặp sách học sinh dung tích lớn ba lô trường tiểu học ba lô trường trung học ba lô nam nữ đơn giản túi máy tính kinh doanh</t>
+          <t>balo hello kitty balo học sinh Ba lô học sinh đại học dung tích lớn thoải mái Hàn Quốc ba lô học sinh trung học nữ ba lô cặp sách hình vịt hoạt hình dễ thương dễ thương</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫406.080</t>
+          <t>₫403.920</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -924,22 +924,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/Lm2uvfGI6</t>
+          <t>https://s.shopee.vn/1BL9uSc5bL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824if-mpghprn6rgu97e.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgf8d61jb4b2d.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_45512220556</t>
+          <t>shopee_47862218379</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>068ebd4b7dcd40c730b6824c1a132f90</t>
+          <t>fa30ebfee016a53d0f28e79b7fbd8919</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ba lô balo da nữ Trẻ em ngày trẻ em bút chì mới cặp sách kt mèo ba lô ba lô trẻ em mẫu giáo bé gái ba lô dây rút túi đau</t>
+          <t>balo nhỏ balo hello kitty Ba lô đơn giản, túi khiêu vũ, ba lô hai dây, thiết kế bắt mắt, nhẹ gọn phù hợp học đường, cặp sách cho học sinh cấp hai và cấp ba, dễ phối đồ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫264.600</t>
+          <t>₫402.840</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W5T7Eecx9</t>
+          <t>https://s.shopee.vn/4AylTyQfVx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j7-mpgmu3ixwe0w27.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i3-mphm3qwfng1u11.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_53612210400</t>
+          <t>shopee_47862271030</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6f38ca329b74eaeae813ba5b09e934fc</t>
+          <t>bebd98cd961d7c5870d10a4d6ced6e5e</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>balo cho bé trai balo da Ba lô hai vai ba lô du lịch thời trang instagram có thể cầm tay đơn giản sức chứa lớn mẫu mới cho nữ ba lô gọn nhẹ cặp sách</t>
+          <t>balo balo nữ hàn quốc Ba lô đeo hai vai cho nam, túi du lịch công sở sức chứa lớn, ba lô đựng máy tính thời trang sành điệu, cặp sách học sinh cấp hai, cấp ba và sinh viên</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫246.240</t>
+          <t>₫338.040</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/gOtJXdzcC</t>
+          <t>https://s.shopee.vn/4LIBgHQ2B0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824il-mpgf6xsmf0um55.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gb-mpgmfmcey8zkd4.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_45712209882</t>
+          <t>shopee_45262235420</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>26bed99f3e2953b9b4655506074f1437</t>
+          <t>caf40f77cf658483280c372f312e3d1c</t>
         </is>
       </c>
     </row>
@@ -1045,17 +1045,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>balo học sinh cấp 2 balo đi học Cặp sách học sinh ba lô cá tính thời trang phong cách Hàn Quốc cho nữ học sinh trung học ba lô đi học dễ phối đồ học sinh tiểu học ba lô du lịch dung tích lớn túi ni lông trường học ngoại khóa</t>
+          <t>balo nữ balo da Balo nhỏ dễ thương phong cách ins kiểu Nhật dành cho nữ; cặp sách học sinh cấp hai; balo du lịch đeo hai dây nhẹ nhàng cho học sinh cấp ba</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫459.000</t>
+          <t>₫384.480</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/qiJVqdMHF</t>
+          <t>https://s.shopee.vn/4VbbsaPOq3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ad-mqj4bslj1l3fff.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgkad9m04cifb.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_44963847577</t>
+          <t>shopee_44081706775</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>69fbfad24c101b9fb1a3655e594eaf2d</t>
+          <t>d9923c72e24f554ec9f07147ab2d3589</t>
         </is>
       </c>
     </row>
@@ -1092,17 +1092,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cặp sách cho bé lớp 1 cặp sách nữ Ba lô mini ba lô táo đỏ đáng yêu nữ ba lô hoạt hình Nhật Bản túi vải nhỏ kiểu tây ba lô học sinh</t>
+          <t>balo cho bé trai balo Cặp sách màu trơn dung tích lớn phong cách Hàn Quốc tối giản, balo hai dây nam nữ học sinh cấp hai – cấp ba kiểu dáng bắt mắt, balo thường ngày</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫375.840</t>
+          <t>₫502.200</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1112,22 +1112,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/111ji9ciwI</t>
+          <t>https://s.shopee.vn/4fv24tOlV6</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gl-mpgc6zz301sbc8.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824h4-mphnn9kn0mbl92.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_42581705612</t>
+          <t>shopee_49562263043</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5794aafc81d054d2152cc6f6f3588399</t>
+          <t>45b2ea36dd9337286eb82a8a84eca91c</t>
         </is>
       </c>
     </row>
@@ -1139,17 +1139,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>balo hello kitty balo học sinh Ba lô học sinh đại học dung tích lớn thoải mái Hàn Quốc ba lô học sinh trung học nữ ba lô cặp sách hình vịt hoạt hình dễ thương dễ thương</t>
+          <t>balo nữ hàn quốc balo đi học Cặp sách ba lô nữ sinh học sinh tiểu học ba lô dung tích lớn phong cách học đường giá trị cao ba lô dễ phối dễ thương cho bé gái</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫403.920</t>
+          <t>₫231.120</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1BL9uSc5bL</t>
+          <t>https://s.shopee.vn/20uGtzYuuK</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgf8d61jb4b2d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8259j-mqbo8qvobtvy12.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_47862218379</t>
+          <t>shopee_46513834378</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fa30ebfee016a53d0f28e79b7fbd8919</t>
+          <t>6dccc799e89677a3b8a91dc9dcb585c2</t>
         </is>
       </c>
     </row>
@@ -1186,42 +1186,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sẵn💝Balo đi học nữ, cặp sách nữ basic, balo laptop 14inch, balo chống thấm, cặp đi học hàn quốc, balo thời trang SIÊU RẺ</t>
+          <t>balo nữ hàn quốc balo đi học Ba lô nữ có giá trị cao cho học sinh trung học cơ sở mẫu mới ba lô thường ngày thời trang học sinh trung học ba lô túi máy tính cặp sách nam</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫240.000</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2k+</t>
+          <t>₫461.160</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40fLHfRIqu</t>
+          <t>https://s.shopee.vn/19CWJgWy0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mi4533uwkpvrf3.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ah-mqj2yz9kxo1t5a.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_27562400542</t>
+          <t>shopee_57213814691</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5f9c2c15a47c3763a333e24aac9f5902</t>
+          <t>12ce00c571c0b8c4cb1f0a3e9e7504ca</t>
         </is>
       </c>
     </row>
@@ -1233,17 +1233,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>balo nhỏ balo hello kitty Ba lô đơn giản, túi khiêu vũ, ba lô hai dây, thiết kế bắt mắt, nhẹ gọn phù hợp học đường, cặp sách cho học sinh cấp hai và cấp ba, dễ phối đồ</t>
+          <t>balo học sinh cấp 2 balo đi học Cặp sách có thể giấu đồ, ba lô nữ phong cách Mori, ba lô dung tích lớn dành cho học sinh trung học cơ sở và trung học phổ thông phiên bản Hàn Quốc, ba lô màu tương phản</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫402.840</t>
+          <t>₫552.960</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4AylTyQfVx</t>
+          <t>https://s.shopee.vn/BScicftd3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i3-mphm3qwfng1u11.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8258t-mqj3s80qcw7g6d.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_47862271030</t>
+          <t>shopee_43132502044</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>bebd98cd961d7c5870d10a4d6ced6e5e</t>
+          <t>86734ce868b965f11b930b3e43b25e2c</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>balo balo nữ hàn quốc Ba lô đeo hai vai cho nam, túi du lịch công sở sức chứa lớn, ba lô đựng máy tính thời trang sành điệu, cặp sách học sinh cấp hai, cấp ba và sinh viên</t>
+          <t>balo học sinh cấp 2 balo đi học Cặp sách học sinh ba lô cá tính thời trang phong cách Hàn Quốc cho nữ học sinh trung học ba lô đi học dễ phối đồ học sinh tiểu học ba lô du lịch dung tích lớn túi ni lông trường học ngoại khóa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫338.040</t>
+          <t>₫459.000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1300,22 +1300,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LIBgHQ2B0</t>
+          <t>https://s.shopee.vn/qiJVqdMHF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gb-mpgmfmcey8zkd4.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ad-mqj4bslj1l3fff.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_45262235420</t>
+          <t>shopee_44963847577</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>caf40f77cf658483280c372f312e3d1c</t>
+          <t>69fbfad24c101b9fb1a3655e594eaf2d</t>
         </is>
       </c>
     </row>
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>balo nữ balo da Balo nhỏ dễ thương phong cách ins kiểu Nhật dành cho nữ; cặp sách học sinh cấp hai; balo du lịch đeo hai dây nhẹ nhàng cho học sinh cấp ba</t>
+          <t>cặp sách cho bé lớp 1 cặp sách nữ Ba lô mini ba lô táo đỏ đáng yêu nữ ba lô hoạt hình Nhật Bản túi vải nhỏ kiểu tây ba lô học sinh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫384.480</t>
+          <t>₫375.840</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1347,22 +1347,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4VbbsaPOq3</t>
+          <t>https://s.shopee.vn/111ji9ciwI</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgkad9m04cifb.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gl-mpgc6zz301sbc8.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_44081706775</t>
+          <t>shopee_42581705612</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>d9923c72e24f554ec9f07147ab2d3589</t>
+          <t>5794aafc81d054d2152cc6f6f3588399</t>
         </is>
       </c>
     </row>
@@ -1374,42 +1374,1078 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>balo cho bé trai balo Cặp sách màu trơn dung tích lớn phong cách Hàn Quốc tối giản, balo hai dây nam nữ học sinh cấp hai – cấp ba kiểu dáng bắt mắt, balo thường ngày</t>
+          <t>Sẵn💝Balo đi học nữ, cặp sách nữ basic, balo laptop 14inch, balo chống thấm, cặp đi học hàn quốc, balo thời trang SIÊU RẺ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫502.200</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>₫240.000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/40fLHfRIqu</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mi4533uwkpvrf3.webp</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>shopee_27562400542</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5f9c2c15a47c3763a333e24aac9f5902</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tấm lót đáy balo hổ trợ giảm mất form, giảm xụ phần đáy balo cặp sách khi đựng sách vở laptop nặng</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>₫35.000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>40k+</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22931544947?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfngwemcu6fc39.webp</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>shopee_22931544947</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>4c1404834ecc6a9c4dfd7b3f1ffdde3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Balo cho bé KNOTE cặp sách cấp 1 2 chất liệu vải sức chứa lớn kiểu dáng dễ thương dày dặn chống nước</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>₫329.000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27022611207?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4lh3n33z52oa2.webp</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>shopee_27022611207</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ec692d7a008482c100513fc23a742d29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BAGSMART Ba Lô Thường Ngày Du Lịch 14.3inch Ba Lô Laptop Daypack SchoolBag Cao Đẳng Túi Đựng Sách Làm Việc Mặt Sau Máy Tính Dễ Thương Chống Nước</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>₫586.280</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43556339364?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-820l4-mq1nly9hts018a.webp</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>shopee_43556339364</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ac48e54041e1cdc1480c78e7c8370856</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Móc khóa TÊN theo yêu cầu, thẻ tên treo balo, cặp sách, nametag cho bé 18K</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>₫19.800</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45356600205?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpp6sa7xpiq592.webp</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>shopee_45356600205</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>b0c27bd15cdc9e0634d4b83d47d7c4c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Balo đi học Ulzzang Hàn Quốc trơn basic nam nữ cặp sách đi chơi du lịch thời trang Unisex BL03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>₫115.000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">872 </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/20977181092?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqyccmr0pqti51.webp</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>shopee_20977181092</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>bf28e8a630ff63486d985a7d2f054f1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Balo cho bé mẫu giáo bé trai bé gái, cặp sách trẻ em mầm non đi học từ 2–5 tuổi hoạt hình dễ thương</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>₫59.000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">755 </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/13187078063?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m39yvtz753gc26.webp</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>shopee_13187078063</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2d7286552ad3ca83a40b81a325bcc370</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Móc khoá gấu bông cute treo balo cặp sách ml01 ( KHÔNG KÊU BÍP BÍP)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>₫13.000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28319432367?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m3aebdqnwrss1b.webp</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>shopee_28319432367</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>4a6379b8754508b0ad828f255ab3ffcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Balo đi học nam nữ Cặp đi học unisex nhiều ngăn chống nước Luci Bag cặp sách đựng vừa laptop 15,6 inch basic B50</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>₫220.000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42151531320?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpz4z6mdgavg19.webp</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>shopee_42151531320</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>6beca9328f8d8243e7e7689d147f535d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Móc khoá bông con mèo đáng yêu treo ba lo cặp sách ga12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>₫20.000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28719290302?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m37n8pbmdgx82c.webp</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>shopee_28719290302</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>94a70a6072279569b2adf47f4862ef08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Balo da đi học nam nữ, balo da nhiều ngăn đi học đi chơi, cặp sách nữ thời trang, ba lô chống nước BL13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">580 </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56263034976?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq1toufns5xqe5.webp</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>shopee_56263034976</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>a4b9f909bc4490bc5500660fee713ea0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Balo nữ đi học thời trang hàn quốc,cặp sách đi học nữ dễ thương, Balo ulzzang nhiều ngăn chống nước</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>₫279.000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28402501227?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwx4dfpz853td0.webp</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>shopee_28402501227</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7b0200a706275c55ba0ff6fd8a228be8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Móc khoá búp bê treo balo cặp sách phụ kiện quà tặng (KHÔNG CÓ PHỤ KIỆN ) mq03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>₫23.000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">498 </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24415449457?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lt4rfgr2hu3da9.webp</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>shopee_24415449457</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>76f2642c874c7842bafce370a0ed0cca</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Móc treo ba lô, cặp sách hai đầu bằng thép không gỉ – móc treo bên cạnh bàn làm việc, bàn học – có thể tháo rời</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>₫14.799</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>9k+</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25597309034?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfdsynptw1e2db.webp</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>shopee_25597309034</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>970a3ab9a1d51ee6e7d60aa6bce8180e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Balo nữ cặp đi học nam nữ GUZI BAG cặp sách nam nữ thời trang basic đơn giản họa tiết ngôi sao BL08 SLEEPYCHIC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>₫170.000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">506 </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42301614689?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-ma0syy5ii2jyc8.webp</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>shopee_42301614689</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>e65fbda291be3d81b26f4e76a1f77523</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Balo cho bé BABYTREE cặp sách trẻ em chống gù lưng chất liệu cao cấp nhiều ngăn đa dạng màu sắc</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>₫329.000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">376 </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28580011314?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7ho5s8f22k6e0.webp</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>shopee_28580011314</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>7fc1214b5a8dd6dedcc8cfdb811729bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù Thẻ Hình Kurumi Cho Bé Trai Gái Chống Nước Ba lô cấp 1 ( bé lớp 2-6) Cặp Sách Học Sinh Tiểu Học</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>₫170.000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24341874090?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m6o43wxx3b6g3f.webp</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>shopee_24341874090</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>44be2ce255f511ab666351b32b43ffa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cặp sách đi học cấp 2, cấp 3 NATOLI Cặp đa năng, Balo đa năng nhiều ngăn BST Classic Multifunctional Backpack B17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>₫459.000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">414 </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24182570256?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqzz2dv7rbwhcf.webp</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>shopee_24182570256</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0dcaa35f40ce9f4b9e8ee68ae8be92db</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>COMBO 5 khoá cài, khoá mũ bảo hiểm, balo, cặp sách 2cm, 2,5cm (Đo lọt lòng)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>₫12.000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29201991132?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwbh3d386b4r4c.webp</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>shopee_29201991132</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>6e785e5c26dbb055187668758dd780aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Móc khoá gấu má hồng treo balo cặp sách thời trang ga21</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>₫16.000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">338 </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24100652843?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rbn3-lnbp3sjycl4ha5.webp</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>shopee_24100652843</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4d52e7b788164b03a697159b70b57566</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Balo Đi Học Cho Bé Cấp 1 Tiểu Học Dễ Thương Chống Gù - Cặp Sách Học Sinh Capybara Kuromi Melody Tặng Kèm Móc Khóa</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>₫209.000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://s.shopee.vn/4fv24tOlV6</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824h4-mphnn9kn0mbl92.webp</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>shopee_49562263043</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>45b2ea36dd9337286eb82a8a84eca91c</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255 </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41053739148?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqqw2ykedpfnec.webp</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>shopee_41053739148</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>76dee7e7a569419eb92454e88ce26ae7</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Vy0J4aovB</t>
+          <t>https://s.shopee.vn/AAFydeRGZJ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gHQVNaBaE</t>
+          <t>https://s.shopee.vn/AKZOpxQdEM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qaqhgZYFH</t>
+          <t>https://s.shopee.vn/AUsp2GPztP</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDh6IYHZN</t>
+          <t>https://s.shopee.vn/8AUuFyYscz</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LX7IbXeEQ</t>
+          <t>https://s.shopee.vn/8KoKSHYFI2</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2VqXUuX0tT</t>
+          <t>https://s.shopee.vn/8V7keaXbx5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/Lm2uvfGI6</t>
+          <t>https://s.shopee.vn/9041FVVhwE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W5T7Eecx9</t>
+          <t>https://s.shopee.vn/9ANRRoV4bH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/gOtJXdzcC</t>
+          <t>https://s.shopee.vn/1Lea7PytUm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1BL9uSc5bL</t>
+          <t>https://s.shopee.vn/1qaqiKwzTv</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4AylTyQfVx</t>
+          <t>https://s.shopee.vn/2BDh6wvio1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LIBgHQ2B0</t>
+          <t>https://s.shopee.vn/2LX7JFv5T4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4VbbsaPOq3</t>
+          <t>https://s.shopee.vn/2VqXVYuS87</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4fv24tOlV6</t>
+          <t>https://s.shopee.vn/19CWy3yCe</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20uGtzYuuK</t>
+          <t>https://s.shopee.vn/80BU3fZVxw</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/19CWJgWy0</t>
+          <t>https://s.shopee.vn/8fRAqtWyc8</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BScicftd3</t>
+          <t>https://s.shopee.vn/8pkb3CWLHB</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/qiJVqdMHF</t>
+          <t>https://s.shopee.vn/1Vy0JiyG9p</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/111ji9ciwI</t>
+          <t>https://s.shopee.vn/1gHQW1xcos</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">118 </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40fLHfRIqu</t>
+          <t>https://s.shopee.vn/20uGudwM8y</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5f9c2c15a47c3763a333e24aac9f5902</t>
+          <t>72105f7344fdd7d1ccf0ef6cdc956747</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22931544947?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/BScjH3Krh</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1459,7 +1459,6 @@
           <t>shopee_22931544947</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>4c1404834ecc6a9c4dfd7b3f1ffdde3f</t>
@@ -1499,7 +1498,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27022611207?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/Lm2va2hWk</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1512,7 +1511,6 @@
           <t>shopee_27022611207</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>ec692d7a008482c100513fc23a742d29</t>
@@ -1552,7 +1550,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/43556339364?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/W5T7t24Bn</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1565,7 +1563,6 @@
           <t>shopee_43556339364</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>ac48e54041e1cdc1480c78e7c8370856</t>
@@ -1588,7 +1585,6 @@
           <t>₫19.800</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>1k+</t>
@@ -1601,7 +1597,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45356600205?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/gOtKC1Qqq</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1614,7 +1610,6 @@
           <t>shopee_45356600205</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>b0c27bd15cdc9e0634d4b83d47d7c4c2</t>
@@ -1654,7 +1649,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/20977181092?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/qiJWV0nVt</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1667,7 +1662,6 @@
           <t>shopee_20977181092</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>bf28e8a630ff63486d985a7d2f054f1c</t>
@@ -1707,7 +1701,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/13187078063?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/111jio0AAw</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1720,7 +1714,6 @@
           <t>shopee_13187078063</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>2d7286552ad3ca83a40b81a325bcc370</t>
@@ -1743,7 +1736,6 @@
           <t>₫13.000</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>4k+</t>
@@ -1756,7 +1748,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28319432367?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1BL9v6zWpz</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1769,7 +1761,6 @@
           <t>shopee_28319432367</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>4a6379b8754508b0ad828f255ab3ffcf</t>
@@ -1809,7 +1800,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42151531320?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/40fLIJok5Y</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1822,7 +1813,6 @@
           <t>shopee_42151531320</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>6beca9328f8d8243e7e7689d147f535d</t>
@@ -1845,7 +1835,6 @@
           <t>₫20.000</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>2k+</t>
@@ -1858,7 +1847,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28719290302?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4AylUco6kb</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1871,7 +1860,6 @@
           <t>shopee_28719290302</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>94a70a6072279569b2adf47f4862ef08</t>
@@ -1911,7 +1899,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56263034976?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4LIBgvnTPe</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1924,7 +1912,6 @@
           <t>shopee_56263034976</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>a4b9f909bc4490bc5500660fee713ea0</t>
@@ -1964,7 +1951,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28402501227?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4VbbtEmq4h</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1977,7 +1964,6 @@
           <t>shopee_28402501227</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>7b0200a706275c55ba0ff6fd8a228be8</t>
@@ -2000,7 +1986,6 @@
           <t>₫23.000</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t xml:space="preserve">498 </t>
@@ -2013,7 +1998,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24415449457?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4fv25XmCjk</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2026,7 +2011,6 @@
           <t>shopee_24415449457</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>76f2642c874c7842bafce370a0ed0cca</t>
@@ -2066,7 +2050,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25597309034?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4qESHqlZOn</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2079,7 +2063,6 @@
           <t>shopee_25597309034</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>970a3ab9a1d51ee6e7d60aa6bce8180e</t>
@@ -2119,7 +2102,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42301614689?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/50XsU9kw3q</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2132,7 +2115,6 @@
           <t>shopee_42301614689</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>e65fbda291be3d81b26f4e76a1f77523</t>
@@ -2172,7 +2154,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28580011314?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5ArIgSkIit</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2185,7 +2167,6 @@
           <t>shopee_28580011314</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>7fc1214b5a8dd6dedcc8cfdb811729bd</t>
@@ -2225,7 +2206,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24341874090?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2g9xhrtonQ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2238,7 +2219,6 @@
           <t>shopee_24341874090</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>44be2ce255f511ab666351b32b43ffa1</t>
@@ -2278,7 +2258,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24182570256?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2qTNuAtBST</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2291,7 +2271,6 @@
           <t>shopee_24182570256</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>0dcaa35f40ce9f4b9e8ee68ae8be92db</t>
@@ -2314,7 +2293,6 @@
           <t>₫12.000</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>2k+</t>
@@ -2327,7 +2305,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29201991132?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/30mo6TsY7W</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2340,7 +2318,6 @@
           <t>shopee_29201991132</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>6e785e5c26dbb055187668758dd780aa</t>
@@ -2363,7 +2340,6 @@
           <t>₫16.000</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">338 </t>
@@ -2376,7 +2352,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24100652843?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3B6EImrumZ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2389,7 +2365,6 @@
           <t>shopee_24100652843</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>4d52e7b788164b03a697159b70b57566</t>
@@ -2429,7 +2404,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41053739148?trace=%7B%22trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.8JmKUyr7T8b.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3LPeV5rHRc</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2442,10 +2417,4082 @@
           <t>shopee_41053739148</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>76dee7e7a569419eb92454e88ce26ae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Móc khoá nhồi bông con gián đáng yêu treo balo cặp sách ml03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>₫17.000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">839 </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3Vj4hOqe6f</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn2m85l0o7i83a.webp</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>shopee_52008273256</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1c3f75f69682b0777bfcc0a37090f2b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Làn Giỏ Gắn Sau Baga Xe Đạp Đựng Balo - Cặp Sách - Đồ Đi Chợ Hàng To Dày Chắc Chắn Loại Xịn</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>₫126.100</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3g2Uthq0li</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjc8iqfydvr903.webp</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>shopee_24162034749</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>13b40fb16a414611a8b80db0aebd3b59</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cặp Sách Balo Nam Trung Học Cơ Sở Dung Tích Lớn Balo Du Lịch Đơn Giản Thường Ngày Học Sinh Đại Học Nữ Sinh Trung Học</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>₫148.125</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">618 </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3qLv60pNQl</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4r1emxgw7sg33.webp</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>shopee_29319714034</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1b2485cfc5af956979aaaabf6466cd95</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Móc khoá lông quái vật một mắt dùng treo balo cặp sách mh02</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>₫15.789</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332 </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6pzWfWdxLM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqojmetiqcjx88.webp</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>shopee_23784312811</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2e1de80d628b282c1536daeb7ffde45f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Balo nam nữ đi học cặp sách đi học thời trang hàn quốc, balo ulzzang nhiều ngăn đựng laptop chống nước</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>₫278.274</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296 </t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6fg6TDeagL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwoi0lxc00d751.webp</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>shopee_29802157458</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1282bb699496389d1169a7da1c01fb13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Balo chống gù đi học cho bé trai in hình người nhện batman, cặp sách bé trai đi học cấp 1 2 E105</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>₫162.965</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7AcN48cgfS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rats-ma8p3bff96eb7c.webp</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>shopee_43252231130</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>a7963039ce35c36e401bb7961dd5e569</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Balo da trơn nam nữ đi học cặp sách thời trang đơn giản nhiều ngăn có ngăn bí mật chống sốc BL29</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>₫184.000</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241 </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/70IwrpdK0R</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ly53e68gz1k16b.webp</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>shopee_25258609297</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>8f9f7bce034f723906e0dfe6f71d77bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cặp Đi Học - Balo Học Sinh Cho Bé Trai, Bé Gái Đựng Sách Vở Đi Học Chất Liệu Vải Dù Chống Nước, Chống Xước</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>₫75.000</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7VFDSkbPzY</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lyau9pk0heap8e.webp</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>shopee_29728766600</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1fd0fe582f5904846f2dce34c4150c0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Balo nam nữ, cặp sách đi học cấp 2 3 thời trang</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>₫59.400</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">537 </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7KvnGRc3KX</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m8usktdi4znr44.webp</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>shopee_25894380610</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>e8bc611ba60b6012c1f3bd265fbc14d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>cặp sách nữ mới học sinh tiểu học lớp 1-3-6 ba lô giảm gánh nặng sức chứa lớn cho trẻ em từ 6-9-12 tuổi</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>₫171.500</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7ps3rMa9Je</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rceq-m6inphl6rdzv99.webp</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>shopee_29426973856</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>f51863fcbfdfb6e0fbdefe2c0eae31d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Balo nam nữ, Balo học sinh cấp 2 cấp 3, cặp sách nhiều ngăn đựng laptop chống nước thời trang Ba Vy FASHION BL04ABC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>₫360.000</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252 </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7fYdf3amed</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lxr83bilp1p72f.webp</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>shopee_23450241802</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>8f20fdfa36820b8ebcb352fd6a2bdd14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Balo học sinh siêu nhẹ hình thỏ, khủng long cho bé trai, bé gái từ lớp 3-7, chống thấm nước, cặp sách tiện dụng.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5VU954j23E</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ratp-mb0jlqkwo5ihaf.webp</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>shopee_29487599068</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>8a3407268157e4c6ca74e655288c802b</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Balo đi học Hàn Quốc da trơn basic nam nữ cặp sách đi chơi du lịch thời trang size đại _BL024</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>₫75.000</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>9k+</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5LAisljfOD</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7st6kwd27ra84.webp</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>shopee_26826737964</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>bd37aea996276aacb181cfd7ea217ee8</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù Cho Bé Trai Gái Chống Nước Ba lô cấp 1 Cặp Sách Học Sinh Tiểu Học hàng đẹ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>₫179.000</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194 </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5q6zTghlNK</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mc3u4jfjy2y2ed.webp</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>shopee_27603042519</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>c92046fbe4c81a2cacd610eb667ee412</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Balo nữ ba lô màu pastel dập sao lấp lánh tặng kèm charm, cặp sách nữ đi học đi chơi vải dù chống nước dung tích lớn</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>₫185.976</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193 </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5fnZHNiOiJ</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9npzlrtq12a7.webp</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>shopee_53913773253</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>64d8facb296875fce2db55c4a502568c</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Balo cho bé QPENZ cặp sách trẻ em từ mầm non đến lớp 6 chống gù nhiều ngăn chuẩn form cao cấp</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>₫329.000</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231 </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6AjpsIgUhQ</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m3syjsw071ksd2.webp</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>shopee_29570669182</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>4869ac1f355e2efa3763133459cb4df8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Balo cho bé mẫu giáo bé trai bé gái , cặp sách trẻ em mầm non đi học từ 2 – 5 tuổi hoạ tiết hoạt hình dễ thương.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>₫84.900</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254 </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/60QPfzh82P</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdxo-m18b6z9hjgwu70.webp</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>shopee_14092980912</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>17e22a639aed7898dcbdd0166abe10fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>[CÓ SẴN] Balo thời trang Hàn Quốc, cặp sách đi học nữ dành cho học sinh, sinh viên, vừa laptop 15.6 inch, vải trượt nước</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>₫235.000</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163 </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6VMgGufE1W</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mni4ie25cyrl69.webp</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>shopee_50259506478</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>dd20357b48b5c440bacc85204408ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BAGSMART Ba lô đựng laptop đại học Túi đựng sách chống nước cho máy tính xách tay 14 Inch, Ba lô đựng laptop du lịch thông thường dành cho nữ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>₫502.200</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6L3G4bfrMV</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824ie-mpvy8g1ga8zz5c.webp</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>shopee_29888660896</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>59ab6e7a1109fa36ee5828bcf79a76b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cặp Đi Học - Balo Học Sinh Cho Bé Trai, Bé Gái Đựng Sách Vở Đi Học Chất Liệu Vải Dù Chống Nước, Chống Xước Nhiều Mẫu Mã</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>₫75.000</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>6k+</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9V0HqQTnw8</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lyau9pk0heap8e.webp</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>shopee_44353562979</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>91bc43a59ff4722f9739b38d08f8fec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Bộ áo mưa có lưng che balo - Bộ mưa Sơn Thủy đeo balo, cặp sách dành cho người lớn, nhựa PVC siêu dai, siêu chống thấm</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>₫315.000</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">429 </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9Kgre7URH7</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mb6zdgvbcno7fb.webp</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>shopee_40405228242</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>f022cdf0097fd95404b19b41ea95b780</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù Cho Bé Tiểu Học (Tặng 10 Món Phụ Kiện) Chống Nước, Cặp Sách Đẹp Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>₫183.000</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9pd8F2SXGE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-821f8-mh97n66xzi8856.webp</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>shopee_49101749110</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>261e8d20c3c7d47746ab9b0bd5979d8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Móc Khóa Chữ Hoạt Hình Sáng Tạo Dễ Thương Mica Trong Suốt, trang trí góc học tập, Treo cặp sách balo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>₫5.862</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9fJi2jTAbD</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8260w-mj42xbhbr1ms15.webp</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>shopee_57804151605</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>870c6635923158e4d5b34b43fde54755</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù Cho Bé Trai Gái Chống Nước Ba lô cấp 1 Cặp Sách Học Sinh Tiểu Học hàng đẹ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>₫175.900</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/AAFydeRGaK</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwmhi304xfx509.webp</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>shopee_40215001645</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>3b3b6da43403395f6227f940fed57c9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cặp Đi Học - Balo Học Sinh Cho Bé Trai, Bé Gái Đựng Sách Vở Đi Học Chất Liệu Vải Dù Chống Nước, Chống Xước</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>₫79.000</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201 </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9zwYRLRtvJ</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rd60-m759lrd8do980e.webp</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>shopee_26628972888</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>d5dbab592a1aeb83df2ff2282f28afda</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Combo 10 Khoá cài, khoá mũ bảo hiểm, balo, cặp sách 2cm, 2,5cm</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>₫9.950</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">575 </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/AUsp2GPzuQ</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lys7h8lexpr5f8.webp</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>shopee_24533615860</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>17d50a19da6c39d946cd63355f13f732</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Móc khóa mica in Logo của các trường đại học, cao đẳng... móc khóa treo balo, cặp sách</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>₫13.720</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/AKZOpxQdFP</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meyozrxgadqd46.webp</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>shopee_40126123352</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1d1d7562ccac7647a8ba79409af08336</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Balo nữ đi học thời trang, cặp sách Balo nữ cấp 1, cấp 2 đi học dễ thương, Balo ulzzang có ngăn trong suốt đựng gấu</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>₫285.000</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">325 </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8AUuFyYse0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbg6he3k7k906c.webp</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>shopee_42005984047</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>b1739845eac27156066fd41b2d3699fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Móc khoá quả lông đáng yêu treo balo cặp sách mq25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>₫18.500</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/80BU3fZVyz</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ra2m-mb902olm3uyee5.webp</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>shopee_26937823110</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>73961464e6eea62b303bcb8c5d291708</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Balo nữ dung tích lớn mẫu mới hình chú cún con dễ thương cặp sách học sinh trung học cơ sở đa năng nhẹ dễ thương hàn</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>₫199.999</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165 </t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8V7keaXby6</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgaw75fd30uia3.webp</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>shopee_28293446174</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>dab705a1203ea9356c71f18b2af0af00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Balo nữ ba lô màu pastel dập sao lấp lánh tặng kèm charm, cặp sách nữ đi học đi chơivải dù chống nước dung tích lớn</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>₫188.823</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144 </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8KoKSHYFJ5</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9npbfgsooxbd.webp</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>shopee_43232530256</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>b9eae3656b446923e4f5c54b4410286f</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Balo nữ ba lô màu pastel chấm bi đính cánh thiên thần tặng kèm charm, cặp sách nữ đi học đi chơi dung tích lớn</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>₫214.850</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18 </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8pkb3CWLIC</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9nr5gz9f5t97.webp</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>shopee_48714896773</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>5312e243c81747a156146b99fd503c9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Balo nữ ba lô kẻ caro phối chấm bi đính nơ tặng kèm hai charm siêu xinh, cặp sách nữ pastel đi học đi chơi dung tích lớn</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>₫249.035</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18 </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8fRAqtWydB</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9non44revg15.webp</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>shopee_27845398656</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1177b4557297482cc58e66fb31d73a9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Balo Nữ Cỡ Lớn Thiết Kế Mới Đáng Yêu Thời Trang Theo Phong Cách Nhật Hàn Cho Nữ ,cặp sách nữ#1199</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>₫165.505</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">391 </t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9ANRRoV4cI</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mos0yfj912j108.webp</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>shopee_40058200626</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>907c2c184e3fd1884ed1bc00c2cf9493</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Bộ áo mưa có lưng che balo - Bộ mưa Sơn Thủy đeo balo, cặp sách dành cho người lớn, nhựa PVC siêu dai, chống thấm ST2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>₫315.000</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9041FVVhxH</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mb6yz34mxal3e2.webp</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>shopee_43705228144</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>08a01c38c80bbb1602efe02b17d6c404</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Balo chống gù học viên cấp 1 ZMCG-40 Cặp sách tiểu học chống nước, cặp chống gù cho bé trai, bé gái</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>₫325.000</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157 </t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1Vy0JiyGAq</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqrucxfp297182.webp</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>shopee_29716592772</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0d29ec7969c6034e65d4783ef7eb0197</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù Cho Bé Cấp 1 Zoyzoii Chính Hãng Cặp Đi Học Cao Cấp Cho Bé Trai Bé Gái Lớp 1 2 3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>₫879.000</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151 </t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1Lea7PytVp</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9blb8eassxza7.webp</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>shopee_23461552475</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>3fa3fc4cc39b4079a91b8c5afa2100c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Balo đi học Nam -Nữ gấu Quảng Châu size to 40cm đựng sách vở a4 cùng laptop-chất liệu da dày đẹp,quai bản to đệm lưới êm</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>₫125.000</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91 </t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1qaqiKwzUw</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqqa78qtw3r4fa.webp</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>shopee_47813871518</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>4d2359043c80420917f6145d976d5c67</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ba lô học sinh trung học cơ sở dung tích lớn cặp sách học sinh trung học phổ thông cảm giác thiết kế phong cách</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>₫186.260</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137 </t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1gHQW1xcpv</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8226v-mhlk0dutowld6a.webp</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>shopee_44476842293</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>a21d70967e678b1e2b093dc185ff4d80</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Balo nữ đi học cặp đi học nữ nhiều ngăn thời trang Ulzzang Hàn Quốc vải dù mịn chống nước.#1199</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>₫178.888</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152 </t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2BDh6wvip2</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp7tfg1getc2c2.webp</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>shopee_41414473248</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>4ea75d5b272de7717079aeab16a99eac</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Balo nữ đi học, cặp sách nữ đi học thời trang hàn quốc, Balo nữ dễ thương ulzzang có ngăn trong suốt đựng gấu</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>₫279.000</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150 </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/20uGudwMA1</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meaw22za9czkf5.webp</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>shopee_24796595464</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>bfef0c11190f01dfcb638623414eda63</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cặp Sách Mẫu Mới Nữ Sinh Trung Học Phổ Thông Ba Lô Đeo Hai Vai Dung Tích Lớn Dễ Phối Gọn Nhẹ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>₫199.140</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207 </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2VqXVYuS98</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rfhs-m43ludmokdx6f0.webp</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>shopee_28021377904</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>91d6b0e94de555b8cc30b2eee415a805</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Balo nữ cặp đi học nữ chống nước nhiều ngăn Ba lô đựng sách vở vừa laptop 15.6inch tặng kèm túi nhỏ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>₫150.000</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133 </t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2LX7JFv5U7</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp78pvnkj09a1c.webp</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>shopee_29503296734</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>87f902ab5977e69dd916a834c8fa520a</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Balo nữ đi học thời trang hàn quốc,cặp sách đi học nữ dễ thương, Balo ulzzang nhiều ngăn chống nước</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>₫233.574</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/BScjH3Ksi</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdwu-ly2qb9aobi7n85.webp</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>shopee_26006223317</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0059bf9255b21c77db6538cee95d7a6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Balo nam nữ thời trang đi học, cặp sách nữ đi học nhiều ngăn hàn quốc, ba lô đi chơi đi làm, balo học sinh cấp 2 BL12</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>₫160.000</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159 </t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/19CWy3yDh</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq1s7ar07j0s59.webp</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>shopee_51313045223</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>8e437d27a785343afc8f2c4bdd9fac52</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Balo Phong Cách Hàn Quốc, Balo Cặp Sách Học Sinh Tiểu Học Bé Gái Bé Trai Có Nhiều Ngăn Chứa Tiện Lợi</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>₫49.000</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95 </t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/W5T7t24Co</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqfl0mzey9s16d.webp</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>shopee_53863661316</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>7c1f70fb120eed704daa822c02144b4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Móc khoá May mắn tới treo balo cặp sách tăng bạn bè người yêu nlp shop</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>₫10.360</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">374 </t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/Lm2va2hXn</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpyf2jj7qd4w7d.webp</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>shopee_53305443993</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>92cbb814d51fb41916a1a2c189deed5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Balo Cặp Sách Bản Vuông Siêu Nhẹ Hình Kuromi Dễ Thương – Chống Gù, Dành Cho Bé Gái Lớp 1–6 tuổi H345</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>₫211.220</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/qiJWV0nWu</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8261z-mllh2h0yz8jz26.webp</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>shopee_55356948413</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>20c277c8c2144c06635b52a16d259dc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Balo học sinh cấp 2 cấp 3 ONETOP nhiều ngăn chống nước tốt , cặp sách nam đi học đựng laptop 15,6 inch</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>₫155.000</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34 </t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/gOtKC1Qrt</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq7kp8nih69s36.webp</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>shopee_52508184318</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>9b5b6c0b17220c4a82f6864a28cdd1ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Balo lười phong cách mùa xuân mới dành cho học sinh trung học cơ sở nữ ba lô du lịch dung tích lớn cặp sách sinh viên</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>₫205.884</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149 </t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1BL9v6zWr0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-822zx-mhx0xrhv2cqo8b.webp</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>shopee_47952710379</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2a697511d7ddcce19952afcd199f5e5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>[HÀNG ĐẸP] Balo chống gù quai ngang, chống thấm nước, cặp sách đi học lớp 1 - 5, học sinh cấp 1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>₫206.994</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/111jio0ABz</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdyx-ly2qbl86uynnc1.webp</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>shopee_26806049216</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>03b51348b72b2aba4b499140f523b380</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cặp sách học sinh tiểu học Ba lô học sinh nam nữ một hai ba bốn năm năm sáu lớp chống nước phim hoạt hình trẻ em</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>₫316.344</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">864 </t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4AylUco6lc</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ravi-masimx5q5h0i92.webp</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>shopee_29837378357</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>3e3fd27274e1d3caa643aa1a7ce82b26</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Cặp sách học sinh tiểu học mẫu mới hoạt hình ba lô culomi cho bé gái dễ thương lớp 1-3-6</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>₫193.835</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">724 </t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/40fLIJok6b</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ra24-mb8k16ca66sp92.webp</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>shopee_43805350210</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>2ca5ef9b610933c43628fe8fe1c834c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Mèo bông treo cặp sách balo + Còi Kêu Bíp Bíp đáng yêu ga12</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>₫14.980</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127 </t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4VbbtEmq5i</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmr6l8zrnpj4dc.webp</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>shopee_25688943433</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>a7f7e543b784476efb4a9b97b13aa2e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Móc Khoá Gấu Bông Mèo Đen Nhạc Sĩ Cầm Đàn, Charm Treo Túi Xách, Balo, Cặp Sách Cute Dễ Thương</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>₫38.000</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257 </t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4LIBgvnTQh</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825a2-mr03i9pl2gb03e.webp</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>shopee_56554422157</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>d4a06624bf5c5d5a871ece29c3ed37d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Balo mầm non cho bé trai bé gái ZENZIN KIDS từ 1-5 tuổi đi, cặp đi học mẫu giáo trẻ em đựng quần áo bỉm sữa, sách vở</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>₫96.000</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115 </t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4qESHqlZPo</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mesfiz06vpc720.webp</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>shopee_25054837757</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>52d650122b1aed9b58fcc31463c843ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ba lô kiểu mới, ba lô nữ Hàn Quốc, màu tương phản đơn giản, dễ kết hợp với cặp sách học sinh trung học, phong cách đại h</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>₫213.002</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210 </t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4fv25XmCkn</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rfi8-m3wemjsamlyabe.webp</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>shopee_27220948957</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>4a38235f279d62a8a6f5b6299d693122</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Móc khoá chuột treo balo cặp sách quà tặng mt10</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>₫16.000</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">314 </t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5ArIgSkIju</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lv5jhqjgi4mxf1.webp</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>shopee_25179189888</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>4bdf5640a65b16746e18b597166f5a19</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Mẫu mới Balo chống gù cho học sinh cấp 1, Cặp sách chống gù chống gù cho học sinh lớp 1-lớp 6</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>₫299.000</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95 </t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/50XsU9kw4t</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mazdxurn05vle5.webp</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>shopee_23016169658</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>9f422e02962dd73972a0884d27424fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Balo Học Sinh Cặp Sách Đi Học Họa Tiết Thêu BA47</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>₫234.220</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98 </t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2qTNuAtBTU</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjv7sxjq68sgbb.webp</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>shopee_50405256141</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>7d98b70caa611161420854532b83efd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Balo nữ đi học thời trang hàn quốc, cặp sách nữ đi học dễ thương tặng kèm 2 GẤU, Balo ulzzang chất liệu vải chống nước</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>₫280.000</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133 </t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41655991167?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbexyh48faaf6c.webp</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>shopee_41655991167</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>9c59b07ad414182144f476e85b0025a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Balo đi học đi chơi hình gấu đựng quần áo tập sách bl mars hộp vuông</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>₫46.920</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">339 </t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25820732217?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfyxs1j5vrwub2.webp</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>shopee_25820732217</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>b47dccb58d653c5e32b68f93a031d29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Móc khóa gấu âm nhạc dễ thương – Treo balo, cặp sách, chìa khóa</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>₫10.790</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187 </t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40057529130?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbufoq7n67w258.webp</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>shopee_40057529130</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>b489b322e01fcf442d8aecbf2dda39d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Cặp sách hoạt hình mẫu giáo mẫu giáo mẫu mới cho bé Sesame túi nhỏ chất liệu lặn mini gọn nhẹ ba lô trẻ em</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>₫208.937</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24770824608?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rcey-ltax6wnln9c512.webp</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>shopee_24770824608</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>17c444143b50f17665a67ddb6da9d382</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Balo cặp sách cho bé trai - gái mầm non hoạt hình , ba lô trẻ em mẫu giáo siêu ngộ nghĩnh.</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>₫79.900</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140 </t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22828261628?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4ote4lgul7381.webp</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>shopee_22828261628</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>39b82fd027eaa738da29293c90bd61b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Balo Học Sinh OLANG Chống Gù, Siêu Nhẹ, Chống Nước, Cặp Sách Tiểu Học Bé Trai Bé Gái</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>₫547.800</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131 </t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55608340899?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr1941lqjw8xbd.webp</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>shopee_55608340899</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>d3b4b6f06555e672009ebe66122f0124</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>[MUA 1 TẶNG 1] Cặp sách balo cho học sinh tiểu học Kitty Kuromi 36x27x19</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>₫259.000</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126 </t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24305818849?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn8t7vbmg3k4f1.webp</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>shopee_24305818849</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>ac4cb46bc5ac0d6ade31cc3c5ccb2c9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Balo nam nữ đi học chống nước nhiều ngăn quai đệm kèm gấu dễ thương cặp sách đựng laptop đi làm học sinh.b4015</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>₫175.855</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">483 </t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49605963749?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqd4rh2c3bbj51.webp</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>shopee_49605963749</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>7edfe29c13da3e1a27746b323f3c3cf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Balo nam nữ đi học chống nước nhiều ngăn quai đệm kèm gấu dễ thương ZONY cặp sách đựng laptop đi làm học sinh 291</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>₫275.000</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112 </t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/16453035442?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lw81j6clp9sp25.webp</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>shopee_16453035442</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0eb62825803109c6cf68e94e11852dd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Móc khoá thỏ dễ thương phụ kiện thời trang treo balo cặp sách móc khoá bạc mq08</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>₫21.000</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791 </t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27504285078?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lxdd66gc4onv39.webp</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>shopee_27504285078</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0c2f38ef139e1d59b06804a41466f2ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Balo JD V2 Nhiều Sticker Nhỏ Cá Tính | Cặp Đi Học Đựng Sách Vở Laptop 15.6 Inch Chất Dù Chống Nước Size 42cm</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>₫275.000</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51 </t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51313756213?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqhbmw3n8mpuce.webp</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>shopee_51313756213</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0414d16c37333b82dc446aebf28bf5cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Cặp sách chống gù DIOOGLT Balo Phi Hành Gia Siêu Nhẹ Thoáng Khí Cho Bé Tiểu Học</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26960129769?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mck5l2ksms0se2.webp</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>shopee_26960129769</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>e091a6de578007c4c593b037ce489681</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Balo nữ đi học trơn basic vải chống thấm, bền đẹp, dễ phối đồ, cặp sách nữ style Hàn Quốc, đựng laptop 14inch</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>₫235.000</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77 </t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24059687930?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mf9ezpw9hlhnef.webp</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>shopee_24059687930</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>a0d206cdb7ec907b457410b2d9f91bf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>balo đi học boy phố chất liệu vải dù chống nước. balo hottrend Nam -nữ thời trang trẻ đựng sách vở và laptop bền đẹp</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>₫132.000</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53708380842?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmr3t89xkqh127.webp</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>shopee_53708380842</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>7497a2886bcebffe093a9b6a89cf0788</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>( Tặng Kèm Móc Khoá Và Huy Hiệu) Balo Chống Gù Cho Bé Trai Gái Chống Nước Balo Cấp 1 Cặp Sách Học Sinh Tiểu Học</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98 </t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26378174133?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnk7w220c45e67.webp</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>shopee_26378174133</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>4684bb1d9114f9408dcab981a59dc044</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>(Full Hộp) Mở Bán Kèm Móc Khóa Balo KittyCow Size32 Size40 DaPu thời trang đi du lịch đi học đựng sách vở A4 BL98</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>₫125.000</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81 </t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47053854972?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq53gn91a41u1b.webp</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>shopee_47053854972</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>3c0f64d069b40707ad03d8a171dda8ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Balo capybara KNOTE cặp sách học sinh dày dặn form chuẩn cao cấp cho bé từ mầm non đến cấp 2</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>₫329.000</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100 </t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28929879693?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7g8es7z0el404.webp</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>shopee_28929879693</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>6ecfa5b1e98f1bd25ea777651b0c167d</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Balo nữ ba lô màu pastel thỏ chấm bi tặng kèm charm, cặp sách nữ đi học đi chơi da pu chống nước dung tích lớn</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>₫197.758</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95 </t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/52363877345?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9nrot8eaddf5.webp</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>shopee_52363877345</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>29fea3bbde0ab37884bd157649d7b429</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Balo đi học nam nữ M4M NEW BASIC Backpack BM002 Cặp sách chống nước nhiều ngăn đựng laptop 15.6 inch</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>₫400.366</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29487759408?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mlug651sp72982.webp</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>shopee_29487759408</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>edc725922ec1225162460fc0a64cd9ef</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ba lô balo nữ Balo hai dây nam sức chứa lớn, balo công sở du lịch, balo đựng máy tính, balo leo núi, cặp sách cho học sinh cấp hai, cấp ba và sinh viên mới</t>
+          <t>[HÀNG ĐẸP] Balo chống gù quai ngang, chống thấm nước, cặp sách đi học lớp 1 - 5, học sinh cấp 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫406.080</t>
+          <t>₫206.994</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,22 +506,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AAFydeRGZJ</t>
+          <t>https://s.shopee.vn/111jio0ABz</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824he-mphj3jd8ghe795.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdyx-ly2qbl86uynnc1.webp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>shopee_43581717685</t>
+          <t>shopee_26806049216</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>a19c668113d92115e35797b4a5937e66</t>
+          <t>03b51348b72b2aba4b499140f523b380</t>
         </is>
       </c>
     </row>
@@ -528,42 +533,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>balo nhỏ balo cho bé gái Cặp sách túi đi học nữ sinh đại học ba lô chống nước học sinh cấp 2 ba lô ba lô du lịch leo núi màu trơn phong cách Hàn Quốc</t>
+          <t>balo đi học boy phố chất liệu vải dù chống nước. balo hottrend Nam -nữ thời trang trẻ đựng sách vở và laptop bền đẹp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫486.000</t>
+          <t>₫132.000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AKZOpxQdEM</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53708380842?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gr-mpg9mvm0ssn63b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmr3t89xkqh127.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_55562188110</t>
+          <t>shopee_53708380842</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>34435c447873629ead327f2be54813b2</t>
+          <t>7497a2886bcebffe093a9b6a89cf0788</t>
         </is>
       </c>
     </row>
@@ -575,42 +585,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>balo đi học balo hello kitty Ba lô nhỏ đầy màu sắc dành cho Xiaomi, ba lô thể thao du lịch thường ngày nam nữ 20 lít, ba lô cặp sách chống nước</t>
+          <t>Balo đi học Nam -Nữ gấu Quảng Châu size to 40cm đựng sách vở a4 cùng laptop-chất liệu da dày đẹp,quai bản to đệm lưới êm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫441.720</t>
+          <t>₫125.000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91 </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AUsp2GPztP</t>
+          <t>https://s.shopee.vn/1qaqiKwzUw</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gs-mpgiy09gklxq09.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqqa78qtw3r4fa.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_57112205850</t>
+          <t>shopee_47813871518</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>54d878c6c65625fc02a00b34e30d3c12</t>
+          <t>4d2359043c80420917f6145d976d5c67</t>
         </is>
       </c>
     </row>
@@ -622,17 +637,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>balo da nữ balo học sinh cấp 2 Balo sọc xanh sữa bạc hà ba lô búp bê táo sang trọng trái tim thiếu nữ đáng yêu ba lô quà tặng cặp sách học sinh</t>
+          <t>Cặp sách hoạt hình mẫu giáo mẫu giáo mẫu mới cho bé Sesame túi nhỏ chất liệu lặn mini gọn nhẹ ba lô trẻ em</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫319.680</t>
+          <t>₫208.937</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7k+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -642,22 +662,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8AUuFyYscz</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24770824608?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gv-mpgcomu01z4b60.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rcey-ltax6wnln9c512.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_29495051765</t>
+          <t>shopee_24770824608</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>f3a841a3c0957cd70fa49d3ccef86a06</t>
+          <t>17c444143b50f17665a67ddb6da9d382</t>
         </is>
       </c>
     </row>
@@ -669,17 +689,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>balo nữ cặp sách nữ Cặp sách trong suốt mẫu mới 2023 ba lô thoáng khí học sinh trung học nữ ba lô nam trung học màu hồng xanh lá cây ba lô du lịch</t>
+          <t>Ba lô học sinh trung học cơ sở dung tích lớn cặp sách học sinh trung học phổ thông cảm giác thiết kế phong cách</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫449.280</t>
+          <t>₫186.260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137 </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -689,22 +714,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8KoKSHYFI2</t>
+          <t>https://s.shopee.vn/1gHQW1xcpv</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i8-mphi79coqk245c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8226v-mhlk0dutowld6a.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_46162260924</t>
+          <t>shopee_44476842293</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6a56f947a0131e736ae385e94fd682de</t>
+          <t>a21d70967e678b1e2b093dc185ff4d80</t>
         </is>
       </c>
     </row>
@@ -716,17 +741,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cặp sách cho bé lớp 1 ba lô Balo nữ phong cách sóng chấm bi ba lô nữ nhỏ ba lô du lịch học sinh đáng yêu mẫu mới mùa xuân 2026 cặp sách nhỏ</t>
+          <t>Cặp sách học sinh tiểu học mẫu mới hoạt hình ba lô culomi cho bé gái dễ thương lớp 1-3-6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫439.560</t>
+          <t>₫193.835</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">724 </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -736,22 +766,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8V7keaXbx5</t>
+          <t>https://s.shopee.vn/40fLIJok6b</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j1-mpgg0qfn8um9bc.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ra24-mb8k16ca66sp92.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_42181702947</t>
+          <t>shopee_43805350210</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3e694351ee8088216a2e44475e09884f</t>
+          <t>2ca5ef9b610933c43628fe8fe1c834c2</t>
         </is>
       </c>
     </row>
@@ -763,17 +793,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>balo cho bé gái balo học sinh cấp 2 Túi du lịch cặp sách học sinh dung tích lớn ba lô trường tiểu học ba lô trường trung học ba lô nam nữ đơn giản túi máy tính kinh doanh</t>
+          <t>Balo nữ dung tích lớn mẫu mới hình chú cún con dễ thương cặp sách học sinh trung học cơ sở đa năng nhẹ dễ thương hàn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫406.080</t>
+          <t>₫199.999</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165 </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,22 +818,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9041FVVhwE</t>
+          <t>https://s.shopee.vn/8V7keaXby6</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824if-mpghprn6rgu97e.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgaw75fd30uia3.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_45512220556</t>
+          <t>shopee_28293446174</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>068ebd4b7dcd40c730b6824c1a132f90</t>
+          <t>dab705a1203ea9356c71f18b2af0af00</t>
         </is>
       </c>
     </row>
@@ -810,42 +845,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ba lô balo da nữ Trẻ em ngày trẻ em bút chì mới cặp sách kt mèo ba lô ba lô trẻ em mẫu giáo bé gái ba lô dây rút túi đau</t>
+          <t>Balo mầm non cho bé trai bé gái ZENZIN KIDS từ 1-5 tuổi đi, cặp đi học mẫu giáo trẻ em đựng quần áo bỉm sữa, sách vở</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫264.600</t>
+          <t>₫96.000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115 </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9ANRRoV4bH</t>
+          <t>https://s.shopee.vn/4qESHqlZPo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j7-mpgmu3ixwe0w27.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mesfiz06vpc720.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_53612210400</t>
+          <t>shopee_25054837757</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6f38ca329b74eaeae813ba5b09e934fc</t>
+          <t>52d650122b1aed9b58fcc31463c843ed</t>
         </is>
       </c>
     </row>
@@ -857,42 +897,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>balo cho bé trai balo da Ba lô hai vai ba lô du lịch thời trang instagram có thể cầm tay đơn giản sức chứa lớn mẫu mới cho nữ ba lô gọn nhẹ cặp sách</t>
+          <t>Balo Phong Cách Hàn Quốc, Balo Cặp Sách Học Sinh Tiểu Học Bé Gái Bé Trai Có Nhiều Ngăn Chứa Tiện Lợi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫246.240</t>
+          <t>₫49.000</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">95 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Lea7PytUm</t>
+          <t>https://s.shopee.vn/W5T7t24Co</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824il-mpgf6xsmf0um55.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqfl0mzey9s16d.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_45712209882</t>
+          <t>shopee_53863661316</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26bed99f3e2953b9b4655506074f1437</t>
+          <t>7c1f70fb120eed704daa822c02144b4a</t>
         </is>
       </c>
     </row>
@@ -904,17 +949,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>balo hello kitty balo học sinh Ba lô học sinh đại học dung tích lớn thoải mái Hàn Quốc ba lô học sinh trung học nữ ba lô cặp sách hình vịt hoạt hình dễ thương dễ thương</t>
+          <t>cặp sách nữ mới học sinh tiểu học lớp 1-3-6 ba lô giảm gánh nặng sức chứa lớn cho trẻ em từ 6-9-12 tuổi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫403.920</t>
+          <t>₫171.500</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -924,22 +974,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qaqiKwzTv</t>
+          <t>https://s.shopee.vn/7ps3rMa9Je</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgf8d61jb4b2d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rceq-m6inphl6rdzv99.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_47862218379</t>
+          <t>shopee_29426973856</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fa30ebfee016a53d0f28e79b7fbd8919</t>
+          <t>f51863fcbfdfb6e0fbdefe2c0eae31d9</t>
         </is>
       </c>
     </row>
@@ -951,17 +1001,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>balo nhỏ balo hello kitty Ba lô đơn giản, túi khiêu vũ, ba lô hai dây, thiết kế bắt mắt, nhẹ gọn phù hợp học đường, cặp sách cho học sinh cấp hai và cấp ba, dễ phối đồ</t>
+          <t>Balo nữ đi học thời trang hàn quốc,cặp sách đi học nữ dễ thương, Balo ulzzang nhiều ngăn chống nước</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫402.840</t>
+          <t>₫233.574</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -971,22 +1026,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDh6wvio1</t>
+          <t>https://s.shopee.vn/BScjH3Ksi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i3-mphm3qwfng1u11.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdwu-ly2qb9aobi7n85.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_47862271030</t>
+          <t>shopee_26006223317</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>bebd98cd961d7c5870d10a4d6ced6e5e</t>
+          <t>0059bf9255b21c77db6538cee95d7a6f</t>
         </is>
       </c>
     </row>
@@ -998,17 +1053,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>balo balo nữ hàn quốc Ba lô đeo hai vai cho nam, túi du lịch công sở sức chứa lớn, ba lô đựng máy tính thời trang sành điệu, cặp sách học sinh cấp hai, cấp ba và sinh viên</t>
+          <t>Balo học sinh cấp 2 cấp 3 ONETOP nhiều ngăn chống nước tốt , cặp sách nam đi học đựng laptop 15,6 inch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫338.040</t>
+          <t>₫155.000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1018,22 +1078,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LX7JFv5T4</t>
+          <t>https://s.shopee.vn/gOtKC1Qrt</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gb-mpgmfmcey8zkd4.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq7kp8nih69s36.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_45262235420</t>
+          <t>shopee_52508184318</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>caf40f77cf658483280c372f312e3d1c</t>
+          <t>9b5b6c0b17220c4a82f6864a28cdd1ae</t>
         </is>
       </c>
     </row>
@@ -1045,17 +1105,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>balo nữ balo da Balo nhỏ dễ thương phong cách ins kiểu Nhật dành cho nữ; cặp sách học sinh cấp hai; balo du lịch đeo hai dây nhẹ nhàng cho học sinh cấp ba</t>
+          <t>Ba lô kiểu mới, ba lô nữ Hàn Quốc, màu tương phản đơn giản, dễ kết hợp với cặp sách học sinh trung học, phong cách đại h</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫384.480</t>
+          <t>₫213.002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1065,22 +1130,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2VqXVYuS87</t>
+          <t>https://s.shopee.vn/4fv25XmCkn</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgkad9m04cifb.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rfi8-m3wemjsamlyabe.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_44081706775</t>
+          <t>shopee_27220948957</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>d9923c72e24f554ec9f07147ab2d3589</t>
+          <t>4a38235f279d62a8a6f5b6299d693122</t>
         </is>
       </c>
     </row>
@@ -1092,17 +1157,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>balo cho bé trai balo Cặp sách màu trơn dung tích lớn phong cách Hàn Quốc tối giản, balo hai dây nam nữ học sinh cấp hai – cấp ba kiểu dáng bắt mắt, balo thường ngày</t>
+          <t>Balo chống gù đi học cho bé trai in hình người nhện batman, cặp sách bé trai đi học cấp 1 2 E105</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫502.200</t>
+          <t>₫162.965</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1112,22 +1182,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/19CWy3yCe</t>
+          <t>https://s.shopee.vn/7AcN48cgfS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824h4-mphnn9kn0mbl92.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rats-ma8p3bff96eb7c.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_49562263043</t>
+          <t>shopee_43252231130</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>45b2ea36dd9337286eb82a8a84eca91c</t>
+          <t>a7963039ce35c36e401bb7961dd5e569</t>
         </is>
       </c>
     </row>
@@ -1139,42 +1209,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>balo nữ hàn quốc balo đi học Cặp sách ba lô nữ sinh học sinh tiểu học ba lô dung tích lớn phong cách học đường giá trị cao ba lô dễ phối dễ thương cho bé gái</t>
+          <t>Móc khóa mica in Logo của các trường đại học, cao đẳng... móc khóa treo balo, cặp sách</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫231.120</t>
+          <t>₫13.720</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/80BU3fZVxw</t>
+          <t>https://s.shopee.vn/AKZOpxQdFP</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8259j-mqbo8qvobtvy12.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meyozrxgadqd46.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_46513834378</t>
+          <t>shopee_40126123352</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6dccc799e89677a3b8a91dc9dcb585c2</t>
+          <t>1d1d7562ccac7647a8ba79409af08336</t>
         </is>
       </c>
     </row>
@@ -1186,42 +1261,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>balo nữ hàn quốc balo đi học Ba lô nữ có giá trị cao cho học sinh trung học cơ sở mẫu mới ba lô thường ngày thời trang học sinh trung học ba lô túi máy tính cặp sách nam</t>
+          <t>Balo Đi Học Cho Bé Cấp 1 Tiểu Học Dễ Thương Chống Gù - Cặp Sách Học Sinh Capybara Kuromi Melody Tặng Kèm Móc Khóa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫461.160</t>
+          <t>₫209.000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8fRAqtWyc8</t>
+          <t>https://s.shopee.vn/3LPeV5rHRc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ah-mqj2yz9kxo1t5a.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqqw2ykedpfnec.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_57213814691</t>
+          <t>shopee_41053739148</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12ce00c571c0b8c4cb1f0a3e9e7504ca</t>
+          <t>76dee7e7a569419eb92454e88ce26ae7</t>
         </is>
       </c>
     </row>
@@ -1233,17 +1313,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>balo học sinh cấp 2 balo đi học Cặp sách có thể giấu đồ, ba lô nữ phong cách Mori, ba lô dung tích lớn dành cho học sinh trung học cơ sở và trung học phổ thông phiên bản Hàn Quốc, ba lô màu tương phản</t>
+          <t>ba lô balo nữ Balo hai dây nam sức chứa lớn, balo công sở du lịch, balo đựng máy tính, balo leo núi, cặp sách cho học sinh cấp hai, cấp ba và sinh viên mới</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫552.960</t>
+          <t>₫406.080</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1253,22 +1333,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8pkb3CWLHB</t>
+          <t>https://s.shopee.vn/AAFydeRGZJ</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8258t-mqj3s80qcw7g6d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824he-mphj3jd8ghe795.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_43132502044</t>
+          <t>shopee_43581717685</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>86734ce868b965f11b930b3e43b25e2c</t>
+          <t>a19c668113d92115e35797b4a5937e66</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1360,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>balo học sinh cấp 2 balo đi học Cặp sách học sinh ba lô cá tính thời trang phong cách Hàn Quốc cho nữ học sinh trung học ba lô đi học dễ phối đồ học sinh tiểu học ba lô du lịch dung tích lớn túi ni lông trường học ngoại khóa</t>
+          <t>balo nhỏ balo cho bé gái Cặp sách túi đi học nữ sinh đại học ba lô chống nước học sinh cấp 2 ba lô ba lô du lịch leo núi màu trơn phong cách Hàn Quốc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫459.000</t>
+          <t>₫486.000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1300,22 +1380,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Vy0JiyG9p</t>
+          <t>https://s.shopee.vn/AKZOpxQdEM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ad-mqj4bslj1l3fff.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gr-mpg9mvm0ssn63b.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_44963847577</t>
+          <t>shopee_55562188110</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>69fbfad24c101b9fb1a3655e594eaf2d</t>
+          <t>34435c447873629ead327f2be54813b2</t>
         </is>
       </c>
     </row>
@@ -1327,17 +1407,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cặp sách cho bé lớp 1 cặp sách nữ Ba lô mini ba lô táo đỏ đáng yêu nữ ba lô hoạt hình Nhật Bản túi vải nhỏ kiểu tây ba lô học sinh</t>
+          <t>balo đi học balo hello kitty Ba lô nhỏ đầy màu sắc dành cho Xiaomi, ba lô thể thao du lịch thường ngày nam nữ 20 lít, ba lô cặp sách chống nước</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫375.840</t>
+          <t>₫441.720</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1347,22 +1427,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gHQW1xcos</t>
+          <t>https://s.shopee.vn/AUsp2GPztP</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gl-mpgc6zz301sbc8.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gs-mpgiy09gklxq09.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_42581705612</t>
+          <t>shopee_57112205850</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>5794aafc81d054d2152cc6f6f3588399</t>
+          <t>54d878c6c65625fc02a00b34e30d3c12</t>
         </is>
       </c>
     </row>
@@ -1374,42 +1454,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sẵn💝Balo đi học nữ, cặp sách nữ basic, balo laptop 14inch, balo chống thấm, cặp đi học hàn quốc, balo thời trang SIÊU RẺ</t>
+          <t>balo da nữ balo học sinh cấp 2 Balo sọc xanh sữa bạc hà ba lô búp bê táo sang trọng trái tim thiếu nữ đáng yêu ba lô quà tặng cặp sách học sinh</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫240.000</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118 </t>
+          <t>₫319.680</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>45%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20uGudwM8y</t>
+          <t>https://s.shopee.vn/8AUuFyYscz</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mi4533uwkpvrf3.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gv-mpgcomu01z4b60.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_27562400542</t>
+          <t>shopee_29495051765</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>72105f7344fdd7d1ccf0ef6cdc956747</t>
+          <t>f3a841a3c0957cd70fa49d3ccef86a06</t>
         </is>
       </c>
     </row>
@@ -1421,47 +1501,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tấm lót đáy balo hổ trợ giảm mất form, giảm xụ phần đáy balo cặp sách khi đựng sách vở laptop nặng</t>
+          <t>balo nữ cặp sách nữ Cặp sách trong suốt mẫu mới 2023 ba lô thoáng khí học sinh trung học nữ ba lô nam trung học màu hồng xanh lá cây ba lô du lịch</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>₫35.000</t>
+          <t>₫449.280</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>40k+</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BScjH3Krh</t>
+          <t>https://s.shopee.vn/8KoKSHYFI2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfngwemcu6fc39.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i8-mphi79coqk245c.webp</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>shopee_22931544947</t>
+          <t>shopee_46162260924</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4c1404834ecc6a9c4dfd7b3f1ffdde3f</t>
+          <t>6a56f947a0131e736ae385e94fd682de</t>
         </is>
       </c>
     </row>
@@ -1473,47 +1548,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Balo cho bé KNOTE cặp sách cấp 1 2 chất liệu vải sức chứa lớn kiểu dáng dễ thương dày dặn chống nước</t>
+          <t>cặp sách cho bé lớp 1 ba lô Balo nữ phong cách sóng chấm bi ba lô nữ nhỏ ba lô du lịch học sinh đáng yêu mẫu mới mùa xuân 2026 cặp sách nhỏ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>₫329.000</t>
+          <t>₫439.560</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1k+</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/Lm2va2hWk</t>
+          <t>https://s.shopee.vn/8V7keaXbx5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4lh3n33z52oa2.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j1-mpgg0qfn8um9bc.webp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>shopee_27022611207</t>
+          <t>shopee_42181702947</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ec692d7a008482c100513fc23a742d29</t>
+          <t>3e694351ee8088216a2e44475e09884f</t>
         </is>
       </c>
     </row>
@@ -1525,47 +1595,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BAGSMART Ba Lô Thường Ngày Du Lịch 14.3inch Ba Lô Laptop Daypack SchoolBag Cao Đẳng Túi Đựng Sách Làm Việc Mặt Sau Máy Tính Dễ Thương Chống Nước</t>
+          <t>balo cho bé gái balo học sinh cấp 2 Túi du lịch cặp sách học sinh dung tích lớn ba lô trường tiểu học ba lô trường trung học ba lô nam nữ đơn giản túi máy tính kinh doanh</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>₫586.280</t>
+          <t>₫406.080</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28%</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1k+</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W5T7t24Bn</t>
+          <t>https://s.shopee.vn/9041FVVhwE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-820l4-mq1nly9hts018a.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824if-mpghprn6rgu97e.webp</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>shopee_43556339364</t>
+          <t>shopee_45512220556</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ac48e54041e1cdc1480c78e7c8370856</t>
+          <t>068ebd4b7dcd40c730b6824c1a132f90</t>
         </is>
       </c>
     </row>
@@ -1577,42 +1642,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Móc khóa TÊN theo yêu cầu, thẻ tên treo balo, cặp sách, nametag cho bé 18K</t>
+          <t>ba lô balo da nữ Trẻ em ngày trẻ em bút chì mới cặp sách kt mèo ba lô ba lô trẻ em mẫu giáo bé gái ba lô dây rút túi đau</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>₫19.800</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1k+</t>
+          <t>₫264.600</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>45%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/gOtKC1Qqq</t>
+          <t>https://s.shopee.vn/9ANRRoV4bH</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpp6sa7xpiq592.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824j7-mpgmu3ixwe0w27.webp</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>shopee_45356600205</t>
+          <t>shopee_53612210400</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>b0c27bd15cdc9e0634d4b83d47d7c4c2</t>
+          <t>6f38ca329b74eaeae813ba5b09e934fc</t>
         </is>
       </c>
     </row>
@@ -1624,47 +1689,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Balo đi học Ulzzang Hàn Quốc trơn basic nam nữ cặp sách đi chơi du lịch thời trang Unisex BL03</t>
+          <t>balo cho bé trai balo da Ba lô hai vai ba lô du lịch thời trang instagram có thể cầm tay đơn giản sức chứa lớn mẫu mới cho nữ ba lô gọn nhẹ cặp sách</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>₫115.000</t>
+          <t>₫246.240</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872 </t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/qiJWV0nVt</t>
+          <t>https://s.shopee.vn/1Lea7PytUm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqyccmr0pqti51.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824il-mpgf6xsmf0um55.webp</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>shopee_20977181092</t>
+          <t>shopee_45712209882</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>bf28e8a630ff63486d985a7d2f054f1c</t>
+          <t>26bed99f3e2953b9b4655506074f1437</t>
         </is>
       </c>
     </row>
@@ -1676,47 +1736,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Balo cho bé mẫu giáo bé trai bé gái, cặp sách trẻ em mầm non đi học từ 2–5 tuổi hoạt hình dễ thương</t>
+          <t>balo hello kitty balo học sinh Ba lô học sinh đại học dung tích lớn thoải mái Hàn Quốc ba lô học sinh trung học nữ ba lô cặp sách hình vịt hoạt hình dễ thương dễ thương</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>₫59.000</t>
+          <t>₫403.920</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">755 </t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/111jio0AAw</t>
+          <t>https://s.shopee.vn/1qaqiKwzTv</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m39yvtz753gc26.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgf8d61jb4b2d.webp</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>shopee_13187078063</t>
+          <t>shopee_47862218379</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2d7286552ad3ca83a40b81a325bcc370</t>
+          <t>fa30ebfee016a53d0f28e79b7fbd8919</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1783,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Móc khoá gấu bông cute treo balo cặp sách ml01 ( KHÔNG KÊU BÍP BÍP)</t>
+          <t>balo nhỏ balo hello kitty Ba lô đơn giản, túi khiêu vũ, ba lô hai dây, thiết kế bắt mắt, nhẹ gọn phù hợp học đường, cặp sách cho học sinh cấp hai và cấp ba, dễ phối đồ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>₫13.000</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>4k+</t>
+          <t>₫402.840</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>45%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1748,22 +1803,22 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1BL9v6zWpz</t>
+          <t>https://s.shopee.vn/2BDh6wvio1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m3aebdqnwrss1b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824i3-mphm3qwfng1u11.webp</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>shopee_28319432367</t>
+          <t>shopee_47862271030</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4a6379b8754508b0ad828f255ab3ffcf</t>
+          <t>bebd98cd961d7c5870d10a4d6ced6e5e</t>
         </is>
       </c>
     </row>
@@ -1775,22 +1830,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Balo đi học nam nữ Cặp đi học unisex nhiều ngăn chống nước Luci Bag cặp sách đựng vừa laptop 15,6 inch basic B50</t>
+          <t>balo balo nữ hàn quốc Ba lô đeo hai vai cho nam, túi du lịch công sở sức chứa lớn, ba lô đựng máy tính thời trang sành điệu, cặp sách học sinh cấp hai, cấp ba và sinh viên</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>₫220.000</t>
+          <t>₫338.040</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1k+</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1800,22 +1850,22 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40fLIJok5Y</t>
+          <t>https://s.shopee.vn/2LX7JFv5T4</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpz4z6mdgavg19.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gb-mpgmfmcey8zkd4.webp</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>shopee_42151531320</t>
+          <t>shopee_45262235420</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6beca9328f8d8243e7e7689d147f535d</t>
+          <t>caf40f77cf658483280c372f312e3d1c</t>
         </is>
       </c>
     </row>
@@ -1827,42 +1877,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Móc khoá bông con mèo đáng yêu treo ba lo cặp sách ga12</t>
+          <t>balo nữ balo da Balo nhỏ dễ thương phong cách ins kiểu Nhật dành cho nữ; cặp sách học sinh cấp hai; balo du lịch đeo hai dây nhẹ nhàng cho học sinh cấp ba</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>₫20.000</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2k+</t>
+          <t>₫384.480</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>45%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4AylUco6kb</t>
+          <t>https://s.shopee.vn/2VqXVYuS87</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m37n8pbmdgx82c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824jc-mpgkad9m04cifb.webp</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>shopee_28719290302</t>
+          <t>shopee_44081706775</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>94a70a6072279569b2adf47f4862ef08</t>
+          <t>d9923c72e24f554ec9f07147ab2d3589</t>
         </is>
       </c>
     </row>
@@ -1874,47 +1924,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Balo da đi học nam nữ, balo da nhiều ngăn đi học đi chơi, cặp sách nữ thời trang, ba lô chống nước BL13</t>
+          <t>balo cho bé trai balo Cặp sách màu trơn dung tích lớn phong cách Hàn Quốc tối giản, balo hai dây nam nữ học sinh cấp hai – cấp ba kiểu dáng bắt mắt, balo thường ngày</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>₫189.000</t>
+          <t>₫502.200</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14%</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">580 </t>
+          <t>45%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LIBgvnTPe</t>
+          <t>https://s.shopee.vn/19CWy3yCe</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq1toufns5xqe5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824h4-mphnn9kn0mbl92.webp</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>shopee_56263034976</t>
+          <t>shopee_49562263043</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>a4b9f909bc4490bc5500660fee713ea0</t>
+          <t>45b2ea36dd9337286eb82a8a84eca91c</t>
         </is>
       </c>
     </row>
@@ -1926,47 +1971,47 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Balo nữ đi học thời trang hàn quốc,cặp sách đi học nữ dễ thương, Balo ulzzang nhiều ngăn chống nước</t>
+          <t>Balo Học Sinh OLANG Chống Gù, Siêu Nhẹ, Chống Nước, Cặp Sách Tiểu Học Bé Trai Bé Gái</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>₫279.000</t>
+          <t>₫547.800</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">131 </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4VbbtEmq4h</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55608340899?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwx4dfpz853td0.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr1941lqjw8xbd.webp</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>shopee_28402501227</t>
+          <t>shopee_55608340899</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>7b0200a706275c55ba0ff6fd8a228be8</t>
+          <t>d3b4b6f06555e672009ebe66122f0124</t>
         </is>
       </c>
     </row>
@@ -1978,42 +2023,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Móc khoá búp bê treo balo cặp sách phụ kiện quà tặng (KHÔNG CÓ PHỤ KIỆN ) mq03</t>
+          <t>Cặp Sách Mẫu Mới Nữ Sinh Trung Học Phổ Thông Ba Lô Đeo Hai Vai Dung Tích Lớn Dễ Phối Gọn Nhẹ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>₫23.000</t>
+          <t>₫199.140</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>43%</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">498 </t>
+          <t xml:space="preserve">207 </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4fv25XmCjk</t>
+          <t>https://s.shopee.vn/2VqXVYuS98</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lt4rfgr2hu3da9.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rfhs-m43ludmokdx6f0.webp</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>shopee_24415449457</t>
+          <t>shopee_28021377904</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>76f2642c874c7842bafce370a0ed0cca</t>
+          <t>91d6b0e94de555b8cc30b2eee415a805</t>
         </is>
       </c>
     </row>
@@ -2025,47 +2075,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Móc treo ba lô, cặp sách hai đầu bằng thép không gỉ – móc treo bên cạnh bàn làm việc, bàn học – có thể tháo rời</t>
+          <t>Balo lười phong cách mùa xuân mới dành cho học sinh trung học cơ sở nữ ba lô du lịch dung tích lớn cặp sách sinh viên</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>₫14.799</t>
+          <t>₫205.884</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9k+</t>
+          <t xml:space="preserve">149 </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4qESHqlZOn</t>
+          <t>https://s.shopee.vn/1BL9v6zWr0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfdsynptw1e2db.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-822zx-mhx0xrhv2cqo8b.webp</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>shopee_25597309034</t>
+          <t>shopee_47952710379</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>970a3ab9a1d51ee6e7d60aa6bce8180e</t>
+          <t>2a697511d7ddcce19952afcd199f5e5a</t>
         </is>
       </c>
     </row>
@@ -2077,47 +2127,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Balo nữ cặp đi học nam nữ GUZI BAG cặp sách nam nữ thời trang basic đơn giản họa tiết ngôi sao BL08 SLEEPYCHIC</t>
+          <t>BAGSMART Ba lô đựng laptop đại học Túi đựng sách chống nước cho máy tính xách tay 14 Inch, Ba lô đựng laptop du lịch thông thường dành cho nữ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>₫170.000</t>
+          <t>₫502.200</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">506 </t>
+          <t>7k+</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/50XsU9kw3q</t>
+          <t>https://s.shopee.vn/6L3G4bfrMV</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-ma0syy5ii2jyc8.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824ie-mpvy8g1ga8zz5c.webp</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>shopee_42301614689</t>
+          <t>shopee_29888660896</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>e65fbda291be3d81b26f4e76a1f77523</t>
+          <t>59ab6e7a1109fa36ee5828bcf79a76b0</t>
         </is>
       </c>
     </row>
@@ -2129,47 +2179,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Balo cho bé BABYTREE cặp sách trẻ em chống gù lưng chất liệu cao cấp nhiều ngăn đa dạng màu sắc</t>
+          <t>Cặp sách học sinh tiểu học Ba lô học sinh nam nữ một hai ba bốn năm năm sáu lớp chống nước phim hoạt hình trẻ em</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>₫329.000</t>
+          <t>₫316.344</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">376 </t>
+          <t xml:space="preserve">864 </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5ArIgSkIit</t>
+          <t>https://s.shopee.vn/4AylUco6lc</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7ho5s8f22k6e0.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ravi-masimx5q5h0i92.webp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>shopee_28580011314</t>
+          <t>shopee_29837378357</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>7fc1214b5a8dd6dedcc8cfdb811729bd</t>
+          <t>3e3fd27274e1d3caa643aa1a7ce82b26</t>
         </is>
       </c>
     </row>
@@ -2181,47 +2231,47 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Balo Chống Gù Thẻ Hình Kurumi Cho Bé Trai Gái Chống Nước Ba lô cấp 1 ( bé lớp 2-6) Cặp Sách Học Sinh Tiểu Học</t>
+          <t>Balo nam nữ, cặp sách đi học cấp 2 3 thời trang</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>₫170.000</t>
+          <t>₫59.400</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">537 </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9xhrtonQ</t>
+          <t>https://s.shopee.vn/7KvnGRc3KX</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m6o43wxx3b6g3f.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m8usktdi4znr44.webp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>shopee_24341874090</t>
+          <t>shopee_25894380610</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>44be2ce255f511ab666351b32b43ffa1</t>
+          <t>e8bc611ba60b6012c1f3bd265fbc14d3</t>
         </is>
       </c>
     </row>
@@ -2233,47 +2283,47 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cặp sách đi học cấp 2, cấp 3 NATOLI Cặp đa năng, Balo đa năng nhiều ngăn BST Classic Multifunctional Backpack B17</t>
+          <t>Mẫu mới Balo chống gù cho học sinh cấp 1, Cặp sách chống gù chống gù cho học sinh lớp 1-lớp 6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>₫459.000</t>
+          <t>₫299.000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">414 </t>
+          <t xml:space="preserve">95 </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2qTNuAtBST</t>
+          <t>https://s.shopee.vn/50XsU9kw4t</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqzz2dv7rbwhcf.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mazdxurn05vle5.webp</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>shopee_24182570256</t>
+          <t>shopee_23016169658</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0dcaa35f40ce9f4b9e8ee68ae8be92db</t>
+          <t>9f422e02962dd73972a0884d27424fee</t>
         </is>
       </c>
     </row>
@@ -2285,17 +2335,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COMBO 5 khoá cài, khoá mũ bảo hiểm, balo, cặp sách 2cm, 2,5cm (Đo lọt lòng)</t>
+          <t>balo nữ hàn quốc balo đi học Cặp sách ba lô nữ sinh học sinh tiểu học ba lô dung tích lớn phong cách học đường giá trị cao ba lô dễ phối dễ thương cho bé gái</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>₫12.000</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2k+</t>
+          <t>₫231.120</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2305,22 +2355,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/30mo6TsY7W</t>
+          <t>https://s.shopee.vn/80BU3fZVxw</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwbh3d386b4r4c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8259j-mqbo8qvobtvy12.webp</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>shopee_29201991132</t>
+          <t>shopee_46513834378</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>6e785e5c26dbb055187668758dd780aa</t>
+          <t>6dccc799e89677a3b8a91dc9dcb585c2</t>
         </is>
       </c>
     </row>
@@ -2332,42 +2382,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Móc khoá gấu má hồng treo balo cặp sách thời trang ga21</t>
+          <t>balo nữ hàn quốc balo đi học Ba lô nữ có giá trị cao cho học sinh trung học cơ sở mẫu mới ba lô thường ngày thời trang học sinh trung học ba lô túi máy tính cặp sách nam</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>₫16.000</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">338 </t>
+          <t>₫461.160</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B6EImrumZ</t>
+          <t>https://s.shopee.vn/8fRAqtWyc8</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rbn3-lnbp3sjycl4ha5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ah-mqj2yz9kxo1t5a.webp</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>shopee_24100652843</t>
+          <t>shopee_57213814691</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4d52e7b788164b03a697159b70b57566</t>
+          <t>12ce00c571c0b8c4cb1f0a3e9e7504ca</t>
         </is>
       </c>
     </row>
@@ -2379,47 +2429,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Balo Đi Học Cho Bé Cấp 1 Tiểu Học Dễ Thương Chống Gù - Cặp Sách Học Sinh Capybara Kuromi Melody Tặng Kèm Móc Khóa</t>
+          <t>balo học sinh cấp 2 balo đi học Cặp sách có thể giấu đồ, ba lô nữ phong cách Mori, ba lô dung tích lớn dành cho học sinh trung học cơ sở và trung học phổ thông phiên bản Hàn Quốc, ba lô màu tương phản</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>₫209.000</t>
+          <t>₫552.960</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255 </t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LPeV5rHRc</t>
+          <t>https://s.shopee.vn/8pkb3CWLHB</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqqw2ykedpfnec.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8258t-mqj3s80qcw7g6d.webp</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>shopee_41053739148</t>
+          <t>shopee_43132502044</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>76dee7e7a569419eb92454e88ce26ae7</t>
+          <t>86734ce868b965f11b930b3e43b25e2c</t>
         </is>
       </c>
     </row>
@@ -2431,42 +2476,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Móc khoá nhồi bông con gián đáng yêu treo balo cặp sách ml03</t>
+          <t>balo học sinh cấp 2 balo đi học Cặp sách học sinh ba lô cá tính thời trang phong cách Hàn Quốc cho nữ học sinh trung học ba lô đi học dễ phối đồ học sinh tiểu học ba lô du lịch dung tích lớn túi ni lông trường học ngoại khóa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>₫17.000</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839 </t>
+          <t>₫459.000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>40%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3Vj4hOqe6f</t>
+          <t>https://s.shopee.vn/1Vy0JiyG9p</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn2m85l0o7i83a.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ad-mqj4bslj1l3fff.webp</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>shopee_52008273256</t>
+          <t>shopee_44963847577</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1c3f75f69682b0777bfcc0a37090f2b9</t>
+          <t>69fbfad24c101b9fb1a3655e594eaf2d</t>
         </is>
       </c>
     </row>
@@ -2478,47 +2523,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Làn Giỏ Gắn Sau Baga Xe Đạp Đựng Balo - Cặp Sách - Đồ Đi Chợ Hàng To Dày Chắc Chắn Loại Xịn</t>
+          <t>cặp sách cho bé lớp 1 cặp sách nữ Ba lô mini ba lô táo đỏ đáng yêu nữ ba lô hoạt hình Nhật Bản túi vải nhỏ kiểu tây ba lô học sinh</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>₫126.100</t>
+          <t>₫375.840</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2k+</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3g2Uthq0li</t>
+          <t>https://s.shopee.vn/1gHQW1xcos</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjc8iqfydvr903.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824gl-mpgc6zz301sbc8.webp</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>shopee_24162034749</t>
+          <t>shopee_42581705612</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>13b40fb16a414611a8b80db0aebd3b59</t>
+          <t>5794aafc81d054d2152cc6f6f3588399</t>
         </is>
       </c>
     </row>
@@ -2530,47 +2570,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cặp Sách Balo Nam Trung Học Cơ Sở Dung Tích Lớn Balo Du Lịch Đơn Giản Thường Ngày Học Sinh Đại Học Nữ Sinh Trung Học</t>
+          <t>Balo Chống Gù Cho Bé Tiểu Học (Tặng 10 Món Phụ Kiện) Chống Nước, Cặp Sách Đẹp Cho Học Sinh</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>₫148.125</t>
+          <t>₫183.000</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">618 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLv60pNQl</t>
+          <t>https://s.shopee.vn/9pd8F2SXGE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4r1emxgw7sg33.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-821f8-mh97n66xzi8856.webp</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>shopee_29319714034</t>
+          <t>shopee_49101749110</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1b2485cfc5af956979aaaabf6466cd95</t>
+          <t>261e8d20c3c7d47746ab9b0bd5979d8a</t>
         </is>
       </c>
     </row>
@@ -2582,47 +2622,47 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Móc khoá lông quái vật một mắt dùng treo balo cặp sách mh02</t>
+          <t>Balo đi học Ulzzang Hàn Quốc trơn basic nam nữ cặp sách đi chơi du lịch thời trang Unisex BL03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>₫15.789</t>
+          <t>₫115.000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">332 </t>
+          <t xml:space="preserve">872 </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6pzWfWdxLM</t>
+          <t>https://s.shopee.vn/qiJWV0nVt</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqojmetiqcjx88.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqyccmr0pqti51.webp</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>shopee_23784312811</t>
+          <t>shopee_20977181092</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2e1de80d628b282c1536daeb7ffde45f</t>
+          <t>bf28e8a630ff63486d985a7d2f054f1c</t>
         </is>
       </c>
     </row>
@@ -2634,22 +2674,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Balo nam nữ đi học cặp sách đi học thời trang hàn quốc, balo ulzzang nhiều ngăn đựng laptop chống nước</t>
+          <t>Balo nữ cặp đi học nam nữ GUZI BAG cặp sách nam nữ thời trang basic đơn giản họa tiết ngôi sao BL08 SLEEPYCHIC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>₫278.274</t>
+          <t>₫170.000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">296 </t>
+          <t xml:space="preserve">506 </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2659,22 +2699,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6fg6TDeagL</t>
+          <t>https://s.shopee.vn/50XsU9kw3q</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwoi0lxc00d751.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-ma0syy5ii2jyc8.webp</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>shopee_29802157458</t>
+          <t>shopee_42301614689</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1282bb699496389d1169a7da1c01fb13</t>
+          <t>e65fbda291be3d81b26f4e76a1f77523</t>
         </is>
       </c>
     </row>
@@ -2686,47 +2726,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Balo chống gù đi học cho bé trai in hình người nhện batman, cặp sách bé trai đi học cấp 1 2 E105</t>
+          <t>Cặp Đi Học - Balo Học Sinh Cho Bé Trai, Bé Gái Đựng Sách Vở Đi Học Chất Liệu Vải Dù Chống Nước, Chống Xước</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>₫162.965</t>
+          <t>₫79.000</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">201 </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7AcN48cgfS</t>
+          <t>https://s.shopee.vn/9zwYRLRtvJ</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rats-ma8p3bff96eb7c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rd60-m759lrd8do980e.webp</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>shopee_43252231130</t>
+          <t>shopee_26628972888</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>a7963039ce35c36e401bb7961dd5e569</t>
+          <t>d5dbab592a1aeb83df2ff2282f28afda</t>
         </is>
       </c>
     </row>
@@ -2738,47 +2778,47 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Balo da trơn nam nữ đi học cặp sách thời trang đơn giản nhiều ngăn có ngăn bí mật chống sốc BL29</t>
+          <t>Balo cặp sách cho bé trai - gái mầm non hoạt hình , ba lô trẻ em mẫu giáo siêu ngộ nghĩnh.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>₫184.000</t>
+          <t>₫79.900</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">241 </t>
+          <t xml:space="preserve">140 </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70IwrpdK0R</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22828261628?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ly53e68gz1k16b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4ote4lgul7381.webp</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>shopee_25258609297</t>
+          <t>shopee_22828261628</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8f9f7bce034f723906e0dfe6f71d77bf</t>
+          <t>39b82fd027eaa738da29293c90bd61b9</t>
         </is>
       </c>
     </row>
@@ -2842,47 +2882,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Balo nam nữ, cặp sách đi học cấp 2 3 thời trang</t>
+          <t>Cặp Đi Học - Balo Học Sinh Cho Bé Trai, Bé Gái Đựng Sách Vở Đi Học Chất Liệu Vải Dù Chống Nước, Chống Xước Nhiều Mẫu Mã</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>₫59.400</t>
+          <t>₫75.000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">537 </t>
+          <t>6k+</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7KvnGRc3KX</t>
+          <t>https://s.shopee.vn/9V0HqQTnw8</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m8usktdi4znr44.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lyau9pk0heap8e.webp</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>shopee_25894380610</t>
+          <t>shopee_44353562979</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>e8bc611ba60b6012c1f3bd265fbc14d3</t>
+          <t>91bc43a59ff4722f9739b38d08f8fec3</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2934,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>cặp sách nữ mới học sinh tiểu học lớp 1-3-6 ba lô giảm gánh nặng sức chứa lớn cho trẻ em từ 6-9-12 tuổi</t>
+          <t>Cặp Sách Balo Nam Trung Học Cơ Sở Dung Tích Lớn Balo Du Lịch Đơn Giản Thường Ngày Học Sinh Đại Học Nữ Sinh Trung Học</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>₫171.500</t>
+          <t>₫148.125</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">618 </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2919,22 +2959,22 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7ps3rMa9Je</t>
+          <t>https://s.shopee.vn/3qLv60pNQl</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rceq-m6inphl6rdzv99.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4r1emxgw7sg33.webp</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>shopee_29426973856</t>
+          <t>shopee_29319714034</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>f51863fcbfdfb6e0fbdefe2c0eae31d9</t>
+          <t>1b2485cfc5af956979aaaabf6466cd95</t>
         </is>
       </c>
     </row>
@@ -2946,47 +2986,47 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Balo nam nữ, Balo học sinh cấp 2 cấp 3, cặp sách nhiều ngăn đựng laptop chống nước thời trang Ba Vy FASHION BL04ABC</t>
+          <t>Móc Khoá Gấu Bông Mèo Đen Nhạc Sĩ Cầm Đàn, Charm Treo Túi Xách, Balo, Cặp Sách Cute Dễ Thương</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>₫360.000</t>
+          <t>₫38.000</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">252 </t>
+          <t xml:space="preserve">257 </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7fYdf3amed</t>
+          <t>https://s.shopee.vn/4LIBgvnTQh</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lxr83bilp1p72f.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825a2-mr03i9pl2gb03e.webp</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>shopee_23450241802</t>
+          <t>shopee_56554422157</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>8f20fdfa36820b8ebcb352fd6a2bdd14</t>
+          <t>d4a06624bf5c5d5a871ece29c3ed37d1</t>
         </is>
       </c>
     </row>
@@ -2998,47 +3038,47 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Balo học sinh siêu nhẹ hình thỏ, khủng long cho bé trai, bé gái từ lớp 3-7, chống thấm nước, cặp sách tiện dụng.</t>
+          <t>Cặp sách chống gù DIOOGLT Balo Phi Hành Gia Siêu Nhẹ Thoáng Khí Cho Bé Tiểu Học</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>₫149.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20k+</t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VU954j23E</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26960129769?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ratp-mb0jlqkwo5ihaf.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mck5l2ksms0se2.webp</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>shopee_29487599068</t>
+          <t>shopee_26960129769</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8a3407268157e4c6ca74e655288c802b</t>
+          <t>e091a6de578007c4c593b037ce489681</t>
         </is>
       </c>
     </row>
@@ -3050,47 +3090,47 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Balo đi học Hàn Quốc da trơn basic nam nữ cặp sách đi chơi du lịch thời trang size đại _BL024</t>
+          <t>Balo cho bé KNOTE cặp sách cấp 1 2 chất liệu vải sức chứa lớn kiểu dáng dễ thương dày dặn chống nước</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>₫75.000</t>
+          <t>₫329.000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>9k+</t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5LAisljfOD</t>
+          <t>https://s.shopee.vn/Lm2va2hWk</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7st6kwd27ra84.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4lh3n33z52oa2.webp</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>shopee_26826737964</t>
+          <t>shopee_27022611207</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>bd37aea996276aacb181cfd7ea217ee8</t>
+          <t>ec692d7a008482c100513fc23a742d29</t>
         </is>
       </c>
     </row>
@@ -3102,47 +3142,47 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Balo Chống Gù Cho Bé Trai Gái Chống Nước Ba lô cấp 1 Cặp Sách Học Sinh Tiểu Học hàng đẹ</t>
+          <t>Balo đi học nam nữ Cặp đi học unisex nhiều ngăn chống nước Luci Bag cặp sách đựng vừa laptop 15,6 inch basic B50</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>₫179.000</t>
+          <t>₫220.000</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">194 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q6zTghlNK</t>
+          <t>https://s.shopee.vn/40fLIJok5Y</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mc3u4jfjy2y2ed.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpz4z6mdgavg19.webp</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>shopee_27603042519</t>
+          <t>shopee_42151531320</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>c92046fbe4c81a2cacd610eb667ee412</t>
+          <t>6beca9328f8d8243e7e7689d147f535d</t>
         </is>
       </c>
     </row>
@@ -3154,47 +3194,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Balo nữ ba lô màu pastel dập sao lấp lánh tặng kèm charm, cặp sách nữ đi học đi chơi vải dù chống nước dung tích lớn</t>
+          <t>Balo cho bé BABYTREE cặp sách trẻ em chống gù lưng chất liệu cao cấp nhiều ngăn đa dạng màu sắc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>₫185.976</t>
+          <t>₫329.000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">193 </t>
+          <t xml:space="preserve">376 </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5fnZHNiOiJ</t>
+          <t>https://s.shopee.vn/5ArIgSkIit</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9npzlrtq12a7.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7ho5s8f22k6e0.webp</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>shopee_53913773253</t>
+          <t>shopee_28580011314</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>64d8facb296875fce2db55c4a502568c</t>
+          <t>7fc1214b5a8dd6dedcc8cfdb811729bd</t>
         </is>
       </c>
     </row>
@@ -3258,47 +3298,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Balo cho bé mẫu giáo bé trai bé gái , cặp sách trẻ em mầm non đi học từ 2 – 5 tuổi hoạ tiết hoạt hình dễ thương.</t>
+          <t>Balo capybara KNOTE cặp sách học sinh dày dặn form chuẩn cao cấp cho bé từ mầm non đến cấp 2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>₫84.900</t>
+          <t>₫329.000</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">254 </t>
+          <t xml:space="preserve">100 </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/60QPfzh82P</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28929879693?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdxo-m18b6z9hjgwu70.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7g8es7z0el404.webp</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>shopee_14092980912</t>
+          <t>shopee_28929879693</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>17e22a639aed7898dcbdd0166abe10fc</t>
+          <t>6ecfa5b1e98f1bd25ea777651b0c167d</t>
         </is>
       </c>
     </row>
@@ -3310,42 +3350,47 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>[CÓ SẴN] Balo thời trang Hàn Quốc, cặp sách đi học nữ dành cho học sinh, sinh viên, vừa laptop 15.6 inch, vải trượt nước</t>
+          <t>Balo nữ cặp đi học nữ chống nước nhiều ngăn Ba lô đựng sách vở vừa laptop 15.6inch tặng kèm túi nhỏ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>₫235.000</t>
+          <t>₫150.000</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>36%</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">163 </t>
+          <t xml:space="preserve">133 </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VMgGufE1W</t>
+          <t>https://s.shopee.vn/2LX7JFv5U7</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mni4ie25cyrl69.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp78pvnkj09a1c.webp</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>shopee_50259506478</t>
+          <t>shopee_29503296734</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>dd20357b48b5c440bacc85204408ba38</t>
+          <t>87f902ab5977e69dd916a834c8fa520a</t>
         </is>
       </c>
     </row>
@@ -3357,47 +3402,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BAGSMART Ba lô đựng laptop đại học Túi đựng sách chống nước cho máy tính xách tay 14 Inch, Ba lô đựng laptop du lịch thông thường dành cho nữ</t>
+          <t>Cặp sách đi học cấp 2, cấp 3 NATOLI Cặp đa năng, Balo đa năng nhiều ngăn BST Classic Multifunctional Backpack B17</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>₫502.200</t>
+          <t>₫459.000</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7k+</t>
+          <t xml:space="preserve">414 </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L3G4bfrMV</t>
+          <t>https://s.shopee.vn/2qTNuAtBST</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-824ie-mpvy8g1ga8zz5c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqzz2dv7rbwhcf.webp</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>shopee_29888660896</t>
+          <t>shopee_24182570256</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>59ab6e7a1109fa36ee5828bcf79a76b0</t>
+          <t>0dcaa35f40ce9f4b9e8ee68ae8be92db</t>
         </is>
       </c>
     </row>
@@ -3409,47 +3454,47 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cặp Đi Học - Balo Học Sinh Cho Bé Trai, Bé Gái Đựng Sách Vở Đi Học Chất Liệu Vải Dù Chống Nước, Chống Xước Nhiều Mẫu Mã</t>
+          <t>Balo nam nữ đi học chống nước nhiều ngăn quai đệm kèm gấu dễ thương cặp sách đựng laptop đi làm học sinh.b4015</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>₫75.000</t>
+          <t>₫175.855</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6k+</t>
+          <t xml:space="preserve">483 </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9V0HqQTnw8</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49605963749?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lyau9pk0heap8e.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqd4rh2c3bbj51.webp</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>shopee_44353562979</t>
+          <t>shopee_49605963749</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>91bc43a59ff4722f9739b38d08f8fec3</t>
+          <t>7edfe29c13da3e1a27746b323f3c3cf6</t>
         </is>
       </c>
     </row>
@@ -3461,47 +3506,47 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bộ áo mưa có lưng che balo - Bộ mưa Sơn Thủy đeo balo, cặp sách dành cho người lớn, nhựa PVC siêu dai, siêu chống thấm</t>
+          <t>Balo nữ ba lô màu pastel dập sao lấp lánh tặng kèm charm, cặp sách nữ đi học đi chơivải dù chống nước dung tích lớn</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>₫315.000</t>
+          <t>₫188.823</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">429 </t>
+          <t xml:space="preserve">144 </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9Kgre7URH7</t>
+          <t>https://s.shopee.vn/8KoKSHYFJ5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mb6zdgvbcno7fb.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9npbfgsooxbd.webp</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>shopee_40405228242</t>
+          <t>shopee_43232530256</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>f022cdf0097fd95404b19b41ea95b780</t>
+          <t>b9eae3656b446923e4f5c54b4410286f</t>
         </is>
       </c>
     </row>
@@ -3513,47 +3558,47 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Balo Chống Gù Cho Bé Tiểu Học (Tặng 10 Món Phụ Kiện) Chống Nước, Cặp Sách Đẹp Cho Học Sinh</t>
+          <t>(Full Hộp) Mở Bán Kèm Móc Khóa Balo KittyCow Size32 Size40 DaPu thời trang đi du lịch đi học đựng sách vở A4 BL98</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>₫183.000</t>
+          <t>₫125.000</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">81 </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9pd8F2SXGE</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47053854972?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-821f8-mh97n66xzi8856.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq53gn91a41u1b.webp</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>shopee_49101749110</t>
+          <t>shopee_47053854972</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>261e8d20c3c7d47746ab9b0bd5979d8a</t>
+          <t>3c0f64d069b40707ad03d8a171dda8ba</t>
         </is>
       </c>
     </row>
@@ -3565,47 +3610,47 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Móc Khóa Chữ Hoạt Hình Sáng Tạo Dễ Thương Mica Trong Suốt, trang trí góc học tập, Treo cặp sách balo</t>
+          <t>Balo đi học đi chơi hình gấu đựng quần áo tập sách bl mars hộp vuông</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>₫5.862</t>
+          <t>₫46.920</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">339 </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9fJi2jTAbD</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25820732217?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8260w-mj42xbhbr1ms15.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfyxs1j5vrwub2.webp</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>shopee_57804151605</t>
+          <t>shopee_25820732217</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>870c6635923158e4d5b34b43fde54755</t>
+          <t>b47dccb58d653c5e32b68f93a031d29f</t>
         </is>
       </c>
     </row>
@@ -3617,42 +3662,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Balo Chống Gù Cho Bé Trai Gái Chống Nước Ba lô cấp 1 Cặp Sách Học Sinh Tiểu Học hàng đẹ</t>
+          <t>Balo Chống Gù Cho Bé Cấp 1 Zoyzoii Chính Hãng Cặp Đi Học Cao Cấp Cho Bé Trai Bé Gái Lớp 1 2 3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>₫175.900</t>
+          <t>₫879.000</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>31%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3k+</t>
+          <t xml:space="preserve">151 </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AAFydeRGaK</t>
+          <t>https://s.shopee.vn/1Lea7PytVp</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwmhi304xfx509.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9blb8eassxza7.webp</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>shopee_40215001645</t>
+          <t>shopee_23461552475</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>3b3b6da43403395f6227f940fed57c9c</t>
+          <t>3fa3fc4cc39b4079a91b8c5afa2100c6</t>
         </is>
       </c>
     </row>
@@ -3664,47 +3714,47 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cặp Đi Học - Balo Học Sinh Cho Bé Trai, Bé Gái Đựng Sách Vở Đi Học Chất Liệu Vải Dù Chống Nước, Chống Xước</t>
+          <t>Tấm lót đáy balo hổ trợ giảm mất form, giảm xụ phần đáy balo cặp sách khi đựng sách vở laptop nặng</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>₫79.000</t>
+          <t>₫35.000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">201 </t>
+          <t>40k+</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9zwYRLRtvJ</t>
+          <t>https://s.shopee.vn/BScjH3Krh</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rd60-m759lrd8do980e.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfngwemcu6fc39.webp</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>shopee_26628972888</t>
+          <t>shopee_22931544947</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>d5dbab592a1aeb83df2ff2282f28afda</t>
+          <t>4c1404834ecc6a9c4dfd7b3f1ffdde3f</t>
         </is>
       </c>
     </row>
@@ -3716,47 +3766,47 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Combo 10 Khoá cài, khoá mũ bảo hiểm, balo, cặp sách 2cm, 2,5cm</t>
+          <t>Balo nữ ba lô màu pastel dập sao lấp lánh tặng kèm charm, cặp sách nữ đi học đi chơi vải dù chống nước dung tích lớn</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>₫9.950</t>
+          <t>₫185.976</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">575 </t>
+          <t xml:space="preserve">193 </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AUsp2GPzuQ</t>
+          <t>https://s.shopee.vn/5fnZHNiOiJ</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lys7h8lexpr5f8.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9npzlrtq12a7.webp</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>shopee_24533615860</t>
+          <t>shopee_53913773253</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>17d50a19da6c39d946cd63355f13f732</t>
+          <t>64d8facb296875fce2db55c4a502568c</t>
         </is>
       </c>
     </row>
@@ -3768,47 +3818,47 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Móc khóa mica in Logo của các trường đại học, cao đẳng... móc khóa treo balo, cặp sách</t>
+          <t>( Tặng Kèm Móc Khoá Và Huy Hiệu) Balo Chống Gù Cho Bé Trai Gái Chống Nước Balo Cấp 1 Cặp Sách Học Sinh Tiểu Học</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>₫13.720</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">98 </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AKZOpxQdFP</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26378174133?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meyozrxgadqd46.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnk7w220c45e67.webp</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>shopee_40126123352</t>
+          <t>shopee_26378174133</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1d1d7562ccac7647a8ba79409af08336</t>
+          <t>4684bb1d9114f9408dcab981a59dc044</t>
         </is>
       </c>
     </row>
@@ -3820,47 +3870,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Balo nữ đi học thời trang, cặp sách Balo nữ cấp 1, cấp 2 đi học dễ thương, Balo ulzzang có ngăn trong suốt đựng gấu</t>
+          <t>Balo đi học Hàn Quốc da trơn basic nam nữ cặp sách đi chơi du lịch thời trang size đại _BL024</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>₫285.000</t>
+          <t>₫75.000</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">325 </t>
+          <t>9k+</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8AUuFyYse0</t>
+          <t>https://s.shopee.vn/5LAisljfOD</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbg6he3k7k906c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7st6kwd27ra84.webp</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>shopee_42005984047</t>
+          <t>shopee_26826737964</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>b1739845eac27156066fd41b2d3699fd</t>
+          <t>bd37aea996276aacb181cfd7ea217ee8</t>
         </is>
       </c>
     </row>
@@ -3872,42 +3922,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Móc khoá quả lông đáng yêu treo balo cặp sách mq25</t>
+          <t>Balo nữ ba lô màu pastel thỏ chấm bi tặng kèm charm, cặp sách nữ đi học đi chơi da pu chống nước dung tích lớn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>₫18.500</t>
+          <t>₫197.758</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>29%</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">95 </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/80BU3fZVyz</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/52363877345?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ra2m-mb902olm3uyee5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9nrot8eaddf5.webp</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>shopee_26937823110</t>
+          <t>shopee_52363877345</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>73961464e6eea62b303bcb8c5d291708</t>
+          <t>29fea3bbde0ab37884bd157649d7b429</t>
         </is>
       </c>
     </row>
@@ -3919,47 +3974,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Balo nữ dung tích lớn mẫu mới hình chú cún con dễ thương cặp sách học sinh trung học cơ sở đa năng nhẹ dễ thương hàn</t>
+          <t>Balo nữ ba lô màu pastel chấm bi đính cánh thiên thần tặng kèm charm, cặp sách nữ đi học đi chơi dung tích lớn</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>₫199.999</t>
+          <t>₫214.850</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">165 </t>
+          <t xml:space="preserve">18 </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8V7keaXby6</t>
+          <t>https://s.shopee.vn/8pkb3CWLIC</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgaw75fd30uia3.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9nr5gz9f5t97.webp</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>shopee_28293446174</t>
+          <t>shopee_48714896773</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>dab705a1203ea9356c71f18b2af0af00</t>
+          <t>5312e243c81747a156146b99fd503c9b</t>
         </is>
       </c>
     </row>
@@ -3971,22 +4026,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Balo nữ ba lô màu pastel dập sao lấp lánh tặng kèm charm, cặp sách nữ đi học đi chơivải dù chống nước dung tích lớn</t>
+          <t>Balo nữ ba lô kẻ caro phối chấm bi đính nơ tặng kèm hai charm siêu xinh, cặp sách nữ pastel đi học đi chơi dung tích lớn</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>₫188.823</t>
+          <t>₫249.035</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">144 </t>
+          <t xml:space="preserve">18 </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3996,22 +4051,22 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8KoKSHYFJ5</t>
+          <t>https://s.shopee.vn/8fRAqtWydB</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9npbfgsooxbd.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9non44revg15.webp</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>shopee_43232530256</t>
+          <t>shopee_27845398656</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>b9eae3656b446923e4f5c54b4410286f</t>
+          <t>1177b4557297482cc58e66fb31d73a9f</t>
         </is>
       </c>
     </row>
@@ -4023,47 +4078,47 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Balo nữ ba lô màu pastel chấm bi đính cánh thiên thần tặng kèm charm, cặp sách nữ đi học đi chơi dung tích lớn</t>
+          <t>BAGSMART Ba Lô Thường Ngày Du Lịch 14.3inch Ba Lô Laptop Daypack SchoolBag Cao Đẳng Túi Đựng Sách Làm Việc Mặt Sau Máy Tính Dễ Thương Chống Nước</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>₫214.850</t>
+          <t>₫586.280</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8pkb3CWLIC</t>
+          <t>https://s.shopee.vn/W5T7t24Bn</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9nr5gz9f5t97.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-820l4-mq1nly9hts018a.webp</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>shopee_48714896773</t>
+          <t>shopee_43556339364</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>5312e243c81747a156146b99fd503c9b</t>
+          <t>ac48e54041e1cdc1480c78e7c8370856</t>
         </is>
       </c>
     </row>
@@ -4075,47 +4130,47 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Balo nữ ba lô kẻ caro phối chấm bi đính nơ tặng kèm hai charm siêu xinh, cặp sách nữ pastel đi học đi chơi dung tích lớn</t>
+          <t>Balo Chống Gù Cho Bé Trai Gái Chống Nước Ba lô cấp 1 Cặp Sách Học Sinh Tiểu Học hàng đẹ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>₫249.035</t>
+          <t>₫179.000</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 </t>
+          <t xml:space="preserve">194 </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8fRAqtWydB</t>
+          <t>https://s.shopee.vn/5q6zTghlNK</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9non44revg15.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mc3u4jfjy2y2ed.webp</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>shopee_27845398656</t>
+          <t>shopee_27603042519</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1177b4557297482cc58e66fb31d73a9f</t>
+          <t>c92046fbe4c81a2cacd610eb667ee412</t>
         </is>
       </c>
     </row>
@@ -4127,47 +4182,47 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Balo Nữ Cỡ Lớn Thiết Kế Mới Đáng Yêu Thời Trang Theo Phong Cách Nhật Hàn Cho Nữ ,cặp sách nữ#1199</t>
+          <t>Móc khóa gấu âm nhạc dễ thương – Treo balo, cặp sách, chìa khóa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>₫165.505</t>
+          <t>₫10.790</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">391 </t>
+          <t xml:space="preserve">187 </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9ANRRoV4cI</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40057529130?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mos0yfj912j108.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbufoq7n67w258.webp</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>shopee_40058200626</t>
+          <t>shopee_40057529130</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>907c2c184e3fd1884ed1bc00c2cf9493</t>
+          <t>b489b322e01fcf442d8aecbf2dda39d2</t>
         </is>
       </c>
     </row>
@@ -4179,47 +4234,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bộ áo mưa có lưng che balo - Bộ mưa Sơn Thủy đeo balo, cặp sách dành cho người lớn, nhựa PVC siêu dai, chống thấm ST2</t>
+          <t>Balo nam nữ thời trang đi học, cặp sách nữ đi học nhiều ngăn hàn quốc, ba lô đi chơi đi làm, balo học sinh cấp 2 BL12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>₫315.000</t>
+          <t>₫160.000</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">159 </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9041FVVhxH</t>
+          <t>https://s.shopee.vn/19CWy3yDh</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mb6yz34mxal3e2.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq1s7ar07j0s59.webp</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>shopee_43705228144</t>
+          <t>shopee_51313045223</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>08a01c38c80bbb1602efe02b17d6c404</t>
+          <t>8e437d27a785343afc8f2c4bdd9fac52</t>
         </is>
       </c>
     </row>
@@ -4231,47 +4286,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Balo chống gù học viên cấp 1 ZMCG-40 Cặp sách tiểu học chống nước, cặp chống gù cho bé trai, bé gái</t>
+          <t>Balo nam nữ đi học chống nước nhiều ngăn quai đệm kèm gấu dễ thương ZONY cặp sách đựng laptop đi làm học sinh 291</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>₫325.000</t>
+          <t>₫275.000</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">157 </t>
+          <t xml:space="preserve">112 </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Vy0JiyGAq</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/16453035442?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqrucxfp297182.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lw81j6clp9sp25.webp</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>shopee_29716592772</t>
+          <t>shopee_16453035442</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0d29ec7969c6034e65d4783ef7eb0197</t>
+          <t>0eb62825803109c6cf68e94e11852dd3</t>
         </is>
       </c>
     </row>
@@ -4283,22 +4338,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Balo Chống Gù Cho Bé Cấp 1 Zoyzoii Chính Hãng Cặp Đi Học Cao Cấp Cho Bé Trai Bé Gái Lớp 1 2 3</t>
+          <t>Balo học sinh siêu nhẹ hình thỏ, khủng long cho bé trai, bé gái từ lớp 3-7, chống thấm nước, cặp sách tiện dụng.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>₫879.000</t>
+          <t>₫149.000</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">151 </t>
+          <t>20k+</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4308,22 +4363,22 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Lea7PytVp</t>
+          <t>https://s.shopee.vn/5VU954j23E</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9blb8eassxza7.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ratp-mb0jlqkwo5ihaf.webp</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>shopee_23461552475</t>
+          <t>shopee_29487599068</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>3fa3fc4cc39b4079a91b8c5afa2100c6</t>
+          <t>8a3407268157e4c6ca74e655288c802b</t>
         </is>
       </c>
     </row>
@@ -4335,47 +4390,47 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Balo đi học Nam -Nữ gấu Quảng Châu size to 40cm đựng sách vở a4 cùng laptop-chất liệu da dày đẹp,quai bản to đệm lưới êm</t>
+          <t>Balo chống gù học viên cấp 1 ZMCG-40 Cặp sách tiểu học chống nước, cặp chống gù cho bé trai, bé gái</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>₫125.000</t>
+          <t>₫325.000</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">91 </t>
+          <t xml:space="preserve">157 </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qaqiKwzUw</t>
+          <t>https://s.shopee.vn/1Vy0JiyGAq</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqqa78qtw3r4fa.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqrucxfp297182.webp</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>shopee_47813871518</t>
+          <t>shopee_29716592772</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>4d2359043c80420917f6145d976d5c67</t>
+          <t>0d29ec7969c6034e65d4783ef7eb0197</t>
         </is>
       </c>
     </row>
@@ -4387,22 +4442,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ba lô học sinh trung học cơ sở dung tích lớn cặp sách học sinh trung học phổ thông cảm giác thiết kế phong cách</t>
+          <t>Balo nữ đi học thời trang hàn quốc, cặp sách nữ đi học dễ thương tặng kèm 2 GẤU, Balo ulzzang chất liệu vải chống nước</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>₫186.260</t>
+          <t>₫280.000</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">137 </t>
+          <t xml:space="preserve">133 </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4412,22 +4467,22 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gHQW1xcpv</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41655991167?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8226v-mhlk0dutowld6a.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbexyh48faaf6c.webp</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>shopee_44476842293</t>
+          <t>shopee_41655991167</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>a21d70967e678b1e2b093dc185ff4d80</t>
+          <t>9c59b07ad414182144f476e85b0025a9</t>
         </is>
       </c>
     </row>
@@ -4439,47 +4494,47 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Balo nữ đi học cặp đi học nữ nhiều ngăn thời trang Ulzzang Hàn Quốc vải dù mịn chống nước.#1199</t>
+          <t>[MUA 1 TẶNG 1] Cặp sách balo cho học sinh tiểu học Kitty Kuromi 36x27x19</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>₫178.888</t>
+          <t>₫259.000</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">152 </t>
+          <t xml:space="preserve">126 </t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDh6wvip2</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24305818849?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp7tfg1getc2c2.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn8t7vbmg3k4f1.webp</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>shopee_41414473248</t>
+          <t>shopee_24305818849</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>4ea75d5b272de7717079aeab16a99eac</t>
+          <t>ac4cb46bc5ac0d6ade31cc3c5ccb2c9e</t>
         </is>
       </c>
     </row>
@@ -4491,47 +4546,47 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Balo nữ đi học, cặp sách nữ đi học thời trang hàn quốc, Balo nữ dễ thương ulzzang có ngăn trong suốt đựng gấu</t>
+          <t>Móc khoá May mắn tới treo balo cặp sách tăng bạn bè người yêu nlp shop</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>₫279.000</t>
+          <t>₫10.360</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">150 </t>
+          <t xml:space="preserve">374 </t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20uGudwMA1</t>
+          <t>https://s.shopee.vn/Lm2va2hXn</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meaw22za9czkf5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpyf2jj7qd4w7d.webp</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>shopee_24796595464</t>
+          <t>shopee_53305443993</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>bfef0c11190f01dfcb638623414eda63</t>
+          <t>92cbb814d51fb41916a1a2c189deed5e</t>
         </is>
       </c>
     </row>
@@ -4543,22 +4598,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cặp Sách Mẫu Mới Nữ Sinh Trung Học Phổ Thông Ba Lô Đeo Hai Vai Dung Tích Lớn Dễ Phối Gọn Nhẹ</t>
+          <t>Balo nam nữ đi học cặp sách đi học thời trang hàn quốc, balo ulzzang nhiều ngăn đựng laptop chống nước</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>₫199.140</t>
+          <t>₫278.274</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">207 </t>
+          <t xml:space="preserve">296 </t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4568,22 +4623,22 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2VqXVYuS98</t>
+          <t>https://s.shopee.vn/6fg6TDeagL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rfhs-m43ludmokdx6f0.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwoi0lxc00d751.webp</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>shopee_28021377904</t>
+          <t>shopee_29802157458</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>91d6b0e94de555b8cc30b2eee415a805</t>
+          <t>1282bb699496389d1169a7da1c01fb13</t>
         </is>
       </c>
     </row>
@@ -4595,47 +4650,47 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Balo nữ cặp đi học nữ chống nước nhiều ngăn Ba lô đựng sách vở vừa laptop 15.6inch tặng kèm túi nhỏ</t>
+          <t>Balo da trơn nam nữ đi học cặp sách thời trang đơn giản nhiều ngăn có ngăn bí mật chống sốc BL29</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>₫150.000</t>
+          <t>₫184.000</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">133 </t>
+          <t xml:space="preserve">241 </t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LX7JFv5U7</t>
+          <t>https://s.shopee.vn/70IwrpdK0R</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp78pvnkj09a1c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ly53e68gz1k16b.webp</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>shopee_29503296734</t>
+          <t>shopee_25258609297</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>87f902ab5977e69dd916a834c8fa520a</t>
+          <t>8f9f7bce034f723906e0dfe6f71d77bf</t>
         </is>
       </c>
     </row>
@@ -4647,22 +4702,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Balo nữ đi học thời trang hàn quốc,cặp sách đi học nữ dễ thương, Balo ulzzang nhiều ngăn chống nước</t>
+          <t>Balo nam nữ, Balo học sinh cấp 2 cấp 3, cặp sách nhiều ngăn đựng laptop chống nước thời trang Ba Vy FASHION BL04ABC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>₫233.574</t>
+          <t>₫360.000</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t xml:space="preserve">252 </t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4672,22 +4727,22 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BScjH3Ksi</t>
+          <t>https://s.shopee.vn/7fYdf3amed</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdwu-ly2qb9aobi7n85.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lxr83bilp1p72f.webp</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>shopee_26006223317</t>
+          <t>shopee_23450241802</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0059bf9255b21c77db6538cee95d7a6f</t>
+          <t>8f20fdfa36820b8ebcb352fd6a2bdd14</t>
         </is>
       </c>
     </row>
@@ -4699,47 +4754,47 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Balo nam nữ thời trang đi học, cặp sách nữ đi học nhiều ngăn hàn quốc, ba lô đi chơi đi làm, balo học sinh cấp 2 BL12</t>
+          <t>Móc treo ba lô, cặp sách hai đầu bằng thép không gỉ – móc treo bên cạnh bàn làm việc, bàn học – có thể tháo rời</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>₫160.000</t>
+          <t>₫14.799</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">159 </t>
+          <t>9k+</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/19CWy3yDh</t>
+          <t>https://s.shopee.vn/4qESHqlZOn</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq1s7ar07j0s59.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfdsynptw1e2db.webp</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>shopee_51313045223</t>
+          <t>shopee_25597309034</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>8e437d27a785343afc8f2c4bdd9fac52</t>
+          <t>970a3ab9a1d51ee6e7d60aa6bce8180e</t>
         </is>
       </c>
     </row>
@@ -4751,47 +4806,47 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Balo Phong Cách Hàn Quốc, Balo Cặp Sách Học Sinh Tiểu Học Bé Gái Bé Trai Có Nhiều Ngăn Chứa Tiện Lợi</t>
+          <t>Bộ áo mưa có lưng che balo - Bộ mưa Sơn Thủy đeo balo, cặp sách dành cho người lớn, nhựa PVC siêu dai, chống thấm ST2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>₫49.000</t>
+          <t>₫315.000</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W5T7t24Co</t>
+          <t>https://s.shopee.vn/9041FVVhxH</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqfl0mzey9s16d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mb6yz34mxal3e2.webp</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>shopee_53863661316</t>
+          <t>shopee_43705228144</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>7c1f70fb120eed704daa822c02144b4a</t>
+          <t>08a01c38c80bbb1602efe02b17d6c404</t>
         </is>
       </c>
     </row>
@@ -4803,47 +4858,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Móc khoá May mắn tới treo balo cặp sách tăng bạn bè người yêu nlp shop</t>
+          <t>Balo Cặp Sách Bản Vuông Siêu Nhẹ Hình Kuromi Dễ Thương – Chống Gù, Dành Cho Bé Gái Lớp 1–6 tuổi H345</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>₫10.360</t>
+          <t>₫211.220</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">374 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/Lm2va2hXn</t>
+          <t>https://s.shopee.vn/qiJWV0nWu</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpyf2jj7qd4w7d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8261z-mllh2h0yz8jz26.webp</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>shopee_53305443993</t>
+          <t>shopee_55356948413</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>92cbb814d51fb41916a1a2c189deed5e</t>
+          <t>20c277c8c2144c06635b52a16d259dc0</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4910,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Balo Cặp Sách Bản Vuông Siêu Nhẹ Hình Kuromi Dễ Thương – Chống Gù, Dành Cho Bé Gái Lớp 1–6 tuổi H345</t>
+          <t>Balo cho bé mẫu giáo bé trai bé gái, cặp sách trẻ em mầm non đi học từ 2–5 tuổi hoạt hình dễ thương</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>₫211.220</t>
+          <t>₫59.000</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4870,32 +4925,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">755 </t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/qiJWV0nWu</t>
+          <t>https://s.shopee.vn/111jio0AAw</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8261z-mllh2h0yz8jz26.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m39yvtz753gc26.webp</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>shopee_55356948413</t>
+          <t>shopee_13187078063</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>20c277c8c2144c06635b52a16d259dc0</t>
+          <t>2d7286552ad3ca83a40b81a325bcc370</t>
         </is>
       </c>
     </row>
@@ -4907,22 +4962,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Balo học sinh cấp 2 cấp 3 ONETOP nhiều ngăn chống nước tốt , cặp sách nam đi học đựng laptop 15,6 inch</t>
+          <t>Bộ áo mưa có lưng che balo - Bộ mưa Sơn Thủy đeo balo, cặp sách dành cho người lớn, nhựa PVC siêu dai, siêu chống thấm</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>₫155.000</t>
+          <t>₫315.000</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">34 </t>
+          <t xml:space="preserve">429 </t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4932,22 +4987,22 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/gOtKC1Qrt</t>
+          <t>https://s.shopee.vn/9Kgre7URH7</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq7kp8nih69s36.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mb6zdgvbcno7fb.webp</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>shopee_52508184318</t>
+          <t>shopee_40405228242</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>9b5b6c0b17220c4a82f6864a28cdd1ae</t>
+          <t>f022cdf0097fd95404b19b41ea95b780</t>
         </is>
       </c>
     </row>
@@ -4959,22 +5014,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Balo lười phong cách mùa xuân mới dành cho học sinh trung học cơ sở nữ ba lô du lịch dung tích lớn cặp sách sinh viên</t>
+          <t>Balo nữ đi học thời trang, cặp sách Balo nữ cấp 1, cấp 2 đi học dễ thương, Balo ulzzang có ngăn trong suốt đựng gấu</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>₫205.884</t>
+          <t>₫285.000</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">149 </t>
+          <t xml:space="preserve">325 </t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4984,22 +5039,22 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1BL9v6zWr0</t>
+          <t>https://s.shopee.vn/8AUuFyYse0</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-822zx-mhx0xrhv2cqo8b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbg6he3k7k906c.webp</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>shopee_47952710379</t>
+          <t>shopee_42005984047</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2a697511d7ddcce19952afcd199f5e5a</t>
+          <t>b1739845eac27156066fd41b2d3699fd</t>
         </is>
       </c>
     </row>
@@ -5011,22 +5066,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>[HÀNG ĐẸP] Balo chống gù quai ngang, chống thấm nước, cặp sách đi học lớp 1 - 5, học sinh cấp 1</t>
+          <t>Balo nữ đi học, cặp sách nữ đi học thời trang hàn quốc, Balo nữ dễ thương ulzzang có ngăn trong suốt đựng gấu</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>₫206.994</t>
+          <t>₫279.000</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">150 </t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5036,22 +5091,22 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/111jio0ABz</t>
+          <t>https://s.shopee.vn/20uGudwMA1</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdyx-ly2qbl86uynnc1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meaw22za9czkf5.webp</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>shopee_26806049216</t>
+          <t>shopee_24796595464</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>03b51348b72b2aba4b499140f523b380</t>
+          <t>bfef0c11190f01dfcb638623414eda63</t>
         </is>
       </c>
     </row>
@@ -5063,22 +5118,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cặp sách học sinh tiểu học Ba lô học sinh nam nữ một hai ba bốn năm năm sáu lớp chống nước phim hoạt hình trẻ em</t>
+          <t>Balo nữ đi học thời trang hàn quốc,cặp sách đi học nữ dễ thương, Balo ulzzang nhiều ngăn chống nước</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>₫316.344</t>
+          <t>₫279.000</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">864 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5088,22 +5143,22 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4AylUco6lc</t>
+          <t>https://s.shopee.vn/4VbbtEmq4h</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ravi-masimx5q5h0i92.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwx4dfpz853td0.webp</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>shopee_29837378357</t>
+          <t>shopee_28402501227</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>3e3fd27274e1d3caa643aa1a7ce82b26</t>
+          <t>7b0200a706275c55ba0ff6fd8a228be8</t>
         </is>
       </c>
     </row>
@@ -5115,47 +5170,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cặp sách học sinh tiểu học mẫu mới hoạt hình ba lô culomi cho bé gái dễ thương lớp 1-3-6</t>
+          <t>Balo Nữ Cỡ Lớn Thiết Kế Mới Đáng Yêu Thời Trang Theo Phong Cách Nhật Hàn Cho Nữ ,cặp sách nữ#1199</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>₫193.835</t>
+          <t>₫165.505</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">724 </t>
+          <t xml:space="preserve">391 </t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40fLIJok6b</t>
+          <t>https://s.shopee.vn/9ANRRoV4cI</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ra24-mb8k16ca66sp92.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mos0yfj912j108.webp</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>shopee_43805350210</t>
+          <t>shopee_40058200626</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2ca5ef9b610933c43628fe8fe1c834c2</t>
+          <t>907c2c184e3fd1884ed1bc00c2cf9493</t>
         </is>
       </c>
     </row>
@@ -5167,47 +5222,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Mèo bông treo cặp sách balo + Còi Kêu Bíp Bíp đáng yêu ga12</t>
+          <t>Balo Chống Gù Thẻ Hình Kurumi Cho Bé Trai Gái Chống Nước Ba lô cấp 1 ( bé lớp 2-6) Cặp Sách Học Sinh Tiểu Học</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>₫14.980</t>
+          <t>₫170.000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">127 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4VbbtEmq5i</t>
+          <t>https://s.shopee.vn/2g9xhrtonQ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmr6l8zrnpj4dc.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m6o43wxx3b6g3f.webp</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>shopee_25688943433</t>
+          <t>shopee_24341874090</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>a7f7e543b784476efb4a9b97b13aa2e3</t>
+          <t>44be2ce255f511ab666351b32b43ffa1</t>
         </is>
       </c>
     </row>
@@ -5219,47 +5274,47 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Móc Khoá Gấu Bông Mèo Đen Nhạc Sĩ Cầm Đàn, Charm Treo Túi Xách, Balo, Cặp Sách Cute Dễ Thương</t>
+          <t>Balo cho bé mẫu giáo bé trai bé gái , cặp sách trẻ em mầm non đi học từ 2 – 5 tuổi hoạ tiết hoạt hình dễ thương.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>₫38.000</t>
+          <t>₫84.900</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">257 </t>
+          <t xml:space="preserve">254 </t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LIBgvnTQh</t>
+          <t>https://s.shopee.vn/60QPfzh82P</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825a2-mr03i9pl2gb03e.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdxo-m18b6z9hjgwu70.webp</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>shopee_56554422157</t>
+          <t>shopee_14092980912</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>d4a06624bf5c5d5a871ece29c3ed37d1</t>
+          <t>17e22a639aed7898dcbdd0166abe10fc</t>
         </is>
       </c>
     </row>
@@ -5271,47 +5326,47 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Balo mầm non cho bé trai bé gái ZENZIN KIDS từ 1-5 tuổi đi, cặp đi học mẫu giáo trẻ em đựng quần áo bỉm sữa, sách vở</t>
+          <t>Balo da đi học nam nữ, balo da nhiều ngăn đi học đi chơi, cặp sách nữ thời trang, ba lô chống nước BL13</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>₫96.000</t>
+          <t>₫189.000</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">115 </t>
+          <t xml:space="preserve">580 </t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4qESHqlZPo</t>
+          <t>https://s.shopee.vn/4LIBgvnTPe</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mesfiz06vpc720.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq1toufns5xqe5.webp</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>shopee_25054837757</t>
+          <t>shopee_56263034976</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>52d650122b1aed9b58fcc31463c843ed</t>
+          <t>a4b9f909bc4490bc5500660fee713ea0</t>
         </is>
       </c>
     </row>
@@ -5323,47 +5378,47 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ba lô kiểu mới, ba lô nữ Hàn Quốc, màu tương phản đơn giản, dễ kết hợp với cặp sách học sinh trung học, phong cách đại h</t>
+          <t>Combo 10 Khoá cài, khoá mũ bảo hiểm, balo, cặp sách 2cm, 2,5cm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>₫213.002</t>
+          <t>₫9.950</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">210 </t>
+          <t xml:space="preserve">575 </t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4fv25XmCkn</t>
+          <t>https://s.shopee.vn/AUsp2GPzuQ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rfi8-m3wemjsamlyabe.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lys7h8lexpr5f8.webp</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>shopee_27220948957</t>
+          <t>shopee_24533615860</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4a38235f279d62a8a6f5b6299d693122</t>
+          <t>17d50a19da6c39d946cd63355f13f732</t>
         </is>
       </c>
     </row>
@@ -5375,42 +5430,47 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Móc khoá chuột treo balo cặp sách quà tặng mt10</t>
+          <t>Balo Học Sinh Cặp Sách Đi Học Họa Tiết Thêu BA47</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>₫16.000</t>
+          <t>₫234.220</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>6%</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">314 </t>
+          <t xml:space="preserve">98 </t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5ArIgSkIju</t>
+          <t>https://s.shopee.vn/2qTNuAtBTU</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lv5jhqjgi4mxf1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjv7sxjq68sgbb.webp</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>shopee_25179189888</t>
+          <t>shopee_50405256141</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>4bdf5640a65b16746e18b597166f5a19</t>
+          <t>7d98b70caa611161420854532b83efd9</t>
         </is>
       </c>
     </row>
@@ -5422,47 +5482,47 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mẫu mới Balo chống gù cho học sinh cấp 1, Cặp sách chống gù chống gù cho học sinh lớp 1-lớp 6</t>
+          <t>Balo nữ đi học cặp đi học nữ nhiều ngăn thời trang Ulzzang Hàn Quốc vải dù mịn chống nước.#1199</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>₫299.000</t>
+          <t>₫178.888</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 </t>
+          <t xml:space="preserve">152 </t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/50XsU9kw4t</t>
+          <t>https://s.shopee.vn/2BDh6wvip2</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mazdxurn05vle5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp7tfg1getc2c2.webp</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>shopee_23016169658</t>
+          <t>shopee_41414473248</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>9f422e02962dd73972a0884d27424fee</t>
+          <t>4ea75d5b272de7717079aeab16a99eac</t>
         </is>
       </c>
     </row>
@@ -5474,47 +5534,47 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Balo Học Sinh Cặp Sách Đi Học Họa Tiết Thêu BA47</t>
+          <t>Làn Giỏ Gắn Sau Baga Xe Đạp Đựng Balo - Cặp Sách - Đồ Đi Chợ Hàng To Dày Chắc Chắn Loại Xịn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>₫234.220</t>
+          <t>₫126.100</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">98 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2qTNuAtBTU</t>
+          <t>https://s.shopee.vn/3g2Uthq0li</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjv7sxjq68sgbb.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjc8iqfydvr903.webp</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>shopee_50405256141</t>
+          <t>shopee_24162034749</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>7d98b70caa611161420854532b83efd9</t>
+          <t>13b40fb16a414611a8b80db0aebd3b59</t>
         </is>
       </c>
     </row>
@@ -5526,47 +5586,47 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Balo nữ đi học thời trang hàn quốc, cặp sách nữ đi học dễ thương tặng kèm 2 GẤU, Balo ulzzang chất liệu vải chống nước</t>
+          <t>Balo đi học nam nữ M4M NEW BASIC Backpack BM002 Cặp sách chống nước nhiều ngăn đựng laptop 15.6 inch</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>₫280.000</t>
+          <t>₫400.366</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">133 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41655991167?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29487759408?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbexyh48faaf6c.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mlug651sp72982.webp</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>shopee_41655991167</t>
+          <t>shopee_29487759408</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>9c59b07ad414182144f476e85b0025a9</t>
+          <t>edc725922ec1225162460fc0a64cd9ef</t>
         </is>
       </c>
     </row>
@@ -5578,47 +5638,47 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Balo đi học đi chơi hình gấu đựng quần áo tập sách bl mars hộp vuông</t>
+          <t>Balo JD V2 Nhiều Sticker Nhỏ Cá Tính | Cặp Đi Học Đựng Sách Vở Laptop 15.6 Inch Chất Dù Chống Nước Size 42cm</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>₫46.920</t>
+          <t>₫275.000</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">339 </t>
+          <t xml:space="preserve">51 </t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25820732217?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51313756213?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfyxs1j5vrwub2.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqhbmw3n8mpuce.webp</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>shopee_25820732217</t>
+          <t>shopee_51313756213</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>b47dccb58d653c5e32b68f93a031d29f</t>
+          <t>0414d16c37333b82dc446aebf28bf5cb</t>
         </is>
       </c>
     </row>
@@ -5630,22 +5690,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Móc khóa gấu âm nhạc dễ thương – Treo balo, cặp sách, chìa khóa</t>
+          <t>Móc Khóa Chữ Hoạt Hình Sáng Tạo Dễ Thương Mica Trong Suốt, trang trí góc học tập, Treo cặp sách balo</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>₫10.790</t>
+          <t>₫5.862</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">187 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5655,22 +5715,22 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40057529130?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/9fJi2jTAbD</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbufoq7n67w258.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8260w-mj42xbhbr1ms15.webp</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>shopee_40057529130</t>
+          <t>shopee_57804151605</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>b489b322e01fcf442d8aecbf2dda39d2</t>
+          <t>870c6635923158e4d5b34b43fde54755</t>
         </is>
       </c>
     </row>
@@ -5682,47 +5742,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cặp sách hoạt hình mẫu giáo mẫu giáo mẫu mới cho bé Sesame túi nhỏ chất liệu lặn mini gọn nhẹ ba lô trẻ em</t>
+          <t>Móc khoá lông quái vật một mắt dùng treo balo cặp sách mh02</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>₫208.937</t>
+          <t>₫15.789</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>7k+</t>
+          <t xml:space="preserve">332 </t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24770824608?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/6pzWfWdxLM</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rcey-ltax6wnln9c512.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqojmetiqcjx88.webp</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>shopee_24770824608</t>
+          <t>shopee_23784312811</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>17c444143b50f17665a67ddb6da9d382</t>
+          <t>2e1de80d628b282c1536daeb7ffde45f</t>
         </is>
       </c>
     </row>
@@ -5734,47 +5794,47 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Balo cặp sách cho bé trai - gái mầm non hoạt hình , ba lô trẻ em mẫu giáo siêu ngộ nghĩnh.</t>
+          <t>Mèo bông treo cặp sách balo + Còi Kêu Bíp Bíp đáng yêu ga12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>₫79.900</t>
+          <t>₫14.980</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">140 </t>
+          <t xml:space="preserve">127 </t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22828261628?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4VbbtEmq5i</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m4ote4lgul7381.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmr6l8zrnpj4dc.webp</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>shopee_22828261628</t>
+          <t>shopee_25688943433</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>39b82fd027eaa738da29293c90bd61b9</t>
+          <t>a7f7e543b784476efb4a9b97b13aa2e3</t>
         </is>
       </c>
     </row>
@@ -5786,47 +5846,42 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Balo Học Sinh OLANG Chống Gù, Siêu Nhẹ, Chống Nước, Cặp Sách Tiểu Học Bé Trai Bé Gái</t>
+          <t>Móc khoá gấu bông cute treo balo cặp sách ml01 ( KHÔNG KÊU BÍP BÍP)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>₫547.800</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>44%</t>
+          <t>₫13.000</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">131 </t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55608340899?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1BL9v6zWpz</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr1941lqjw8xbd.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m3aebdqnwrss1b.webp</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>shopee_55608340899</t>
+          <t>shopee_28319432367</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>d3b4b6f06555e672009ebe66122f0124</t>
+          <t>4a6379b8754508b0ad828f255ab3ffcf</t>
         </is>
       </c>
     </row>
@@ -5838,47 +5893,42 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Cặp sách balo cho học sinh tiểu học Kitty Kuromi 36x27x19</t>
+          <t>Balo Chống Gù Cho Bé Trai Gái Chống Nước Ba lô cấp 1 Cặp Sách Học Sinh Tiểu Học hàng đẹ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>₫259.000</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>26%</t>
+          <t>₫175.900</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">126 </t>
+          <t>3k+</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24305818849?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/AAFydeRGaK</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn8t7vbmg3k4f1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwmhi304xfx509.webp</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>shopee_24305818849</t>
+          <t>shopee_40215001645</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>ac4cb46bc5ac0d6ade31cc3c5ccb2c9e</t>
+          <t>3b3b6da43403395f6227f940fed57c9c</t>
         </is>
       </c>
     </row>
@@ -5890,47 +5940,42 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Balo nam nữ đi học chống nước nhiều ngăn quai đệm kèm gấu dễ thương cặp sách đựng laptop đi làm học sinh.b4015</t>
+          <t>COMBO 5 khoá cài, khoá mũ bảo hiểm, balo, cặp sách 2cm, 2,5cm (Đo lọt lòng)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>₫175.855</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>32%</t>
+          <t>₫12.000</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">483 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49605963749?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/30mo6TsY7W</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqd4rh2c3bbj51.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lwbh3d386b4r4c.webp</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>shopee_49605963749</t>
+          <t>shopee_29201991132</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>7edfe29c13da3e1a27746b323f3c3cf6</t>
+          <t>6e785e5c26dbb055187668758dd780aa</t>
         </is>
       </c>
     </row>
@@ -5942,47 +5987,42 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Balo nam nữ đi học chống nước nhiều ngăn quai đệm kèm gấu dễ thương ZONY cặp sách đựng laptop đi làm học sinh 291</t>
+          <t>Móc khoá bông con mèo đáng yêu treo ba lo cặp sách ga12</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>₫275.000</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>27%</t>
+          <t>₫20.000</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">112 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/16453035442?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4AylUco6kb</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lw81j6clp9sp25.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m37n8pbmdgx82c.webp</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>shopee_16453035442</t>
+          <t>shopee_28719290302</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>0eb62825803109c6cf68e94e11852dd3</t>
+          <t>94a70a6072279569b2adf47f4862ef08</t>
         </is>
       </c>
     </row>
@@ -5994,17 +6034,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Móc khoá thỏ dễ thương phụ kiện thời trang treo balo cặp sách móc khoá bạc mq08</t>
+          <t>Móc khóa TÊN theo yêu cầu, thẻ tên treo balo, cặp sách, nametag cho bé 18K</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>₫21.000</t>
+          <t>₫19.800</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">791 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6014,22 +6054,22 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27504285078?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/gOtKC1Qqq</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lxdd66gc4onv39.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpp6sa7xpiq592.webp</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>shopee_27504285078</t>
+          <t>shopee_45356600205</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>0c2f38ef139e1d59b06804a41466f2ea</t>
+          <t>b0c27bd15cdc9e0634d4b83d47d7c4c2</t>
         </is>
       </c>
     </row>
@@ -6041,47 +6081,42 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Balo JD V2 Nhiều Sticker Nhỏ Cá Tính | Cặp Đi Học Đựng Sách Vở Laptop 15.6 Inch Chất Dù Chống Nước Size 42cm</t>
+          <t>Móc khoá quả lông đáng yêu treo balo cặp sách mq25</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>₫275.000</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2%</t>
+          <t>₫18.500</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">51 </t>
+          <t>1k+</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51313756213?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/80BU3fZVyz</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqhbmw3n8mpuce.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ra2m-mb902olm3uyee5.webp</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>shopee_51313756213</t>
+          <t>shopee_26937823110</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>0414d16c37333b82dc446aebf28bf5cb</t>
+          <t>73961464e6eea62b303bcb8c5d291708</t>
         </is>
       </c>
     </row>
@@ -6093,47 +6128,42 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cặp sách chống gù DIOOGLT Balo Phi Hành Gia Siêu Nhẹ Thoáng Khí Cho Bé Tiểu Học</t>
+          <t>Móc khoá nhồi bông con gián đáng yêu treo balo cặp sách ml03</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>₫189.000</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>37%</t>
+          <t>₫17.000</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">839 </t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26960129769?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3Vj4hOqe6f</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mck5l2ksms0se2.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn2m85l0o7i83a.webp</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>shopee_26960129769</t>
+          <t>shopee_52008273256</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>e091a6de578007c4c593b037ce489681</t>
+          <t>1c3f75f69682b0777bfcc0a37090f2b9</t>
         </is>
       </c>
     </row>
@@ -6145,42 +6175,42 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Balo nữ đi học trơn basic vải chống thấm, bền đẹp, dễ phối đồ, cặp sách nữ style Hàn Quốc, đựng laptop 14inch</t>
+          <t>Móc khoá thỏ dễ thương phụ kiện thời trang treo balo cặp sách móc khoá bạc mq08</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>₫235.000</t>
+          <t>₫21.000</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">77 </t>
+          <t xml:space="preserve">791 </t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24059687930?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27504285078?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mf9ezpw9hlhnef.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lxdd66gc4onv39.webp</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>shopee_24059687930</t>
+          <t>shopee_27504285078</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>a0d206cdb7ec907b457410b2d9f91bf8</t>
+          <t>0c2f38ef139e1d59b06804a41466f2ea</t>
         </is>
       </c>
     </row>
@@ -6192,47 +6222,42 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>balo đi học boy phố chất liệu vải dù chống nước. balo hottrend Nam -nữ thời trang trẻ đựng sách vở và laptop bền đẹp</t>
+          <t>Móc khoá búp bê treo balo cặp sách phụ kiện quà tặng (KHÔNG CÓ PHỤ KIỆN ) mq03</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>₫132.000</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>54%</t>
+          <t>₫23.000</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">498 </t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53708380842?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4fv25XmCjk</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmr3t89xkqh127.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lt4rfgr2hu3da9.webp</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>shopee_53708380842</t>
+          <t>shopee_24415449457</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>7497a2886bcebffe093a9b6a89cf0788</t>
+          <t>76f2642c874c7842bafce370a0ed0cca</t>
         </is>
       </c>
     </row>
@@ -6244,47 +6269,42 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>( Tặng Kèm Móc Khoá Và Huy Hiệu) Balo Chống Gù Cho Bé Trai Gái Chống Nước Balo Cấp 1 Cặp Sách Học Sinh Tiểu Học</t>
+          <t>Móc khoá gấu má hồng treo balo cặp sách thời trang ga21</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>₫189.000</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>30%</t>
+          <t>₫16.000</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">98 </t>
+          <t xml:space="preserve">338 </t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26378174133?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3B6EImrumZ</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnk7w220c45e67.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rbn3-lnbp3sjycl4ha5.webp</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>shopee_26378174133</t>
+          <t>shopee_24100652843</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>4684bb1d9114f9408dcab981a59dc044</t>
+          <t>4d52e7b788164b03a697159b70b57566</t>
         </is>
       </c>
     </row>
@@ -6296,47 +6316,42 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>(Full Hộp) Mở Bán Kèm Móc Khóa Balo KittyCow Size32 Size40 DaPu thời trang đi du lịch đi học đựng sách vở A4 BL98</t>
+          <t>Móc khoá chuột treo balo cặp sách quà tặng mt10</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>₫125.000</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>32%</t>
+          <t>₫16.000</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">81 </t>
+          <t xml:space="preserve">314 </t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/47053854972?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5ArIgSkIju</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq53gn91a41u1b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lv5jhqjgi4mxf1.webp</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>shopee_47053854972</t>
+          <t>shopee_25179189888</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>3c0f64d069b40707ad03d8a171dda8ba</t>
+          <t>4bdf5640a65b16746e18b597166f5a19</t>
         </is>
       </c>
     </row>
@@ -6348,47 +6363,42 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Balo capybara KNOTE cặp sách học sinh dày dặn form chuẩn cao cấp cho bé từ mầm non đến cấp 2</t>
+          <t>[CÓ SẴN] Balo thời trang Hàn Quốc, cặp sách đi học nữ dành cho học sinh, sinh viên, vừa laptop 15.6 inch, vải trượt nước</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>₫329.000</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>37%</t>
+          <t>₫235.000</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100 </t>
+          <t xml:space="preserve">163 </t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28929879693?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/6VMgGufE1W</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7g8es7z0el404.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mni4ie25cyrl69.webp</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>shopee_28929879693</t>
+          <t>shopee_50259506478</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>6ecfa5b1e98f1bd25ea777651b0c167d</t>
+          <t>dd20357b48b5c440bacc85204408ba38</t>
         </is>
       </c>
     </row>
@@ -6400,47 +6410,42 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Balo nữ ba lô màu pastel thỏ chấm bi tặng kèm charm, cặp sách nữ đi học đi chơi da pu chống nước dung tích lớn</t>
+          <t>Sẵn💝Balo đi học nữ, cặp sách nữ basic, balo laptop 14inch, balo chống thấm, cặp đi học hàn quốc, balo thời trang SIÊU RẺ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>₫197.758</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>29%</t>
+          <t>₫240.000</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">95 </t>
+          <t xml:space="preserve">118 </t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/52363877345?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/20uGudwM8y</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr9nrot8eaddf5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mi4533uwkpvrf3.webp</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>shopee_52363877345</t>
+          <t>shopee_27562400542</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>29fea3bbde0ab37884bd157649d7b429</t>
+          <t>72105f7344fdd7d1ccf0ef6cdc956747</t>
         </is>
       </c>
     </row>
@@ -6452,47 +6457,83 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Balo đi học nam nữ M4M NEW BASIC Backpack BM002 Cặp sách chống nước nhiều ngăn đựng laptop 15.6 inch</t>
+          <t>Balo nữ đi học trơn basic vải chống thấm, bền đẹp, dễ phối đồ, cặp sách nữ style Hàn Quốc, đựng laptop 14inch</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>₫400.366</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2%</t>
+          <t>₫235.000</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">77 </t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29487759408?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24059687930?trace=%7B%22trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AaMN7vvJnof.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mlug651sp72982.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mf9ezpw9hlhnef.webp</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>shopee_29487759408</t>
+          <t>shopee_24059687930</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>edc725922ec1225162460fc0a64cd9ef</t>
+          <t>a0d206cdb7ec907b457410b2d9f91bf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>fddf</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>f123a0e5020ec86a68d0e36b8d157d67</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -6517,7 +6517,11 @@
           <t>fddf</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>dfdf</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
@@ -6533,7 +6537,7 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>f123a0e5020ec86a68d0e36b8d157d67</t>
+          <t>7218848ef88eb38e968573b83a69c00c</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">255 </t>
+          <t xml:space="preserve">293 </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LPeV5rHRc</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41053739148?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>76dee7e7a569419eb92454e88ce26ae7</t>
+          <t>35bc40a13105c83e41f536f7fee33799</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1k+</t>
+          <t xml:space="preserve">568 </t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2g9xhrtonQ</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24341874090?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>44be2ce255f511ab666351b32b43ffa1</t>
+          <t>4c3776fbe95c7794c1c5d61b410419dd</t>
         </is>
       </c>
     </row>
@@ -6363,17 +6363,18 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>[CÓ SẴN] Balo thời trang Hàn Quốc, cặp sách đi học nữ dành cho học sinh, sinh viên, vừa laptop 15.6 inch, vải trượt nước</t>
+          <t>[MỞ BÁN] Balo thời trang Hàn Quốc, cặp sách đi học nữ dành cho học sinh, sinh viên, vừa laptop 15.6 inch, vải trượt nước</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>₫235.000</t>
-        </is>
-      </c>
+          <t>₫255.000</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">163 </t>
+          <t xml:space="preserve">170 </t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6383,7 +6384,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VMgGufE1W</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50259506478?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6398,7 +6399,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>dd20357b48b5c440bacc85204408ba38</t>
+          <t>5406ada3dbddc0ced10a0b2c9786d52d</t>
         </is>
       </c>
     </row>
@@ -6499,45 +6500,3719 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tên mới</t>
+          <t>Balo đi học nam nữ thương hiệu NATOLI nhiều ngăn chống nước tốt - Basic Backpack B2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Liên hệ</t>
+          <t>₫274.000</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>fddf</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>dfdf</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/12786241026?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mrb4d24075l3e7.webp</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>shopee_12786241026</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>7218848ef88eb38e968573b83a69c00c</t>
+          <t>142fc98b0479c1913415c41583ea10a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Balo chống gù cao cấp Thiên Long - Cặp chống gù cho bé tiểu học, chất bền, nhẹ, chống thấm nước, đệm mút êm, thoải mái</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>₫344.300</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25568932150?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq51syoz95ora5.webp</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>shopee_25568932150</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>a0fff64b64ddc5ab349d15c75a8615ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù OLANG Cho Bé 6-12 Tuổi, Balo Học Sinh Tiểu Học Đệm Lưng 3D Thoáng Khí, Vải Chống Nước Siêu Nhẹ Cao Cấp</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>₫581.725</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56713099028?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr12z45zdse91d.webp</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>shopee_56713099028</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>c98fb66868a0fd82c574cbef93f6d442</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Balo Học Sinh Cao Cấp OLANG F119 Lớp 1-6, Đệm Lưng 3D, Chống Gù, Chống Nước, Dung Tích Lớn</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>₫600.520</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54613090783?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr12zrjiwg79cb.webp</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>shopee_54613090783</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>de72b9cda3d14ecd37941d030d9c6eda</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Balo Da Berise Basic Leather Pack, Unisex nam nữ, Đựng vừa Laptop 15,6inch, Da cao cấp chống nước</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>₫229.000</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40969951751?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn5fh6kvbbwkce.webp</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>shopee_40969951751</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>794d1f4cc35b7009300725e7c4409330</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Balo da đi học nam nữ GENBAG balo nhiều ngăn chống thấm nước BL01</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>₫210.020</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/46005253047?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqafytm2skcg73.webp</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>shopee_46005253047</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>556babd01163c0c0e923000aae89e91c</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Balo chống gù cao cấp hàng xuất Anh cho bé tiểu học - Kháng nước, siêu nhẹ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>₫479.000</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25543568266?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m87ikqn7tw8y23.webp</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>shopee_25543568266</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>7dca66471c3e00a536f70c2127221db0</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Balo Tiểu Học In Hình Kuromi - Balo Học Sinh Chống Gù 3D Nổi Chất Liệu Chống Thấm Nước Cho Bé.</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>₫169.999</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28954981942?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lxjk73pp7hsp7e.webp</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>shopee_28954981942</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>9dcbfc4c40de214b87ed4b26b5022abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Balo chống gù cho bé tiểu học cao cấp Thiên Long - Cặp chống gù giúp bé thoải mái, chống thấm nước</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>₫344.000</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29301644212?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9af5okdvc02d2.webp</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>shopee_29301644212</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>e249fa28c6e60de1ea14595f7501c2f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>[Durlapue]（Mùa quay lại trường học）Ba lô nữ nhẹ chống thấm nước đơn giản đơn giản thời trang</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>₫297.964</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42556968584?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-mbm8g38r82ls05.webp</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>shopee_42556968584</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>b4c426193bbc9c5d3478c3a750bddda7</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Balo Mầm Non Cho Bé Trai Bé Gái 1-5 Tuổi Đi Học Mẫu Giáo, Siêu Nhẹ Chống Thấm Nước</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>₫86.000</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48063823427?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqlakvte9dse76.webp</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>shopee_48063823427</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>fa018a2b56e9d3530edd5d7e44808d32</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>[TẶNG Quà ] Balo Capi chống gù, cặp đi học cho bé tiểu học lớp 1-6, balo học sinh chống nước</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>₫173.000</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41607252587?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbrixobmhfbp47.webp</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>shopee_41607252587</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>e95e2a9b24b0a94c28b8b57cef0c09e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù In Hình Kuromi Hot Hít🍀FREESHIP🍀Balo Tiểu Học Chống Gù 3D Nổi Chất Liệu Chống Thấm Nước Cho Bé</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>₫129.000</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">913 </t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25133967352?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg3d13u6g93d8d.webp</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>shopee_25133967352</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>5ed3ff313c75689968d5e1f1b91131be</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Balo da cao cấp chất liệu da PU dầy dặn chống thấm nước. MINTAS M235</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>₫189.900</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950 </t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29885010055?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mout0j6iht7074.webp</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>shopee_29885010055</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>358450f48207c17b35b97dd41e01d42d</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Balo khổ A4, Túi học thêm, Cặp học sinh lớp 1~6 chất liệu vải Oxford chống thấm nước (DP060GDQT)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>₫89.000</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27455668787?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m79ujkjms3jw1b.webp</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>shopee_27455668787</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>297c30abe3c667f847cb784e07c4863e</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Balo Da Thời Trang Cao Cấp PANDAS Form Đứng, Phù Hợp Laptop 14 inch, Chống Thấm, Có Ngăn Bình Nước (850)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>₫229.000</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56950859978?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mlelwkagfw2709.webp</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>shopee_56950859978</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>ae3849df5d9c961a654bb25a3701069d</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>[Ảnh thật] Balo da PU hàng cao cấp Balo D-NAP chống nước thời trang nam và nữ - kích thước 30cm x 43cm BL46</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>₫219.000</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858 </t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24482474371?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m54frz1qgyt254.webp</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>shopee_24482474371</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>ead580c4a4cd04923dc5b0dac6e337f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù Cho Bé Tiểu Học, Cặp Học Sinh Cấp 1 Siêu Nhẹ Chống Nước Họa Tiết 3D Tặng Móc Khóa HS05</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>₫183.000</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55260914195?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mdmk6bn217l8af.webp</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>shopee_55260914195</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>f3bcb72b9e39a99e9437797e17e6c824</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Balo Tiểu Học OLANG 2505 Cho Bé Trai Bé Gái Lớp 1-6, Chống Gù, Siêu Nhẹ, Cặp Học Sinh Cao Cấp</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>₫784.060</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41832336485?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr12yjmmy8zpd4.webp</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>shopee_41832336485</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>56d83bd99930cf8a6276cff114f0126d</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Cặp LADODA C167 hỗ trợ chống gù trượt nước nam nữ (18–30kg) tiểu học siêu nhẹ, thiết kế đáng yêu</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>₫375.000</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53705510584?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr5koxs518ufe6.webp</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>shopee_53705510584</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>f66693fe7e657f7c1d027a717f0baf28</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>OLANG F919 Cặp Sách Chống Gù Cho Học Sinh Tiểu Học, Siêu Nhẹ, Chống Nước, Nhiều Ngăn Lớp 1-6</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>₫620.420</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40382148065?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr1485546z9i08.webp</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>shopee_40382148065</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>fad146b4f4db95eb9f8a137440bf649f</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Cặp hỗ trợ chống gù cho tiểu học (18-30kg) LADODA C166 hình in cute trượt nước</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>₫350.000</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28780935103?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mr5kxsczocg1c1.webp</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>shopee_28780935103</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>802720d85b12ce364b07bf6a03cea9ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Balo Saierna Chống Gù Cao Cấp Cho Học Sinh Tiểu Học, Cặp Nhiều Ngăn, NHU Y SHOP</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>₫209.000</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/16199716805?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7udmhfgyss3f7.webp</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>shopee_16199716805</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>5b0f255691ec15107b92a48b8de254c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>AD40 Ba Lô Chống Gù, Cặp Chống Gù Cho Học Sinh Tiểu Học Chống Thấm Nước</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>₫175.421</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">675 </t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28305499797?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lxt7ibz8ll9512.webp</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>shopee_28305499797</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>7edd5a9924b19b19a6c3c126f9a78194</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Cặp Học Thêm Cho Học Sinh Tiểu Học Canvas 3 Ngăn Đựng Vở A4 Chống Nước Bền Đẹp – San Shop</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>₫47.800</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">678 </t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41220882203?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mot4iybffci582.webp</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>shopee_41220882203</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>721ad0bd518d2995a106358e64fc34f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ba lô chống gù cho bé cặp chống gù tiểu học xuất anh Tochang bé trai bé gái cặp đi học chống nước siêu nhẹ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>₫359.000</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">394 </t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42254749186?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mb38hbi58z9o49.webp</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>shopee_42254749186</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>ebc4ac272fb328a72b9434faacc0e54a</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Hang mới Balo chống gù cho bé tiểu học siêu nhẹ mẫu mới 2024 hàng quảng châu siêu đẹp balochong gutieuhoc cặp học sinh</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>₫198.920</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">873 </t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45661570203?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-823ri-mozd19g6biffd1.webp</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>shopee_45661570203</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>4ab3356088cd19e83b870d23c18609ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Balo chống gù bảo vệ cột sống cho bé từ lớp 1-6 ZMCG3-07,Cặp hoc sinh chống gù cho bé tiểu học</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>₫359.000</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422 </t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/41508012310?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mc0httzoohgqa2.webp</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>shopee_41508012310</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>7c038057e9c6cd3a6b4b739fb7fae24c</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Balo Chống Gù Cho Bé Tiểu Học, Cặp Học Sinh Cấp 1 Siêu Nhẹ Chống Nước Họa Tiết 3D Tặng Móc Khóa HS05</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>₫189.900</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">373 </t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27790274754?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mdmk6bn217l8af.webp</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>shopee_27790274754</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>3aaf4c17bb59bbfab81b7dd3c4f5c20f</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Cặp hỗ trợ chống gù tiểu học nam nữ (18-30kg) LADODA C159 học tiết đáng yêu</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>₫340.000</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263 </t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25642159563?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqrer7tyxjpeae.webp</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>shopee_25642159563</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>01a24f6ba3d1888f2be40a33aeca920e</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Túi Xách Học Thêm-Cặp đi học thêm màu sắc hoạt hình Học Sinh Tiểu Học Đủ Mẫu,Quà Tặng Học Sinh Cuối Năm</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>₫65.000</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330 </t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24814781076?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn41g7ewojd081.webp</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>shopee_24814781076</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>226382526545b48d545da55ff67ae98b</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Túi Xách Học Thêm Cho Học Sinh Tiểu Học Đủ Mẫu Cho Bé Trai Bé Gái - Cặp đi học thêm cho bé màu sắc hoạt hình sinh động</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>₫47.999</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">480 </t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25269838114?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lza5161tby5dca.webp</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>shopee_25269838114</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>4b9bc799d85a783dbd9b39bf07b37560</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Balo thời trang Hazin cho nữ học sinh, sinh viên đi học chống thấm phong cách Ulzzang, họa tiết gấu đựng vừa laptop</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>₫193.000</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/22064721598?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mi9zel553zlv5d.webp</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>shopee_22064721598</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>8fc93fc34f7564c94248a4ea1f220f8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Balo Đi học và dã ngoại cỡ lớn da gạo ô vuông cho giấy A4 và laptop 14 inch thời trang học sinh, sinh viên- BL014</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>₫83.659</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231 </t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42815451633?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-820l4-mdyai5e9khs2da.webp</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>shopee_42815451633</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>cb8b38eec92dec202cae45e67e6ae4a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Balo Laptop Nam Nữ Đi Học Chống Nước Đựng Laptop 15.6 Inch Cho Sinh Viên Đi Làm Nhiều Ngăn Hadi travel B26</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>₫133.525</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24495202197?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq5wrk16g9vx2a.webp</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>shopee_24495202197</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>50fe1cbb204e47cca60c88e324ad7608</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>balo nữ hàn quốc ARADA 2 in 1 đựng laptop 17 inch chống nước ba lô đi học Dung Tích Lớn balo du lịch sinh viên đại học</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>₫470.969</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40365469667?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mdyfj2hpolja00.webp</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>shopee_40365469667</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>83aba975b69a8c1f11c8cfd7b421b1ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ARADA Ba lô máy tính xách tay kiểu Hàn Quốc 15,6 inch Unisex không thấm nước cho sinh viên đại học</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>₫389.000</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212 </t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/28239618382?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-md5vgji1t2fw04.webp</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>shopee_28239618382</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>f97e86640341231e776bd842be0f83c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CÓ SẴN 🎒 BALO nữ đi học basic đơn giản dễ phối đồ, vải chống thấm nước, vừa laptop 14inch cho học sinh, sinh viên</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>₫230.000</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">477 </t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/19287136833?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkbzo3o2lblud6.webp</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>shopee_19287136833</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>5892d06ca4644356b6e17c74b2706450</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Balo Học Sinh, Sinh Viên Da Cao Cấp VAV-BAG100 – Đựng Laptop – Form Đứng Chống Sốc.</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>₫169.000</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42760585393?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mcpp7pzu1zdo8d.webp</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>shopee_42760585393</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>6d36947ad4145b282d9e7a531c5ba29c</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>[QMS] Balo Nữ Ulzzang Đi Học Thêu Nơ, Balo Học Sinh Sinh Viên Chống Nước Đựng Laptop 14 Inch</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>₫180.000</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179 </t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50563230508?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqx77gvrbuva3a.webp</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>shopee_50563230508</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>38a8b76f21b77dfea0646df1b2e532cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Balô Vải Oxford Nữ Balô Du Lịch Túi Đi Học Dành Cho Học Sinh Sinh Viên Dung Tích Lớn Đựng Laptop B394</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>₫281.200</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150 </t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/46200621388?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mghupm3awjda95.webp</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>shopee_46200621388</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>dcc7e3aee6b97756431ec5c4a4c02e3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Ba lô hình chú chó con dễ thương, ba lô phù hợp học sinh cấp 2,3,sinh viên kháng nước vừa laptop, trượt nước S3 B5524</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>₫119.000</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42318907089?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-memljislgttw42.webp</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>shopee_42318907089</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>cb952400a49edc5eb34ec42348797a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>👍👍Balo Thời Trang Nam Nữ Đi Học Vải Nylon Chống Nước Basic, Sức Chứa Lớn Đựng Laptop, Cho Học Sinh Sinh Viên.B3365</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>₫139.187</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">630 </t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50957107200?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn6npf8kh1xg5f.webp</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>shopee_50957107200</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>81584921d5a6206884e666afafdf767d</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Balo Da Bóng Unisex BL024 – Balo Học Sinh, Sinh Viên Đựng Laptop, Sách Vở, Thời Trang Hàn Quốc Ulzzang</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>₫77.900</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56300798433?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgoicq461i4q27.webp</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>shopee_56300798433</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>3d9634cca49c9ef27105e1cffbf08121</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Balo Đi Học, Balo Nữ Màu Pastel Thời Trang, Balo Đa Năng Đi Chơi Du Lịch Hè, vừa Laptop 15.6 Inch, Balo Chống Nước</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>₫230.000</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93 </t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29172069525?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfy5carze51o0d.webp</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>shopee_29172069525</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>72fd37c6b6a047469d2e763184a99489</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Balo Đi Học Cho Học Sinh Cấp 2, Cấp 3 – Sinh Viên Đựng Laptop 15.6 inch – Chống Nước, Đệm Lưng Thoáng Khí</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>₫169.000</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27892216460?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meb66tb4zc3kdf.webp</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>shopee_27892216460</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>1e9253b1ee83a0fda373e94aa479310a</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>( SẴN) Balo học sinh, sinh viên đi học đi chơi, Balo nữ đa năng kẻ caro Hàn Quốc, vừa laptop 15.6inch, vải chống nước</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>₫260.000</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96 </t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40959365974?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-miv56hwlukg7fd.webp</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>shopee_40959365974</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>68f26579448ddc850b6f0c786d4ac461</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>EDISON Balo Học Sinh Sinh Viên Chống Nước Nhẹ Chống Sốc Laptop Dung Tích Lớn Nhiều Ngăn Cho Nam Nữ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>₫909.000</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84 </t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/49202574852?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-820l4-mgw8xmb2mm8f9a.webp</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>shopee_49202574852</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>fae2814408a4755ab1c5cbc726b99cb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Balo hai vai mở rộng ba lô du lịch gọn nhẹ dung tích lớn cho nam nữ cặp sách sinh viên đại học đa chức năng</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>₫292.204</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">536 </t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42053827646?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ravd-masided7sb9f7d.webp</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>shopee_42053827646</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>78e35d5a3c76b68170eac29382cad0e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Ba lô nam ba lô đi công sở ba lô du lịch ngoài trời dung tích lớn ba lô máy tính đi lại sinh viên đại học</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>₫110.000</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46 </t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56407636172?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-82610-mm7na6fgrbpfb7.webp</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>shopee_56407636172</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>58bbc54b53d3354afc0938adedcacb04</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Balo đựng laptop 15.6 inch ARADA phiên bản Hàn Quốc dành cho sinh viên đại học chống nước có cổng sạc USB</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>₫377.540</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879 </t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/44370553010?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mez56sspwfm061.webp</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>shopee_44370553010</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>cf5b3e244af9008200ff22e86a845fe7</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Balo Unisex thời trang Hàn Quốc, phong cách trẻ trung LALABAG</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>₫265.000</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26089714964?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-md9db98098ik92.webp</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>shopee_26089714964</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>96570d79bc3e94baac973f8be60f878c</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Balo thời trang nam nữ da đẹp size đại đựng vừa sách a4 đi học đi chơi đi làm phong cách hàn quốc - BL024</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>₫75.000</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29756694965?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7r98o-lzjzn5kw713ha5.webp</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>shopee_29756694965</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>91cc26c3608db36b344fe80c43de275e</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Balo nữ da mềm trơn đi học thời trang phong cách hàn quốc - BL024</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>₫75.000</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26251733464?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lw43nh07ytw99c.webp</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>shopee_26251733464</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>dc550e10b6d50118eb1cda4b184dbbb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Túi xách Tote nữ họa tiết gấu dễ thương thiết kế trẻ trung phong cách Hàn Quốc, Túi Balo nhung đa năng thời trang TXN158</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>₫70.500</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">833 </t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27683778277?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m8pvo1f9qa100b.webp</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>shopee_27683778277</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>7c73ba9ac625607730148de53ca28ecc</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Balo nữ đi học đi làm đi chơi ba lô thời trang bassic phong cách hàn quốc họa tiết xinh size 40 TXN BẢO NHI _BL030</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>₫81.000</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25596050937?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mc79nuiwgij93a.webp</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>shopee_25596050937</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>28aa5588f70a718ed1bc91707d4cea8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Balo học sinh thương hiệu ONETOP nhiều ngăn chống nước, cặp đi học nam nữ cấp 2 cấp 3 phong cách hàn quốc</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>₫142.198</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822 </t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/56956512701?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mrd5vin4fbicaa.webp</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>shopee_56956512701</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>6f1bc2c046a7d00c04b7c1cc621c4ced</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>(025) Balo trơn chất liệu vải bố chống thấm nước, Balo đeo vai thiết kế trẻ trung, năng động phong cách Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>₫46.800</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>8k+</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25670704093?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lt9sx622yw0pa6.webp</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>shopee_25670704093</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>1b60c666d960cfe5eda9d09618d08c79</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Balo da đi học 5 mặt chống sốc GENBAG balo nam nữ có ngăn bí mật phong cách Hàn Quốc BL29</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>₫168.999</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25158608291?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnqyvbdpzu2r0a.webp</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>shopee_25158608291</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>481611d890c5b42c6789d7f2f52b5f9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Balo nữ vải szie 40 họa tiết nơ dễ thương phong cách Hàn Quốc balo đi học cute kèm charm - BL022</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>₫105.000</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">776 </t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54607738602?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mm785e6nx5ab72.webp</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>shopee_54607738602</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>3a9228e307e530750dd7320730fa5021</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Balo Học Sinh ONETOP Graffiti Chống Nước Nhiều Ngăn, Cặp Đi Học Nam Nữ Cấp 2 Cấp 3 Phong Cách Hàn Quốc Đựng Laptop 15.6</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>₫155.000</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">443 </t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55358189173?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mrd5mf0dhfya7e.webp</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>shopee_55358189173</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>827dcb009db678472e0a1c7a83d0dbd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Balo học tập, công sở size 40 với quai to họa tiết Hello Kitty dễ thương, phong cách thời trang Hàn Quốc - BL037</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>₫84.900</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/42014267551?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7ras8-mdo42e1p1sc1c5.webp</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>shopee_42014267551</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>fe88a0602924d1eef7c061c1107e4661</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>[Durlapue]（Mùa quay lại trường học）-Ba lô chống thấm nước nơ xếp ly phong cách Hàn Quốc mới dành cho nữ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>₫231.463</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">471 </t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43651748626?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-ma22hk0dzl4se4.webp</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>shopee_43651748626</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>135c101ce049a6084f4b92809e158d9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Balo học sinh cấp 2, balo nữ hàn quốc họa tiết ngôi sao màu pastel nhiều ngăn phong cách ulzzang y2k B862 gagastore</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>₫239.000</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">739 </t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43501497881?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-moxk64nnwf7m1b.webp</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>shopee_43501497881</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>38ac772384ad45975b868d4841fc39ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Balo đi học nữ balo thời trang basic phong cách Hàn Quốc nhiêu ngăn BL24</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>₫214.000</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">346 </t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/50310277514?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mo3e0ots1vyea7.webp</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>shopee_50310277514</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>64d53a2b38afce2273c15f991b72c519</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Ba lô Macoco thời trang Hàn Quốc phong cách thanh lịch cá tính nhiều ngăn - Zen 66</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24085008514?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m0wt9xwimasv38.webp</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>shopee_24085008514</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>41e740a10ae540a7ab3fe43d15556a59</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Balo Nữ Đi Học Da PU Size 40, Balo Họa Tiết Sao Laptop Đựng Vừa A4 Kèm Charm Ngôi Sao Phong Cách Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>₫173.000</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">405 </t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48364013851?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqxpx42vyrr81f.webp</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>shopee_48364013851</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>73fb1e95315f99e26cc338c192d0810b</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Túi xách Tote nữ họa tiết gấu dễ thương thiết kế nơ buộc trẻ trung phong cách Hàn Quốc, Balo nhung phối màu DK083</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>₫72.900</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">417 </t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/29034084271?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m8ryivaro6tece.webp</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>shopee_29034084271</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>cf0fa2b7901effa5ba6746bb4f9d717e</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Balo da nam nữ đi học phong cách hàn quốc size 40 vừa sách vở, A4,laptop</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>₫105.000</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277 </t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/46156305288?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkbq4ws43ksja4.webp</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>shopee_46156305288</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>1dde1f4d5a22a6ecac6603947a748da2</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>BALO DA ĐẸP ĐEO VAI ĐI HỌC ĐI CHƠI PHONG CÁCH HÀN QUỐC - BL024</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>₫75.000</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26278940418?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7ra0g-m73fp23881414d.webp</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>shopee_26278940418</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>61ec1c64dd6afda4a9da017e375b49ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Túi xách nữ đeo chéo đeo vai,đeo balo đi học,đi chơi phong cách thời trang hàn quốc tối giản cao cấp mới Có móc khóa</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>₫157.000</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293 </t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/27441712905?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mesd7btfyj2b90.webp</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>shopee_27441712905</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>b57969e9fe3f5887adee2fe3b0d6a706</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -1286,7 +1286,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41053739148?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/7Kvs0646Ba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/Lm2va2hWk</t>
+          <t>https://s.shopee.vn/1BLEelRZgz</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W5T7t24Bn</t>
+          <t>https://s.shopee.vn/4LIGQaFWGe</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24341874090?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/7VFICP3Sqd</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6371,7 +6371,6 @@
           <t>₫255.000</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t xml:space="preserve">170 </t>
@@ -6384,7 +6383,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50259506478?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/6Ajubx8XYV</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6530,7 +6529,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/12786241026?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/W5XrXU72n</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6543,7 +6542,6 @@
           <t>shopee_12786241026</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>142fc98b0479c1913415c41583ea10a0</t>
@@ -6583,7 +6581,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25568932150?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/19HGcW13i</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6596,7 +6594,6 @@
           <t>shopee_25568932150</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>a0fff64b64ddc5ab349d15c75a8615ec</t>
@@ -6636,7 +6633,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56713099028?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/BShSvVNil</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6649,7 +6646,6 @@
           <t>shopee_56713099028</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>c98fb66868a0fd82c574cbef93f6d442</t>
@@ -6689,7 +6685,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54613090783?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/111oSSSD1w</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6702,7 +6698,6 @@
           <t>shopee_54613090783</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>de72b9cda3d14ecd37941d030d9c6eda</t>
@@ -6742,7 +6737,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40969951751?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/gOy3qTThu</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6755,7 +6750,6 @@
           <t>shopee_40969951751</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>794d1f4cc35b7009300725e7c4409330</t>
@@ -6795,7 +6789,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/46005253047?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/qiOG9SqMx</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6808,7 +6802,6 @@
           <t>shopee_46005253047</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>556babd01163c0c0e923000aae89e91c</t>
@@ -6848,7 +6841,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25543568266?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4VbgctEsvh</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6861,7 +6854,6 @@
           <t>shopee_25543568266</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>7dca66471c3e00a536f70c2127221db0</t>
@@ -6884,7 +6876,6 @@
           <t>₫169.999</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>1k+</t>
@@ -6897,7 +6888,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28954981942?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/40fQ1yGmwc</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6910,7 +6901,6 @@
           <t>shopee_28954981942</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>9dcbfc4c40de214b87ed4b26b5022abe</t>
@@ -6950,7 +6940,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29301644212?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4AyqEHG9bf</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6963,7 +6953,6 @@
           <t>shopee_29301644212</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>e249fa28c6e60de1ea14595f7501c2f6</t>
@@ -7003,7 +6992,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42556968584?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/50XxDoCyuq</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7016,7 +7005,6 @@
           <t>shopee_42556968584</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>b4c426193bbc9c5d3478c3a750bddda7</t>
@@ -7056,7 +7044,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48063823427?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5ArNQ7CLZt</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -7069,7 +7057,6 @@
           <t>shopee_48063823427</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>fa018a2b56e9d3530edd5d7e44808d32</t>
@@ -7109,7 +7096,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41607252587?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4fv6pCEFao</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7122,7 +7109,6 @@
           <t>shopee_41607252587</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>e95e2a9b24b0a94c28b8b57cef0c09e4</t>
@@ -7162,7 +7148,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25133967352?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4qEX1VDcFr</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7175,7 +7161,6 @@
           <t>shopee_25133967352</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>5ed3ff313c75689968d5e1f1b91131be</t>
@@ -7215,7 +7200,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29885010055?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/30msq8KayW</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -7228,7 +7213,6 @@
           <t>shopee_29885010055</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>358450f48207c17b35b97dd41e01d42d</t>
@@ -7268,7 +7252,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27455668787?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3B6J2RJxdZ</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7281,7 +7265,6 @@
           <t>shopee_27455668787</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>297c30abe3c667f847cb784e07c4863e</t>
@@ -7321,7 +7304,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56950859978?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2gA2RWLreU</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7334,7 +7317,6 @@
           <t>shopee_56950859978</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>ae3849df5d9c961a654bb25a3701069d</t>
@@ -7374,7 +7356,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24482474371?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2qTSdpLEJX</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -7387,7 +7369,6 @@
           <t>shopee_24482474371</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>ead580c4a4cd04923dc5b0dac6e337f8</t>
@@ -7427,7 +7408,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55260914195?trace=%7B%22trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3IVYO5K0dRx.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3g2ZdMI3ci</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7440,7 +7421,6 @@
           <t>shopee_55260914195</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>f3bcb72b9e39a99e9437797e17e6c824</t>
@@ -7480,7 +7460,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41832336485?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3qLzpfHQHl</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7493,7 +7473,6 @@
           <t>shopee_41832336485</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>56d83bd99930cf8a6276cff114f0126d</t>
@@ -7533,7 +7512,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53705510584?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3LPjEkJKIg</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7546,7 +7525,6 @@
           <t>shopee_53705510584</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>f66693fe7e657f7c1d027a717f0baf28</t>
@@ -7586,7 +7564,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40382148065?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/3Vj9R3Igxj</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7599,7 +7577,6 @@
           <t>shopee_40382148065</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>fad146b4f4db95eb9f8a137440bf649f</t>
@@ -7639,7 +7616,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28780935103?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/70J1bU5MrQ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7652,7 +7629,6 @@
           <t>shopee_28780935103</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>802720d85b12ce364b07bf6a03cea9ea</t>
@@ -7692,7 +7668,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/16199716805?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/7AcRnn4jWT</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7705,7 +7681,6 @@
           <t>shopee_16199716805</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>5b0f255691ec15107b92a48b8de254c9</t>
@@ -7745,7 +7720,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28305499797?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/6fgBCs6dXO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -7758,7 +7733,6 @@
           <t>shopee_28305499797</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>7edd5a9924b19b19a6c3c126f9a78194</t>
@@ -7798,7 +7772,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41220882203?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/6pzbPB60CR</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7811,7 +7785,6 @@
           <t>shopee_41220882203</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>721ad0bd518d2995a106358e64fc34f5</t>
@@ -7851,7 +7824,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42254749186?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/7fYiOi2pVc</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7864,7 +7837,6 @@
           <t>shopee_42254749186</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>ebc4ac272fb328a72b9434faacc0e54a</t>
@@ -7904,7 +7876,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45661570203?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/7ps8b12CAf</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7917,7 +7889,6 @@
           <t>shopee_45661570203</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>4ab3356088cd19e83b870d23c18609ee</t>
@@ -7957,7 +7928,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/41508012310?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5fne12ARZI</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7970,7 +7941,6 @@
           <t>shopee_41508012310</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>7c038057e9c6cd3a6b4b739fb7fae24c</t>
@@ -7993,7 +7963,6 @@
           <t>₫189.900</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t xml:space="preserve">373 </t>
@@ -8006,7 +7975,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27790274754?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5q74DL9oEL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8019,7 +7988,6 @@
           <t>shopee_27790274754</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>3aaf4c17bb59bbfab81b7dd3c4f5c20f</t>
@@ -8059,7 +8027,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25642159563?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5LAncQBiFG</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8072,7 +8040,6 @@
           <t>shopee_25642159563</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>01a24f6ba3d1888f2be40a33aeca920e</t>
@@ -8095,7 +8062,6 @@
           <t>₫65.000</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t xml:space="preserve">330 </t>
@@ -8108,7 +8074,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24814781076?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5VUDojB4uJ</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8121,7 +8087,6 @@
           <t>shopee_24814781076</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>226382526545b48d545da55ff67ae98b</t>
@@ -8144,7 +8109,6 @@
           <t>₫47.999</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t xml:space="preserve">480 </t>
@@ -8157,7 +8121,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25269838114?trace=%7B%22trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.3Vxm8aXmL33.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/6L3KoG7uDU</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -8170,7 +8134,6 @@
           <t>shopee_25269838114</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>4b9bc799d85a783dbd9b39bf07b37560</t>
@@ -8210,7 +8173,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22064721598?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/6VMl0Z7GsX</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8223,7 +8186,6 @@
           <t>shopee_22064721598</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>8fc93fc34f7564c94248a4ea1f220f8a</t>
@@ -8263,7 +8225,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42815451633?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/60QUPe9AtS</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -8276,7 +8238,6 @@
           <t>shopee_42815451633</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>cb8b38eec92dec202cae45e67e6ae4a4</t>
@@ -8316,7 +8277,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24495202197?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/9fJmmNvDSC</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8329,7 +8290,6 @@
           <t>shopee_24495202197</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>50fe1cbb204e47cca60c88e324ad7608</t>
@@ -8369,7 +8329,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40365469667?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/9pdCygua7F</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8382,7 +8342,6 @@
           <t>shopee_40365469667</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>83aba975b69a8c1f11c8cfd7b421b1ed</t>
@@ -8422,7 +8381,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28239618382?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/9KgwNlwU8A</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8435,7 +8394,6 @@
           <t>shopee_28239618382</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>f97e86640341231e776bd842be0f83c9</t>
@@ -8458,7 +8416,6 @@
           <t>₫230.000</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t xml:space="preserve">477 </t>
@@ -8471,7 +8428,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/19287136833?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/9V0Ma4vqnD</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -8484,7 +8441,6 @@
           <t>shopee_19287136833</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>5892d06ca4644356b6e17c74b2706450</t>
@@ -8524,7 +8480,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42760585393?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/AKZTZbsg6O</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -8537,7 +8493,6 @@
           <t>shopee_42760585393</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>6d36947ad4145b282d9e7a531c5ba29c</t>
@@ -8577,7 +8532,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50563230508?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/AUstlus2lR</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8590,7 +8545,6 @@
           <t>shopee_50563230508</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>38a8b76f21b77dfea0646df1b2e532cf</t>
@@ -8630,7 +8584,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/46200621388?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/9zwdAztwmM</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8643,7 +8597,6 @@
           <t>shopee_46200621388</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>dcc7e3aee6b97756431ec5c4a4c02e3a</t>
@@ -8683,7 +8636,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42318907089?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/AAG3NItJRP</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8696,7 +8649,6 @@
           <t>shopee_42318907089</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>cb952400a49edc5eb34ec42348797a82</t>
@@ -8736,7 +8688,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50957107200?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8KoPBw0IA4</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8749,7 +8701,6 @@
           <t>shopee_50957107200</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>81584921d5a6206884e666afafdf767d</t>
@@ -8789,7 +8740,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56300798433?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8V7pOEzep7</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -8802,7 +8753,6 @@
           <t>shopee_56300798433</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
           <t>3d9634cca49c9ef27105e1cffbf08121</t>
@@ -8825,7 +8775,6 @@
           <t>₫230.000</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t xml:space="preserve">93 </t>
@@ -8838,7 +8787,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29172069525?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/80BYnK1Yq2</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -8851,7 +8800,6 @@
           <t>shopee_29172069525</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>72fd37c6b6a047469d2e763184a99489</t>
@@ -8874,7 +8822,6 @@
           <t>₫169.000</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>3k+</t>
@@ -8887,7 +8834,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27892216460?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8AUyzd0vV5</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8900,7 +8847,6 @@
           <t>shopee_27892216460</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>1e9253b1ee83a0fda373e94aa479310a</t>
@@ -8923,7 +8869,6 @@
           <t>₫260.000</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t xml:space="preserve">96 </t>
@@ -8936,7 +8881,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40959365974?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/9045z9xkoG</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8949,7 +8894,6 @@
           <t>shopee_40959365974</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>68f26579448ddc850b6f0c786d4ac461</t>
@@ -8972,7 +8916,6 @@
           <t>₫909.000</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
           <t xml:space="preserve">84 </t>
@@ -8985,7 +8928,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/49202574852?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/9ANWBSx7TJ</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8998,7 +8941,6 @@
           <t>shopee_49202574852</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>fae2814408a4755ab1c5cbc726b99cb8</t>
@@ -9038,7 +8980,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42053827646?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8fRFaXz1UE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9051,7 +8993,6 @@
           <t>shopee_42053827646</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>78e35d5a3c76b68170eac29382cad0e9</t>
@@ -9091,7 +9032,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56407636172?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8pkfmqyO9H</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9104,7 +9045,6 @@
           <t>shopee_56407636172</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>58bbc54b53d3354afc0938adedcacb04</t>
@@ -9144,7 +9084,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44370553010?trace=%7B%22trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.84pFGsAtNo1.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1qavRzP2Lw</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9157,7 +9097,6 @@
           <t>shopee_44370553010</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>cf5b3e244af9008200ff22e86a845fe7</t>
@@ -9180,7 +9119,6 @@
           <t>₫265.000</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>2k+</t>
@@ -9193,7 +9131,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26089714964?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1gHVFgPfgv</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9206,7 +9144,6 @@
           <t>shopee_26089714964</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>96570d79bc3e94baac973f8be60f878c</t>
@@ -9246,7 +9183,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29756694965?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1Vy53NQJ1u</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9259,7 +9196,6 @@
           <t>shopee_29756694965</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>91cc26c3608db36b344fe80c43de275e</t>
@@ -9299,7 +9235,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26251733464?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1Leer4QwMt</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9312,7 +9248,6 @@
           <t>shopee_26251733464</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>dc550e10b6d50118eb1cda4b184dbbb0</t>
@@ -9352,7 +9287,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27683778277?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2VqcFDMV08</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -9365,7 +9300,6 @@
           <t>shopee_27683778277</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>7c73ba9ac625607730148de53ca28ecc</t>
@@ -9405,7 +9339,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25596050937?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2LXC2uN8L7</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -9418,7 +9352,6 @@
           <t>shopee_25596050937</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>28aa5588f70a718ed1bc91707d4cea8c</t>
@@ -9458,7 +9391,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/56956512701?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2BDlqbNlg6</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -9471,7 +9404,6 @@
           <t>shopee_56956512701</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>6f1bc2c046a7d00c04b7c1cc621c4ced</t>
@@ -9511,7 +9443,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25670704093?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/20uLeIOP15</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -9524,7 +9456,6 @@
           <t>shopee_25670704093</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
           <t>1b60c666d960cfe5eda9d09618d08c79</t>
@@ -9564,7 +9495,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25158608291?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/W5XrXU73o</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -9577,7 +9508,6 @@
           <t>shopee_25158608291</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>481611d890c5b42c6789d7f2f52b5f9a</t>
@@ -9617,7 +9547,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54607738602?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/Lm7fEUkOn</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9630,7 +9560,6 @@
           <t>shopee_54607738602</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>3a9228e307e530750dd7320730fa5021</t>
@@ -9670,7 +9599,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55358189173?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/BShSvVNjm</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -9683,7 +9612,6 @@
           <t>shopee_55358189173</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
           <t>827dcb009db678472e0a1c7a83d0dbd3</t>
@@ -9723,7 +9651,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/42014267551?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/19HGcW14l</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -9736,7 +9664,6 @@
           <t>shopee_42014267551</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>fe88a0602924d1eef7c061c1107e4661</t>
@@ -9776,7 +9703,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/43651748626?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1BLEelRZi0</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -9789,7 +9716,6 @@
           <t>shopee_43651748626</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
           <t>135c101ce049a6084f4b92809e158d9c</t>
@@ -9829,7 +9755,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/43501497881?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/111oSSSD2z</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9842,7 +9768,6 @@
           <t>shopee_43501497881</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
           <t>38ac772384ad45975b868d4841fc39ef</t>
@@ -9882,7 +9807,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/50310277514?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/qiOG9SqNy</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9895,7 +9820,6 @@
           <t>shopee_50310277514</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
           <t>64d53a2b38afce2273c15f991b72c519</t>
@@ -9918,7 +9842,6 @@
           <t>₫149.000</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>4k+</t>
@@ -9931,7 +9854,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24085008514?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/gOy3qTTix</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9944,7 +9867,6 @@
           <t>shopee_24085008514</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>41e740a10ae540a7ab3fe43d15556a59</t>
@@ -9984,7 +9906,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48364013851?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4VbgctEswi</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -9997,7 +9919,6 @@
           <t>shopee_48364013851</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
           <t>73fb1e95315f99e26cc338c192d0810b</t>
@@ -10037,7 +9958,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/29034084271?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4LIGQaFWHh</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -10050,7 +9971,6 @@
           <t>shopee_29034084271</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
           <t>cf0fa2b7901effa5ba6746bb4f9d717e</t>
@@ -10090,7 +10010,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/46156305288?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/4AyqEHG9cg</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -10103,7 +10023,6 @@
           <t>shopee_46156305288</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
           <t>1dde1f4d5a22a6ecac6603947a748da2</t>
@@ -10143,7 +10062,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26278940418?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/40fQ1yGmxf</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -10156,7 +10075,6 @@
           <t>shopee_26278940418</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
           <t>61ec1c64dd6afda4a9da017e375b49ea</t>
@@ -10196,7 +10114,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27441712905?trace=%7B%22trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.AGawu0l8lDF.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5ArNQ7CLau</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -10209,7 +10127,6 @@
           <t>shopee_27441712905</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
           <t>b57969e9fe3f5887adee2fe3b0d6a706</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K231"/>
+  <dimension ref="A1:K307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,7 +714,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/50XxDoCyuq</t>
+          <t>https://s.shopee.vn/4fv6prwjc5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2BDlqbNlg6</t>
+          <t>https://s.shopee.vn/7fYiPNlJXT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1BLEelRZi0</t>
+          <t>https://s.shopee.vn/3Vj9Rj1Azl</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8fRFaXz1UE</t>
+          <t>https://s.shopee.vn/6L3KovqOF5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8pkfmqyO9H</t>
+          <t>https://s.shopee.vn/6pzbPqoUEC</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BShSvVNjm</t>
+          <t>https://s.shopee.vn/3B6J372Rff</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9fJmmNvDSC</t>
+          <t>https://s.shopee.vn/9KgwORey9R</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6fgBCs6dXO</t>
+          <t>https://s.shopee.vn/1gHVGM89hj</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5ArNQ7CLau</t>
+          <t>https://s.shopee.vn/4qEX2Aw6I9</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7Kvs0646Ba</t>
+          <t>https://s.shopee.vn/2LXC3a5cLv</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3g2ZdMI3ci</t>
+          <t>https://s.shopee.vn/gOy4WBxjR</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2VqcFDMV08</t>
+          <t>https://s.shopee.vn/7Kvs0lmaDN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7ps8b12CAf</t>
+          <t>https://s.shopee.vn/2VqcFt4z0w</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/20uLeIOP15</t>
+          <t>https://s.shopee.vn/2gA2SC4LgW</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AAG3NItJRP</t>
+          <t>https://s.shopee.vn/5VUDpOtYvo</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/30msq8KayW</t>
+          <t>https://s.shopee.vn/19HHIEV5F</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W5XrXU73o</t>
+          <t>https://s.shopee.vn/2qTSeV3iLZ</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1BLEelRZgz</t>
+          <t>https://s.shopee.vn/3qLzqKzuIo</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LIGQaFWHh</t>
+          <t>https://s.shopee.vn/4LIGRFy0J0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7fYiOi2pVc</t>
+          <t>https://s.shopee.vn/20uLey6t1p</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6VMl0Z7GsX</t>
+          <t>https://s.shopee.vn/9ANWC8fbUM</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/111oSSSD1w</t>
+          <t>https://s.shopee.vn/3LPjFQ1oJh</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4qEX1VDcFr</t>
+          <t>https://s.shopee.vn/BShTbDrkG</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40fQ1yGmxf</t>
+          <t>https://s.shopee.vn/4fv6prwjd6</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/Lm7fEUkOn</t>
+          <t>https://s.shopee.vn/30msqo350c</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8KoPBw0IA4</t>
+          <t>https://s.shopee.vn/5LAnd5uCGn</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/BShSvVNil</t>
+          <t>https://s.shopee.vn/3Vj9Rj1Ayi</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9KgwNlwU8A</t>
+          <t>https://s.shopee.vn/9fJmn3dhTX</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1qavRzP2Lw</t>
+          <t>https://s.shopee.vn/6fgBDXp7ZB</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6pzbPB60CR</t>
+          <t>https://s.shopee.vn/2BDlrH6Fgq</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3Vj9R3Igxj</t>
+          <t>https://s.shopee.vn/1Vy5438n2e</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/111oSSSD2z</t>
+          <t>https://s.shopee.vn/3g2Ze20Xeo</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/60QUPe9AtS</t>
+          <t>https://s.shopee.vn/9045zpgEpL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/qiOG9SqMx</t>
+          <t>https://s.shopee.vn/4AyqEwydcu</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8V7pOEzep7</t>
+          <t>https://s.shopee.vn/5q74E0sIFu</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/19HGcW14l</t>
+          <t>https://s.shopee.vn/3LPjFQ1oKi</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3B6J2RJxdZ</t>
+          <t>https://s.shopee.vn/W5XsDCb4M</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2LXC2uN8L7</t>
+          <t>https://s.shopee.vn/7ps8bgkgCU</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4LIGQaFWGe</t>
+          <t>https://s.shopee.vn/40fQ2dzGxt</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5ArNQ7CLZt</t>
+          <t>https://s.shopee.vn/5ArNQmupbC</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Leer4QwMt</t>
+          <t>https://s.shopee.vn/7VFID4lwsO</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/19HGcW13i</t>
+          <t>https://s.shopee.vn/30msqo34zb</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5fne12ARZI</t>
+          <t>https://s.shopee.vn/80BYnzk2r3</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9zwdAztwmM</t>
+          <t>https://s.shopee.vn/AKZTaHbA7j</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AKZTZbsg6O</t>
+          <t>https://s.shopee.vn/9zwdBfcQnd</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9pdCygua7F</t>
+          <t>https://s.shopee.vn/9pdCzMd48Y</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/W5XrXU72n</t>
+          <t>https://s.shopee.vn/3B6J372Rec</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4VbgctEswi</t>
+          <t>https://s.shopee.vn/4AyqEwyddx</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4fv6pCEFao</t>
+          <t>https://s.shopee.vn/50XxETvSwB</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4AyqEHG9bf</t>
+          <t>https://s.shopee.vn/4qEX2Aw6H6</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1Vy53NQJ1u</t>
+          <t>https://s.shopee.vn/70J1c9nqtH</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2gA2RWLreU</t>
+          <t>https://s.shopee.vn/Lm7fuDEPL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3qLzpfHQHl</t>
+          <t>https://s.shopee.vn/1BLEfRA3iY</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/2qTSdpLEJX</t>
+          <t>https://s.shopee.vn/qiOGpBKOS</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/qiOG9SqNy</t>
+          <t>https://s.shopee.vn/3qLzqKzuJr</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7AcRnn4jWT</t>
+          <t>https://s.shopee.vn/1qavSf7WMk</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4AyqEHG9cg</t>
+          <t>https://s.shopee.vn/4VbgdYxMy3</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/gOy3qTThu</t>
+          <t>https://s.shopee.vn/3g2Ze20Xdn</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/70J1bU5MrQ</t>
+          <t>https://s.shopee.vn/1Leerk9QNd</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/7VFICP3Sqd</t>
+          <t>https://s.shopee.vn/8AUz0IjPW4</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/AUstlus2lR</t>
+          <t>https://s.shopee.vn/AUstmaaWmk</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/4VbgctEsvh</t>
+          <t>https://s.shopee.vn/4VbgdYxMx0</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/3LPjEkJKIg</t>
+          <t>https://s.shopee.vn/111oT8Ah3X</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5LAncQBiFG</t>
+          <t>https://s.shopee.vn/8KoPCbimB9</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/gOy3qTTix</t>
+          <t>https://s.shopee.vn/40fQ2dzGyu</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/8AUyzd0vV5</t>
+          <t>https://s.shopee.vn/6Ajuccr1a0</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/1gHVFgPfgv</t>
+          <t>https://s.shopee.vn/7AcRoSnDYI</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/40fQ1yGmwc</t>
+          <t>https://s.shopee.vn/4LIGRFy0Hz</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6L3KoG7uDU</t>
+          <t>https://s.shopee.vn/8fRFbDhVVF</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9V0Ma4vqnD</t>
+          <t>https://s.shopee.vn/AAG3NybnSe</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5q74DL9oEL</t>
+          <t>https://s.shopee.vn/8V7pOui8qA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/5VUDojB4uJ</t>
+          <t>https://s.shopee.vn/8pkfnWgsAG</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/6Ajubx8XYV</t>
+          <t>https://s.shopee.vn/9V0MakeKoS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9045z9xkoG</t>
+          <t>https://s.shopee.vn/60QUQJreuz</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/80BYnK1Yq2</t>
+          <t>https://s.shopee.vn/5fne1hsvat</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://s.shopee.vn/9ANWBSx7TJ</t>
+          <t>https://s.shopee.vn/6VMl1Epku6</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/1673220598?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/50XxETvSxC</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -10179,7 +10179,6 @@
           <t>shopee_1673220598</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>f542367b523db84ab2a944f708b38993</t>
@@ -10219,7 +10218,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25431491077?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/5ArNQmupcF</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -10232,7 +10231,6 @@
           <t>shopee_25431491077</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>2f45c5b54764022934269b4ba9c3e89c</t>
@@ -10272,7 +10270,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24261863092?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/19HHIEV6G</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -10285,7 +10283,6 @@
           <t>shopee_24261863092</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>f50a21a39445efba757f1cf3bbc2ddb0</t>
@@ -10325,7 +10322,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27368480819?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/BShTbDrlJ</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -10338,7 +10335,6 @@
           <t>shopee_27368480819</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>cdcff92e59c8b4643868c29d0f2a4dfa</t>
@@ -10361,7 +10357,6 @@
           <t>₫39.800</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>3k+</t>
@@ -10374,7 +10369,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/20541920720?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/Lm7fuDEQM</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -10387,7 +10382,6 @@
           <t>shopee_20541920720</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>a7cf32879bd67b5fb7bac7cd59b02f4e</t>
@@ -10427,7 +10421,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/20682080257?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/W5XsDCb5P</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -10440,7 +10434,6 @@
           <t>shopee_20682080257</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>06c03fa7fa38c777fef4f7aab54a8a70</t>
@@ -10480,7 +10473,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/17296399349?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/gOy4WBxkS</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -10493,7 +10486,6 @@
           <t>shopee_17296399349</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>c903ff7f692f3de40cb97366d5d74bc9</t>
@@ -10533,7 +10525,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/27074209091?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/qiOGpBKPV</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -10546,7 +10538,6 @@
           <t>shopee_27074209091</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>e24009c4c3f67eca32b658b4a84d298f</t>
@@ -10569,7 +10560,6 @@
           <t>₫25.000</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>80k+</t>
@@ -10582,7 +10572,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44022750137?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/111oT8Ah4Y</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10595,7 +10585,6 @@
           <t>shopee_44022750137</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>8e93fcb887ccd356ec0482b05ea8af33</t>
@@ -10635,7 +10624,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51604321607?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1BLEfRA3jb</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -10648,7 +10637,6 @@
           <t>shopee_51604321607</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>803f1f97744abb5cc7f325a293afe870</t>
@@ -10671,7 +10659,6 @@
           <t>₫23.000</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>2k+</t>
@@ -10684,7 +10671,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/12277243708?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1Leerk9QOe</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -10697,7 +10684,6 @@
           <t>shopee_12277243708</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
           <t>4f683ef923c93ced0adb9d27c645f1e6</t>
@@ -10737,7 +10723,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/57907058607?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1Vy5438n3h</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10750,7 +10736,6 @@
           <t>shopee_57907058607</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>e50b35551e8ae66dceb59f9428b0ea1c</t>
@@ -10773,7 +10758,6 @@
           <t>₫25.900</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>90k+</t>
@@ -10786,7 +10770,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44454010377?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1gHVGM89ik</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -10799,7 +10783,6 @@
           <t>shopee_44454010377</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>5d50e5b3d9586fd598776de0ef137d40</t>
@@ -10839,7 +10822,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/28864631323?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/1qavSf7WNn</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -10852,7 +10835,6 @@
           <t>shopee_28864631323</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
           <t>abf4f665a8a7b2bf5126725c9fb2829e</t>
@@ -10892,7 +10874,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24321666467?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/20uLey6t2q</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10905,7 +10887,6 @@
           <t>shopee_24321666467</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>163426b2eace442bde105c7b12026e10</t>
@@ -10945,7 +10926,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53410142220?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2BDlrH6Fht</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -10958,7 +10939,6 @@
           <t>shopee_53410142220</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
           <t>9d559852126d814f92acb3a21762e1cb</t>
@@ -10998,7 +10978,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/44123327891?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2LXC3a5cMw</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -11011,7 +10991,6 @@
           <t>shopee_44123327891</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
           <t>3cb6f33300012f7593ca15c028a9931c</t>
@@ -11051,7 +11030,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/8999521115?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/2VqcFt4z1z</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -11064,7 +11043,6 @@
           <t>shopee_8999521115</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
           <t>a9c1d3dc31a69e5cb81c6b2d76fde1c0</t>
@@ -11104,7 +11082,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/43832340267?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/80BYnzk2s4</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -11117,7 +11095,6 @@
           <t>shopee_43832340267</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>e9092c49f67a8f04390605acaea4c25e</t>
@@ -11157,7 +11134,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/22350875332?trace=%7B%22trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5JMXHF9g7RR.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8AUz0IjPX7</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -11170,7 +11147,6 @@
           <t>shopee_22350875332</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
           <t>7cf3c4575106ebcb261d8ec561504bea</t>
@@ -11210,7 +11186,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/18109428728?trace=%7B%22trace_id%22%3A%220.5G8f9Nh2Uev.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5G8f9Nh2Uev.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8KoPCbimCA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -11223,7 +11199,6 @@
           <t>shopee_18109428728</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
           <t>6d33f327c100f22c383060af5b8c75af</t>
@@ -11263,7 +11238,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/11463887013?trace=%7B%22trace_id%22%3A%220.5G8f9Nh2Uev.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5G8f9Nh2Uev.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8V7pOui8rD</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -11276,7 +11251,6 @@
           <t>shopee_11463887013</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
           <t>66680942049d05fc43cc6ad9dd514508</t>
@@ -11316,7 +11290,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/16186040746?trace=%7B%22trace_id%22%3A%220.5G8f9Nh2Uev.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5G8f9Nh2Uev.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8fRFbDhVWG</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -11329,7 +11303,6 @@
           <t>shopee_16186040746</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
           <t>32ad22ae7247784849eedd3a0a173aa2</t>
@@ -11369,7 +11342,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53453208880?trace=%7B%22trace_id%22%3A%220.5G8f9Nh2Uev.200%22%2C%22list_type%22%3A200%2C%22exp_group_ids%22%3A%5B673099%5D%2C%22root_trace_id%22%3A%220.5G8f9Nh2Uev.200%22%2C%22root_list_type%22%3A200%7D</t>
+          <t>https://s.shopee.vn/8pkfnWgsBJ</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -11382,7 +11355,6 @@
           <t>shopee_53453208880</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
           <t>d007083cecc51b1bb3805d3a62eeeb6e</t>
@@ -11435,7 +11407,6 @@
           <t>shopee_17623986106</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
           <t>58ad6449bec695abcb2c45cbf0990bce</t>
@@ -11458,7 +11429,6 @@
           <t>₫50.000</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>8k+</t>
@@ -11484,7 +11454,6 @@
           <t>shopee_56512636546</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
           <t>dc8d05741d8a7bd1ae9d55774aeef2ed</t>
@@ -11537,7 +11506,6 @@
           <t>shopee_27101354213</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
           <t>b02abfc812082c602fd5077a27fc842e</t>
@@ -11590,7 +11558,6 @@
           <t>shopee_40172245650</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
           <t>c2f582fa92697e8279114cedca226070</t>
@@ -11643,7 +11610,6 @@
           <t>shopee_42170566678</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>328f5640914da1783ff30b4c66469016</t>
@@ -11696,7 +11662,6 @@
           <t>shopee_25776717011</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
           <t>8f6f2efeb34640ae8c44db8acd5820e1</t>
@@ -11749,7 +11714,6 @@
           <t>shopee_43982320015</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>41662b47d2f7090e7fd09e57bd9f5b06</t>
@@ -11802,7 +11766,6 @@
           <t>shopee_23247343618</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>a70e2182b1531a0a418c9a1d4e759340</t>
@@ -11855,7 +11818,6 @@
           <t>shopee_19029797413</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>1ef61390110c88fc606be44b2ddc771c</t>
@@ -11908,7 +11870,6 @@
           <t>shopee_41981938230</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
           <t>594facf4faedf3e1056191739b0f1852</t>
@@ -11961,7 +11922,6 @@
           <t>shopee_54609619756</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
           <t>c6222ace926fdf232112dd104f60f991</t>
@@ -12014,7 +11974,6 @@
           <t>shopee_18214898352</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
           <t>652a9ed91117d7ac8daeb358c65f2bbc</t>
@@ -12067,7 +12026,6 @@
           <t>shopee_18290497666</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
           <t>77ef377e46b9cf785f04f77a3010166c</t>
@@ -12120,7 +12078,6 @@
           <t>shopee_24716735775</t>
         </is>
       </c>
-      <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
           <t>8ca49ffc1cea5486c8ccd429808d72f2</t>
@@ -12173,7 +12130,6 @@
           <t>shopee_26173173856</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
           <t>9e338fadf9695acbc28c404f5b5b05c8</t>
@@ -12226,10 +12182,3876 @@
           <t>shopee_44253348012</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
           <t>68ade2a671a49bec5036331a8805394a</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Bút Chì Kim Pastel Deli Ngòi 0.5-0.7mm Đệm Tay Siêu Êm Cao Cấp Kèm Đầu Tẩy Cải Tiến Học Sinh</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>₫8.000</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1Vy54HH1P7</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m2f6j22zf7w246.webp</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>shopee_25286799722</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>002d4be393ab47f1d595b752a12d5efd</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Bút Chì Kim Pastel Deli Ngòi 0.5-0.7mm Có Đệm Tay Định Vị Êm Không Đau Tay Kèm Đầu Tẩy Tiện Lợi</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>₫13.000</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1gHVGaGO4A</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mlxditt4syyo52.webp</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>shopee_26416102479</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>5ba417c6485949f8d0944fd6d40f6ebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Ruột bút chì kim 0.5mm Deli, ngòi chì kim 100 chiếc 2B, lõi chì bấm nhỏ gọn tiện lợi phù hợp cho học sinh, văn phòng</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>₫5.000</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1qavStFkjD</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m2uedvuujbw060.webp</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>shopee_18885720611</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>d198f3da094e58eb184eba63e65e62fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>[Deli VPP]Bút Chì Kim Pastel Deli Ngòi 0.5-0.7mm Đệm Tay Siêu Êm Cao Cấp Kèm Đầu Tẩy Cải Tiến Cho Học Sinh Dân Văn Phòng</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>₫5.000</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>40k+</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/20uLfCF7OG</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mma0p6alozr9c5.webp</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>shopee_25286894018</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>1e337e40b7dd590f83babe3d15ca203c</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>[DEAL SỐC 5K] Bút Chì Kim Học Sinh Deli Ngòi 0.5/0.7mm Thân Nhựa Trong Suốt Cao Cấp Có Đầu Tẩy Thiết Kế Cải Tiến Mới</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>₫16.200</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2BDlrVEU3J</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rasl-mb3d3pfhn2ief5.webp</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>shopee_43154767871</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>688cbc0b57f2c9b81dad923556acf1d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Ruột Bút Chì Kim 0.5mm Deli - Ngòi Chì Kim 100 Chiếc 2B Lõi Chì Bấm Nhỏ Gọn Tiện Lợi Phù Hợp Cho Học Sin</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>₫30.600</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2LXC3oDqiM</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rbkl-lnih83nxtyuocc.webp</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>shopee_23685230225</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>4484f8bea6d4c003c1e09bd86cf6f8ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Bút chì kim bấm ngòi 2mm Deli - Bút chì bấm học sinh cao cấp kèm đầu gọt cải tiến chì đậm rõ nét cho học sinh, văn phòng</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>₫10.000</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2VqcG7DDNP</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m71zz3s4ymqp1b.webp</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>shopee_18282774704</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>2d0de32889c2bd0eee7e512442b1cc3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>(TẶNG NGÒI) Bút chì kim Deli bấm thân/ bấm đầu ngòi 0.5-0.7mm cao cấp kèm đầu tẩy - Cải tiến cho học sinh, dân văn phòng</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>₫8.000</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">864 </t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/19HHWMjRw</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7qukw-ljc7qqp06uhe5a.webp</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>shopee_21077759283</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>826d49f599c0789e67f83c4d4111b641</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Bút Chì Kim Kèm100 Ngòi Học Sinh Deli - Thân Nhựa Cao Cấp Ngòi 0.5/ 0.7mm Có Đầu Tẩy Tiện Lợi Thiết Kế Cải Tiến Mới</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>₫11.000</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">870 </t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/BShTpM66z</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9gv2lk3ajce39.webp</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>shopee_27685209547</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>daa330f5c080518a26375c39b6ce4e56</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Bút Chì Kim Pastel Deli Ngòi 0.5-0.7mm Đệm Tay Siêu Êm Cao Cấp Kèm Đầu Tẩy Cho Học Sinh, Văn Phòng</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>₫5.000</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>40k+</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/Lm7g8LSm2</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mrclzyvhswe840.webp</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>shopee_27163385953</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>5fc5b1925395db832206a1844038ccdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Bút Chì Kim Scribe Deli Màu Pastel Ngòi 0.5mm/0.7mm Deli, Bút Chì Bấm Cơ Học Có Đầu Tẩy Thiết Kế Chống Gãy Ngòi</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>₫11.000</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">852 </t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/W5XsRKpR5</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lug94r11ibki0f.webp</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>shopee_25366201521</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>d10bc87b334a1c588c0528cfc0068689</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Ruột bút chì kim 0.5mm Deli, ngòi chì kim 100 chiếc 2B, lõi chì bấm nhỏ gọn tiện lợi phù hợp cho học sinh, văn phòng</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>₫5.000</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/gOy4kKC68</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rd64-lx5mf8ejgn3de8.webp</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>shopee_29604176876</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>50394241c73bcdbb6db1c7e102f748ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Bút chì kim bấm 0.5/0.7mm có tẩy, chất lượng cao, dễ dàng thay ruột chì | Stacom MP2015 (0.5mm) MP2017 (0.7mm)</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>₫3.200</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/qiOH3JYlB</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjhw8q888s1yaf.webp</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>shopee_28218120752</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>f3852887fd80e970df25e1ecc3b80c79</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Bút Chì Kim Bấm Kèm Gọt Chì Ngòi 2mm Deli - Đồ Dùng Học Tập Dễ Thương Màu Pastel Phù Họp Học Sinh</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>₫10.000</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">712 </t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/111oTMIvQE</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mo6rlx5io3yc33.webp</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>shopee_22079755720</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>6fb73fcaa6194eac07d7b9e1123c8e31</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Bút Chì Bấm Pentel A255 Chính Hãng Ngòi 0.5mm - Bút Chì Kim Siêu Bền Cho Học Sinh, Vẽ Kỹ Thuật</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>₫17.480</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672 </t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1BLEffII5H</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmjqt9ykm8eddd.webp</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>shopee_9754936253</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>517fc6a274908bc7e729542e7edfd4c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>BC01 combo Bút Chì Bấm c.thủy Vỏ Kim Loại 2b Ngòi 0.5 / 0.7</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>₫11.000</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">652 </t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/40fQ2s7VKq</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-9nv28i797rkvb6.webp</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>shopee_19167207655</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>3f954fda3f0939ff6da0993e2cbbc6c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Bút chì kim học sinh Deli kèm đầu tẩy - Ngòi 0.5/0.7mm - Vỏ kim loại không hao mòn chống gỉ- bảo vệ ngòi chì khi sử dụng</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>₫8.000</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">587 </t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4AyqFB6rzt</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134211-7qukw-lh5yq6fce0ab1d.webp</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>shopee_10116506391</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>a622e13cdb4fa8357927622be193ceb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Bút Chì Kim Bấm Thân Bấm Đầu Ngòi 0.5 0.7mm Cao Cấp Kèm Đầu Tẩy Deli - Bút Chì Cơ Học Thay Ngòi Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>₫15.000</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">574 </t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4LIGRU6Eew</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mofk4wh58dmo43.webp</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>shopee_21681189714</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>6bc92617b43539daa11d1d2b21e3bd43</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Bút chì kim bấm Deli ngòi 0.5mm màu trắng dễ thương cao cấp cải tiến có đầu tẩy cho học sinh văn phòng nhỏ gọn tiện lợi</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>₫12.000</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">545 </t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4Vbgdn5bJz</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ln2cvklem4ab8e.webp</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>shopee_23758460664</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>e5dbe2bdb9e956e5f1d9c9b58d203fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>[🔥GIÁ HỜI] Bút Chì Kim Pastel Deli Ngòi 0.5-0.7mm Đệm Tay Siêu Êm Cao Cấp Kèm Đầu Tẩy Cải Tiến Học Sinh</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>₫9.000</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4fv6q64xz2</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m2f6j22zf7w246.webp</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>shopee_46712319071</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>14499f3a78cbf781af10311eebdda9e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Thước kẻ trong suốt Deli - 18/ 20/ 30cm - Chất liệu PS bền chống trầy xước - Phù hợp với học sinh dân văn phòng học tập</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/4qEX2P4Ke5</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m7208j7y8ext39.webp</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>shopee_4075434566</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>3f6c56cd88dc469cdb84ed41e905ef7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Thước Kẻ Oyin Màu Trong Suốt 20 Cm Deli - Họa Tiết Cute Trong Suốt Dễ Nhìn Tỷ Lệ Đo Chuẩn Xác Phù Hợp Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/50XxEi3hJ8</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m93yvbzg5s9054.webp</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>shopee_24794677982</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>64853ac676b185447f68465df76de4ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Thước Kẻ 15/18/20/30cm Trong Suốt Cao Cấp Deli, Thước Đo Tỷ Lệ Chuẩn, Đo Chính Xác, Siêu Bền, Dụng Cụ Học Tập Học Sinh</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5ArNR133yB</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp21k68ux8ni6d.webp</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>shopee_22672043589</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>0f960ef167ca68cd94af752f08bfe512</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Thước Kẻ Nhựa Trong Suốt 18/20/30cm Học Sinh Deli - Dụng Cụ Học Sinh Cao Cấp Gía Tốt Thước Thẳng Văn Phò</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2gA2SQCa2i</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lyg1k493cskh3b.webp</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>shopee_2921607138</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>61d14b077707a5c24410c6df8ccad297</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Set Dụng Cụ Học Tập Quà Tặng Học Sinh Giá Rẻ - Sổ Tay, Bút Chì, Thước Kẻ, Bao Bì Gói Quà Đẹp Dịp Tổng Kết Năm Học, 1/6</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>₫12.000</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2qTSejBwhl</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9ihgsawkqbod3.webp</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>shopee_28186400056</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>5c86eaa3206b3f54a46155181c881067</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Bộ 4 thước kẻ hoạt hình dễ thương Bộ thước kẻ học sinh Thước tam giác thước đo góc Dụng cụ học tập.</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>₫3.000</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/30msr2BJMo</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mkkpzyje5ts4f3.webp</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>shopee_43319637181</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>4a08836ffdf34dc0e3f3ac44c027220a</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Set Dụng Cụ Học Tập Quà Tặng Học Sinh Giá Rẻ - Sổ Tay, Bút Chì, Thước Kẻ, Bao Bì Gói Quà Đẹp Dịp Tổng Kết Cuối Năm &amp; 1/6</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>₫9.500</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3B6J3LAg1r</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9v6vhzx2vr83b.webp</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>shopee_27886681000</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>146e71ef10df2b8cd97d9a024a2ba52f</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>🔥Thước kẻ đa năng CY360 5 trong 1 Decorme thước hình học đa năng xoay 360 độ kẻ được nhiều hình tiện dụng cho học sinh</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>₫18.620</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3LPjFeA2gu</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rd5s-m6unqxs9i1sid7.webp</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>shopee_26428043931</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>e37dafd911f32b3096006c315245d55d</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Thước Kẻ Oyin Màu Trong Suốt 20 Cm Deli - Họa Tiết Cute Trong Suốt Dễ Nhìn Tỷ Lệ Đo Chuẩn Xác Phù Hợp Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3Vj9Rx9PLx</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rava-mal1v7rw7ks369.webp</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>shopee_27137215310</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>a1d44acf881ef3e7ea7c3de78ae5fddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Bộ thước kẻ mèo con Apple màu đỏ mới dành cho học sinh - Thước đo văn phòng phẩm - Bộ tam giác và thước đo</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>₫21.000</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3g2ZeG8m10</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-820l4-moewn885g4jk2d.webp</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>shopee_46410783223</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>76c69ffdb21beb4c093ac3b240132d3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Bộ Thước Kẻ Đa Năng Hình Thú Ngộ Nghĩnh - Full Set [Thước Đo Góc, Thước 20cm, Thước Tam Giác]</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>₫9.880</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/3qLzqZ88g3</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mejpwuz48ow278.webp</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>shopee_40318668577</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>9c76e9c1921a6f7be5420b130bc2e868</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Bộ thước kẻ, thước đo độ, eke Deli cho học sinh bộ dụng cụ học tập 4 chiếc Trong suốt, dễ nhìn và đo chính xác</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>₫13.000</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7AcRogvRui</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgywrnmt93pqd8.webp</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>shopee_6591643740</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>6a3bd423cb4eae6eaad0c338263e0635</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Thước kẻ trong suốt Deli 18/ 20/ 30cm - Chất liệu PS bền chống trầy xước - Phù hợp với học sinh dân văn phòng học tập</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/70J1cNw5Fh</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqwtraxo8z5x7e.webp</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>shopee_43381999782</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>fc8c11732d00c57f84823994f1c4a427</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Set 4 Thước Eke, Thước Kẻ, Thước Đo Độ, Thước Tam Giác Hình Capybara, Kuromi, Panda - Tiện Dụng Dành Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>₫12.000</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6pzbQ4wiag</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqbpd9962bcx89.webp</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>shopee_22348329578</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>20d1ad9bd136f99f192f764f63a81365</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Thước Kẻ PuPuBaBy Màu Trong Suốt 15 Cm Deli - Họa Tiết Cute Dễ Nhìn Tỷ Lệ Đo Chuẩn Xác Phù Hợp Cho Học Sinh Sinh Viên</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6fgBDlxLvf</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-ma5dalwbul4z05.webp</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>shopee_27186887210</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>145db849103780f10484cc8a04cdfec9</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>(Bán sỉ) Bộ Dụng Cụ Học Tập 5 Món: Bút Chì HB, Gôm, Đồ Chuốt và,Thước Kẻ</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>₫12.000</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7ps8busuYu</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnuveqxj864ge4.webp</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>shopee_50107990845</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>219f8817eea097600273824590b32860</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Thước kẻ trong suốt Deli - 18/ 20/ 30cm - Chất liệu PS bền chống trầy xước - Phù hợp với học sinh dân văn phòng học tập</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7fYiPbtXtt</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m2hmcp4j443657.webp</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>shopee_22176937143</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>3541d2aae288e60e25b626092b155b08</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Thước Kẻ PuPuBaBy Màu Trong Suốt 15 Cm Deli - Họa Tiết Cute Dễ Nhìn Tỷ Lệ Đo Chuẩn Xác Phù Hợp Cho Học Sinh Sinh Viên</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>₫7.000</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7VFIDIuBEs</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7ratw-mal1q5zm6z68b9.webp</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>shopee_43953179296</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>855fe1dbf71613d9c0d51613f28d735e</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Vỏ gối cotton hàn đũi sơ đậu nành vỏ gối nằm kẻ đũi dày dặn có khoá kéo nhiều mẫu kích thước 45x65 được chọn mẫu</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>₫17.405</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/7Kvs0zuoZr</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m8292r5p8adj5e.webp</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>shopee_29731621581</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>4a39ee5174722d63f7e8106a26bc05ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>(sỉ 7.5 K ) Bộ thước kẻ eke 4 chi tiết dụng cụ học tập cho học sinh, sinh viên đồ dùng văn phòng phẩm</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>₫14.000</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5q74EF0Wca</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mdovr5hjz967ea.webp</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>shopee_27661982766</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>597dd7891a8451f98c4746930c5ead59</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>[CÓ SIZE MỚI] Nước Tẩy Trang làm sạch sâu dịu nhẹ cho mọi loại da - Garnier Micellar Cleansing Water 400ml &amp; 700ml</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>₫175.000</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>50k+</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5fne1w19xZ</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825b7-mrb63vh99hxo2f.webp</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>shopee_10707015149</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>b6b5a9caab5efaba5982e0af79167f5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>[AMINO MICELLAR MỚI] Nước tẩy trang làm sạch sâu, loại bỏ bụi bẩn &amp; trang điểm 3-in-1 L'Oreal Paris Micellar Water 400ml</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>500k+</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5VUDpd1nIY</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-825ay-mrbpoqy6p15311.webp</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>shopee_591989399</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>12592257390e601e4efe63da4e7efee9</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>[Quà tặng không bán] Nước làm sạch và tẩy trang giúp căng mịn da L'Oreal Paris Pure Revitalift Hyaluronic Acid 95ml</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>₫700.000</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>60k+</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/5LAndK2QdX</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7ra0g-m9mhb031rqf65c.webp</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>shopee_18950954164</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>00f1f45897eb99284b6ebbd31b796ffc</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>[CHÍNH HÃNG ĐỘC QUYỀN] Tẩy Tế Bào Chết Body Dove Chăm Da Sáng Mịn 280G</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>₫185.000</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>50k+</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6VMl1SxzGm</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mrbdkphjlwqo5a.webp</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>shopee_20567055749</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>a617668cdbf71423871e8ea021427347</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>[Quà tặng không bán] Nước làm sạch và tẩy trang mềm mịn cho da dầu L'Oreal Paris Revitalift Crystal Micellar Water 95ml</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>₫700.000</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>40k+</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6L3Kp9ycbl</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7ra0g-m9mhb65osyv6f7.webp</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>shopee_16937139521</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>90dd6178a717f65e4719b8a1db9c63f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>DRCEUTICS Dung Dịch Tẩy Tế Bào Chết Hóa Học Basic BHA 2% In Alcohol - Nền Cồn (100ml - 200ml)</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>₫120.000</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/6AjucqzFwk</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mfj5ki74tbm2ad.webp</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>shopee_16590407739</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>a61f1707751d4d7d72afff7d264ffd99</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>[MUA 2 GIẢM 37%] Combo 1 Hũ Tẩy Da Chết Cơ Thể Cà Phê Đắk Lắk Cocoon 200ml + Túi Refill Tẩy Da Chết Cà Phê 200ml</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>300k+</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/60QUQXztHj</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq3a2o6mr4zy1c.webp</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>shopee_42868482461</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>16449be24e00f96a663002ce12d7f86d</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>[MUA 2 GIẢM 42%] Combo 2 Nước tẩy trang bí đao Cocoon tẩy sạch makeup &amp; giảm dầu 500ml</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>₫349.000</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9pdCzalIVU</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mpn5b3unu2ocf9.webp</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>shopee_24922427465</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>203ea3dc589c14792f6696844ca06cf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>VB _ Bộ đôi nước tẩy trang giúp làm sạch sâu 3-in-1 L'Oreal Paris Micellar Water (400ml x2)</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>₫394.000</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9fJmnHlvqT</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134305-81ztc-mrbprq8sxk3o5b.webp</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>shopee_41952191926</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>c81c5782d9cf60d69b95eb99156009ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Kem Tẩy Lông OTOU Tẩy Lông Vùng Kín, Nách, Tay, Chân Nhanh Chóng Triệt Lông An Toàn Không Đau</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>₫55.000</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9V0MaymZBS</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-81ztc-mqrdizg9g26m63.webp</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>shopee_42232668438</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>636dbde31532a6af3e7904ef0a546276</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Kem Đánh Răng - JASMEEN Làm Trắng Răng loại bỏ cao răng hôi miệng tẩy ố vàng -100g</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>₫85.000</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9KgwOfnCWR</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-820l4-mgootict807d88.webp</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>shopee_43525157170</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>aa16c10dda7054414bbfac975ddaed1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>[THƯỜNG] Găng Tay Tẩy Tế Bào Chết GLAGLOW Cao Cấp</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>₫112.700</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>20k+</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/AUstmoil9g</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lrgtlkwjuz7o89.webp</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>shopee_13742486888</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>81d2cfce6669b8ae8a7ac7a880d5a647</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>(Bông Loại 1) Bông Tẩy Trang Lamer 201 Miếng, Bông Tẩy Trang Lamer 120 Miếng</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>₫29.500</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/AKZTaVjOUf</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdw2-mdbanscovz7df5.webp</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>shopee_42762371030</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>9e671228de9a5eea2b90ab3d2d478234</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Hộp 3 dao cạo tỉa lông mày hàng nội địa Trung cao cấp đúc hộp chắc chắn</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>₫9.992</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/AAG3OCk1pe</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgqc6giqsykt22.webp</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>shopee_29550819388</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>620dc52cdc4cbdacde9f588ffca52fec</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>DRCEUTICS REFILL NƯỚC TẨY TRANG OLIVE – DẠNG NƯỚC &amp; SỮA | TIẾT KIỆM – DỊU NHẸ, PHÙ HỢP MỌI LOẠI DA (480ml)</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>₫95.000</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9zwdBtkfAd</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-me9och5ayc5gb5.webp</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>shopee_42259402594</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>9d8196d6046fac003b62e0cc353c14d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>[Quà tặng không bán] Nước Tẩy Trang Mắt và Môi Chuyên Dụng 2 lớp Maybelline New York Eye &amp; Lip Makeup Remover 70ML</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>₫700.000</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>300k+</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8V7pP8qNDM</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-8259x-meyu2g2jmwatd3.webp</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>shopee_26108963065</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>ebdbe0f8fe1584bf457388df57e2485b</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>[QUÀ TẶNG KHÔNG BÁN] JUDYDOLL Bông Tẩy Trang 50 Miếng</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>₫550.000</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8KoPCpr0YL</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-820lw-mo3jbi8fkglfff.webp</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>shopee_28311001428</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>11eced41c511c204d9e15d348fb37372</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>[QUÀ TẶNG KHÔNG BÁN] Bông tẩy trang 30 miếng L'Oreal Paris</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>₫700.000</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>30k+</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8AUz0WrdtK</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-81zvt-miler330phc03f.webp</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>shopee_57753515897</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>cfaa9cff495c7d65c425e7c2a5288baf</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>[VHL x Cocoon] COMBO 02 Nước Tẩy Trang Sen Hậu Giang Cocoon 500ml</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>₫618.000</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/80BYoDsHEJ</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhpwa6qto7b489.webp</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>shopee_26093752406</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>752c23fbe53ad2310819cb0af4e1770f</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Bọt Vệ Sinh Bồn Cầu Vệ Sinh Sạch Vết Bẩn Toilet Bồn Cầu, Làm Trắng Cặn Bám Đa Năng- diệt khuẩn 500ml</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>₫35.000</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/9ANWCMnprY</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mi751d4dsf0o71.webp</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>shopee_27492774473</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>9ab09c0a966af5521c0d3c10f1988f6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>( sỉ 7K )Bộ dụng cụ học tập 5 món giá rẻ dễ thương cute đồ dùng học sinh đẹp cho bé NATO BHT04</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>₫12.500</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">634 </t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/904603oTCX</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lnis0vb8xpf145.webp</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>shopee_3975588831</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>72b962df297d0c4e023359e6d3472310</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Bộ Quà Tặng Dụng Cụ Học Tập 6 Món Cho Học Sinh – Hộp Giấy Có Quai Xách Bút Chì, Tẩy, Gọt, Thước, Sổ Ghi Chép</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>₫13.500</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>8k+</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8pkfnkp6XW</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmsr3hz9qu4k6e.webp</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>shopee_26731650460</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>8f2cea3f3df095da80f6939b1a3b4606</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>( sỉ 8K ) Bộ dụng cụ học tập 5 món có hộp_set đồ dùng học tập_quà tặng cho học sinh_quà noel giá rẻ</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>₫14.000</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">750 </t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/8fRFbRpjsV</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meqkvzv67mkn9c.webp</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>shopee_23076605498</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>06e11752801bb209e5c1ca9aeabae864</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>MW Bộ bút dạ lỏng,Acrylic Marker,đầu cọ mềm 48/60/80/120/168 màu - Trang trí đa chất liệu,Dụng cụ học tập văn phòng phẩm</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>₫334.326</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>1k+</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1qavStFkkC</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-modhtzbftm32a2.webp</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>shopee_46454533197</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>f6e24a20d0070f2087bdca3a30ce98be</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Bộ thước kẻ compa 8 món Deli chuyên dụng cụ học tập cho học sinh eke thước kẻ tẩy chì đồ dung học tập - 9591</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>₫75.860</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">575 </t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1gHVGaGO5B</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m6wfpqcyl6xzc7.webp</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>shopee_21068318029</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>e512446e82319c11bea68b18e7a6ceec</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>[🔥SỐC 15K] Bộ 4 thước kẻ, thước đo độ, eke cho học sinh - Bộ dụng cụ học tập 4 chiếc trong suốt, dễ nhìn, đo chính xác</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>₫9.000</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1Vy54HH1QA</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mqmvyi8q445e16.webp</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>shopee_18585452098</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>d932fe527c11944919e6574a2624990d</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>( si 8k )Bộ dụng cụ học tập 5 món HỘP gồm bút chì + tẩy + thước kẻ + gọt bút chì cho học sinh dễ thương</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>₫13.500</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821 </t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1LeeryHel9</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-meqyq78pee4lca.webp</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>shopee_19083117066</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>c11d9b6983cbec9321aaafadbf946450</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Bộ 5 Dụng Cụ Học Tập Bút Chì Hoạt Hình - Quà Tặng Học Sinh - Đồ Dùng Học Đường-Quà Tết</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>₫11.000</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">703 </t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2VqcG7DDOO</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mcd7cnpyjwat71.webp</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>shopee_41959101526</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>fb62e0d5d324b161cb3dc6dec9b8dfcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Set Hộp Qùa Bộ Dụng Cụ Học Tập 7 Món Cao Cấp - Bộ Quà Tặng Dành Cho Các Bé Rất Dễ Thương</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>₫69.000</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418 </t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2LXC3oDqjN</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-7rdvd-lxglzdt4zm886b.webp</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>shopee_29904781803</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>96b5490f2a0180e8165844a4d9a520de</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Bộ 4 Thước Kẻ Trong Suốt Deli, Bộ Dụng Cụ Học Tập Thước Kẻ, Thước Đo Độ, Eke Cho Học Sinh Đơn Vị Rõ Ràng Đo Chính Xác</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>₫14.000</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>5k+</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/2BDlrVEU4M</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgywrnmt93pqd8.webp</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>shopee_47112861900</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>8ca9a21d470dea81566825d9ee627468</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Bộ thước kẻ 4 món đo độ, túi eke học sinh Deli tỷ lệ chuẩn dụng cụ học tập đầy đủ</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>₫17.000</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">434 </t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/20uLfCF7PL</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgga5xfpy97284.webp</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>shopee_8383481604</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>a99d23ddb529e3630eebb98961b230a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Bộ dụng cụ học tập 7 món Capybara bút chì hộp bút thước gọt món cho bé_đồ dùng học tập giá rẻ_văn phòng phẩm giá sỉ</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>₫39.800</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">371 </t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/W5XsRKpS4</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mn3pf7z6eww5a4.webp</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>shopee_20475453702</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>30c95b8398d20f9583af1742d9bb9b60</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Set dụng cụ học tập 5 món 5 màu cho bé giá rẻ_bộ đồ dùng học tập cho bé</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>₫15.000</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>7k+</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/Lm7g8LSn3</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-ln17shoizgm01a.webp</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>shopee_17699249773</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>a5c2490485c8bf56f8a79f29669c4488</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Bộ Quà tặng dụng cụ chọ tập 6 Trong 1, văn phòng phẩm học tập cho bé, Quà Tặng thiếu nhi 1/6 cho bé</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>₫26.460</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686 </t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/BShTpM682</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lx8fknplejfd63.webp</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>shopee_25478391430</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>d8d7af21c7f487974724df4342dec5f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Bộ dập ghim mini đơn giản, tiện lợi, dễ dàng đóng ghim bài kiểm tra, hồ sơ, dụng cụ học tập cho học sinh, văn phòng phẩm</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>₫15.000</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">436 </t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/19HHWMjT1</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mmsr6o45d1xdd4.webp</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>shopee_40229855367</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>983c93b2d840123a03626ba2ca0493f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Set quà tặng dụng cụ học tập 5 món cho bé,Quà tặng giáng sinh</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>₫35.000</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">397 </t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://s.shopee.vn/1BLEffII6G</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-m48gnypq5c5re2.webp</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>shopee_23280861810</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>696e662476773df5cbf09fce8b8dd194</t>
         </is>
       </c>
     </row>
